--- a/Vergleich_Ergebnisse_MitWerten.xlsx
+++ b/Vergleich_Ergebnisse_MitWerten.xlsx
@@ -1088,7 +1088,7 @@
         <v>101.85</v>
       </c>
       <c r="T2" t="n">
-        <v>241.39</v>
+        <v>152.78</v>
       </c>
       <c r="U2" t="n">
         <v>101.85</v>
@@ -1151,49 +1151,49 @@
         <v>101.85</v>
       </c>
       <c r="AO2" t="n">
-        <v>101.85</v>
+        <v>101.852209</v>
       </c>
       <c r="AP2" t="n">
-        <v>101.85</v>
+        <v>101.852209</v>
       </c>
       <c r="AQ2" t="n">
-        <v>101.85</v>
+        <v>101.852209</v>
       </c>
       <c r="AR2" t="n">
-        <v>101.85</v>
+        <v>101.852209</v>
       </c>
       <c r="AS2" t="n">
-        <v>101.85</v>
+        <v>101.852209</v>
       </c>
       <c r="AT2" t="n">
-        <v>101.85</v>
+        <v>101.852209</v>
       </c>
       <c r="AU2" t="n">
-        <v>101.85</v>
+        <v>101.852209</v>
       </c>
       <c r="AV2" t="n">
-        <v>101.85</v>
+        <v>101.852209</v>
       </c>
       <c r="AW2" t="n">
-        <v>101.85</v>
+        <v>101.852209</v>
       </c>
       <c r="AX2" t="n">
-        <v>101.85</v>
+        <v>101.852209</v>
       </c>
       <c r="AY2" t="n">
-        <v>101.85</v>
+        <v>101.852209</v>
       </c>
       <c r="AZ2" t="n">
-        <v>101.85</v>
+        <v>101.852209</v>
       </c>
       <c r="BA2" t="n">
-        <v>101.85</v>
+        <v>101.852209</v>
       </c>
       <c r="BB2" t="n">
-        <v>101.85</v>
+        <v>101.852209</v>
       </c>
       <c r="BC2" t="n">
-        <v>101.85</v>
+        <v>101.852209</v>
       </c>
       <c r="BD2" t="n">
         <v>101.85</v>
@@ -1305,7 +1305,7 @@
         <v>4684.25</v>
       </c>
       <c r="T3" t="n">
-        <v>3314.73</v>
+        <v>3806.56</v>
       </c>
       <c r="U3" t="n">
         <v>8709.389999999999</v>
@@ -1368,49 +1368,49 @@
         <v>53630.86</v>
       </c>
       <c r="AO3" t="n">
-        <v>10886.7</v>
+        <v>10906.919669</v>
       </c>
       <c r="AP3" t="n">
-        <v>9352.77</v>
+        <v>9362.468311000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10400.39</v>
+        <v>10407.455775</v>
       </c>
       <c r="AR3" t="n">
-        <v>6897.42</v>
+        <v>6898.773753</v>
       </c>
       <c r="AS3" t="n">
-        <v>9258.809999999999</v>
+        <v>9258.810020999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>10400.39</v>
+        <v>10407.455775</v>
       </c>
       <c r="AU3" t="n">
-        <v>6897.42</v>
+        <v>6898.773753</v>
       </c>
       <c r="AV3" t="n">
-        <v>9258.809999999999</v>
+        <v>9258.810020999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>10400.39</v>
+        <v>10407.455775</v>
       </c>
       <c r="AX3" t="n">
-        <v>11339.68</v>
+        <v>11362.038</v>
       </c>
       <c r="AY3" t="n">
-        <v>9638.08</v>
+        <v>9648.79916</v>
       </c>
       <c r="AZ3" t="n">
-        <v>10745.52</v>
+        <v>10745.520087</v>
       </c>
       <c r="BA3" t="n">
-        <v>12086.92</v>
+        <v>12098.88528</v>
       </c>
       <c r="BB3" t="n">
-        <v>11414.09</v>
+        <v>11427.906064</v>
       </c>
       <c r="BC3" t="n">
-        <v>21287.98</v>
+        <v>21367.697597</v>
       </c>
       <c r="BD3" t="n">
         <v>4824.91</v>
@@ -1522,7 +1522,7 @@
         <v>29123.29</v>
       </c>
       <c r="T4" t="n">
-        <v>25599.24</v>
+        <v>27407.25</v>
       </c>
       <c r="U4" t="n">
         <v>55656.04</v>
@@ -1585,49 +1585,49 @@
         <v>347487.64</v>
       </c>
       <c r="AO4" t="n">
-        <v>68440.89999999999</v>
+        <v>68466.16565700001</v>
       </c>
       <c r="AP4" t="n">
-        <v>68439.84</v>
+        <v>68475.316318</v>
       </c>
       <c r="AQ4" t="n">
-        <v>65123.56</v>
+        <v>65130.125853</v>
       </c>
       <c r="AR4" t="n">
-        <v>39720.62</v>
+        <v>39723.098262</v>
       </c>
       <c r="AS4" t="n">
-        <v>65514.02</v>
+        <v>65514.020637</v>
       </c>
       <c r="AT4" t="n">
-        <v>65123.56</v>
+        <v>65130.125853</v>
       </c>
       <c r="AU4" t="n">
-        <v>39720.62</v>
+        <v>39723.098262</v>
       </c>
       <c r="AV4" t="n">
-        <v>65514.02</v>
+        <v>65514.020637</v>
       </c>
       <c r="AW4" t="n">
-        <v>65123.56</v>
+        <v>65130.125853</v>
       </c>
       <c r="AX4" t="n">
-        <v>69592.17999999999</v>
+        <v>69620.121629</v>
       </c>
       <c r="AY4" t="n">
-        <v>69582.02</v>
+        <v>69621.238382</v>
       </c>
       <c r="AZ4" t="n">
-        <v>65795.89999999999</v>
+        <v>65795.90010100001</v>
       </c>
       <c r="BA4" t="n">
-        <v>73921.64</v>
+        <v>73948.37510799999</v>
       </c>
       <c r="BB4" t="n">
-        <v>80943.98</v>
+        <v>80993.94625199999</v>
       </c>
       <c r="BC4" t="n">
-        <v>134392.38</v>
+        <v>134742.986723</v>
       </c>
       <c r="BD4" t="n">
         <v>29014.39</v>
@@ -1739,7 +1739,7 @@
         <v>582465.79</v>
       </c>
       <c r="T5" t="n">
-        <v>511984.74</v>
+        <v>548144.9300000001</v>
       </c>
       <c r="U5" t="n">
         <v>1113120.73</v>
@@ -1802,49 +1802,49 @@
         <v>6949752.7</v>
       </c>
       <c r="AO5" t="n">
-        <v>1368818.05</v>
+        <v>1369323.313142</v>
       </c>
       <c r="AP5" t="n">
-        <v>1368796.9</v>
+        <v>1369506.326353</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1302471.22</v>
+        <v>1302602.517066</v>
       </c>
       <c r="AR5" t="n">
-        <v>794412.4399999999</v>
+        <v>794461.965246</v>
       </c>
       <c r="AS5" t="n">
-        <v>1310280.41</v>
+        <v>1310280.412735</v>
       </c>
       <c r="AT5" t="n">
-        <v>1302471.22</v>
+        <v>1302602.517066</v>
       </c>
       <c r="AU5" t="n">
-        <v>794412.4399999999</v>
+        <v>794461.965246</v>
       </c>
       <c r="AV5" t="n">
-        <v>1310280.41</v>
+        <v>1310280.412735</v>
       </c>
       <c r="AW5" t="n">
-        <v>1302471.22</v>
+        <v>1302602.517066</v>
       </c>
       <c r="AX5" t="n">
-        <v>1391843.59</v>
+        <v>1392402.432589</v>
       </c>
       <c r="AY5" t="n">
-        <v>1391640.46</v>
+        <v>1392424.767634</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1315918</v>
+        <v>1315918.002027</v>
       </c>
       <c r="BA5" t="n">
-        <v>1478432.84</v>
+        <v>1478967.502155</v>
       </c>
       <c r="BB5" t="n">
-        <v>1618879.59</v>
+        <v>1619878.925042</v>
       </c>
       <c r="BC5" t="n">
-        <v>2687847.57</v>
+        <v>2694859.734457</v>
       </c>
       <c r="BD5" t="n">
         <v>580287.86</v>
@@ -1956,7 +1956,7 @@
         <v>4684253.66</v>
       </c>
       <c r="T6" t="n">
-        <v>7855780.79</v>
+        <v>5709841.66</v>
       </c>
       <c r="U6" t="n">
         <v>8709388.439999999</v>
@@ -2019,49 +2019,49 @@
         <v>53630856.95</v>
       </c>
       <c r="AO6" t="n">
-        <v>10886702.57</v>
+        <v>10906919.66873</v>
       </c>
       <c r="AP6" t="n">
-        <v>9352773.34</v>
+        <v>9362468.311319999</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10400388.97</v>
+        <v>10407455.775289</v>
       </c>
       <c r="AR6" t="n">
-        <v>6897418.11</v>
+        <v>6898773.753023</v>
       </c>
       <c r="AS6" t="n">
-        <v>9258810.02</v>
+        <v>9258810.021251</v>
       </c>
       <c r="AT6" t="n">
-        <v>10400388.97</v>
+        <v>10407455.775289</v>
       </c>
       <c r="AU6" t="n">
-        <v>6897418.11</v>
+        <v>6898773.753023</v>
       </c>
       <c r="AV6" t="n">
-        <v>9258810.02</v>
+        <v>9258810.021251</v>
       </c>
       <c r="AW6" t="n">
-        <v>10400388.97</v>
+        <v>10407455.775289</v>
       </c>
       <c r="AX6" t="n">
-        <v>11339683.58</v>
+        <v>11362037.999848</v>
       </c>
       <c r="AY6" t="n">
-        <v>9638081.220000001</v>
+        <v>9648799.159546999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>10745520.09</v>
+        <v>10745520.087169</v>
       </c>
       <c r="BA6" t="n">
-        <v>12086922.43</v>
+        <v>12098885.280235</v>
       </c>
       <c r="BB6" t="n">
-        <v>11414089.6</v>
+        <v>11427906.063827</v>
       </c>
       <c r="BC6" t="n">
-        <v>21287983.69</v>
+        <v>21367697.597221</v>
       </c>
       <c r="BD6" t="n">
         <v>4824908.32</v>
@@ -2173,7 +2173,7 @@
         <v>140527.61</v>
       </c>
       <c r="T7" t="n">
-        <v>235673.42</v>
+        <v>171295.25</v>
       </c>
       <c r="U7" t="n">
         <v>261281.65</v>
@@ -2236,49 +2236,49 @@
         <v>1608925.71</v>
       </c>
       <c r="AO7" t="n">
-        <v>326601.08</v>
+        <v>327207.590062</v>
       </c>
       <c r="AP7" t="n">
-        <v>280583.2</v>
+        <v>280874.04934</v>
       </c>
       <c r="AQ7" t="n">
-        <v>312011.67</v>
+        <v>312223.673259</v>
       </c>
       <c r="AR7" t="n">
-        <v>206922.54</v>
+        <v>206963.212591</v>
       </c>
       <c r="AS7" t="n">
-        <v>277764.3</v>
+        <v>277764.300638</v>
       </c>
       <c r="AT7" t="n">
-        <v>312011.67</v>
+        <v>312223.673259</v>
       </c>
       <c r="AU7" t="n">
-        <v>206922.54</v>
+        <v>206963.212591</v>
       </c>
       <c r="AV7" t="n">
-        <v>277764.3</v>
+        <v>277764.300638</v>
       </c>
       <c r="AW7" t="n">
-        <v>312011.67</v>
+        <v>312223.673259</v>
       </c>
       <c r="AX7" t="n">
-        <v>340190.51</v>
+        <v>340861.139995</v>
       </c>
       <c r="AY7" t="n">
-        <v>289142.44</v>
+        <v>289463.974786</v>
       </c>
       <c r="AZ7" t="n">
-        <v>322365.6</v>
+        <v>322365.602615</v>
       </c>
       <c r="BA7" t="n">
-        <v>362607.67</v>
+        <v>362966.558407</v>
       </c>
       <c r="BB7" t="n">
-        <v>342422.69</v>
+        <v>342837.181915</v>
       </c>
       <c r="BC7" t="n">
-        <v>638639.51</v>
+        <v>641030.927917</v>
       </c>
       <c r="BD7" t="n">
         <v>144747.25</v>
@@ -2390,7 +2390,7 @@
         <v>477101.58</v>
       </c>
       <c r="T8" t="n">
-        <v>800128.63</v>
+        <v>581559.98</v>
       </c>
       <c r="U8" t="n">
         <v>887070.45</v>
@@ -2453,49 +2453,49 @@
         <v>5462421.24</v>
       </c>
       <c r="AO8" t="n">
-        <v>1108834.7</v>
+        <v>1110893.859717</v>
       </c>
       <c r="AP8" t="n">
-        <v>952600.62</v>
+        <v>953588.077545</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1059302.59</v>
+        <v>1060022.358942</v>
       </c>
       <c r="AR8" t="n">
-        <v>702517.27</v>
+        <v>702655.344917</v>
       </c>
       <c r="AS8" t="n">
-        <v>943030.25</v>
+        <v>943030.251738</v>
       </c>
       <c r="AT8" t="n">
-        <v>1059302.59</v>
+        <v>1060022.358942</v>
       </c>
       <c r="AU8" t="n">
-        <v>702517.27</v>
+        <v>702655.344917</v>
       </c>
       <c r="AV8" t="n">
-        <v>943030.25</v>
+        <v>943030.251738</v>
       </c>
       <c r="AW8" t="n">
-        <v>1059302.59</v>
+        <v>1060022.358942</v>
       </c>
       <c r="AX8" t="n">
-        <v>1154971.82</v>
+        <v>1157248.667017</v>
       </c>
       <c r="AY8" t="n">
-        <v>981659.86</v>
+        <v>982751.506891</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1094454.96</v>
+        <v>1094454.955832</v>
       </c>
       <c r="BA8" t="n">
-        <v>1231079.75</v>
+        <v>1232298.19009</v>
       </c>
       <c r="BB8" t="n">
-        <v>1162550.24</v>
+        <v>1163957.474824</v>
       </c>
       <c r="BC8" t="n">
-        <v>2168228.16</v>
+        <v>2176347.197742</v>
       </c>
       <c r="BD8" t="n">
         <v>491427.57</v>
@@ -2607,7 +2607,7 @@
         <v>9542031.65</v>
       </c>
       <c r="T9" t="n">
-        <v>16002572.51</v>
+        <v>11631199.7</v>
       </c>
       <c r="U9" t="n">
         <v>17741409</v>
@@ -2670,49 +2670,49 @@
         <v>109248424.83</v>
       </c>
       <c r="AO9" t="n">
-        <v>22176694.07</v>
+        <v>22217877.194337</v>
       </c>
       <c r="AP9" t="n">
-        <v>19052012.47</v>
+        <v>19071761.550893</v>
       </c>
       <c r="AQ9" t="n">
-        <v>21186051.79</v>
+        <v>21200447.178848</v>
       </c>
       <c r="AR9" t="n">
-        <v>14050345.39</v>
+        <v>14053106.898331</v>
       </c>
       <c r="AS9" t="n">
-        <v>18860605.03</v>
+        <v>18860605.034767</v>
       </c>
       <c r="AT9" t="n">
-        <v>21186051.79</v>
+        <v>21200447.178848</v>
       </c>
       <c r="AU9" t="n">
-        <v>14050345.39</v>
+        <v>14053106.898331</v>
       </c>
       <c r="AV9" t="n">
-        <v>18860605.03</v>
+        <v>18860605.034767</v>
       </c>
       <c r="AW9" t="n">
-        <v>21186051.79</v>
+        <v>21200447.178848</v>
       </c>
       <c r="AX9" t="n">
-        <v>23099436.4</v>
+        <v>23144973.340341</v>
       </c>
       <c r="AY9" t="n">
-        <v>19633197.22</v>
+        <v>19655030.137816</v>
       </c>
       <c r="AZ9" t="n">
-        <v>21889099.12</v>
+        <v>21889099.116633</v>
       </c>
       <c r="BA9" t="n">
-        <v>24621594.95</v>
+        <v>24645963.801796</v>
       </c>
       <c r="BB9" t="n">
-        <v>23251004.75</v>
+        <v>23279149.496485</v>
       </c>
       <c r="BC9" t="n">
-        <v>43364563.2</v>
+        <v>43526943.954842</v>
       </c>
       <c r="BD9" t="n">
         <v>9828551.390000001</v>
@@ -2824,7 +2824,7 @@
         <v>617629.1899999999</v>
       </c>
       <c r="T10" t="n">
-        <v>1035802.05</v>
+        <v>752855.23</v>
       </c>
       <c r="U10" t="n">
         <v>1148352.1</v>
@@ -2887,49 +2887,49 @@
         <v>7071346.95</v>
       </c>
       <c r="AO10" t="n">
-        <v>1435435.78</v>
+        <v>1438101.449779</v>
       </c>
       <c r="AP10" t="n">
-        <v>1233183.82</v>
+        <v>1234462.126884</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1371314.26</v>
+        <v>1372246.032201</v>
       </c>
       <c r="AR10" t="n">
-        <v>909439.8100000001</v>
+        <v>909618.557507</v>
       </c>
       <c r="AS10" t="n">
-        <v>1220794.55</v>
+        <v>1220794.552376</v>
       </c>
       <c r="AT10" t="n">
-        <v>1371314.26</v>
+        <v>1372246.032201</v>
       </c>
       <c r="AU10" t="n">
-        <v>909439.8100000001</v>
+        <v>909618.557507</v>
       </c>
       <c r="AV10" t="n">
-        <v>1220794.55</v>
+        <v>1220794.552376</v>
       </c>
       <c r="AW10" t="n">
-        <v>1371314.26</v>
+        <v>1372246.032201</v>
       </c>
       <c r="AX10" t="n">
-        <v>1495162.33</v>
+        <v>1498109.807012</v>
       </c>
       <c r="AY10" t="n">
-        <v>1270802.3</v>
+        <v>1272215.481677</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1416820.56</v>
+        <v>1416820.558447</v>
       </c>
       <c r="BA10" t="n">
-        <v>1593687.42</v>
+        <v>1595264.748497</v>
       </c>
       <c r="BB10" t="n">
-        <v>1504972.93</v>
+        <v>1506794.656739</v>
       </c>
       <c r="BC10" t="n">
-        <v>2806867.67</v>
+        <v>2817378.125659</v>
       </c>
       <c r="BD10" t="n">
         <v>636174.8199999999</v>
@@ -6663,22 +6663,22 @@
         <v>56.17</v>
       </c>
       <c r="AX69" t="n">
-        <v>56.17</v>
+        <v>56.169811</v>
       </c>
       <c r="AY69" t="n">
-        <v>56.17</v>
+        <v>56.169811</v>
       </c>
       <c r="AZ69" t="n">
-        <v>56.17</v>
+        <v>56.169811</v>
       </c>
       <c r="BA69" t="n">
-        <v>56.17</v>
+        <v>56.169811</v>
       </c>
       <c r="BB69" t="n">
-        <v>56.17</v>
+        <v>56.169811</v>
       </c>
       <c r="BC69" t="n">
-        <v>56.17</v>
+        <v>56.169811</v>
       </c>
       <c r="BD69" t="n">
         <v>56.17</v>
@@ -6808,22 +6808,22 @@
         <v>678.47</v>
       </c>
       <c r="AX70" t="n">
-        <v>346.03</v>
+        <v>346.033836</v>
       </c>
       <c r="AY70" t="n">
-        <v>349.97</v>
+        <v>349.973595</v>
       </c>
       <c r="AZ70" t="n">
-        <v>342.52</v>
+        <v>342.52281</v>
       </c>
       <c r="BA70" t="n">
-        <v>367.77</v>
+        <v>367.627087</v>
       </c>
       <c r="BB70" t="n">
-        <v>355.34</v>
+        <v>355.337476</v>
       </c>
       <c r="BC70" t="n">
-        <v>358.14</v>
+        <v>358.119686</v>
       </c>
       <c r="BD70" t="n">
         <v>101.23</v>
@@ -6953,22 +6953,22 @@
         <v>5781.07</v>
       </c>
       <c r="AX71" t="n">
-        <v>3001.77</v>
+        <v>3001.77199</v>
       </c>
       <c r="AY71" t="n">
-        <v>3004.6</v>
+        <v>3004.599698</v>
       </c>
       <c r="AZ71" t="n">
-        <v>3000.5</v>
+        <v>3000.499816</v>
       </c>
       <c r="BA71" t="n">
-        <v>3012.92</v>
+        <v>3012.866474</v>
       </c>
       <c r="BB71" t="n">
-        <v>3019</v>
+        <v>3018.999172</v>
       </c>
       <c r="BC71" t="n">
-        <v>3010.54</v>
+        <v>3010.34957</v>
       </c>
       <c r="BD71" t="n">
         <v>862.48</v>
@@ -7098,22 +7098,22 @@
         <v>21411382.48</v>
       </c>
       <c r="AX72" t="n">
-        <v>11117679.43</v>
+        <v>11117674.035221</v>
       </c>
       <c r="AY72" t="n">
-        <v>11128149.31</v>
+        <v>11128147.028276</v>
       </c>
       <c r="AZ72" t="n">
         <v>11112962.28</v>
       </c>
       <c r="BA72" t="n">
-        <v>11158955.69</v>
+        <v>11158764.716978</v>
       </c>
       <c r="BB72" t="n">
-        <v>11181477.15</v>
+        <v>11181478.413399</v>
       </c>
       <c r="BC72" t="n">
-        <v>11150159.41</v>
+        <v>11149442.85076</v>
       </c>
       <c r="BD72" t="n">
         <v>3194384.08</v>
@@ -7243,22 +7243,22 @@
         <v>1759006.73</v>
       </c>
       <c r="AX73" t="n">
-        <v>897124.76</v>
+        <v>897124.758788</v>
       </c>
       <c r="AY73" t="n">
-        <v>907338.95</v>
+        <v>907338.94971</v>
       </c>
       <c r="AZ73" t="n">
         <v>888022.1</v>
       </c>
       <c r="BA73" t="n">
-        <v>953472.3100000001</v>
+        <v>953107.262016</v>
       </c>
       <c r="BB73" t="n">
-        <v>921244.3</v>
+        <v>921245.3093129999</v>
       </c>
       <c r="BC73" t="n">
-        <v>928503.62</v>
+        <v>928458.444287</v>
       </c>
       <c r="BD73" t="n">
         <v>262438.28</v>
@@ -7388,22 +7388,22 @@
         <v>35180.13</v>
       </c>
       <c r="AX74" t="n">
-        <v>17942.5</v>
+        <v>17942.495176</v>
       </c>
       <c r="AY74" t="n">
-        <v>18146.78</v>
+        <v>18146.778994</v>
       </c>
       <c r="AZ74" t="n">
-        <v>17760.44</v>
+        <v>17760.442</v>
       </c>
       <c r="BA74" t="n">
-        <v>19069.45</v>
+        <v>19062.14524</v>
       </c>
       <c r="BB74" t="n">
-        <v>18424.89</v>
+        <v>18424.906186</v>
       </c>
       <c r="BC74" t="n">
-        <v>18570.07</v>
+        <v>18569.168886</v>
       </c>
       <c r="BD74" t="n">
         <v>5248.77</v>
@@ -7533,22 +7533,22 @@
         <v>141147.25</v>
       </c>
       <c r="AX75" t="n">
-        <v>71987.61</v>
+        <v>71987.611678</v>
       </c>
       <c r="AY75" t="n">
-        <v>72807.22</v>
+        <v>72807.22478400001</v>
       </c>
       <c r="AZ75" t="n">
-        <v>71257.19</v>
+        <v>71257.190787</v>
       </c>
       <c r="BA75" t="n">
-        <v>76509.08</v>
+        <v>76479.79257400001</v>
       </c>
       <c r="BB75" t="n">
-        <v>73923.03</v>
+        <v>73923.107057</v>
       </c>
       <c r="BC75" t="n">
-        <v>74505.53</v>
+        <v>74501.90766899999</v>
       </c>
       <c r="BD75" t="n">
         <v>21058.73</v>
@@ -7678,22 +7678,22 @@
         <v>2822945.01</v>
       </c>
       <c r="AX76" t="n">
-        <v>1439752.23</v>
+        <v>1439752.233559</v>
       </c>
       <c r="AY76" t="n">
-        <v>1456144.5</v>
+        <v>1456144.495673</v>
       </c>
       <c r="AZ76" t="n">
-        <v>1425143.82</v>
+        <v>1425143.81573</v>
       </c>
       <c r="BA76" t="n">
-        <v>1530181.7</v>
+        <v>1529595.851487</v>
       </c>
       <c r="BB76" t="n">
-        <v>1478460.51</v>
+        <v>1478462.141132</v>
       </c>
       <c r="BC76" t="n">
-        <v>1490110.65</v>
+        <v>1490038.153372</v>
       </c>
       <c r="BD76" t="n">
         <v>421174.54</v>
@@ -7823,22 +7823,22 @@
         <v>176327.39</v>
       </c>
       <c r="AX77" t="n">
-        <v>89930.11</v>
+        <v>89930.106854</v>
       </c>
       <c r="AY77" t="n">
-        <v>90954</v>
+        <v>90954.003778</v>
       </c>
       <c r="AZ77" t="n">
-        <v>89017.63</v>
+        <v>89017.632787</v>
       </c>
       <c r="BA77" t="n">
-        <v>95578.53</v>
+        <v>95541.937815</v>
       </c>
       <c r="BB77" t="n">
-        <v>92347.91</v>
+        <v>92348.01324299999</v>
       </c>
       <c r="BC77" t="n">
-        <v>93075.60000000001</v>
+        <v>93071.076554</v>
       </c>
       <c r="BD77" t="n">
         <v>26307.49</v>
@@ -7962,22 +7962,22 @@
         <v>768.5599999999999</v>
       </c>
       <c r="AX79" t="n">
-        <v>768.5599999999999</v>
+        <v>768.562373</v>
       </c>
       <c r="AY79" t="n">
-        <v>768.5599999999999</v>
+        <v>768.562373</v>
       </c>
       <c r="AZ79" t="n">
-        <v>768.5599999999999</v>
+        <v>768.562373</v>
       </c>
       <c r="BA79" t="n">
-        <v>768.5599999999999</v>
+        <v>768.562373</v>
       </c>
       <c r="BB79" t="n">
-        <v>768.5599999999999</v>
+        <v>768.562373</v>
       </c>
       <c r="BC79" t="n">
-        <v>768.5599999999999</v>
+        <v>768.562373</v>
       </c>
       <c r="BJ79" t="n">
         <v>768.5599999999999</v>
@@ -8071,22 +8071,22 @@
         <v>693.52</v>
       </c>
       <c r="AX80" t="n">
-        <v>362.46</v>
+        <v>362.458</v>
       </c>
       <c r="AY80" t="n">
-        <v>362.46</v>
+        <v>362.458</v>
       </c>
       <c r="AZ80" t="n">
-        <v>362.46</v>
+        <v>362.458</v>
       </c>
       <c r="BA80" t="n">
-        <v>362.46</v>
+        <v>362.458</v>
       </c>
       <c r="BB80" t="n">
-        <v>362.46</v>
+        <v>362.458</v>
       </c>
       <c r="BC80" t="n">
-        <v>362.46</v>
+        <v>362.458</v>
       </c>
       <c r="BJ80" t="n">
         <v>196.21</v>
@@ -8180,22 +8180,22 @@
         <v>6075.25</v>
       </c>
       <c r="AX81" t="n">
-        <v>3175.13</v>
+        <v>3175.13208</v>
       </c>
       <c r="AY81" t="n">
-        <v>3175.13</v>
+        <v>3175.13208</v>
       </c>
       <c r="AZ81" t="n">
-        <v>3175.13</v>
+        <v>3175.13208</v>
       </c>
       <c r="BA81" t="n">
-        <v>3175.13</v>
+        <v>3175.13208</v>
       </c>
       <c r="BB81" t="n">
-        <v>3175.13</v>
+        <v>3175.13208</v>
       </c>
       <c r="BC81" t="n">
-        <v>3175.13</v>
+        <v>3175.13208</v>
       </c>
       <c r="BJ81" t="n">
         <v>1718.82</v>
@@ -8725,22 +8725,22 @@
         <v>1066029.83</v>
       </c>
       <c r="AX86" t="n">
-        <v>557143.16</v>
+        <v>557143.161118</v>
       </c>
       <c r="AY86" t="n">
-        <v>557143.16</v>
+        <v>557143.161118</v>
       </c>
       <c r="AZ86" t="n">
-        <v>557143.16</v>
+        <v>557143.161118</v>
       </c>
       <c r="BA86" t="n">
-        <v>557143.16</v>
+        <v>557143.161118</v>
       </c>
       <c r="BB86" t="n">
-        <v>557143.16</v>
+        <v>557143.161118</v>
       </c>
       <c r="BC86" t="n">
-        <v>557143.16</v>
+        <v>557143.161118</v>
       </c>
       <c r="BJ86" t="n">
         <v>301603.09</v>
@@ -8834,22 +8834,22 @@
         <v>15990447.42</v>
       </c>
       <c r="AX87" t="n">
-        <v>8357147.42</v>
+        <v>8357147.416774</v>
       </c>
       <c r="AY87" t="n">
-        <v>8357147.42</v>
+        <v>8357147.416774</v>
       </c>
       <c r="AZ87" t="n">
-        <v>8357147.42</v>
+        <v>8357147.416774</v>
       </c>
       <c r="BA87" t="n">
-        <v>8357147.42</v>
+        <v>8357147.416774</v>
       </c>
       <c r="BB87" t="n">
-        <v>8357147.42</v>
+        <v>8357147.416774</v>
       </c>
       <c r="BC87" t="n">
-        <v>8357147.42</v>
+        <v>8357147.416774</v>
       </c>
       <c r="BJ87" t="n">
         <v>4524046.34</v>
@@ -8943,22 +8943,22 @@
         <v>1551495.23</v>
       </c>
       <c r="AX88" t="n">
-        <v>810863.76</v>
+        <v>810863.761118</v>
       </c>
       <c r="AY88" t="n">
-        <v>810863.76</v>
+        <v>810863.761118</v>
       </c>
       <c r="AZ88" t="n">
-        <v>810863.76</v>
+        <v>810863.761118</v>
       </c>
       <c r="BA88" t="n">
-        <v>810863.76</v>
+        <v>810863.761118</v>
       </c>
       <c r="BB88" t="n">
-        <v>810863.76</v>
+        <v>810863.761118</v>
       </c>
       <c r="BC88" t="n">
-        <v>810863.76</v>
+        <v>810863.761118</v>
       </c>
       <c r="BJ88" t="n">
         <v>438951.84</v>
@@ -9025,22 +9025,22 @@
         </is>
       </c>
       <c r="AO90" t="n">
-        <v>671.3200000000001</v>
+        <v>671.321089</v>
       </c>
       <c r="AP90" t="n">
-        <v>671.3200000000001</v>
+        <v>671.321089</v>
       </c>
       <c r="AQ90" t="n">
-        <v>671.3200000000001</v>
+        <v>671.321089</v>
       </c>
       <c r="AR90" t="n">
-        <v>671.3200000000001</v>
+        <v>671.321089</v>
       </c>
       <c r="AS90" t="n">
-        <v>671.3200000000001</v>
+        <v>671.321089</v>
       </c>
       <c r="AT90" t="n">
-        <v>671.3200000000001</v>
+        <v>671.321089</v>
       </c>
       <c r="AU90" t="n">
         <v>0</v>
@@ -9052,22 +9052,22 @@
         <v>0</v>
       </c>
       <c r="AX90" t="n">
-        <v>671.3200000000001</v>
+        <v>671.321089</v>
       </c>
       <c r="AY90" t="n">
-        <v>671.3200000000001</v>
+        <v>671.321089</v>
       </c>
       <c r="AZ90" t="n">
-        <v>671.3200000000001</v>
+        <v>671.321089</v>
       </c>
       <c r="BA90" t="n">
-        <v>671.3200000000001</v>
+        <v>671.321089</v>
       </c>
       <c r="BB90" t="n">
-        <v>671.3200000000001</v>
+        <v>671.321089</v>
       </c>
       <c r="BC90" t="n">
-        <v>671.3200000000001</v>
+        <v>671.321089</v>
       </c>
     </row>
     <row r="91">
@@ -9293,49 +9293,49 @@
         </is>
       </c>
       <c r="AO94" t="n">
-        <v>900.04</v>
+        <v>900.0374399999999</v>
       </c>
       <c r="AP94" t="n">
-        <v>900.04</v>
+        <v>900.0374399999999</v>
       </c>
       <c r="AQ94" t="n">
-        <v>900.04</v>
+        <v>900.0374399999999</v>
       </c>
       <c r="AR94" t="n">
-        <v>900.04</v>
+        <v>900.0374399999999</v>
       </c>
       <c r="AS94" t="n">
-        <v>900.04</v>
+        <v>900.0374399999999</v>
       </c>
       <c r="AT94" t="n">
-        <v>900.04</v>
+        <v>900.0374399999999</v>
       </c>
       <c r="AU94" t="n">
-        <v>900.04</v>
+        <v>900.0374399999999</v>
       </c>
       <c r="AV94" t="n">
-        <v>900.04</v>
+        <v>900.0374399999999</v>
       </c>
       <c r="AW94" t="n">
-        <v>900.04</v>
+        <v>900.0374399999999</v>
       </c>
       <c r="AX94" t="n">
-        <v>900.04</v>
+        <v>900.0374399999999</v>
       </c>
       <c r="AY94" t="n">
-        <v>900.04</v>
+        <v>900.0374399999999</v>
       </c>
       <c r="AZ94" t="n">
-        <v>900.04</v>
+        <v>900.0374399999999</v>
       </c>
       <c r="BA94" t="n">
-        <v>900.04</v>
+        <v>900.0374399999999</v>
       </c>
       <c r="BB94" t="n">
-        <v>900.04</v>
+        <v>900.0374399999999</v>
       </c>
       <c r="BC94" t="n">
-        <v>900.04</v>
+        <v>900.0374399999999</v>
       </c>
     </row>
     <row r="95">
@@ -9494,22 +9494,22 @@
         </is>
       </c>
       <c r="AO97" t="n">
-        <v>191595.04</v>
+        <v>191595.038721</v>
       </c>
       <c r="AP97" t="n">
-        <v>191595.04</v>
+        <v>191595.038721</v>
       </c>
       <c r="AQ97" t="n">
-        <v>191595.04</v>
+        <v>191595.038721</v>
       </c>
       <c r="AR97" t="n">
-        <v>191595.04</v>
+        <v>191595.038721</v>
       </c>
       <c r="AS97" t="n">
-        <v>191595.04</v>
+        <v>191595.038721</v>
       </c>
       <c r="AT97" t="n">
-        <v>191595.04</v>
+        <v>191595.038721</v>
       </c>
       <c r="AU97" t="n">
         <v>0</v>
@@ -9521,22 +9521,22 @@
         <v>0</v>
       </c>
       <c r="AX97" t="n">
-        <v>191595.04</v>
+        <v>191595.038721</v>
       </c>
       <c r="AY97" t="n">
-        <v>191595.04</v>
+        <v>191595.038721</v>
       </c>
       <c r="AZ97" t="n">
-        <v>191595.04</v>
+        <v>191595.038721</v>
       </c>
       <c r="BA97" t="n">
-        <v>191595.04</v>
+        <v>191595.038721</v>
       </c>
       <c r="BB97" t="n">
-        <v>191595.04</v>
+        <v>191595.038721</v>
       </c>
       <c r="BC97" t="n">
-        <v>191595.04</v>
+        <v>191595.038721</v>
       </c>
     </row>
     <row r="98">
@@ -9561,22 +9561,22 @@
         </is>
       </c>
       <c r="AO98" t="n">
-        <v>3831900.77</v>
+        <v>3831900.774424</v>
       </c>
       <c r="AP98" t="n">
-        <v>3831900.77</v>
+        <v>3831900.774424</v>
       </c>
       <c r="AQ98" t="n">
-        <v>3831900.77</v>
+        <v>3831900.774424</v>
       </c>
       <c r="AR98" t="n">
-        <v>3831900.77</v>
+        <v>3831900.774424</v>
       </c>
       <c r="AS98" t="n">
-        <v>3831900.77</v>
+        <v>3831900.774424</v>
       </c>
       <c r="AT98" t="n">
-        <v>3831900.77</v>
+        <v>3831900.774424</v>
       </c>
       <c r="AU98" t="n">
         <v>0</v>
@@ -9588,22 +9588,22 @@
         <v>0</v>
       </c>
       <c r="AX98" t="n">
-        <v>3831900.77</v>
+        <v>3831900.774424</v>
       </c>
       <c r="AY98" t="n">
-        <v>3831900.77</v>
+        <v>3831900.774424</v>
       </c>
       <c r="AZ98" t="n">
-        <v>3831900.77</v>
+        <v>3831900.774424</v>
       </c>
       <c r="BA98" t="n">
-        <v>3831900.77</v>
+        <v>3831900.774424</v>
       </c>
       <c r="BB98" t="n">
-        <v>3831900.77</v>
+        <v>3831900.774424</v>
       </c>
       <c r="BC98" t="n">
-        <v>3831900.77</v>
+        <v>3831900.774424</v>
       </c>
     </row>
     <row r="99">
@@ -9628,22 +9628,22 @@
         </is>
       </c>
       <c r="AO99" t="n">
-        <v>301474.04</v>
+        <v>301474.038721</v>
       </c>
       <c r="AP99" t="n">
-        <v>301474.04</v>
+        <v>301474.038721</v>
       </c>
       <c r="AQ99" t="n">
-        <v>301474.04</v>
+        <v>301474.038721</v>
       </c>
       <c r="AR99" t="n">
-        <v>301474.04</v>
+        <v>301474.038721</v>
       </c>
       <c r="AS99" t="n">
-        <v>301474.04</v>
+        <v>301474.038721</v>
       </c>
       <c r="AT99" t="n">
-        <v>301474.04</v>
+        <v>301474.038721</v>
       </c>
       <c r="AU99" t="n">
         <v>109879</v>
@@ -9655,22 +9655,22 @@
         <v>109879</v>
       </c>
       <c r="AX99" t="n">
-        <v>301474.04</v>
+        <v>301474.038721</v>
       </c>
       <c r="AY99" t="n">
-        <v>301474.04</v>
+        <v>301474.038721</v>
       </c>
       <c r="AZ99" t="n">
-        <v>301474.04</v>
+        <v>301474.038721</v>
       </c>
       <c r="BA99" t="n">
-        <v>301474.04</v>
+        <v>301474.038721</v>
       </c>
       <c r="BB99" t="n">
-        <v>301474.04</v>
+        <v>301474.038721</v>
       </c>
       <c r="BC99" t="n">
-        <v>301474.04</v>
+        <v>301474.038721</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" thickBot="1">
@@ -9813,49 +9813,49 @@
         <v>39.32</v>
       </c>
       <c r="AO101" t="n">
-        <v>39.32</v>
+        <v>39.318868</v>
       </c>
       <c r="AP101" t="n">
-        <v>39.32</v>
+        <v>39.318868</v>
       </c>
       <c r="AQ101" t="n">
-        <v>39.32</v>
+        <v>39.318868</v>
       </c>
       <c r="AR101" t="n">
-        <v>39.32</v>
+        <v>39.318868</v>
       </c>
       <c r="AS101" t="n">
-        <v>39.32</v>
+        <v>39.318868</v>
       </c>
       <c r="AT101" t="n">
-        <v>39.32</v>
+        <v>39.318868</v>
       </c>
       <c r="AU101" t="n">
-        <v>39.32</v>
+        <v>39.318868</v>
       </c>
       <c r="AV101" t="n">
-        <v>39.32</v>
+        <v>39.318868</v>
       </c>
       <c r="AW101" t="n">
-        <v>39.32</v>
+        <v>39.318868</v>
       </c>
       <c r="AX101" t="n">
-        <v>39.32</v>
+        <v>39.318868</v>
       </c>
       <c r="AY101" t="n">
-        <v>39.32</v>
+        <v>39.318868</v>
       </c>
       <c r="AZ101" t="n">
-        <v>39.32</v>
+        <v>39.318868</v>
       </c>
       <c r="BA101" t="n">
-        <v>39.32</v>
+        <v>39.318868</v>
       </c>
       <c r="BB101" t="n">
-        <v>39.32</v>
+        <v>39.318868</v>
       </c>
       <c r="BC101" t="n">
-        <v>39.32</v>
+        <v>39.318868</v>
       </c>
       <c r="BD101" t="n">
         <v>39.32</v>
@@ -9967,7 +9967,7 @@
         <v>5764.76</v>
       </c>
       <c r="T102" t="n">
-        <v>5188.98</v>
+        <v>5841.06</v>
       </c>
       <c r="U102" t="n">
         <v>1837.91</v>
@@ -10030,49 +10030,49 @@
         <v>7217.89</v>
       </c>
       <c r="AO102" t="n">
-        <v>4920.99</v>
+        <v>4910.379849</v>
       </c>
       <c r="AP102" t="n">
-        <v>2613.79</v>
+        <v>2614.220676</v>
       </c>
       <c r="AQ102" t="n">
-        <v>2646.7</v>
+        <v>2648.79253</v>
       </c>
       <c r="AR102" t="n">
-        <v>167.71</v>
+        <v>168.42505</v>
       </c>
       <c r="AS102" t="n">
-        <v>2227.41</v>
+        <v>2227.41489</v>
       </c>
       <c r="AT102" t="n">
-        <v>2646.7</v>
+        <v>2648.79253</v>
       </c>
       <c r="AU102" t="n">
-        <v>167.71</v>
+        <v>168.42505</v>
       </c>
       <c r="AV102" t="n">
-        <v>2227.41</v>
+        <v>2227.41489</v>
       </c>
       <c r="AW102" t="n">
-        <v>2646.7</v>
+        <v>2648.79253</v>
       </c>
       <c r="AX102" t="n">
-        <v>5431.89</v>
+        <v>5420.160305</v>
       </c>
       <c r="AY102" t="n">
-        <v>2874.97</v>
+        <v>2875.445172</v>
       </c>
       <c r="AZ102" t="n">
-        <v>2855.83</v>
+        <v>2855.826196</v>
       </c>
       <c r="BA102" t="n">
-        <v>17506.35</v>
+        <v>17519.07675</v>
       </c>
       <c r="BB102" t="n">
-        <v>8874.09</v>
+        <v>8875.043095999999</v>
       </c>
       <c r="BC102" t="n">
-        <v>4632.71</v>
+        <v>4632.886979</v>
       </c>
       <c r="BD102" t="n">
         <v>2403.75</v>
@@ -10184,7 +10184,7 @@
         <v>91267.95</v>
       </c>
       <c r="T103" t="n">
-        <v>54733.52</v>
+        <v>61999.92</v>
       </c>
       <c r="U103" t="n">
         <v>62071.01</v>
@@ -10247,49 +10247,49 @@
         <v>93261.25999999999</v>
       </c>
       <c r="AO103" t="n">
-        <v>185358.41</v>
+        <v>185330.892558</v>
       </c>
       <c r="AP103" t="n">
-        <v>130066.76</v>
+        <v>130117.172388</v>
       </c>
       <c r="AQ103" t="n">
-        <v>236938.24</v>
+        <v>237060.555435</v>
       </c>
       <c r="AR103" t="n">
-        <v>13276.59</v>
+        <v>13322.259796</v>
       </c>
       <c r="AS103" t="n">
-        <v>122709.91</v>
+        <v>122709.905163</v>
       </c>
       <c r="AT103" t="n">
-        <v>236938.24</v>
+        <v>237060.555435</v>
       </c>
       <c r="AU103" t="n">
-        <v>13276.59</v>
+        <v>13322.259796</v>
       </c>
       <c r="AV103" t="n">
-        <v>122709.91</v>
+        <v>122709.905163</v>
       </c>
       <c r="AW103" t="n">
-        <v>236938.24</v>
+        <v>237060.555435</v>
       </c>
       <c r="AX103" t="n">
-        <v>204526.47</v>
+        <v>204496.320569</v>
       </c>
       <c r="AY103" t="n">
-        <v>142508.58</v>
+        <v>142564.282009</v>
       </c>
       <c r="AZ103" t="n">
-        <v>257620.81</v>
+        <v>257620.80604</v>
       </c>
       <c r="BA103" t="n">
-        <v>239852.3</v>
+        <v>239942.755588</v>
       </c>
       <c r="BB103" t="n">
-        <v>161035.2</v>
+        <v>161070.521692</v>
       </c>
       <c r="BC103" t="n">
-        <v>199624.18</v>
+        <v>199627.479776</v>
       </c>
       <c r="BD103" t="n">
         <v>90957.77</v>
@@ -10401,7 +10401,7 @@
         <v>63239.69</v>
       </c>
       <c r="T104" t="n">
-        <v>37906.36</v>
+        <v>42940.88</v>
       </c>
       <c r="U104" t="n">
         <v>43063.61</v>
@@ -10464,49 +10464,49 @@
         <v>64700.44</v>
       </c>
       <c r="AO104" t="n">
-        <v>128539.09</v>
+        <v>128520.323356</v>
       </c>
       <c r="AP104" t="n">
-        <v>90211.67</v>
+        <v>90246.674509</v>
       </c>
       <c r="AQ104" t="n">
-        <v>164358.48</v>
+        <v>164443.319512</v>
       </c>
       <c r="AR104" t="n">
-        <v>9211.379999999999</v>
+        <v>9243.064442999999</v>
       </c>
       <c r="AS104" t="n">
-        <v>85112.42</v>
+        <v>85112.41798100001</v>
       </c>
       <c r="AT104" t="n">
-        <v>164358.48</v>
+        <v>164443.319512</v>
       </c>
       <c r="AU104" t="n">
-        <v>9211.379999999999</v>
+        <v>9243.064442999999</v>
       </c>
       <c r="AV104" t="n">
-        <v>85112.42</v>
+        <v>85112.41798100001</v>
       </c>
       <c r="AW104" t="n">
-        <v>164358.48</v>
+        <v>164443.319512</v>
       </c>
       <c r="AX104" t="n">
-        <v>141831.18</v>
+        <v>141810.620823</v>
       </c>
       <c r="AY104" t="n">
-        <v>98840.8</v>
+        <v>98879.48418100001</v>
       </c>
       <c r="AZ104" t="n">
-        <v>178706</v>
+        <v>178706.002795</v>
       </c>
       <c r="BA104" t="n">
-        <v>166151.77</v>
+        <v>166214.451599</v>
       </c>
       <c r="BB104" t="n">
-        <v>111667.82</v>
+        <v>111692.323476</v>
       </c>
       <c r="BC104" t="n">
-        <v>138497.27</v>
+        <v>138499.571583</v>
       </c>
       <c r="BD104" t="n">
         <v>63075.89</v>
@@ -10618,7 +10618,7 @@
         <v>2824732.08</v>
       </c>
       <c r="T105" t="n">
-        <v>2542602.05</v>
+        <v>2862119.5</v>
       </c>
       <c r="U105" t="n">
         <v>900575.72</v>
@@ -10681,49 +10681,49 @@
         <v>3536763.73</v>
       </c>
       <c r="AO105" t="n">
-        <v>2411284.47</v>
+        <v>2406086.126224</v>
       </c>
       <c r="AP105" t="n">
-        <v>1280759.33</v>
+        <v>1280968.131449</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1296885.41</v>
+        <v>1297908.339691</v>
       </c>
       <c r="AR105" t="n">
-        <v>82176.75</v>
+        <v>82528.274296</v>
       </c>
       <c r="AS105" t="n">
-        <v>1091433.3</v>
+        <v>1091433.296049</v>
       </c>
       <c r="AT105" t="n">
-        <v>1296885.41</v>
+        <v>1297908.339691</v>
       </c>
       <c r="AU105" t="n">
-        <v>82176.75</v>
+        <v>82528.274296</v>
       </c>
       <c r="AV105" t="n">
-        <v>1091433.3</v>
+        <v>1091433.296049</v>
       </c>
       <c r="AW105" t="n">
-        <v>1296885.41</v>
+        <v>1297908.339691</v>
       </c>
       <c r="AX105" t="n">
-        <v>2661625.44</v>
+        <v>2655878.549682</v>
       </c>
       <c r="AY105" t="n">
-        <v>1408737.28</v>
+        <v>1408968.134318</v>
       </c>
       <c r="AZ105" t="n">
-        <v>1399354.84</v>
+        <v>1399354.83594</v>
       </c>
       <c r="BA105" t="n">
-        <v>8578110.25</v>
+        <v>8584347.60743</v>
       </c>
       <c r="BB105" t="n">
-        <v>4348305.16</v>
+        <v>4348771.116954</v>
       </c>
       <c r="BC105" t="n">
-        <v>2270029.37</v>
+        <v>2270114.619598</v>
       </c>
       <c r="BD105" t="n">
         <v>1177835.09</v>
@@ -10835,7 +10835,7 @@
         <v>28247.32</v>
       </c>
       <c r="T106" t="n">
-        <v>25426.02</v>
+        <v>28621.19</v>
       </c>
       <c r="U106" t="n">
         <v>9005.76</v>
@@ -10898,49 +10898,49 @@
         <v>35367.64</v>
       </c>
       <c r="AO106" t="n">
-        <v>24112.84</v>
+        <v>24060.861262</v>
       </c>
       <c r="AP106" t="n">
-        <v>12807.59</v>
+        <v>12809.681314</v>
       </c>
       <c r="AQ106" t="n">
-        <v>12968.85</v>
+        <v>12979.083397</v>
       </c>
       <c r="AR106" t="n">
-        <v>821.77</v>
+        <v>825.282743</v>
       </c>
       <c r="AS106" t="n">
-        <v>10914.33</v>
+        <v>10914.33296</v>
       </c>
       <c r="AT106" t="n">
-        <v>12968.85</v>
+        <v>12979.083397</v>
       </c>
       <c r="AU106" t="n">
-        <v>821.77</v>
+        <v>825.282743</v>
       </c>
       <c r="AV106" t="n">
-        <v>10914.33</v>
+        <v>10914.33296</v>
       </c>
       <c r="AW106" t="n">
-        <v>12968.85</v>
+        <v>12979.083397</v>
       </c>
       <c r="AX106" t="n">
-        <v>26616.25</v>
+        <v>26558.785497</v>
       </c>
       <c r="AY106" t="n">
-        <v>14087.37</v>
+        <v>14089.681343</v>
       </c>
       <c r="AZ106" t="n">
-        <v>13993.55</v>
+        <v>13993.548359</v>
       </c>
       <c r="BA106" t="n">
-        <v>85781.10000000001</v>
+        <v>85843.47607400001</v>
       </c>
       <c r="BB106" t="n">
-        <v>43483.05</v>
+        <v>43487.71117</v>
       </c>
       <c r="BC106" t="n">
-        <v>22700.29</v>
+        <v>22701.146196</v>
       </c>
       <c r="BD106" t="n">
         <v>11778.35</v>
@@ -11052,7 +11052,7 @@
         <v>226663.81</v>
       </c>
       <c r="T107" t="n">
-        <v>204024.97</v>
+        <v>229663.87</v>
       </c>
       <c r="U107" t="n">
         <v>72264.53</v>
@@ -11115,49 +11115,49 @@
         <v>283799.07</v>
       </c>
       <c r="AO107" t="n">
-        <v>193487.7</v>
+        <v>193070.575772</v>
       </c>
       <c r="AP107" t="n">
-        <v>102771.44</v>
+        <v>102788.196976</v>
       </c>
       <c r="AQ107" t="n">
-        <v>104065.44</v>
+        <v>104147.523113</v>
       </c>
       <c r="AR107" t="n">
-        <v>6594.07</v>
+        <v>6622.282246</v>
       </c>
       <c r="AS107" t="n">
-        <v>87579.42999999999</v>
+        <v>87579.431421</v>
       </c>
       <c r="AT107" t="n">
-        <v>104065.44</v>
+        <v>104147.523113</v>
       </c>
       <c r="AU107" t="n">
-        <v>6594.07</v>
+        <v>6622.282246</v>
       </c>
       <c r="AV107" t="n">
-        <v>87579.42999999999</v>
+        <v>87579.431421</v>
       </c>
       <c r="AW107" t="n">
-        <v>104065.44</v>
+        <v>104147.523113</v>
       </c>
       <c r="AX107" t="n">
-        <v>213575.71</v>
+        <v>213114.566091</v>
       </c>
       <c r="AY107" t="n">
-        <v>113040.72</v>
+        <v>113059.248367</v>
       </c>
       <c r="AZ107" t="n">
-        <v>112287.85</v>
+        <v>112287.852434</v>
       </c>
       <c r="BA107" t="n">
-        <v>688329.76</v>
+        <v>688830.261364</v>
       </c>
       <c r="BB107" t="n">
-        <v>348919.26</v>
+        <v>348956.645525</v>
       </c>
       <c r="BC107" t="n">
-        <v>182153.03</v>
+        <v>182159.870296</v>
       </c>
       <c r="BD107" t="n">
         <v>94512.53</v>
@@ -11269,7 +11269,7 @@
         <v>4533276.21</v>
       </c>
       <c r="T108" t="n">
-        <v>4080499.33</v>
+        <v>4593277.47</v>
       </c>
       <c r="U108" t="n">
         <v>1445290.51</v>
@@ -11332,49 +11332,49 @@
         <v>5675981.43</v>
       </c>
       <c r="AO108" t="n">
-        <v>3869754.09</v>
+        <v>3861411.515437</v>
       </c>
       <c r="AP108" t="n">
-        <v>2055428.84</v>
+        <v>2055763.939526</v>
       </c>
       <c r="AQ108" t="n">
-        <v>2081308.82</v>
+        <v>2082950.462263</v>
       </c>
       <c r="AR108" t="n">
-        <v>131881.5</v>
+        <v>132445.644918</v>
       </c>
       <c r="AS108" t="n">
-        <v>1751588.63</v>
+        <v>1751588.628421</v>
       </c>
       <c r="AT108" t="n">
-        <v>2081308.82</v>
+        <v>2082950.462263</v>
       </c>
       <c r="AU108" t="n">
-        <v>131881.5</v>
+        <v>132445.644918</v>
       </c>
       <c r="AV108" t="n">
-        <v>1751588.63</v>
+        <v>1751588.628421</v>
       </c>
       <c r="AW108" t="n">
-        <v>2081308.82</v>
+        <v>2082950.462263</v>
       </c>
       <c r="AX108" t="n">
-        <v>4271514.23</v>
+        <v>4262291.321814</v>
       </c>
       <c r="AY108" t="n">
-        <v>2260814.48</v>
+        <v>2261184.967339</v>
       </c>
       <c r="AZ108" t="n">
-        <v>2245757.05</v>
+        <v>2245757.048672</v>
       </c>
       <c r="BA108" t="n">
-        <v>13766595.19</v>
+        <v>13776605.227288</v>
       </c>
       <c r="BB108" t="n">
-        <v>6978385.11</v>
+        <v>6979132.910491</v>
       </c>
       <c r="BC108" t="n">
-        <v>3643060.59</v>
+        <v>3643197.405919</v>
       </c>
       <c r="BD108" t="n">
         <v>1890250.7</v>
@@ -11486,7 +11486,7 @@
         <v>254911.13</v>
       </c>
       <c r="T109" t="n">
-        <v>229450.99</v>
+        <v>258285.07</v>
       </c>
       <c r="U109" t="n">
         <v>81270.28</v>
@@ -11549,49 +11549,49 @@
         <v>319166.71</v>
       </c>
       <c r="AO109" t="n">
-        <v>217600.55</v>
+        <v>217131.437034</v>
       </c>
       <c r="AP109" t="n">
-        <v>115579.04</v>
+        <v>115597.878291</v>
       </c>
       <c r="AQ109" t="n">
-        <v>117034.29</v>
+        <v>117126.60651</v>
       </c>
       <c r="AR109" t="n">
-        <v>7415.84</v>
+        <v>7447.564989</v>
       </c>
       <c r="AS109" t="n">
-        <v>98493.75999999999</v>
+        <v>98493.76438199999</v>
       </c>
       <c r="AT109" t="n">
-        <v>117034.29</v>
+        <v>117126.60651</v>
       </c>
       <c r="AU109" t="n">
-        <v>7415.84</v>
+        <v>7447.564989</v>
       </c>
       <c r="AV109" t="n">
-        <v>98493.75999999999</v>
+        <v>98493.76438199999</v>
       </c>
       <c r="AW109" t="n">
-        <v>117034.29</v>
+        <v>117126.60651</v>
       </c>
       <c r="AX109" t="n">
-        <v>240191.97</v>
+        <v>239673.351588</v>
       </c>
       <c r="AY109" t="n">
-        <v>127128.1</v>
+        <v>127148.92971</v>
       </c>
       <c r="AZ109" t="n">
-        <v>126281.4</v>
+        <v>126281.400793</v>
       </c>
       <c r="BA109" t="n">
-        <v>774110.86</v>
+        <v>774673.737439</v>
       </c>
       <c r="BB109" t="n">
-        <v>392402.31</v>
+        <v>392444.356694</v>
       </c>
       <c r="BC109" t="n">
-        <v>204853.32</v>
+        <v>204861.016492</v>
       </c>
       <c r="BD109" t="n">
         <v>106290.89</v>
@@ -11733,22 +11733,22 @@
         <v>0.18</v>
       </c>
       <c r="AX111" t="n">
-        <v>0.18</v>
+        <v>0.184096</v>
       </c>
       <c r="AY111" t="n">
-        <v>0.18</v>
+        <v>0.184096</v>
       </c>
       <c r="AZ111" t="n">
-        <v>0.18</v>
+        <v>0.184096</v>
       </c>
       <c r="BA111" t="n">
-        <v>0.18</v>
+        <v>0.184096</v>
       </c>
       <c r="BB111" t="n">
-        <v>0.18</v>
+        <v>0.184096</v>
       </c>
       <c r="BC111" t="n">
-        <v>0.18</v>
+        <v>0.184096</v>
       </c>
       <c r="BD111" t="n">
         <v>0.18</v>
@@ -11878,22 +11878,22 @@
         <v>73123.57000000001</v>
       </c>
       <c r="AX112" t="n">
-        <v>1706.9</v>
+        <v>1706.898717</v>
       </c>
       <c r="AY112" t="n">
-        <v>3889.23</v>
+        <v>3889.233216</v>
       </c>
       <c r="AZ112" t="n">
         <v>0</v>
       </c>
       <c r="BA112" t="n">
-        <v>22153.63</v>
+        <v>22153.630492</v>
       </c>
       <c r="BB112" t="n">
-        <v>32369.68</v>
+        <v>32370.466957</v>
       </c>
       <c r="BC112" t="n">
-        <v>21226.39</v>
+        <v>21201.197174</v>
       </c>
       <c r="BD112" t="n">
         <v>1542.07</v>
@@ -12023,22 +12023,22 @@
         <v>691481.46</v>
       </c>
       <c r="AX113" t="n">
-        <v>69704.23</v>
+        <v>69660.944477</v>
       </c>
       <c r="AY113" t="n">
-        <v>186955.24</v>
+        <v>186899.220532</v>
       </c>
       <c r="AZ113" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA113" t="n">
-        <v>572741.9</v>
+        <v>569679.056934</v>
       </c>
       <c r="BB113" t="n">
-        <v>366179.71</v>
+        <v>366179.531141</v>
       </c>
       <c r="BC113" t="n">
-        <v>427884.05</v>
+        <v>427535.403777</v>
       </c>
       <c r="BD113" t="n">
         <v>59228.06</v>
@@ -12168,22 +12168,22 @@
         <v>544509.98</v>
       </c>
       <c r="AX114" t="n">
-        <v>64987.07</v>
+        <v>64949.189257</v>
       </c>
       <c r="AY114" t="n">
-        <v>171768.21</v>
+        <v>171714.472256</v>
       </c>
       <c r="AZ114" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA114" t="n">
-        <v>526748.49</v>
+        <v>523876.619956</v>
       </c>
       <c r="BB114" t="n">
-        <v>297664.84</v>
+        <v>297663.397741</v>
       </c>
       <c r="BC114" t="n">
-        <v>391380.89</v>
+        <v>391054.833018</v>
       </c>
       <c r="BD114" t="n">
         <v>54976.69</v>
@@ -12313,22 +12313,22 @@
         <v>206939.69</v>
       </c>
       <c r="AX115" t="n">
-        <v>4830.52</v>
+        <v>4830.523368</v>
       </c>
       <c r="AY115" t="n">
-        <v>11006.53</v>
+        <v>11006.530002</v>
       </c>
       <c r="AZ115" t="n">
         <v>0</v>
       </c>
       <c r="BA115" t="n">
-        <v>62694.77</v>
+        <v>62694.774291</v>
       </c>
       <c r="BB115" t="n">
-        <v>91606.17999999999</v>
+        <v>91608.42148800001</v>
       </c>
       <c r="BC115" t="n">
-        <v>60070.7</v>
+        <v>59999.388002</v>
       </c>
       <c r="BD115" t="n">
         <v>4364.05</v>
@@ -12458,22 +12458,22 @@
         <v>6208.19</v>
       </c>
       <c r="AX116" t="n">
-        <v>144.92</v>
+        <v>144.915701</v>
       </c>
       <c r="AY116" t="n">
-        <v>330.2</v>
+        <v>330.1959</v>
       </c>
       <c r="AZ116" t="n">
         <v>0</v>
       </c>
       <c r="BA116" t="n">
-        <v>1880.84</v>
+        <v>1880.843229</v>
       </c>
       <c r="BB116" t="n">
-        <v>2748.19</v>
+        <v>2748.252645</v>
       </c>
       <c r="BC116" t="n">
-        <v>1802.12</v>
+        <v>1799.98164</v>
       </c>
       <c r="BD116" t="n">
         <v>130.92</v>
@@ -12603,22 +12603,22 @@
         <v>13461.72</v>
       </c>
       <c r="AX117" t="n">
-        <v>314.23</v>
+        <v>314.232477</v>
       </c>
       <c r="AY117" t="n">
-        <v>715.99</v>
+        <v>715.990572</v>
       </c>
       <c r="AZ117" t="n">
         <v>0</v>
       </c>
       <c r="BA117" t="n">
-        <v>4078.39</v>
+        <v>4078.38504</v>
       </c>
       <c r="BB117" t="n">
-        <v>5959.11</v>
+        <v>5959.259283</v>
       </c>
       <c r="BC117" t="n">
-        <v>3907.68</v>
+        <v>3903.046293</v>
       </c>
       <c r="BD117" t="n">
         <v>283.89</v>
@@ -12748,22 +12748,22 @@
         <v>403851.72</v>
       </c>
       <c r="AX118" t="n">
-        <v>9426.969999999999</v>
+        <v>9426.974319000001</v>
       </c>
       <c r="AY118" t="n">
-        <v>21479.72</v>
+        <v>21479.717156</v>
       </c>
       <c r="AZ118" t="n">
         <v>0</v>
       </c>
       <c r="BA118" t="n">
-        <v>122351.55</v>
+        <v>122351.55119</v>
       </c>
       <c r="BB118" t="n">
-        <v>178773.41</v>
+        <v>178777.778497</v>
       </c>
       <c r="BC118" t="n">
-        <v>117230.55</v>
+        <v>117091.388803</v>
       </c>
       <c r="BD118" t="n">
         <v>8516.620000000001</v>
@@ -12893,22 +12893,22 @@
         <v>19669.91</v>
       </c>
       <c r="AX119" t="n">
-        <v>459.15</v>
+        <v>459.148178</v>
       </c>
       <c r="AY119" t="n">
-        <v>1046.19</v>
+        <v>1046.186472</v>
       </c>
       <c r="AZ119" t="n">
         <v>0</v>
       </c>
       <c r="BA119" t="n">
-        <v>5959.23</v>
+        <v>5959.228268</v>
       </c>
       <c r="BB119" t="n">
-        <v>8707.299999999999</v>
+        <v>8707.511928</v>
       </c>
       <c r="BC119" t="n">
-        <v>5709.81</v>
+        <v>5703.027933</v>
       </c>
       <c r="BD119" t="n">
         <v>414.81</v>
@@ -13093,49 +13093,49 @@
         <v>55.74</v>
       </c>
       <c r="AO121" t="n">
-        <v>55.74</v>
+        <v>55.744881</v>
       </c>
       <c r="AP121" t="n">
-        <v>55.74</v>
+        <v>55.744881</v>
       </c>
       <c r="AQ121" t="n">
-        <v>55.74</v>
+        <v>55.744881</v>
       </c>
       <c r="AR121" t="n">
-        <v>55.74</v>
+        <v>55.744881</v>
       </c>
       <c r="AS121" t="n">
-        <v>55.74</v>
+        <v>55.744881</v>
       </c>
       <c r="AT121" t="n">
-        <v>55.74</v>
+        <v>55.744881</v>
       </c>
       <c r="AU121" t="n">
-        <v>55.74</v>
+        <v>55.744881</v>
       </c>
       <c r="AV121" t="n">
-        <v>55.74</v>
+        <v>55.744881</v>
       </c>
       <c r="AW121" t="n">
-        <v>55.74</v>
+        <v>55.744881</v>
       </c>
       <c r="AX121" t="n">
-        <v>55.74</v>
+        <v>55.744881</v>
       </c>
       <c r="AY121" t="n">
-        <v>55.74</v>
+        <v>55.744881</v>
       </c>
       <c r="AZ121" t="n">
-        <v>55.74</v>
+        <v>55.744881</v>
       </c>
       <c r="BA121" t="n">
-        <v>55.74</v>
+        <v>55.744881</v>
       </c>
       <c r="BB121" t="n">
-        <v>55.74</v>
+        <v>55.744881</v>
       </c>
       <c r="BC121" t="n">
-        <v>55.74</v>
+        <v>55.744881</v>
       </c>
       <c r="BD121" t="n">
         <v>55.74</v>
@@ -13310,49 +13310,49 @@
         <v>13.94</v>
       </c>
       <c r="AO122" t="n">
-        <v>13.94</v>
+        <v>13.93622</v>
       </c>
       <c r="AP122" t="n">
-        <v>13.94</v>
+        <v>13.93622</v>
       </c>
       <c r="AQ122" t="n">
-        <v>13.94</v>
+        <v>13.93622</v>
       </c>
       <c r="AR122" t="n">
-        <v>13.94</v>
+        <v>13.93622</v>
       </c>
       <c r="AS122" t="n">
-        <v>13.94</v>
+        <v>13.93622</v>
       </c>
       <c r="AT122" t="n">
-        <v>13.94</v>
+        <v>13.93622</v>
       </c>
       <c r="AU122" t="n">
-        <v>13.94</v>
+        <v>13.93622</v>
       </c>
       <c r="AV122" t="n">
-        <v>13.94</v>
+        <v>13.93622</v>
       </c>
       <c r="AW122" t="n">
-        <v>13.94</v>
+        <v>13.93622</v>
       </c>
       <c r="AX122" t="n">
-        <v>13.94</v>
+        <v>13.93622</v>
       </c>
       <c r="AY122" t="n">
-        <v>13.94</v>
+        <v>13.93622</v>
       </c>
       <c r="AZ122" t="n">
-        <v>13.94</v>
+        <v>13.93622</v>
       </c>
       <c r="BA122" t="n">
-        <v>13.94</v>
+        <v>13.93622</v>
       </c>
       <c r="BB122" t="n">
-        <v>13.94</v>
+        <v>13.93622</v>
       </c>
       <c r="BC122" t="n">
-        <v>13.94</v>
+        <v>13.93622</v>
       </c>
       <c r="BD122" t="n">
         <v>13.94</v>
@@ -13464,7 +13464,7 @@
         <v>4303.96</v>
       </c>
       <c r="T123" t="n">
-        <v>8885.610000000001</v>
+        <v>9021.870000000001</v>
       </c>
       <c r="U123" t="n">
         <v>5348.6</v>
@@ -13563,13 +13563,13 @@
         <v>0</v>
       </c>
       <c r="BA123" t="n">
-        <v>1075.96</v>
+        <v>1075.964294</v>
       </c>
       <c r="BB123" t="n">
-        <v>5305.6</v>
+        <v>5306.26559</v>
       </c>
       <c r="BC123" t="n">
-        <v>2886.88</v>
+        <v>2886.879966</v>
       </c>
       <c r="BD123" t="n">
         <v>0</v>
@@ -13681,7 +13681,7 @@
         <v>1075.99</v>
       </c>
       <c r="T124" t="n">
-        <v>2221.4</v>
+        <v>2255.47</v>
       </c>
       <c r="U124" t="n">
         <v>1337.15</v>
@@ -13780,13 +13780,13 @@
         <v>0</v>
       </c>
       <c r="BA124" t="n">
-        <v>268.99</v>
+        <v>268.991073</v>
       </c>
       <c r="BB124" t="n">
-        <v>1326.4</v>
+        <v>1326.566397</v>
       </c>
       <c r="BC124" t="n">
-        <v>721.72</v>
+        <v>721.7199910000001</v>
       </c>
       <c r="BD124" t="n">
         <v>0</v>
@@ -13898,7 +13898,7 @@
         <v>967.33</v>
       </c>
       <c r="T125" t="n">
-        <v>938.89</v>
+        <v>1047.04</v>
       </c>
       <c r="U125" t="n">
         <v>1402.46</v>
@@ -13967,22 +13967,22 @@
         <v>0</v>
       </c>
       <c r="AQ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV125" t="n">
         <v>-0</v>
-      </c>
-      <c r="AR125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT125" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AU125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV125" t="n">
-        <v>0</v>
       </c>
       <c r="AW125" t="n">
         <v>0</v>
@@ -13997,13 +13997,13 @@
         <v>0</v>
       </c>
       <c r="BA125" t="n">
-        <v>340.98</v>
+        <v>435.374629</v>
       </c>
       <c r="BB125" t="n">
-        <v>953.02</v>
+        <v>2006.494199</v>
       </c>
       <c r="BC125" t="n">
-        <v>838.36</v>
+        <v>1022.698736</v>
       </c>
       <c r="BD125" t="n">
         <v>0</v>
@@ -14115,7 +14115,7 @@
         <v>1107.15</v>
       </c>
       <c r="T126" t="n">
-        <v>1074.94</v>
+        <v>1199.16</v>
       </c>
       <c r="U126" t="n">
         <v>1605.09</v>
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="AQ126" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR126" t="n">
         <v>0</v>
@@ -14193,7 +14193,7 @@
         <v>0</v>
       </c>
       <c r="AT126" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU126" t="n">
         <v>0</v>
@@ -14214,13 +14214,13 @@
         <v>0</v>
       </c>
       <c r="BA126" t="n">
-        <v>390.2</v>
+        <v>498.234313</v>
       </c>
       <c r="BB126" t="n">
-        <v>1090.96</v>
+        <v>2296.427835</v>
       </c>
       <c r="BC126" t="n">
-        <v>959.46</v>
+        <v>1170.573153</v>
       </c>
       <c r="BD126" t="n">
         <v>0</v>
@@ -14332,7 +14332,7 @@
         <v>912439.48</v>
       </c>
       <c r="T127" t="n">
-        <v>1883750.25</v>
+        <v>1912636.07</v>
       </c>
       <c r="U127" t="n">
         <v>1133902.9</v>
@@ -14431,13 +14431,13 @@
         <v>0</v>
       </c>
       <c r="BA127" t="n">
-        <v>228104.43</v>
+        <v>228104.430326</v>
       </c>
       <c r="BB127" t="n">
-        <v>1124788.02</v>
+        <v>1124928.305059</v>
       </c>
       <c r="BC127" t="n">
-        <v>612018.55</v>
+        <v>612018.55275</v>
       </c>
       <c r="BD127" t="n">
         <v>0</v>
@@ -14549,7 +14549,7 @@
         <v>11405.49</v>
       </c>
       <c r="T128" t="n">
-        <v>23546.88</v>
+        <v>23907.95</v>
       </c>
       <c r="U128" t="n">
         <v>14173.79</v>
@@ -14648,13 +14648,13 @@
         <v>0</v>
       </c>
       <c r="BA128" t="n">
-        <v>2851.31</v>
+        <v>2851.305379</v>
       </c>
       <c r="BB128" t="n">
-        <v>14059.85</v>
+        <v>14061.603813</v>
       </c>
       <c r="BC128" t="n">
-        <v>7650.23</v>
+        <v>7650.231909</v>
       </c>
       <c r="BD128" t="n">
         <v>0</v>
@@ -14766,7 +14766,7 @@
         <v>119961.86</v>
       </c>
       <c r="T129" t="n">
-        <v>247663.76</v>
+        <v>251461.49</v>
       </c>
       <c r="U129" t="n">
         <v>149078.5</v>
@@ -14865,13 +14865,13 @@
         <v>0</v>
       </c>
       <c r="BA129" t="n">
-        <v>29989.75</v>
+        <v>29989.75098</v>
       </c>
       <c r="BB129" t="n">
-        <v>147880.13</v>
+        <v>147898.572994</v>
       </c>
       <c r="BC129" t="n">
-        <v>80464.39</v>
+        <v>80464.390655</v>
       </c>
       <c r="BD129" t="n">
         <v>0</v>
@@ -14983,7 +14983,7 @@
         <v>1799427.97</v>
       </c>
       <c r="T130" t="n">
-        <v>3714956.4</v>
+        <v>3771922.32</v>
       </c>
       <c r="U130" t="n">
         <v>2236177.44</v>
@@ -15082,13 +15082,13 @@
         <v>0</v>
       </c>
       <c r="BA130" t="n">
-        <v>449846.26</v>
+        <v>449846.264696</v>
       </c>
       <c r="BB130" t="n">
-        <v>2218201.94</v>
+        <v>2218478.594905</v>
       </c>
       <c r="BC130" t="n">
-        <v>1206965.86</v>
+        <v>1206965.859827</v>
       </c>
       <c r="BD130" t="n">
         <v>0</v>
@@ -15200,7 +15200,7 @@
         <v>131367.36</v>
       </c>
       <c r="T131" t="n">
-        <v>271210.64</v>
+        <v>275369.44</v>
       </c>
       <c r="U131" t="n">
         <v>163252.28</v>
@@ -15299,13 +15299,13 @@
         <v>0</v>
       </c>
       <c r="BA131" t="n">
-        <v>32841.06</v>
+        <v>32841.056359</v>
       </c>
       <c r="BB131" t="n">
-        <v>161939.98</v>
+        <v>161960.176807</v>
       </c>
       <c r="BC131" t="n">
-        <v>88114.62</v>
+        <v>88114.622564</v>
       </c>
       <c r="BD131" t="n">
         <v>0</v>
@@ -15498,40 +15498,40 @@
         <v>0</v>
       </c>
       <c r="AO133" t="n">
-        <v>3013.23</v>
+        <v>3032.925845</v>
       </c>
       <c r="AP133" t="n">
-        <v>2230.22</v>
+        <v>2229.342216</v>
       </c>
       <c r="AQ133" t="n">
-        <v>5547.89</v>
+        <v>5551.301984</v>
       </c>
       <c r="AR133" t="n">
         <v>0</v>
       </c>
       <c r="AS133" t="n">
-        <v>3.4</v>
+        <v>3.396204</v>
       </c>
       <c r="AT133" t="n">
-        <v>5547.89</v>
+        <v>5551.301984</v>
       </c>
       <c r="AU133" t="n">
         <v>0</v>
       </c>
       <c r="AV133" t="n">
-        <v>3.4</v>
+        <v>3.396204</v>
       </c>
       <c r="AW133" t="n">
-        <v>5547.89</v>
+        <v>5551.301984</v>
       </c>
       <c r="AX133" t="n">
-        <v>3331.25</v>
+        <v>3353.028963</v>
       </c>
       <c r="AY133" t="n">
-        <v>2470.77</v>
+        <v>2469.796875</v>
       </c>
       <c r="AZ133" t="n">
-        <v>6349.45</v>
+        <v>6349.445344</v>
       </c>
       <c r="BA133" t="n">
         <v>0</v>
@@ -15715,40 +15715,40 @@
         <v>0</v>
       </c>
       <c r="AO134" t="n">
-        <v>511948.6</v>
+        <v>515294.101089</v>
       </c>
       <c r="AP134" t="n">
-        <v>261604.83</v>
+        <v>261501.841957</v>
       </c>
       <c r="AQ134" t="n">
-        <v>515953.43</v>
+        <v>516271.084503</v>
       </c>
       <c r="AR134" t="n">
         <v>0</v>
       </c>
       <c r="AS134" t="n">
-        <v>398.37</v>
+        <v>398.374774</v>
       </c>
       <c r="AT134" t="n">
-        <v>515953.43</v>
+        <v>516271.084503</v>
       </c>
       <c r="AU134" t="n">
         <v>0</v>
       </c>
       <c r="AV134" t="n">
-        <v>398.37</v>
+        <v>398.374774</v>
       </c>
       <c r="AW134" t="n">
-        <v>515953.43</v>
+        <v>516271.084503</v>
       </c>
       <c r="AX134" t="n">
-        <v>565979.88</v>
+        <v>569679.620802</v>
       </c>
       <c r="AY134" t="n">
-        <v>289820.94</v>
+        <v>289707.173455</v>
       </c>
       <c r="AZ134" t="n">
-        <v>590498.42</v>
+        <v>590498.4170369999</v>
       </c>
       <c r="BA134" t="n">
         <v>0</v>
@@ -15940,19 +15940,19 @@
         <v>447644.98</v>
       </c>
       <c r="AR139" t="n">
-        <v>366208.43</v>
+        <v>366198.857555</v>
       </c>
       <c r="AS139" t="n">
-        <v>51360.13</v>
+        <v>51360.1307</v>
       </c>
       <c r="AT139" t="n">
         <v>0</v>
       </c>
       <c r="AU139" t="n">
-        <v>366208.43</v>
+        <v>366198.857555</v>
       </c>
       <c r="AV139" t="n">
-        <v>51360.13</v>
+        <v>51360.1307</v>
       </c>
       <c r="AW139" t="n">
         <v>0</v>
@@ -16013,19 +16013,19 @@
         <v>2238224.92</v>
       </c>
       <c r="AR140" t="n">
-        <v>1831042.13</v>
+        <v>1830994.287775</v>
       </c>
       <c r="AS140" t="n">
-        <v>256800.65</v>
+        <v>256800.653501</v>
       </c>
       <c r="AT140" t="n">
         <v>0</v>
       </c>
       <c r="AU140" t="n">
-        <v>1831042.13</v>
+        <v>1830994.287775</v>
       </c>
       <c r="AV140" t="n">
-        <v>256800.65</v>
+        <v>256800.653501</v>
       </c>
       <c r="AW140" t="n">
         <v>0</v>
@@ -16355,49 +16355,49 @@
         <v>80.41</v>
       </c>
       <c r="AO145" t="n">
-        <v>80.41</v>
+        <v>80.41084499999999</v>
       </c>
       <c r="AP145" t="n">
-        <v>80.41</v>
+        <v>80.41084499999999</v>
       </c>
       <c r="AQ145" t="n">
-        <v>80.41</v>
+        <v>80.41084499999999</v>
       </c>
       <c r="AR145" t="n">
-        <v>80.41</v>
+        <v>80.41084499999999</v>
       </c>
       <c r="AS145" t="n">
-        <v>80.41</v>
+        <v>80.41084499999999</v>
       </c>
       <c r="AT145" t="n">
-        <v>80.41</v>
+        <v>80.41084499999999</v>
       </c>
       <c r="AU145" t="n">
-        <v>80.41</v>
+        <v>80.41084499999999</v>
       </c>
       <c r="AV145" t="n">
-        <v>80.41</v>
+        <v>80.41084499999999</v>
       </c>
       <c r="AW145" t="n">
-        <v>80.41</v>
+        <v>80.41084499999999</v>
       </c>
       <c r="AX145" t="n">
-        <v>80.41</v>
+        <v>80.41084499999999</v>
       </c>
       <c r="AY145" t="n">
-        <v>80.41</v>
+        <v>80.41084499999999</v>
       </c>
       <c r="AZ145" t="n">
-        <v>80.41</v>
+        <v>80.41084499999999</v>
       </c>
       <c r="BA145" t="n">
-        <v>80.41</v>
+        <v>80.41084499999999</v>
       </c>
       <c r="BB145" t="n">
-        <v>80.41</v>
+        <v>80.41084499999999</v>
       </c>
       <c r="BC145" t="n">
-        <v>80.41</v>
+        <v>80.41084499999999</v>
       </c>
       <c r="BD145" t="n">
         <v>80.41</v>
@@ -16509,7 +16509,7 @@
         <v>3904.01</v>
       </c>
       <c r="T146" t="n">
-        <v>908.92</v>
+        <v>941.62</v>
       </c>
       <c r="U146" t="n">
         <v>317.33</v>
@@ -16572,7 +16572,7 @@
         <v>16709.88</v>
       </c>
       <c r="AO146" t="n">
-        <v>7424.41</v>
+        <v>7431.885065</v>
       </c>
       <c r="AP146" t="n">
         <v>0</v>
@@ -16581,7 +16581,7 @@
         <v>0</v>
       </c>
       <c r="AR146" t="n">
-        <v>1804.55</v>
+        <v>1808.639419</v>
       </c>
       <c r="AS146" t="n">
         <v>0</v>
@@ -16590,7 +16590,7 @@
         <v>0</v>
       </c>
       <c r="AU146" t="n">
-        <v>1804.55</v>
+        <v>1808.639419</v>
       </c>
       <c r="AV146" t="n">
         <v>0</v>
@@ -16599,7 +16599,7 @@
         <v>0</v>
       </c>
       <c r="AX146" t="n">
-        <v>8209.09</v>
+        <v>8217.360196</v>
       </c>
       <c r="AY146" t="n">
         <v>0</v>
@@ -16608,10 +16608,10 @@
         <v>0</v>
       </c>
       <c r="BA146" t="n">
-        <v>12879.33</v>
+        <v>12865.644172</v>
       </c>
       <c r="BB146" t="n">
-        <v>157.02</v>
+        <v>157.210491</v>
       </c>
       <c r="BC146" t="n">
         <v>0</v>
@@ -16726,7 +16726,7 @@
         <v>4968.62</v>
       </c>
       <c r="T147" t="n">
-        <v>994.98</v>
+        <v>1030.77</v>
       </c>
       <c r="U147" t="n">
         <v>557.2</v>
@@ -16789,7 +16789,7 @@
         <v>29340.81</v>
       </c>
       <c r="AO147" t="n">
-        <v>9570.6</v>
+        <v>9580.234944</v>
       </c>
       <c r="AP147" t="n">
         <v>0</v>
@@ -16798,7 +16798,7 @@
         <v>0</v>
       </c>
       <c r="AR147" t="n">
-        <v>2326.19</v>
+        <v>2331.466433</v>
       </c>
       <c r="AS147" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
         <v>0</v>
       </c>
       <c r="AU147" t="n">
-        <v>2326.19</v>
+        <v>2331.466433</v>
       </c>
       <c r="AV147" t="n">
         <v>0</v>
@@ -16816,7 +16816,7 @@
         <v>0</v>
       </c>
       <c r="AX147" t="n">
-        <v>10582.11</v>
+        <v>10592.768943</v>
       </c>
       <c r="AY147" t="n">
         <v>0</v>
@@ -16825,10 +16825,10 @@
         <v>0</v>
       </c>
       <c r="BA147" t="n">
-        <v>16602.38</v>
+        <v>16584.741665</v>
       </c>
       <c r="BB147" t="n">
-        <v>171.89</v>
+        <v>172.094709</v>
       </c>
       <c r="BC147" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
         <v>4294415.69</v>
       </c>
       <c r="T148" t="n">
-        <v>999814.76</v>
+        <v>1035783.31</v>
       </c>
       <c r="U148" t="n">
         <v>349063.02</v>
@@ -17006,7 +17006,7 @@
         <v>18380869.14</v>
       </c>
       <c r="AO148" t="n">
-        <v>8166848.24</v>
+        <v>8175073.571221</v>
       </c>
       <c r="AP148" t="n">
         <v>0</v>
@@ -17015,7 +17015,7 @@
         <v>0</v>
       </c>
       <c r="AR148" t="n">
-        <v>1985004.31</v>
+        <v>1989503.36094</v>
       </c>
       <c r="AS148" t="n">
         <v>0</v>
@@ -17024,7 +17024,7 @@
         <v>0</v>
       </c>
       <c r="AU148" t="n">
-        <v>1985004.31</v>
+        <v>1989503.36094</v>
       </c>
       <c r="AV148" t="n">
         <v>0</v>
@@ -17033,7 +17033,7 @@
         <v>0</v>
       </c>
       <c r="AX148" t="n">
-        <v>9030001.119999999</v>
+        <v>9039096.215946</v>
       </c>
       <c r="AY148" t="n">
         <v>0</v>
@@ -17042,10 +17042,10 @@
         <v>0</v>
       </c>
       <c r="BA148" t="n">
-        <v>14167259.79</v>
+        <v>14152208.589738</v>
       </c>
       <c r="BB148" t="n">
-        <v>172723.35</v>
+        <v>172931.54027</v>
       </c>
       <c r="BC148" t="n">
         <v>0</v>
@@ -17160,7 +17160,7 @@
         <v>69647.61</v>
       </c>
       <c r="T149" t="n">
-        <v>16215.18</v>
+        <v>16798.52</v>
       </c>
       <c r="U149" t="n">
         <v>5661.17</v>
@@ -17223,7 +17223,7 @@
         <v>298104.28</v>
       </c>
       <c r="AO149" t="n">
-        <v>132451.43</v>
+        <v>132584.829555</v>
       </c>
       <c r="AP149" t="n">
         <v>0</v>
@@ -17232,7 +17232,7 @@
         <v>0</v>
       </c>
       <c r="AR149" t="n">
-        <v>32193.16</v>
+        <v>32266.127236</v>
       </c>
       <c r="AS149" t="n">
         <v>0</v>
@@ -17241,7 +17241,7 @@
         <v>0</v>
       </c>
       <c r="AU149" t="n">
-        <v>32193.16</v>
+        <v>32266.127236</v>
       </c>
       <c r="AV149" t="n">
         <v>0</v>
@@ -17250,7 +17250,7 @@
         <v>0</v>
       </c>
       <c r="AX149" t="n">
-        <v>146450.2</v>
+        <v>146597.705902</v>
       </c>
       <c r="AY149" t="n">
         <v>0</v>
@@ -17259,10 +17259,10 @@
         <v>0</v>
       </c>
       <c r="BA149" t="n">
-        <v>229767.2</v>
+        <v>229523.092037</v>
       </c>
       <c r="BB149" t="n">
-        <v>2801.26</v>
+        <v>2804.635162</v>
       </c>
       <c r="BC149" t="n">
         <v>0</v>
@@ -17594,7 +17594,7 @@
         <v>313925.09</v>
       </c>
       <c r="T151" t="n">
-        <v>73087.23</v>
+        <v>75716.56</v>
       </c>
       <c r="U151" t="n">
         <v>25516.78</v>
@@ -17657,7 +17657,7 @@
         <v>1343655.66</v>
       </c>
       <c r="AO151" t="n">
-        <v>597002.88</v>
+        <v>597604.16122</v>
       </c>
       <c r="AP151" t="n">
         <v>0</v>
@@ -17666,7 +17666,7 @@
         <v>0</v>
       </c>
       <c r="AR151" t="n">
-        <v>145105.34</v>
+        <v>145434.224769</v>
       </c>
       <c r="AS151" t="n">
         <v>0</v>
@@ -17675,7 +17675,7 @@
         <v>0</v>
       </c>
       <c r="AU151" t="n">
-        <v>145105.34</v>
+        <v>145434.224769</v>
       </c>
       <c r="AV151" t="n">
         <v>0</v>
@@ -17684,7 +17684,7 @@
         <v>0</v>
       </c>
       <c r="AX151" t="n">
-        <v>660100.02</v>
+        <v>660764.880617</v>
       </c>
       <c r="AY151" t="n">
         <v>0</v>
@@ -17693,10 +17693,10 @@
         <v>0</v>
       </c>
       <c r="BA151" t="n">
-        <v>1035637.58</v>
+        <v>1034537.324955</v>
       </c>
       <c r="BB151" t="n">
-        <v>12626.21</v>
+        <v>12641.428505</v>
       </c>
       <c r="BC151" t="n">
         <v>0</v>
@@ -17811,7 +17811,7 @@
         <v>7848127.19</v>
       </c>
       <c r="T152" t="n">
-        <v>1827180.69</v>
+        <v>1892913.9</v>
       </c>
       <c r="U152" t="n">
         <v>637919.38</v>
@@ -17874,7 +17874,7 @@
         <v>33591391.53</v>
       </c>
       <c r="AO152" t="n">
-        <v>14925072.08</v>
+        <v>14940104.030507</v>
       </c>
       <c r="AP152" t="n">
         <v>0</v>
@@ -17883,7 +17883,7 @@
         <v>0</v>
       </c>
       <c r="AR152" t="n">
-        <v>3627633.52</v>
+        <v>3635855.619223</v>
       </c>
       <c r="AS152" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
         <v>0</v>
       </c>
       <c r="AU152" t="n">
-        <v>3627633.52</v>
+        <v>3635855.619223</v>
       </c>
       <c r="AV152" t="n">
         <v>0</v>
@@ -17901,7 +17901,7 @@
         <v>0</v>
       </c>
       <c r="AX152" t="n">
-        <v>16502500.56</v>
+        <v>16519122.015415</v>
       </c>
       <c r="AY152" t="n">
         <v>0</v>
@@ -17910,10 +17910,10 @@
         <v>0</v>
       </c>
       <c r="BA152" t="n">
-        <v>25890939.48</v>
+        <v>25863433.123886</v>
       </c>
       <c r="BB152" t="n">
-        <v>315655.24</v>
+        <v>316035.712619</v>
       </c>
       <c r="BC152" t="n">
         <v>0</v>
@@ -18028,7 +18028,7 @@
         <v>383572.7</v>
       </c>
       <c r="T153" t="n">
-        <v>89302.41</v>
+        <v>92515.08</v>
       </c>
       <c r="U153" t="n">
         <v>31177.94</v>
@@ -18091,7 +18091,7 @@
         <v>1641759.94</v>
       </c>
       <c r="AO153" t="n">
-        <v>729454.3100000001</v>
+        <v>730188.990775</v>
       </c>
       <c r="AP153" t="n">
         <v>0</v>
@@ -18100,7 +18100,7 @@
         <v>0</v>
       </c>
       <c r="AR153" t="n">
-        <v>177298.5</v>
+        <v>177700.352005</v>
       </c>
       <c r="AS153" t="n">
         <v>0</v>
@@ -18109,7 +18109,7 @@
         <v>0</v>
       </c>
       <c r="AU153" t="n">
-        <v>177298.5</v>
+        <v>177700.352005</v>
       </c>
       <c r="AV153" t="n">
         <v>0</v>
@@ -18118,7 +18118,7 @@
         <v>0</v>
       </c>
       <c r="AX153" t="n">
-        <v>806550.22</v>
+        <v>807362.586519</v>
       </c>
       <c r="AY153" t="n">
         <v>0</v>
@@ -18127,10 +18127,10 @@
         <v>0</v>
       </c>
       <c r="BA153" t="n">
-        <v>1265404.77</v>
+        <v>1264060.416993</v>
       </c>
       <c r="BB153" t="n">
-        <v>15427.47</v>
+        <v>15446.063667</v>
       </c>
       <c r="BC153" t="n">
         <v>0</v>
@@ -18254,7 +18254,7 @@
         <v>82.89</v>
       </c>
       <c r="T155" t="n">
-        <v>82.89</v>
+        <v>313.74</v>
       </c>
       <c r="U155" t="n">
         <v>82.89</v>
@@ -18317,49 +18317,49 @@
         <v>82.89</v>
       </c>
       <c r="AO155" t="n">
-        <v>82.89</v>
+        <v>82.886016</v>
       </c>
       <c r="AP155" t="n">
-        <v>82.89</v>
+        <v>82.886016</v>
       </c>
       <c r="AQ155" t="n">
-        <v>82.89</v>
+        <v>82.886016</v>
       </c>
       <c r="AR155" t="n">
-        <v>82.89</v>
+        <v>82.886016</v>
       </c>
       <c r="AS155" t="n">
-        <v>82.89</v>
+        <v>82.886016</v>
       </c>
       <c r="AT155" t="n">
-        <v>82.89</v>
+        <v>82.886016</v>
       </c>
       <c r="AU155" t="n">
-        <v>82.89</v>
+        <v>82.886016</v>
       </c>
       <c r="AV155" t="n">
-        <v>82.89</v>
+        <v>82.886016</v>
       </c>
       <c r="AW155" t="n">
-        <v>82.89</v>
+        <v>82.886016</v>
       </c>
       <c r="AX155" t="n">
-        <v>82.89</v>
+        <v>82.886016</v>
       </c>
       <c r="AY155" t="n">
-        <v>82.89</v>
+        <v>82.886016</v>
       </c>
       <c r="AZ155" t="n">
-        <v>82.89</v>
+        <v>82.886016</v>
       </c>
       <c r="BA155" t="n">
-        <v>82.89</v>
+        <v>82.886016</v>
       </c>
       <c r="BB155" t="n">
-        <v>82.89</v>
+        <v>82.886016</v>
       </c>
       <c r="BC155" t="n">
-        <v>82.89</v>
+        <v>82.886016</v>
       </c>
       <c r="BD155" t="n">
         <v>82.89</v>
@@ -18471,7 +18471,7 @@
         <v>15171.14</v>
       </c>
       <c r="T156" t="n">
-        <v>5581.9</v>
+        <v>5047.96</v>
       </c>
       <c r="U156" t="n">
         <v>16811.26</v>
@@ -18534,49 +18534,49 @@
         <v>116036.47</v>
       </c>
       <c r="AO156" t="n">
-        <v>24177.74</v>
+        <v>24127.70128</v>
       </c>
       <c r="AP156" t="n">
-        <v>10769.38</v>
+        <v>10768.159626</v>
       </c>
       <c r="AQ156" t="n">
-        <v>14427.38</v>
+        <v>14417.283642</v>
       </c>
       <c r="AR156" t="n">
-        <v>16355.52</v>
+        <v>16350.746376</v>
       </c>
       <c r="AS156" t="n">
-        <v>10650.23</v>
+        <v>10650.232106</v>
       </c>
       <c r="AT156" t="n">
-        <v>14427.38</v>
+        <v>14417.283642</v>
       </c>
       <c r="AU156" t="n">
-        <v>16355.52</v>
+        <v>16350.746376</v>
       </c>
       <c r="AV156" t="n">
-        <v>10650.23</v>
+        <v>10650.232106</v>
       </c>
       <c r="AW156" t="n">
-        <v>14427.38</v>
+        <v>14417.283642</v>
       </c>
       <c r="AX156" t="n">
-        <v>26733.09</v>
+        <v>26677.755428</v>
       </c>
       <c r="AY156" t="n">
-        <v>11905.76</v>
+        <v>11904.408139</v>
       </c>
       <c r="AZ156" t="n">
-        <v>15869.84</v>
+        <v>15869.841892</v>
       </c>
       <c r="BA156" t="n">
-        <v>28030.13</v>
+        <v>28030.132357</v>
       </c>
       <c r="BB156" t="n">
-        <v>14082.43</v>
+        <v>14079.135092</v>
       </c>
       <c r="BC156" t="n">
-        <v>39848.24</v>
+        <v>39848.242216</v>
       </c>
       <c r="BD156" t="n">
         <v>11960.77</v>
@@ -18688,7 +18688,7 @@
         <v>43592.36</v>
       </c>
       <c r="T157" t="n">
-        <v>36486.88</v>
+        <v>32996.75</v>
       </c>
       <c r="U157" t="n">
         <v>78637.05</v>
@@ -18751,49 +18751,49 @@
         <v>542776.9300000001</v>
       </c>
       <c r="AO157" t="n">
-        <v>70587.46000000001</v>
+        <v>70441.35469599999</v>
       </c>
       <c r="AP157" t="n">
-        <v>70395.64</v>
+        <v>70387.647547</v>
       </c>
       <c r="AQ157" t="n">
-        <v>67486.11</v>
+        <v>67438.877074</v>
       </c>
       <c r="AR157" t="n">
-        <v>47750.3</v>
+        <v>47736.363762</v>
       </c>
       <c r="AS157" t="n">
-        <v>69616.8</v>
+        <v>69616.797095</v>
       </c>
       <c r="AT157" t="n">
-        <v>67486.11</v>
+        <v>67438.877074</v>
       </c>
       <c r="AU157" t="n">
-        <v>47750.3</v>
+        <v>47736.363762</v>
       </c>
       <c r="AV157" t="n">
-        <v>69616.8</v>
+        <v>69616.797095</v>
       </c>
       <c r="AW157" t="n">
-        <v>67486.11</v>
+        <v>67438.877074</v>
       </c>
       <c r="AX157" t="n">
-        <v>78047.83</v>
+        <v>77886.29388300001</v>
       </c>
       <c r="AY157" t="n">
-        <v>77823.74000000001</v>
+        <v>77814.90184599999</v>
       </c>
       <c r="AZ157" t="n">
-        <v>74233.42</v>
+        <v>74233.423096</v>
       </c>
       <c r="BA157" t="n">
-        <v>81834.59</v>
+        <v>81834.58808</v>
       </c>
       <c r="BB157" t="n">
-        <v>92051.86</v>
+        <v>92030.32208300001</v>
       </c>
       <c r="BC157" t="n">
-        <v>186395.77</v>
+        <v>186395.771569</v>
       </c>
       <c r="BD157" t="n">
         <v>34919.72</v>
@@ -18905,7 +18905,7 @@
         <v>16384831.26</v>
       </c>
       <c r="T158" t="n">
-        <v>6028447.85</v>
+        <v>5451801.16</v>
       </c>
       <c r="U158" t="n">
         <v>18156164.37</v>
@@ -18968,49 +18968,49 @@
         <v>125319383.75</v>
       </c>
       <c r="AO158" t="n">
-        <v>26111963.95</v>
+        <v>26057917.382366</v>
       </c>
       <c r="AP158" t="n">
-        <v>11630932.49</v>
+        <v>11629612.396161</v>
       </c>
       <c r="AQ158" t="n">
-        <v>15581570.9</v>
+        <v>15570666.333761</v>
       </c>
       <c r="AR158" t="n">
-        <v>17663960.46</v>
+        <v>17658806.086259</v>
       </c>
       <c r="AS158" t="n">
-        <v>11502250.67</v>
+        <v>11502250.674575</v>
       </c>
       <c r="AT158" t="n">
-        <v>15581570.9</v>
+        <v>15570666.333761</v>
       </c>
       <c r="AU158" t="n">
-        <v>17663960.46</v>
+        <v>17658806.086259</v>
       </c>
       <c r="AV158" t="n">
-        <v>11502250.67</v>
+        <v>11502250.674575</v>
       </c>
       <c r="AW158" t="n">
-        <v>15581570.9</v>
+        <v>15570666.333761</v>
       </c>
       <c r="AX158" t="n">
-        <v>28871733.23</v>
+        <v>28811975.862278</v>
       </c>
       <c r="AY158" t="n">
-        <v>12858220.23</v>
+        <v>12856760.790432</v>
       </c>
       <c r="AZ158" t="n">
-        <v>17139429.24</v>
+        <v>17139429.243052</v>
       </c>
       <c r="BA158" t="n">
-        <v>30272542.95</v>
+        <v>30272542.946008</v>
       </c>
       <c r="BB158" t="n">
-        <v>15209024.52</v>
+        <v>15205465.899427</v>
       </c>
       <c r="BC158" t="n">
-        <v>43036101.59</v>
+        <v>43036101.593514</v>
       </c>
       <c r="BD158" t="n">
         <v>12917627.06</v>
@@ -19122,7 +19122,7 @@
         <v>192370.06</v>
       </c>
       <c r="T159" t="n">
-        <v>70778.44</v>
+        <v>64008.18</v>
       </c>
       <c r="U159" t="n">
         <v>213166.82</v>
@@ -19185,49 +19185,49 @@
         <v>1471342.39</v>
       </c>
       <c r="AO159" t="n">
-        <v>306573.8</v>
+        <v>305939.25223</v>
       </c>
       <c r="AP159" t="n">
-        <v>136555.76</v>
+        <v>136540.264059</v>
       </c>
       <c r="AQ159" t="n">
-        <v>182939.18</v>
+        <v>182811.156585</v>
       </c>
       <c r="AR159" t="n">
-        <v>207387.98</v>
+        <v>207327.46405</v>
       </c>
       <c r="AS159" t="n">
-        <v>135044.94</v>
+        <v>135044.943105</v>
       </c>
       <c r="AT159" t="n">
-        <v>182939.18</v>
+        <v>182811.156585</v>
       </c>
       <c r="AU159" t="n">
-        <v>207387.98</v>
+        <v>207327.46405</v>
       </c>
       <c r="AV159" t="n">
-        <v>135044.94</v>
+        <v>135044.943105</v>
       </c>
       <c r="AW159" t="n">
-        <v>182939.18</v>
+        <v>182811.156585</v>
       </c>
       <c r="AX159" t="n">
-        <v>338975.53</v>
+        <v>338273.938827</v>
       </c>
       <c r="AY159" t="n">
-        <v>150965.03</v>
+        <v>150947.895206</v>
       </c>
       <c r="AZ159" t="n">
-        <v>201229.6</v>
+        <v>201229.595187</v>
       </c>
       <c r="BA159" t="n">
-        <v>355422.08</v>
+        <v>355422.078292</v>
       </c>
       <c r="BB159" t="n">
-        <v>178565.21</v>
+        <v>178523.432967</v>
       </c>
       <c r="BC159" t="n">
-        <v>505275.71</v>
+        <v>505275.711302</v>
       </c>
       <c r="BD159" t="n">
         <v>151662.51</v>
@@ -19339,7 +19339,7 @@
         <v>217961.8</v>
       </c>
       <c r="T160" t="n">
-        <v>182434.4</v>
+        <v>164983.77</v>
       </c>
       <c r="U160" t="n">
         <v>393185.27</v>
@@ -19402,49 +19402,49 @@
         <v>2713884.66</v>
       </c>
       <c r="AO160" t="n">
-        <v>352937.28</v>
+        <v>352206.773481</v>
       </c>
       <c r="AP160" t="n">
-        <v>351978.19</v>
+        <v>351938.237736</v>
       </c>
       <c r="AQ160" t="n">
-        <v>337430.53</v>
+        <v>337194.385371</v>
       </c>
       <c r="AR160" t="n">
-        <v>238751.49</v>
+        <v>238681.818808</v>
       </c>
       <c r="AS160" t="n">
-        <v>348083.99</v>
+        <v>348083.985477</v>
       </c>
       <c r="AT160" t="n">
-        <v>337430.53</v>
+        <v>337194.385371</v>
       </c>
       <c r="AU160" t="n">
-        <v>238751.49</v>
+        <v>238681.818808</v>
       </c>
       <c r="AV160" t="n">
-        <v>348083.99</v>
+        <v>348083.985477</v>
       </c>
       <c r="AW160" t="n">
-        <v>337430.53</v>
+        <v>337194.385371</v>
       </c>
       <c r="AX160" t="n">
-        <v>390239.17</v>
+        <v>389431.469414</v>
       </c>
       <c r="AY160" t="n">
-        <v>389118.68</v>
+        <v>389074.50923</v>
       </c>
       <c r="AZ160" t="n">
-        <v>371167.12</v>
+        <v>371167.115481</v>
       </c>
       <c r="BA160" t="n">
-        <v>409172.94</v>
+        <v>409172.940402</v>
       </c>
       <c r="BB160" t="n">
-        <v>460259.3</v>
+        <v>460151.610415</v>
       </c>
       <c r="BC160" t="n">
-        <v>931978.86</v>
+        <v>931978.857843</v>
       </c>
       <c r="BD160" t="n">
         <v>174598.59</v>
@@ -19556,7 +19556,7 @@
         <v>1257475.35</v>
       </c>
       <c r="T161" t="n">
-        <v>462661.13</v>
+        <v>1583744.68</v>
       </c>
       <c r="U161" t="n">
         <v>1393418.64</v>
@@ -19619,49 +19619,49 @@
         <v>9617800.390000001</v>
       </c>
       <c r="AO161" t="n">
-        <v>2003996.9</v>
+        <v>1999849.030063</v>
       </c>
       <c r="AP161" t="n">
-        <v>892631.16</v>
+        <v>892529.849151</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1195828.08</v>
+        <v>1194991.200105</v>
       </c>
       <c r="AR161" t="n">
-        <v>1355643.8</v>
+        <v>1355248.222852</v>
       </c>
       <c r="AS161" t="n">
-        <v>882755.3100000001</v>
+        <v>882755.306863</v>
       </c>
       <c r="AT161" t="n">
-        <v>1195828.08</v>
+        <v>1194991.200105</v>
       </c>
       <c r="AU161" t="n">
-        <v>1355643.8</v>
+        <v>1355248.222852</v>
       </c>
       <c r="AV161" t="n">
-        <v>882755.3100000001</v>
+        <v>882755.306863</v>
       </c>
       <c r="AW161" t="n">
-        <v>1195828.08</v>
+        <v>1194991.200105</v>
       </c>
       <c r="AX161" t="n">
-        <v>2215799.02</v>
+        <v>2211212.858529</v>
       </c>
       <c r="AY161" t="n">
-        <v>986820.97</v>
+        <v>986708.961396</v>
       </c>
       <c r="AZ161" t="n">
-        <v>1315387.97</v>
+        <v>1315387.966144</v>
       </c>
       <c r="BA161" t="n">
-        <v>2323305.99</v>
+        <v>2323305.994096</v>
       </c>
       <c r="BB161" t="n">
-        <v>1167236.53</v>
+        <v>1166963.414014</v>
       </c>
       <c r="BC161" t="n">
-        <v>3302862.03</v>
+        <v>3302862.03485</v>
       </c>
       <c r="BD161" t="n">
         <v>991380.22</v>
@@ -19773,7 +19773,7 @@
         <v>31436883.87</v>
       </c>
       <c r="T162" t="n">
-        <v>11566528.34</v>
+        <v>39593616.89</v>
       </c>
       <c r="U162" t="n">
         <v>34835465.91</v>
@@ -19836,49 +19836,49 @@
         <v>240445009.82</v>
       </c>
       <c r="AO162" t="n">
-        <v>50099922.62</v>
+        <v>49996225.751569</v>
       </c>
       <c r="AP162" t="n">
-        <v>22315779.04</v>
+        <v>22313246.228771</v>
       </c>
       <c r="AQ162" t="n">
-        <v>29895702.12</v>
+        <v>29874780.002637</v>
       </c>
       <c r="AR162" t="n">
-        <v>33891095.05</v>
+        <v>33881205.571297</v>
       </c>
       <c r="AS162" t="n">
-        <v>22068882.67</v>
+        <v>22068882.671581</v>
       </c>
       <c r="AT162" t="n">
-        <v>29895702.12</v>
+        <v>29874780.002637</v>
       </c>
       <c r="AU162" t="n">
-        <v>33891095.05</v>
+        <v>33881205.571297</v>
       </c>
       <c r="AV162" t="n">
-        <v>22068882.67</v>
+        <v>22068882.671581</v>
       </c>
       <c r="AW162" t="n">
-        <v>29895702.12</v>
+        <v>29874780.002637</v>
       </c>
       <c r="AX162" t="n">
-        <v>55394975.41</v>
+        <v>55280321.463219</v>
       </c>
       <c r="AY162" t="n">
-        <v>24670524.19</v>
+        <v>24667724.034898</v>
       </c>
       <c r="AZ162" t="n">
-        <v>32884699.15</v>
+        <v>32884699.153608</v>
       </c>
       <c r="BA162" t="n">
-        <v>58082649.85</v>
+        <v>58082649.852398</v>
       </c>
       <c r="BB162" t="n">
-        <v>29180913.13</v>
+        <v>29174085.35035</v>
       </c>
       <c r="BC162" t="n">
-        <v>82571550.87</v>
+        <v>82571550.871246</v>
       </c>
       <c r="BD162" t="n">
         <v>24784505.57</v>
@@ -19990,7 +19990,7 @@
         <v>1667807.21</v>
       </c>
       <c r="T163" t="n">
-        <v>715873.97</v>
+        <v>1812736.63</v>
       </c>
       <c r="U163" t="n">
         <v>1999770.73</v>
@@ -20053,49 +20053,49 @@
         <v>13803027.45</v>
       </c>
       <c r="AO163" t="n">
-        <v>2663507.99</v>
+        <v>2657995.055774</v>
       </c>
       <c r="AP163" t="n">
-        <v>1381165.11</v>
+        <v>1381008.350945</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1716197.8</v>
+        <v>1714996.742062</v>
       </c>
       <c r="AR163" t="n">
-        <v>1801783.27</v>
+        <v>1801257.50571</v>
       </c>
       <c r="AS163" t="n">
-        <v>1365884.24</v>
+        <v>1365884.235445</v>
       </c>
       <c r="AT163" t="n">
-        <v>1716197.8</v>
+        <v>1714996.742062</v>
       </c>
       <c r="AU163" t="n">
-        <v>1801783.27</v>
+        <v>1801257.50571</v>
       </c>
       <c r="AV163" t="n">
-        <v>1365884.24</v>
+        <v>1365884.235445</v>
       </c>
       <c r="AW163" t="n">
-        <v>1716197.8</v>
+        <v>1714996.742062</v>
       </c>
       <c r="AX163" t="n">
-        <v>2945013.72</v>
+        <v>2938918.26677</v>
       </c>
       <c r="AY163" t="n">
-        <v>1526904.67</v>
+        <v>1526731.365832</v>
       </c>
       <c r="AZ163" t="n">
-        <v>1887784.68</v>
+        <v>1887784.676812</v>
       </c>
       <c r="BA163" t="n">
-        <v>3087901.01</v>
+        <v>3087901.01279</v>
       </c>
       <c r="BB163" t="n">
-        <v>1806061.04</v>
+        <v>1805638.457396</v>
       </c>
       <c r="BC163" t="n">
-        <v>4740116.6</v>
+        <v>4740116.603994</v>
       </c>
       <c r="BD163" t="n">
         <v>1317641.33</v>
@@ -20222,7 +20222,7 @@
         <v>14304.45</v>
       </c>
       <c r="T165" t="n">
-        <v>6753.16</v>
+        <v>1474.74</v>
       </c>
       <c r="U165" t="n">
         <v>18342.18</v>
@@ -20285,49 +20285,49 @@
         <v>111415.53</v>
       </c>
       <c r="AO165" t="n">
-        <v>13830.35</v>
+        <v>13688.312389</v>
       </c>
       <c r="AP165" t="n">
-        <v>3285.98</v>
+        <v>3241.636006</v>
       </c>
       <c r="AQ165" t="n">
-        <v>7010.39</v>
+        <v>6960.015765</v>
       </c>
       <c r="AR165" t="n">
-        <v>9455.83</v>
+        <v>9444.694493000001</v>
       </c>
       <c r="AS165" t="n">
-        <v>3206.14</v>
+        <v>3206.135223</v>
       </c>
       <c r="AT165" t="n">
-        <v>7010.39</v>
+        <v>6960.015765</v>
       </c>
       <c r="AU165" t="n">
-        <v>9455.83</v>
+        <v>9444.694493000001</v>
       </c>
       <c r="AV165" t="n">
-        <v>3206.14</v>
+        <v>3206.135223</v>
       </c>
       <c r="AW165" t="n">
-        <v>7010.39</v>
+        <v>6960.015765</v>
       </c>
       <c r="AX165" t="n">
-        <v>15292.07</v>
+        <v>15135.02865</v>
       </c>
       <c r="AY165" t="n">
-        <v>3632.71</v>
+        <v>3583.691122</v>
       </c>
       <c r="AZ165" t="n">
-        <v>7711.3</v>
+        <v>7711.299004</v>
       </c>
       <c r="BA165" t="n">
-        <v>17378.02</v>
+        <v>17320.05896</v>
       </c>
       <c r="BB165" t="n">
-        <v>4047.66</v>
+        <v>3824.368213</v>
       </c>
       <c r="BC165" t="n">
-        <v>44796.58</v>
+        <v>44419.391339</v>
       </c>
       <c r="BD165" t="n">
         <v>6850.16</v>
@@ -20439,7 +20439,7 @@
         <v>1430.45</v>
       </c>
       <c r="T166" t="n">
-        <v>675.3200000000001</v>
+        <v>147.47</v>
       </c>
       <c r="U166" t="n">
         <v>1834.22</v>
@@ -20502,49 +20502,49 @@
         <v>11141.55</v>
       </c>
       <c r="AO166" t="n">
-        <v>1383.03</v>
+        <v/>
       </c>
       <c r="AP166" t="n">
-        <v>328.6</v>
+        <v/>
       </c>
       <c r="AQ166" t="n">
-        <v>701.04</v>
+        <v/>
       </c>
       <c r="AR166" t="n">
-        <v>945.58</v>
+        <v/>
       </c>
       <c r="AS166" t="n">
-        <v>320.61</v>
+        <v/>
       </c>
       <c r="AT166" t="n">
-        <v>701.04</v>
+        <v/>
       </c>
       <c r="AU166" t="n">
-        <v>945.58</v>
+        <v/>
       </c>
       <c r="AV166" t="n">
-        <v>320.61</v>
+        <v/>
       </c>
       <c r="AW166" t="n">
-        <v>701.04</v>
+        <v/>
       </c>
       <c r="AX166" t="n">
-        <v>1529.21</v>
+        <v/>
       </c>
       <c r="AY166" t="n">
-        <v>363.27</v>
+        <v/>
       </c>
       <c r="AZ166" t="n">
-        <v>771.13</v>
+        <v/>
       </c>
       <c r="BA166" t="n">
-        <v>1737.8</v>
+        <v/>
       </c>
       <c r="BB166" t="n">
-        <v>404.77</v>
+        <v/>
       </c>
       <c r="BC166" t="n">
-        <v>4479.66</v>
+        <v/>
       </c>
       <c r="BD166" t="n">
         <v>685.02</v>
@@ -20719,49 +20719,49 @@
         <v>0</v>
       </c>
       <c r="AO167" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AP167" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ167" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR167" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS167" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT167" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU167" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV167" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW167" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX167" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AY167" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ167" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA167" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB167" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC167" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD167" t="n">
         <v>0</v>
@@ -20918,7 +20918,7 @@
         <v>0</v>
       </c>
       <c r="BC169" t="n">
-        <v>693.97</v>
+        <v>0</v>
       </c>
       <c r="BD169" t="n">
         <v>0</v>
@@ -21048,22 +21048,22 @@
         <v>0.1</v>
       </c>
       <c r="AX170" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="AY170" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="AZ170" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="BA170" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="BB170" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="BC170" t="n">
-        <v>0.07000000000000001</v>
+        <v/>
       </c>
       <c r="BD170" t="n">
         <v>0</v>
@@ -21193,22 +21193,22 @@
         <v>0</v>
       </c>
       <c r="AX171" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AY171" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ171" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA171" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB171" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC171" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD171" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
         <v>109419.02</v>
       </c>
       <c r="T173" t="n">
-        <v>50139.08</v>
+        <v>84067.37</v>
       </c>
       <c r="U173" t="n">
         <v>649094.83</v>
@@ -21392,49 +21392,49 @@
         <v>5346126.36</v>
       </c>
       <c r="AO173" t="n">
-        <v>161950.89</v>
+        <v>162464.903939</v>
       </c>
       <c r="AP173" t="n">
-        <v>178893.96</v>
+        <v>179587.988473</v>
       </c>
       <c r="AQ173" t="n">
-        <v>79843.62</v>
+        <v>79937.441143</v>
       </c>
       <c r="AR173" t="n">
-        <v>6507.82</v>
+        <v>6533.787448</v>
       </c>
       <c r="AS173" t="n">
-        <v>173995.22</v>
+        <v>173995.216253</v>
       </c>
       <c r="AT173" t="n">
-        <v>79843.62</v>
+        <v>79937.441143</v>
       </c>
       <c r="AU173" t="n">
-        <v>6507.82</v>
+        <v>6533.787448</v>
       </c>
       <c r="AV173" t="n">
-        <v>173995.22</v>
+        <v>173995.216253</v>
       </c>
       <c r="AW173" t="n">
-        <v>79843.62</v>
+        <v>79937.441143</v>
       </c>
       <c r="AX173" t="n">
-        <v>179100.46</v>
+        <v>179668.892843</v>
       </c>
       <c r="AY173" t="n">
-        <v>197924.84</v>
+        <v>198692.129806</v>
       </c>
       <c r="AZ173" t="n">
-        <v>86955.36</v>
+        <v>86955.358781</v>
       </c>
       <c r="BA173" t="n">
-        <v>254684.47</v>
+        <v>255191.358166</v>
       </c>
       <c r="BB173" t="n">
-        <v>419464.36</v>
+        <v>420452.886826</v>
       </c>
       <c r="BC173" t="n">
-        <v>1476672.81</v>
+        <v>1483683.986264</v>
       </c>
       <c r="BD173" t="n">
         <v>79886.32000000001</v>
@@ -21546,7 +21546,7 @@
         <v>164128.53</v>
       </c>
       <c r="T174" t="n">
-        <v>75208.62</v>
+        <v>126101.06</v>
       </c>
       <c r="U174" t="n">
         <v>973642.24</v>
@@ -21609,49 +21609,49 @@
         <v>8019189.54</v>
       </c>
       <c r="AO174" t="n">
-        <v>242926.33</v>
+        <v>243697.355909</v>
       </c>
       <c r="AP174" t="n">
-        <v>268340.94</v>
+        <v>269381.98271</v>
       </c>
       <c r="AQ174" t="n">
-        <v>119765.44</v>
+        <v>119906.161715</v>
       </c>
       <c r="AR174" t="n">
-        <v>9761.719999999999</v>
+        <v>9800.681172000001</v>
       </c>
       <c r="AS174" t="n">
-        <v>260992.82</v>
+        <v>260992.824379</v>
       </c>
       <c r="AT174" t="n">
-        <v>119765.44</v>
+        <v>119906.161715</v>
       </c>
       <c r="AU174" t="n">
-        <v>9761.719999999999</v>
+        <v>9800.681172000001</v>
       </c>
       <c r="AV174" t="n">
-        <v>260992.82</v>
+        <v>260992.824379</v>
       </c>
       <c r="AW174" t="n">
-        <v>119765.44</v>
+        <v>119906.161715</v>
       </c>
       <c r="AX174" t="n">
-        <v>268650.69</v>
+        <v>269503.339265</v>
       </c>
       <c r="AY174" t="n">
-        <v>296887.26</v>
+        <v>298038.19471</v>
       </c>
       <c r="AZ174" t="n">
-        <v>130433.04</v>
+        <v>130433.038172</v>
       </c>
       <c r="BA174" t="n">
-        <v>382026.71</v>
+        <v>382787.037248</v>
       </c>
       <c r="BB174" t="n">
-        <v>629196.54</v>
+        <v>630679.330238</v>
       </c>
       <c r="BC174" t="n">
-        <v>2215009.22</v>
+        <v>2225525.979397</v>
       </c>
       <c r="BD174" t="n">
         <v>119829.48</v>
@@ -22565,7 +22565,7 @@
         <v>62315469.78</v>
       </c>
       <c r="T191" t="n">
-        <v>44347460.15</v>
+        <v>68638653.17</v>
       </c>
       <c r="U191" t="n">
         <v>64051985.13</v>
@@ -22628,49 +22628,49 @@
         <v>465711556.94</v>
       </c>
       <c r="AO191" t="n">
-        <v>94903343.65000001</v>
+        <v>94847519.26627401</v>
       </c>
       <c r="AP191" t="n">
-        <v>47255121.13</v>
+        <v>47272672.493614</v>
       </c>
       <c r="AQ191" t="n">
-        <v>56994963.51</v>
+        <v>56990078.418173</v>
       </c>
       <c r="AR191" t="n">
-        <v>55532856.23</v>
+        <v>55534514.508192</v>
       </c>
       <c r="AS191" t="n">
-        <v>46512977.11</v>
+        <v>46512977.109192</v>
       </c>
       <c r="AT191" t="n">
-        <v>56994963.51</v>
+        <v>56990078.418173</v>
       </c>
       <c r="AU191" t="n">
-        <v>51700955.46</v>
+        <v>51702613.733769</v>
       </c>
       <c r="AV191" t="n">
-        <v>42681076.33</v>
+        <v>42681076.334769</v>
       </c>
       <c r="AW191" t="n">
-        <v>53163062.73</v>
+        <v>53158177.643749</v>
       </c>
       <c r="AX191" t="n">
-        <v>112906653.99</v>
+        <v>112844935.539866</v>
       </c>
       <c r="AY191" t="n">
-        <v>60231208.3</v>
+        <v>60250611.544079</v>
       </c>
       <c r="AZ191" t="n">
-        <v>70633747.33</v>
+        <v>70633747.32584099</v>
       </c>
       <c r="BA191" t="n">
-        <v>136653207.18</v>
+        <v>136659493.86394</v>
       </c>
       <c r="BB191" t="n">
-        <v>75790442.28</v>
+        <v>75813170.175677</v>
       </c>
       <c r="BC191" t="n">
-        <v>144582529.91</v>
+        <v>144744835.825208</v>
       </c>
       <c r="BD191" t="n">
         <v>49227021.21</v>
@@ -22782,7 +22782,7 @@
         <v>32156101.79</v>
       </c>
       <c r="T192" t="n">
-        <v>22365825.31</v>
+        <v>20027611.3</v>
       </c>
       <c r="U192" t="n">
         <v>32304524.05</v>
@@ -22845,49 +22845,49 @@
         <v>241746504.72</v>
       </c>
       <c r="AO192" t="n">
-        <v>49774379.24</v>
+        <v>49743576.748541</v>
       </c>
       <c r="AP192" t="n">
-        <v>24462045.17</v>
+        <v>24470628.838929</v>
       </c>
       <c r="AQ192" t="n">
-        <v>29476425.28</v>
+        <v>29473610.448741</v>
       </c>
       <c r="AR192" t="n">
-        <v>28826139.63</v>
+        <v>28827191.474518</v>
       </c>
       <c r="AS192" t="n">
-        <v>24050073.99</v>
+        <v>24050073.991875</v>
       </c>
       <c r="AT192" t="n">
-        <v>29476425.28</v>
+        <v>29473610.448741</v>
       </c>
       <c r="AU192" t="n">
-        <v>26628559.63</v>
+        <v>26629611.474518</v>
       </c>
       <c r="AV192" t="n">
-        <v>21852493.99</v>
+        <v>21852493.991875</v>
       </c>
       <c r="AW192" t="n">
-        <v>27278845.28</v>
+        <v>27276030.448741</v>
       </c>
       <c r="AX192" t="n">
-        <v>60076990.66</v>
+        <v>60042935.909909</v>
       </c>
       <c r="AY192" t="n">
-        <v>32095376.2</v>
+        <v>32104865.564009</v>
       </c>
       <c r="AZ192" t="n">
-        <v>37444318.27</v>
+        <v>37444318.26616</v>
       </c>
       <c r="BA192" t="n">
-        <v>73621098.93000001</v>
+        <v>73623882.890044</v>
       </c>
       <c r="BB192" t="n">
-        <v>40553773.13</v>
+        <v>40564848.656339</v>
       </c>
       <c r="BC192" t="n">
-        <v>75466699.52</v>
+        <v>75546382.19537</v>
       </c>
       <c r="BD192" t="n">
         <v>25322628.32</v>
@@ -23011,7 +23011,7 @@
         <v>812931.37</v>
       </c>
       <c r="T194" t="n">
-        <v>706845.8199999999</v>
+        <v>622386.35</v>
       </c>
       <c r="U194" t="n">
         <v>1049245.94</v>
@@ -23101,22 +23101,22 @@
         <v/>
       </c>
       <c r="AX194" t="n">
-        <v>2190138.56</v>
+        <v>2193089.671315</v>
       </c>
       <c r="AY194" t="n">
-        <v>1515211.03</v>
+        <v>1515359.808916</v>
       </c>
       <c r="AZ194" t="n">
-        <v>1880614.32</v>
+        <v>1880614.32068</v>
       </c>
       <c r="BA194" t="n">
-        <v>1830152.18</v>
+        <v>1830322.039061</v>
       </c>
       <c r="BB194" t="n">
-        <v>1426364.04</v>
+        <v>1426638.934273</v>
       </c>
       <c r="BC194" t="n">
-        <v>2490216.4</v>
+        <v>2492605.625692</v>
       </c>
       <c r="BD194" t="n">
         <v>915349.04</v>
@@ -23246,49 +23246,49 @@
         <v>21741971.19</v>
       </c>
       <c r="AO195" t="n">
-        <v>4094917.24</v>
+        <v>4093012.665493</v>
       </c>
       <c r="AP195" t="n">
-        <v>2139598.27</v>
+        <v>2140501.162393</v>
       </c>
       <c r="AQ195" t="n">
-        <v>2550791.15</v>
+        <v>2550756.120882</v>
       </c>
       <c r="AR195" t="n">
-        <v>2401455.53</v>
+        <v>2401555.113504</v>
       </c>
       <c r="AS195" t="n">
-        <v>2104960.03</v>
+        <v>2104960.028744</v>
       </c>
       <c r="AT195" t="n">
-        <v>2550791.15</v>
+        <v>2550756.120882</v>
       </c>
       <c r="AU195" t="n">
-        <v>2209860.49</v>
+        <v>2209960.074783</v>
       </c>
       <c r="AV195" t="n">
-        <v>1913364.99</v>
+        <v>1913364.990023</v>
       </c>
       <c r="AW195" t="n">
-        <v>2359196.12</v>
+        <v>2359161.082161</v>
       </c>
       <c r="AX195" t="n">
-        <v>5065486.61</v>
+        <v>5063381.016248</v>
       </c>
       <c r="AY195" t="n">
-        <v>2903782.97</v>
+        <v>2904781.131849</v>
       </c>
       <c r="AZ195" t="n">
-        <v>3342126.17</v>
+        <v>3342126.165036</v>
       </c>
       <c r="BA195" t="n">
-        <v>6137668.5</v>
+        <v>6138257.898939</v>
       </c>
       <c r="BB195" t="n">
-        <v>3667832.7</v>
+        <v>3669038.102041</v>
       </c>
       <c r="BC195" t="n">
-        <v>6560859.03</v>
+        <v>6568976.647345</v>
       </c>
       <c r="BD195" t="n">
         <v>2090423.84</v>
@@ -23400,7 +23400,7 @@
         <v>2164211.73</v>
       </c>
       <c r="T196" t="n">
-        <v>2075291.82</v>
+        <v>2126184.26</v>
       </c>
       <c r="U196" t="n">
         <v>2973725.44</v>
@@ -23463,49 +23463,49 @@
         <v>14055690.64</v>
       </c>
       <c r="AO196" t="n">
-        <v>4493103.13</v>
+        <v>4493874.155909</v>
       </c>
       <c r="AP196" t="n">
-        <v>4518517.74</v>
+        <v>4519558.78271</v>
       </c>
       <c r="AQ196" t="n">
-        <v>4369942.24</v>
+        <v>4370082.961715</v>
       </c>
       <c r="AR196" t="n">
-        <v>4259938.52</v>
+        <v>4259977.481172</v>
       </c>
       <c r="AS196" t="n">
-        <v>4511169.62</v>
+        <v>4511169.624379</v>
       </c>
       <c r="AT196" t="n">
-        <v>4369942.24</v>
+        <v>4370082.961715</v>
       </c>
       <c r="AU196" t="n">
-        <v>4259938.52</v>
+        <v>4259977.481172</v>
       </c>
       <c r="AV196" t="n">
-        <v>4511169.62</v>
+        <v>4511169.624379</v>
       </c>
       <c r="AW196" t="n">
-        <v>4369942.24</v>
+        <v>4370082.961715</v>
       </c>
       <c r="AX196" t="n">
-        <v>4518827.49</v>
+        <v>4519680.139265</v>
       </c>
       <c r="AY196" t="n">
-        <v>4547064.06</v>
+        <v>4548214.99471</v>
       </c>
       <c r="AZ196" t="n">
-        <v>4380609.84</v>
+        <v>4380609.838172</v>
       </c>
       <c r="BA196" t="n">
-        <v>4632203.51</v>
+        <v>4632963.837248</v>
       </c>
       <c r="BB196" t="n">
-        <v>4879373.34</v>
+        <v>4880856.130238</v>
       </c>
       <c r="BC196" t="n">
-        <v>6465186.02</v>
+        <v>6475702.779397</v>
       </c>
       <c r="BD196" t="n">
         <v>1619891.88</v>
@@ -23617,7 +23617,7 @@
         <v>3494287.99</v>
       </c>
       <c r="T197" t="n">
-        <v>2780640.45</v>
+        <v>3630761.85</v>
       </c>
       <c r="U197" t="n">
         <v>3862823.73</v>
@@ -23680,49 +23680,49 @@
         <v>28773678.39</v>
       </c>
       <c r="AO197" t="n">
-        <v>5859421.27</v>
+        <v>5860185.073173</v>
       </c>
       <c r="AP197" t="n">
-        <v>3293006.84</v>
+        <v>3294044.236799</v>
       </c>
       <c r="AQ197" t="n">
-        <v>4021973.82</v>
+        <v>4022114.503997</v>
       </c>
       <c r="AR197" t="n">
-        <v>5028453.59</v>
+        <v>5028492.306707</v>
       </c>
       <c r="AS197" t="n">
-        <v>3243845.62</v>
+        <v>3243845.619199</v>
       </c>
       <c r="AT197" t="n">
-        <v>4021973.82</v>
+        <v>4022114.503997</v>
       </c>
       <c r="AU197" t="n">
-        <v>4836858.55</v>
+        <v>4836897.267986</v>
       </c>
       <c r="AV197" t="n">
-        <v>3052250.58</v>
+        <v>3052250.580478</v>
       </c>
       <c r="AW197" t="n">
-        <v>3830378.78</v>
+        <v>3830519.465276</v>
       </c>
       <c r="AX197" t="n">
-        <v>7255625.17</v>
+        <v>7256470.687563</v>
       </c>
       <c r="AY197" t="n">
-        <v>4418994</v>
+        <v>4420140.940764</v>
       </c>
       <c r="AZ197" t="n">
-        <v>5222740.49</v>
+        <v>5222740.485715</v>
       </c>
       <c r="BA197" t="n">
-        <v>7967820.69</v>
+        <v>7968579.937999</v>
       </c>
       <c r="BB197" t="n">
-        <v>5094196.73</v>
+        <v>5095677.036313</v>
       </c>
       <c r="BC197" t="n">
-        <v>9051075.43</v>
+        <v>9061582.273035999</v>
       </c>
       <c r="BD197" t="n">
         <v>3005772.88</v>
@@ -23834,7 +23834,7 @@
         <v>-1330076.26</v>
       </c>
       <c r="T198" t="n">
-        <v>-705348.63</v>
+        <v>-1504577.59</v>
       </c>
       <c r="U198" t="n">
         <v>-889098.3</v>
@@ -23897,49 +23897,49 @@
         <v>-14717987.74</v>
       </c>
       <c r="AO198" t="n">
-        <v>-1366318.14</v>
+        <v>-1366310.917264</v>
       </c>
       <c r="AP198" t="n">
-        <v>1225510.89</v>
+        <v>1225514.545911</v>
       </c>
       <c r="AQ198" t="n">
-        <v>347968.41</v>
+        <v>347968.457718</v>
       </c>
       <c r="AR198" t="n">
-        <v>-768515.0699999999</v>
+        <v>-768514.825535</v>
       </c>
       <c r="AS198" t="n">
-        <v>1267324.01</v>
+        <v>1267324.00518</v>
       </c>
       <c r="AT198" t="n">
-        <v>347968.41</v>
+        <v>347968.457718</v>
       </c>
       <c r="AU198" t="n">
-        <v>-576920.03</v>
+        <v>-576919.786814</v>
       </c>
       <c r="AV198" t="n">
-        <v>1458919.04</v>
+        <v>1458919.043901</v>
       </c>
       <c r="AW198" t="n">
-        <v>539563.45</v>
+        <v>539563.496439</v>
       </c>
       <c r="AX198" t="n">
-        <v>-2736797.68</v>
+        <v>-2736790.548298</v>
       </c>
       <c r="AY198" t="n">
-        <v>128070.06</v>
+        <v>128074.053946</v>
       </c>
       <c r="AZ198" t="n">
-        <v>-842130.65</v>
+        <v>-842130.6475430001</v>
       </c>
       <c r="BA198" t="n">
-        <v>-3335617.18</v>
+        <v>-3335616.100751</v>
       </c>
       <c r="BB198" t="n">
-        <v>-214823.39</v>
+        <v>-214820.906075</v>
       </c>
       <c r="BC198" t="n">
-        <v>-2585889.41</v>
+        <v>-2585879.49364</v>
       </c>
       <c r="BD198" t="n">
         <v>-1385881</v>
@@ -24051,7 +24051,7 @@
         <v>3494287.99</v>
       </c>
       <c r="T199" t="n">
-        <v>2780640.45</v>
+        <v>3630761.85</v>
       </c>
       <c r="U199" t="n">
         <v>3862823.73</v>
@@ -24114,49 +24114,49 @@
         <v>28773678.39</v>
       </c>
       <c r="AO199" t="n">
-        <v>5859421.27</v>
+        <v>5860185.073173</v>
       </c>
       <c r="AP199" t="n">
-        <v>3293006.84</v>
+        <v>3294044.236799</v>
       </c>
       <c r="AQ199" t="n">
-        <v>4021973.82</v>
+        <v>4022114.503997</v>
       </c>
       <c r="AR199" t="n">
-        <v>5028453.59</v>
+        <v>5028492.306707</v>
       </c>
       <c r="AS199" t="n">
-        <v>3243845.62</v>
+        <v>3243845.619199</v>
       </c>
       <c r="AT199" t="n">
-        <v>4021973.82</v>
+        <v>4022114.503997</v>
       </c>
       <c r="AU199" t="n">
-        <v>4836858.55</v>
+        <v>4836897.267986</v>
       </c>
       <c r="AV199" t="n">
-        <v>3052250.58</v>
+        <v>3052250.580478</v>
       </c>
       <c r="AW199" t="n">
-        <v>3830378.78</v>
+        <v>3830519.465276</v>
       </c>
       <c r="AX199" t="n">
-        <v>7255625.17</v>
+        <v>7256470.687563</v>
       </c>
       <c r="AY199" t="n">
-        <v>4418994</v>
+        <v>4420140.940764</v>
       </c>
       <c r="AZ199" t="n">
-        <v>5222740.49</v>
+        <v>5222740.485715</v>
       </c>
       <c r="BA199" t="n">
-        <v>7967820.69</v>
+        <v>7968579.937999</v>
       </c>
       <c r="BB199" t="n">
-        <v>5094196.73</v>
+        <v>5095677.036313</v>
       </c>
       <c r="BC199" t="n">
-        <v>9051075.43</v>
+        <v>9061582.273035999</v>
       </c>
       <c r="BD199" t="n">
         <v>3005772.88</v>
@@ -24277,7 +24277,7 @@
         <v>3.83</v>
       </c>
       <c r="T201" t="n">
-        <v>1.96</v>
+        <v>5.49</v>
       </c>
       <c r="U201" t="n">
         <v>2.54</v>
@@ -24340,49 +24340,49 @@
         <v>2.54</v>
       </c>
       <c r="AO201" t="n">
-        <v>3.77</v>
+        <v>3.773345</v>
       </c>
       <c r="AP201" t="n">
-        <v>1.96</v>
+        <v>1.962004</v>
       </c>
       <c r="AQ201" t="n">
-        <v>2.54</v>
+        <v>2.543039</v>
       </c>
       <c r="AR201" t="n">
-        <v>3.77</v>
+        <v>3.773345</v>
       </c>
       <c r="AS201" t="n">
-        <v>1.96</v>
+        <v>1.962004</v>
       </c>
       <c r="AT201" t="n">
-        <v>2.54</v>
+        <v>2.543039</v>
       </c>
       <c r="AU201" t="n">
-        <v>3.77</v>
+        <v>3.773345</v>
       </c>
       <c r="AV201" t="n">
-        <v>1.96</v>
+        <v>1.962004</v>
       </c>
       <c r="AW201" t="n">
-        <v>2.54</v>
+        <v>2.543039</v>
       </c>
       <c r="AX201" t="n">
-        <v>3.77</v>
+        <v>3.773345</v>
       </c>
       <c r="AY201" t="n">
-        <v>1.96</v>
+        <v>1.962004</v>
       </c>
       <c r="AZ201" t="n">
-        <v>2.54</v>
+        <v>2.543039</v>
       </c>
       <c r="BA201" t="n">
-        <v>3.77</v>
+        <v>3.773345</v>
       </c>
       <c r="BB201" t="n">
-        <v>1.96</v>
+        <v>1.962004</v>
       </c>
       <c r="BC201" t="n">
-        <v>2.54</v>
+        <v>2.543039</v>
       </c>
       <c r="BD201" t="n">
         <v>3.77</v>
@@ -24557,7 +24557,7 @@
         <v>5.6</v>
       </c>
       <c r="AO202" t="n">
-        <v>7.62</v>
+        <v>7.621828</v>
       </c>
       <c r="AP202" t="n">
         <v>0</v>
@@ -24566,7 +24566,7 @@
         <v>0</v>
       </c>
       <c r="AR202" t="n">
-        <v>7.62</v>
+        <v>7.621828</v>
       </c>
       <c r="AS202" t="n">
         <v>0</v>
@@ -24575,7 +24575,7 @@
         <v>0</v>
       </c>
       <c r="AU202" t="n">
-        <v>7.62</v>
+        <v>7.621828</v>
       </c>
       <c r="AV202" t="n">
         <v>0</v>
@@ -24584,7 +24584,7 @@
         <v>0</v>
       </c>
       <c r="AX202" t="n">
-        <v>7.62</v>
+        <v>7.621828</v>
       </c>
       <c r="AY202" t="n">
         <v>0</v>
@@ -24593,10 +24593,10 @@
         <v>0</v>
       </c>
       <c r="BA202" t="n">
-        <v>7.62</v>
+        <v>7.621828</v>
       </c>
       <c r="BB202" t="n">
-        <v>8.98</v>
+        <v>8.975327</v>
       </c>
       <c r="BC202" t="n">
         <v>0</v>
@@ -24711,7 +24711,7 @@
         <v>13.58</v>
       </c>
       <c r="T203" t="n">
-        <v>28.89</v>
+        <v>26.3</v>
       </c>
       <c r="U203" t="n">
         <v>11.64</v>
@@ -24810,13 +24810,13 @@
         <v>0</v>
       </c>
       <c r="BA203" t="n">
-        <v>9.630000000000001</v>
+        <v>7.543172</v>
       </c>
       <c r="BB203" t="n">
-        <v>16.99</v>
+        <v>8.071799</v>
       </c>
       <c r="BC203" t="n">
-        <v>10.51</v>
+        <v>8.615892000000001</v>
       </c>
       <c r="BD203" t="n">
         <v>0</v>
@@ -24928,7 +24928,7 @@
         <v>4.49</v>
       </c>
       <c r="T204" t="n">
-        <v>2.87</v>
+        <v>6.41</v>
       </c>
       <c r="U204" t="n">
         <v>2.77</v>
@@ -24991,49 +24991,49 @@
         <v>3.42</v>
       </c>
       <c r="AO204" t="n">
-        <v>4.23</v>
+        <v>5.627349</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.96</v>
+        <v>2.36757</v>
       </c>
       <c r="AQ204" t="n">
-        <v>2.54</v>
+        <v>3.379164</v>
       </c>
       <c r="AR204" t="n">
-        <v>3.95</v>
+        <v>4.871504</v>
       </c>
       <c r="AS204" t="n">
-        <v>1.96</v>
+        <v>2.057219</v>
       </c>
       <c r="AT204" t="n">
-        <v>2.54</v>
+        <v>3.379164</v>
       </c>
       <c r="AU204" t="n">
-        <v>3.95</v>
+        <v>4.871504</v>
       </c>
       <c r="AV204" t="n">
-        <v>1.96</v>
+        <v>2.057219</v>
       </c>
       <c r="AW204" t="n">
-        <v>2.54</v>
+        <v>3.379164</v>
       </c>
       <c r="AX204" t="n">
-        <v>4.23</v>
+        <v>5.627283</v>
       </c>
       <c r="AY204" t="n">
-        <v>1.96</v>
+        <v>2.368207</v>
       </c>
       <c r="AZ204" t="n">
-        <v>2.54</v>
+        <v>3.400892</v>
       </c>
       <c r="BA204" t="n">
-        <v>4.46</v>
+        <v>5.410904</v>
       </c>
       <c r="BB204" t="n">
-        <v>2.15</v>
+        <v>2.251206</v>
       </c>
       <c r="BC204" t="n">
-        <v>2.59</v>
+        <v>3.404274</v>
       </c>
       <c r="BD204" t="n">
         <v>4.23</v>
@@ -25163,22 +25163,22 @@
         <v>1.75</v>
       </c>
       <c r="AX205" t="n">
-        <v>2.08</v>
+        <v>2.328259</v>
       </c>
       <c r="AY205" t="n">
-        <v>1.43</v>
+        <v>1.456749</v>
       </c>
       <c r="AZ205" t="n">
-        <v>1.63</v>
+        <v>1.719266</v>
       </c>
       <c r="BA205" t="n">
-        <v>2.06</v>
+        <v>2.317149</v>
       </c>
       <c r="BB205" t="n">
-        <v>1.41</v>
+        <v>1.433727</v>
       </c>
       <c r="BC205" t="n">
-        <v>1.53</v>
+        <v>1.753914</v>
       </c>
       <c r="BD205" t="n">
         <v>2.09</v>
@@ -25308,22 +25308,22 @@
         <v>3.61</v>
       </c>
       <c r="AX206" t="n">
-        <v>0.71</v>
+        <v>0.706934</v>
       </c>
       <c r="AY206" t="n">
-        <v>0.61</v>
+        <v>0.609259</v>
       </c>
       <c r="AZ206" t="n">
         <v>0</v>
       </c>
       <c r="BA206" t="n">
-        <v>1.13</v>
+        <v>1.137525</v>
       </c>
       <c r="BB206" t="n">
-        <v>2.93</v>
+        <v>2.925288</v>
       </c>
       <c r="BC206" t="n">
-        <v>1.46</v>
+        <v>1.45837</v>
       </c>
       <c r="BD206" t="n">
         <v>0.75</v>
@@ -25453,22 +25453,22 @@
         <v>1.84</v>
       </c>
       <c r="AX207" t="n">
-        <v>2.08</v>
+        <v>2.345615</v>
       </c>
       <c r="AY207" t="n">
-        <v>1.44</v>
+        <v>1.471928</v>
       </c>
       <c r="AZ207" t="n">
-        <v>1.63</v>
+        <v>1.731562</v>
       </c>
       <c r="BA207" t="n">
-        <v>2.11</v>
+        <v>2.38632</v>
       </c>
       <c r="BB207" t="n">
-        <v>1.48</v>
+        <v>1.518307</v>
       </c>
       <c r="BC207" t="n">
-        <v>1.59</v>
+        <v>1.815016</v>
       </c>
       <c r="BD207" t="n">
         <v>2.11</v>
@@ -25580,7 +25580,7 @@
         <v>4.03</v>
       </c>
       <c r="T208" t="n">
-        <v>6.05</v>
+        <v>6.01</v>
       </c>
       <c r="U208" t="n">
         <v>1.89</v>
@@ -25643,49 +25643,49 @@
         <v>4.93</v>
       </c>
       <c r="AO208" t="n">
-        <v>1.69</v>
+        <v>1.689472</v>
       </c>
       <c r="AP208" t="n">
-        <v>1.28</v>
+        <v>1.28091</v>
       </c>
       <c r="AQ208" t="n">
-        <v>0.71</v>
+        <v>0.712261</v>
       </c>
       <c r="AR208" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.805746</v>
       </c>
       <c r="AS208" t="n">
-        <v>1.16</v>
+        <v>1.15722</v>
       </c>
       <c r="AT208" t="n">
-        <v>0.71</v>
+        <v>0.712261</v>
       </c>
       <c r="AU208" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.805746</v>
       </c>
       <c r="AV208" t="n">
-        <v>1.16</v>
+        <v>1.15722</v>
       </c>
       <c r="AW208" t="n">
-        <v>0.71</v>
+        <v>0.712261</v>
       </c>
       <c r="AX208" t="n">
-        <v>1.69</v>
+        <v>1.690095</v>
       </c>
       <c r="AY208" t="n">
-        <v>1.29</v>
+        <v>1.285898</v>
       </c>
       <c r="AZ208" t="n">
-        <v>0.71</v>
+        <v>0.706643</v>
       </c>
       <c r="BA208" t="n">
-        <v>4.66</v>
+        <v>4.660688</v>
       </c>
       <c r="BB208" t="n">
-        <v>3.51</v>
+        <v>3.51362</v>
       </c>
       <c r="BC208" t="n">
-        <v>1.48</v>
+        <v>1.479145</v>
       </c>
       <c r="BD208" t="n">
         <v>1.69</v>
@@ -25797,7 +25797,7 @@
         <v>3.31</v>
       </c>
       <c r="T209" t="n">
-        <v>3.46</v>
+        <v>4.58</v>
       </c>
       <c r="U209" t="n">
         <v>2.42</v>
@@ -25860,49 +25860,49 @@
         <v>2.73</v>
       </c>
       <c r="AO209" t="n">
-        <v>3.4</v>
+        <v>3.863902</v>
       </c>
       <c r="AP209" t="n">
-        <v>2.03</v>
+        <v>2.085177</v>
       </c>
       <c r="AQ209" t="n">
-        <v>2.58</v>
+        <v>2.743047</v>
       </c>
       <c r="AR209" t="n">
-        <v>3.12</v>
+        <v>3.580701</v>
       </c>
       <c r="AS209" t="n">
-        <v>1.91</v>
+        <v>1.960314</v>
       </c>
       <c r="AT209" t="n">
-        <v>2.58</v>
+        <v>2.743047</v>
       </c>
       <c r="AU209" t="n">
-        <v>3.12</v>
+        <v>3.580701</v>
       </c>
       <c r="AV209" t="n">
-        <v>1.91</v>
+        <v>1.960314</v>
       </c>
       <c r="AW209" t="n">
-        <v>2.58</v>
+        <v>2.743047</v>
       </c>
       <c r="AX209" t="n">
-        <v>3.42</v>
+        <v>3.889559</v>
       </c>
       <c r="AY209" t="n">
-        <v>2.04</v>
+        <v>2.097773</v>
       </c>
       <c r="AZ209" t="n">
-        <v>2.61</v>
+        <v>2.777124</v>
       </c>
       <c r="BA209" t="n">
-        <v>3.31</v>
+        <v>3.784086</v>
       </c>
       <c r="BB209" t="n">
-        <v>2</v>
+        <v>2.055793</v>
       </c>
       <c r="BC209" t="n">
-        <v>2.34</v>
+        <v>2.747601</v>
       </c>
       <c r="BD209" t="n">
         <v>3.45</v>
@@ -26014,7 +26014,7 @@
         <v>3.75</v>
       </c>
       <c r="T210" t="n">
-        <v>3.91</v>
+        <v>5.05</v>
       </c>
       <c r="U210" t="n">
         <v>2.49</v>
@@ -26077,49 +26077,49 @@
         <v>2.77</v>
       </c>
       <c r="AO210" t="n">
-        <v>3.56</v>
+        <v>4.577519</v>
       </c>
       <c r="AP210" t="n">
-        <v>2.12</v>
+        <v>2.349362</v>
       </c>
       <c r="AQ210" t="n">
-        <v>2.67</v>
+        <v>3.104497</v>
       </c>
       <c r="AR210" t="n">
-        <v>3.13</v>
+        <v>4.063633</v>
       </c>
       <c r="AS210" t="n">
-        <v>1.99</v>
+        <v>2.315437</v>
       </c>
       <c r="AT210" t="n">
-        <v>2.67</v>
+        <v>3.104497</v>
       </c>
       <c r="AU210" t="n">
-        <v>3.13</v>
+        <v>4.063633</v>
       </c>
       <c r="AV210" t="n">
-        <v>1.99</v>
+        <v>2.315437</v>
       </c>
       <c r="AW210" t="n">
-        <v>2.67</v>
+        <v>3.104497</v>
       </c>
       <c r="AX210" t="n">
-        <v>3.59</v>
+        <v>4.683284</v>
       </c>
       <c r="AY210" t="n">
-        <v>2.14</v>
+        <v>2.391293</v>
       </c>
       <c r="AZ210" t="n">
-        <v>2.71</v>
+        <v>3.174056</v>
       </c>
       <c r="BA210" t="n">
-        <v>3.83</v>
+        <v>5.207111</v>
       </c>
       <c r="BB210" t="n">
-        <v>2.25</v>
+        <v>2.688497</v>
       </c>
       <c r="BC210" t="n">
-        <v>2.42</v>
+        <v>4.681313</v>
       </c>
       <c r="BD210" t="n">
         <v>3.63</v>
@@ -26231,22 +26231,22 @@
         <v>0.18</v>
       </c>
       <c r="AX211" t="n">
-        <v>0.19</v>
+        <v>0.196874</v>
       </c>
       <c r="AY211" t="n">
-        <v>0.16</v>
+        <v>0.16529</v>
       </c>
       <c r="AZ211" t="n">
-        <v>0.17</v>
+        <v>0.174997</v>
       </c>
       <c r="BA211" t="n">
-        <v>0.19</v>
+        <v>0.196505</v>
       </c>
       <c r="BB211" t="n">
-        <v>0.16</v>
+        <v>0.165516</v>
       </c>
       <c r="BC211" t="n">
-        <v>0.17</v>
+        <v>0.176474</v>
       </c>
       <c r="BJ211" t="n">
         <v>0.19</v>
@@ -26410,7 +26410,7 @@
         <v>0.04</v>
       </c>
       <c r="T213" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="U213" t="n">
         <v>0.04</v>
@@ -26477,7 +26477,7 @@
         <v>932.0599999999999</v>
       </c>
       <c r="T214" t="n">
-        <v>928.42</v>
+        <v>1202.28</v>
       </c>
       <c r="U214" t="n">
         <v>674.15</v>
@@ -26862,42 +26862,6 @@
       <c r="AF219" t="n">
         <v>3.35</v>
       </c>
-      <c r="AO219" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AP219" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AQ219" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="AR219" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS219" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AT219" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="AU219" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV219" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AW219" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="AX219" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="AY219" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ219" t="n">
-        <v>3.08</v>
-      </c>
       <c r="BD219" t="n">
         <v>4.7</v>
       </c>
@@ -26954,49 +26918,49 @@
         </is>
       </c>
       <c r="AO220" t="n">
-        <v>1772.86</v>
+        <v>2246.501632</v>
       </c>
       <c r="AP220" t="n">
-        <v>1102.25</v>
+        <v>1209.814573</v>
       </c>
       <c r="AQ220" t="n">
-        <v>1360.19</v>
+        <v>1560.818407</v>
       </c>
       <c r="AR220" t="n">
-        <v>1846.09</v>
+        <v>2007.393143</v>
       </c>
       <c r="AS220" t="n">
-        <v>1094.44</v>
+        <v>1193.091485</v>
       </c>
       <c r="AT220" t="n">
-        <v>1360.19</v>
+        <v>1560.818407</v>
       </c>
       <c r="AU220" t="n">
-        <v>1769.45</v>
+        <v>1930.758315</v>
       </c>
       <c r="AV220" t="n">
-        <v>1017.81</v>
+        <v>1116.456658</v>
       </c>
       <c r="AW220" t="n">
-        <v>1283.55</v>
+        <v>1484.183579</v>
       </c>
       <c r="AX220" t="n">
-        <v>2267.3</v>
+        <v>2795.214597</v>
       </c>
       <c r="AY220" t="n">
-        <v>1528.17</v>
+        <v>1648.940303</v>
       </c>
       <c r="AZ220" t="n">
-        <v>1814.33</v>
+        <v>2037.384807</v>
       </c>
       <c r="BA220" t="n">
-        <v>2373.02</v>
+        <v>3034.457487</v>
       </c>
       <c r="BB220" t="n">
-        <v>1579.74</v>
+        <v>1785.808564</v>
       </c>
       <c r="BC220" t="n">
-        <v>1668.81</v>
+        <v>2734.487704</v>
       </c>
     </row>
     <row r="221" customFormat="1" s="14">
@@ -27043,24 +27007,6 @@
       </c>
       <c r="AA221" t="n">
         <v>3.95</v>
-      </c>
-      <c r="AR221" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AS221" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT221" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AU221" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AV221" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW221" t="n">
-        <v>2.67</v>
       </c>
       <c r="BG221" t="n">
         <v>3.9</v>
@@ -27142,7 +27088,7 @@
         <v>4.49</v>
       </c>
       <c r="T223" t="n">
-        <v>2.87</v>
+        <v>6.41</v>
       </c>
       <c r="U223" t="n">
         <v>2.77</v>
@@ -27205,49 +27151,49 @@
         <v>3.42</v>
       </c>
       <c r="AO223" t="n">
-        <v>4.23</v>
+        <v>5.627349</v>
       </c>
       <c r="AP223" t="n">
-        <v>1.96</v>
+        <v>2.36757</v>
       </c>
       <c r="AQ223" t="n">
-        <v>2.54</v>
+        <v>3.379164</v>
       </c>
       <c r="AR223" t="n">
-        <v>3.95</v>
+        <v>4.871504</v>
       </c>
       <c r="AS223" t="n">
-        <v>1.96</v>
+        <v>2.057219</v>
       </c>
       <c r="AT223" t="n">
-        <v>2.54</v>
+        <v>3.379164</v>
       </c>
       <c r="AU223" t="n">
-        <v>3.95</v>
+        <v>4.871504</v>
       </c>
       <c r="AV223" t="n">
-        <v>1.96</v>
+        <v>2.057219</v>
       </c>
       <c r="AW223" t="n">
-        <v>2.54</v>
+        <v>3.379164</v>
       </c>
       <c r="AX223" t="n">
-        <v>4.23</v>
+        <v>5.627283</v>
       </c>
       <c r="AY223" t="n">
-        <v>1.96</v>
+        <v>2.368207</v>
       </c>
       <c r="AZ223" t="n">
-        <v>2.54</v>
+        <v>3.400892</v>
       </c>
       <c r="BA223" t="n">
-        <v>4.46</v>
+        <v>5.410904</v>
       </c>
       <c r="BB223" t="n">
-        <v>2.15</v>
+        <v>2.251206</v>
       </c>
       <c r="BC223" t="n">
-        <v>2.59</v>
+        <v>3.404274</v>
       </c>
       <c r="BD223" t="n">
         <v>4.23</v>
@@ -27377,22 +27323,22 @@
         <v>0.02</v>
       </c>
       <c r="AX224" t="n">
-        <v>0.02</v>
+        <v>2.333378</v>
       </c>
       <c r="AY224" t="n">
-        <v>0.01</v>
+        <v>1.468153</v>
       </c>
       <c r="AZ224" t="n">
-        <v>0.01</v>
+        <v>1.719266</v>
       </c>
       <c r="BA224" t="n">
-        <v>0.02</v>
+        <v>2.380324</v>
       </c>
       <c r="BB224" t="n">
-        <v>0.01</v>
+        <v>1.520921</v>
       </c>
       <c r="BC224" t="n">
-        <v>0.02</v>
+        <v>1.81099</v>
       </c>
       <c r="BD224" t="n">
         <v>0.02</v>
@@ -27504,7 +27450,7 @@
         <v>3.75</v>
       </c>
       <c r="T225" t="n">
-        <v>3.91</v>
+        <v>5.05</v>
       </c>
       <c r="U225" t="n">
         <v>2.49</v>
@@ -27567,49 +27513,49 @@
         <v>2.77</v>
       </c>
       <c r="AO225" t="n">
-        <v>3.32</v>
+        <v>4.577519</v>
       </c>
       <c r="AP225" t="n">
-        <v>1.97</v>
+        <v>2.349362</v>
       </c>
       <c r="AQ225" t="n">
-        <v>2.41</v>
+        <v>3.104497</v>
       </c>
       <c r="AR225" t="n">
-        <v>3.13</v>
+        <v>4.063633</v>
       </c>
       <c r="AS225" t="n">
-        <v>1.99</v>
+        <v>2.315437</v>
       </c>
       <c r="AT225" t="n">
-        <v>2.41</v>
+        <v>3.104497</v>
       </c>
       <c r="AU225" t="n">
-        <v>3.13</v>
+        <v>4.063633</v>
       </c>
       <c r="AV225" t="n">
-        <v>1.99</v>
+        <v>2.315437</v>
       </c>
       <c r="AW225" t="n">
-        <v>2.41</v>
+        <v>3.104497</v>
       </c>
       <c r="AX225" t="n">
-        <v>3.36</v>
+        <v>4.683284</v>
       </c>
       <c r="AY225" t="n">
-        <v>1.99</v>
+        <v>2.391293</v>
       </c>
       <c r="AZ225" t="n">
-        <v>2.44</v>
+        <v>3.174056</v>
       </c>
       <c r="BA225" t="n">
-        <v>3.83</v>
+        <v>5.207111</v>
       </c>
       <c r="BB225" t="n">
-        <v>2.25</v>
+        <v>2.688497</v>
       </c>
       <c r="BC225" t="n">
-        <v>2.42</v>
+        <v>4.681313</v>
       </c>
       <c r="BD225" t="n">
         <v>3.4</v>
@@ -27766,22 +27712,22 @@
         <v/>
       </c>
       <c r="AX226" t="n">
-        <v>0.18</v>
+        <v>0.19666</v>
       </c>
       <c r="AY226" t="n">
-        <v>0.16</v>
+        <v>0.165223</v>
       </c>
       <c r="AZ226" t="n">
-        <v>0.17</v>
+        <v>0.174781</v>
       </c>
       <c r="BA226" t="n">
-        <v>0.19</v>
+        <v>0.1964</v>
       </c>
       <c r="BB226" t="n">
-        <v>0.16</v>
+        <v>0.165562</v>
       </c>
       <c r="BC226" t="n">
-        <v>0.17</v>
+        <v>0.176403</v>
       </c>
       <c r="BD226" t="n">
         <v>0.05</v>
@@ -27963,7 +27909,7 @@
         <v>0.04</v>
       </c>
       <c r="T228" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="U228" t="n">
         <v>0.04</v>
@@ -28030,7 +27976,7 @@
         <v>932.0599999999999</v>
       </c>
       <c r="T229" t="n">
-        <v>928.42</v>
+        <v>1202.28</v>
       </c>
       <c r="U229" t="n">
         <v>674.15</v>
@@ -28058,49 +28004,49 @@
         </is>
       </c>
       <c r="AO230" t="n">
-        <v>1664.89</v>
+        <v>2246.501632</v>
       </c>
       <c r="AP230" t="n">
-        <v>1032.18</v>
+        <v>1209.814573</v>
       </c>
       <c r="AQ230" t="n">
-        <v>1240.29</v>
+        <v>1560.818407</v>
       </c>
       <c r="AR230" t="n">
-        <v>1574.7</v>
+        <v>2007.393143</v>
       </c>
       <c r="AS230" t="n">
-        <v>1042.07</v>
+        <v>1193.091485</v>
       </c>
       <c r="AT230" t="n">
-        <v>1240.29</v>
+        <v>1560.818407</v>
       </c>
       <c r="AU230" t="n">
-        <v>1498.06</v>
+        <v>1930.758315</v>
       </c>
       <c r="AV230" t="n">
-        <v>965.4400000000001</v>
+        <v>1116.456658</v>
       </c>
       <c r="AW230" t="n">
-        <v>1163.65</v>
+        <v>1484.183579</v>
       </c>
       <c r="AX230" t="n">
-        <v>2147.93</v>
+        <v>2794.670681</v>
       </c>
       <c r="AY230" t="n">
-        <v>1450.53</v>
+        <v>1648.772509</v>
       </c>
       <c r="AZ230" t="n">
-        <v>1676.81</v>
+        <v>2036.838247</v>
       </c>
       <c r="BA230" t="n">
-        <v>2373.02</v>
+        <v>3034.190938</v>
       </c>
       <c r="BB230" t="n">
-        <v>1579.74</v>
+        <v>1785.924788</v>
       </c>
       <c r="BC230" t="n">
-        <v>1668.81</v>
+        <v>2734.30877</v>
       </c>
     </row>
     <row r="231" customFormat="1" s="14">
@@ -28252,7 +28198,7 @@
         <v>1.4</v>
       </c>
       <c r="T233" t="n">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="U233" t="n">
         <v>1.55</v>
@@ -28315,49 +28261,49 @@
         <v>11.51</v>
       </c>
       <c r="AO233" t="n">
-        <v>2.34</v>
+        <v>2.343977</v>
       </c>
       <c r="AP233" t="n">
-        <v>1.32</v>
+        <v>1.317563</v>
       </c>
       <c r="AQ233" t="n">
-        <v>1.61</v>
+        <v>1.608779</v>
       </c>
       <c r="AR233" t="n">
-        <v>2.01</v>
+        <v>2.011313</v>
       </c>
       <c r="AS233" t="n">
-        <v>1.3</v>
+        <v>1.297484</v>
       </c>
       <c r="AT233" t="n">
-        <v>1.61</v>
+        <v>1.608779</v>
       </c>
       <c r="AU233" t="n">
-        <v>1.93</v>
+        <v>1.934678</v>
       </c>
       <c r="AV233" t="n">
-        <v>1.22</v>
+        <v>1.220849</v>
       </c>
       <c r="AW233" t="n">
-        <v>1.53</v>
+        <v>1.532144</v>
       </c>
       <c r="AX233" t="n">
-        <v>2.9</v>
+        <v>2.902468</v>
       </c>
       <c r="AY233" t="n">
-        <v>1.77</v>
+        <v>1.767983</v>
       </c>
       <c r="AZ233" t="n">
-        <v>2.09</v>
+        <v>2.089009</v>
       </c>
       <c r="BA233" t="n">
-        <v>3.19</v>
+        <v>3.187299</v>
       </c>
       <c r="BB233" t="n">
-        <v>2.04</v>
+        <v>2.038186</v>
       </c>
       <c r="BC233" t="n">
-        <v>3.62</v>
+        <v>3.624482</v>
       </c>
       <c r="BD233" t="n">
         <v>1.2</v>
@@ -28469,7 +28415,7 @@
         <v>1.33</v>
       </c>
       <c r="T234" t="n">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="U234" t="n">
         <v>1.16</v>
@@ -28532,49 +28478,49 @@
         <v>8.09</v>
       </c>
       <c r="AO234" t="n">
-        <v>2.25</v>
+        <v>2.246502</v>
       </c>
       <c r="AP234" t="n">
-        <v>1.21</v>
+        <v>1.209815</v>
       </c>
       <c r="AQ234" t="n">
-        <v>1.56</v>
+        <v>1.560818</v>
       </c>
       <c r="AR234" t="n">
-        <v>2.01</v>
+        <v>2.007393</v>
       </c>
       <c r="AS234" t="n">
-        <v>1.19</v>
+        <v>1.193091</v>
       </c>
       <c r="AT234" t="n">
-        <v>1.56</v>
+        <v>1.560818</v>
       </c>
       <c r="AU234" t="n">
-        <v>1.93</v>
+        <v>1.930758</v>
       </c>
       <c r="AV234" t="n">
-        <v>1.12</v>
+        <v>1.116457</v>
       </c>
       <c r="AW234" t="n">
-        <v>1.48</v>
+        <v>1.484184</v>
       </c>
       <c r="AX234" t="n">
-        <v>2.79</v>
+        <v>2.794671</v>
       </c>
       <c r="AY234" t="n">
-        <v>1.65</v>
+        <v>1.648773</v>
       </c>
       <c r="AZ234" t="n">
-        <v>2.04</v>
+        <v>2.036838</v>
       </c>
       <c r="BA234" t="n">
-        <v>3.03</v>
+        <v>3.034191</v>
       </c>
       <c r="BB234" t="n">
-        <v>1.79</v>
+        <v>1.785925</v>
       </c>
       <c r="BC234" t="n">
-        <v>2.73</v>
+        <v>2.734309</v>
       </c>
       <c r="BD234" t="n">
         <v>1.15</v>

--- a/Vergleich_Ergebnisse_MitWerten.xlsx
+++ b/Vergleich_Ergebnisse_MitWerten.xlsx
@@ -1396,16 +1396,16 @@
         <v>4201.343394</v>
       </c>
       <c r="M3" t="n">
-        <v>15339.150776</v>
+        <v>14109.595844</v>
       </c>
       <c r="N3" t="n">
         <v>14760.38</v>
       </c>
       <c r="O3" t="n">
-        <v>15678.088942</v>
+        <v>13582.282007</v>
       </c>
       <c r="P3" t="n">
-        <v>15608.466228</v>
+        <v>13490.115748</v>
       </c>
       <c r="Q3" t="n">
         <v>8990.1</v>
@@ -1414,7 +1414,7 @@
         <v>8990.1</v>
       </c>
       <c r="S3" t="n">
-        <v>15175.781077</v>
+        <v>14265.015766</v>
       </c>
       <c r="T3" t="n">
         <v>10920.316216</v>
@@ -1462,19 +1462,19 @@
         <v>2540.06</v>
       </c>
       <c r="AI3" t="n">
-        <v>17307.54016</v>
+        <v>14652.907635</v>
       </c>
       <c r="AJ3" t="n">
-        <v>16594.758799</v>
+        <v>14231.505279</v>
       </c>
       <c r="AK3" t="n">
-        <v>16457.410371</v>
+        <v>14048.664404</v>
       </c>
       <c r="AL3" t="n">
-        <v>8992.267328</v>
+        <v>8990.1</v>
       </c>
       <c r="AM3" t="n">
-        <v>8992.267328</v>
+        <v>8990.1</v>
       </c>
       <c r="AN3" t="n">
         <v>4549.62682</v>
@@ -1498,13 +1498,13 @@
         <v>3781.578966</v>
       </c>
       <c r="AU3" t="n">
-        <v>13082.707498</v>
+        <v>14676.897612</v>
       </c>
       <c r="AV3" t="n">
-        <v>16482.35778</v>
+        <v>13868.617132</v>
       </c>
       <c r="AW3" t="n">
-        <v>16426.180116</v>
+        <v>13783.370816</v>
       </c>
       <c r="AX3" t="n">
         <v>4558.579497</v>
@@ -1528,16 +1528,16 @@
         <v>4025.522899</v>
       </c>
       <c r="BE3" t="n">
-        <v>21042.991304</v>
+        <v>14576.565927</v>
       </c>
       <c r="BF3" t="n">
         <v>15884.82</v>
       </c>
       <c r="BG3" t="n">
-        <v>12812.349176</v>
+        <v>11366.289181</v>
       </c>
       <c r="BH3" t="n">
-        <v>20608.447375</v>
+        <v>14351.443539</v>
       </c>
       <c r="BI3" t="n">
         <v>10429.45815</v>
@@ -1576,7 +1576,7 @@
         <v>3853.299945</v>
       </c>
       <c r="BU3" t="n">
-        <v>13386.889926</v>
+        <v>13640.765766</v>
       </c>
       <c r="BV3" t="n">
         <v>53630.86</v>
@@ -1585,7 +1585,7 @@
         <v>8990.1</v>
       </c>
       <c r="BX3" t="n">
-        <v>13256.906358</v>
+        <v>13407.483916</v>
       </c>
       <c r="BY3" t="n">
         <v>10470.376375</v>
@@ -1655,25 +1655,25 @@
         <v>27440.703173</v>
       </c>
       <c r="M4" t="n">
-        <v>112611.301058</v>
+        <v>95006.716986</v>
       </c>
       <c r="N4" t="n">
         <v>96402.46000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>94242.746153</v>
+        <v>89512.92002600001</v>
       </c>
       <c r="P4" t="n">
-        <v>93970.73978600001</v>
+        <v>89203.736768</v>
       </c>
       <c r="Q4" t="n">
-        <v>42611.422098</v>
+        <v>46449.412871</v>
       </c>
       <c r="R4" t="n">
-        <v>42611.4221</v>
+        <v>46449.4129</v>
       </c>
       <c r="S4" t="n">
-        <v>111553.140158</v>
+        <v>95411.107753</v>
       </c>
       <c r="T4" t="n">
         <v>71361.166358</v>
@@ -1721,19 +1721,19 @@
         <v>14231.790267</v>
       </c>
       <c r="AI4" t="n">
-        <v>129624.46813</v>
+        <v>100722.508614</v>
       </c>
       <c r="AJ4" t="n">
-        <v>98770.491805</v>
+        <v>92572.45805</v>
       </c>
       <c r="AK4" t="n">
-        <v>98344.415779</v>
+        <v>92035.07767300001</v>
       </c>
       <c r="AL4" t="n">
-        <v>45172.275137</v>
+        <v>48951.031427</v>
       </c>
       <c r="AM4" t="n">
-        <v>45172.275137</v>
+        <v>48951.031427</v>
       </c>
       <c r="AN4" t="n">
         <v>30554.388402</v>
@@ -1757,13 +1757,13 @@
         <v>24733.060085</v>
       </c>
       <c r="AU4" t="n">
-        <v>98415.584271</v>
+        <v>98929.733773</v>
       </c>
       <c r="AV4" t="n">
-        <v>95206.301895</v>
+        <v>88874.65803000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>94975.089373</v>
+        <v>88584.43462299999</v>
       </c>
       <c r="AX4" t="n">
         <v>30106.571205</v>
@@ -1787,16 +1787,16 @@
         <v>30209.887404</v>
       </c>
       <c r="BE4" t="n">
-        <v>167219.755976</v>
+        <v>110515.337822</v>
       </c>
       <c r="BF4" t="n">
         <v>113625.78</v>
       </c>
       <c r="BG4" t="n">
-        <v>91746.043257</v>
+        <v>86045.04023300001</v>
       </c>
       <c r="BH4" t="n">
-        <v>163874.659263</v>
+        <v>108835.885549</v>
       </c>
       <c r="BI4" t="n">
         <v>76874.331326</v>
@@ -1835,7 +1835,7 @@
         <v>29142.505134</v>
       </c>
       <c r="BU4" t="n">
-        <v>110032.908169</v>
+        <v>105494.809351</v>
       </c>
       <c r="BV4" t="n">
         <v>347487.64</v>
@@ -1844,7 +1844,7 @@
         <v>78753.276</v>
       </c>
       <c r="BX4" t="n">
-        <v>109016.673263</v>
+        <v>103489.373733</v>
       </c>
       <c r="BY4" t="n">
         <v>76779.92701</v>
@@ -1914,25 +1914,25 @@
         <v>548814.063463</v>
       </c>
       <c r="M5" t="n">
-        <v>2252226.021157</v>
+        <v>1900134.339724</v>
       </c>
       <c r="N5" t="n">
         <v>1928049.17</v>
       </c>
       <c r="O5" t="n">
-        <v>1884854.923052</v>
+        <v>1790258.400517</v>
       </c>
       <c r="P5" t="n">
-        <v>1879414.795721</v>
+        <v>1784074.73536</v>
       </c>
       <c r="Q5" t="n">
-        <v>852228.441965</v>
+        <v>928988.2574229999</v>
       </c>
       <c r="R5" t="n">
-        <v>852228.442</v>
+        <v>928988.2574</v>
       </c>
       <c r="S5" t="n">
-        <v>2231062.803155</v>
+        <v>1908222.155063</v>
       </c>
       <c r="T5" t="n">
         <v>1427223.327159</v>
@@ -1980,19 +1980,19 @@
         <v>284635.805346</v>
       </c>
       <c r="AI5" t="n">
-        <v>2592489.362592</v>
+        <v>2014450.172282</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1975409.836097</v>
+        <v>1851449.161005</v>
       </c>
       <c r="AK5" t="n">
-        <v>1966888.315579</v>
+        <v>1840701.553465</v>
       </c>
       <c r="AL5" t="n">
-        <v>903445.50274</v>
+        <v>979020.62853</v>
       </c>
       <c r="AM5" t="n">
-        <v>903445.50274</v>
+        <v>979020.62853</v>
       </c>
       <c r="AN5" t="n">
         <v>611087.768041</v>
@@ -2016,13 +2016,13 @@
         <v>494661.201703</v>
       </c>
       <c r="AU5" t="n">
-        <v>1968311.685423</v>
+        <v>1978594.675463</v>
       </c>
       <c r="AV5" t="n">
-        <v>1904126.037899</v>
+        <v>1777493.160599</v>
       </c>
       <c r="AW5" t="n">
-        <v>1899501.787458</v>
+        <v>1771688.692465</v>
       </c>
       <c r="AX5" t="n">
         <v>602131.424096</v>
@@ -2046,16 +2046,16 @@
         <v>604197.748089</v>
       </c>
       <c r="BE5" t="n">
-        <v>3344395.119522</v>
+        <v>2210306.75644</v>
       </c>
       <c r="BF5" t="n">
         <v>2272515.54</v>
       </c>
       <c r="BG5" t="n">
-        <v>1834920.865141</v>
+        <v>1720900.804664</v>
       </c>
       <c r="BH5" t="n">
-        <v>3277493.18525</v>
+        <v>2176717.710973</v>
       </c>
       <c r="BI5" t="n">
         <v>1537486.626519</v>
@@ -2094,7 +2094,7 @@
         <v>582850.102677</v>
       </c>
       <c r="BU5" t="n">
-        <v>2200658.163377</v>
+        <v>2109896.187018</v>
       </c>
       <c r="BV5" t="n">
         <v>6949752.7</v>
@@ -2103,7 +2103,7 @@
         <v>1575065.52</v>
       </c>
       <c r="BX5" t="n">
-        <v>2180333.465269</v>
+        <v>2069787.474667</v>
       </c>
       <c r="BY5" t="n">
         <v>1535598.540197</v>
@@ -2173,16 +2173,16 @@
         <v>6302015.09171</v>
       </c>
       <c r="M6" t="n">
-        <v>23008726.163577</v>
+        <v>21164393.765494</v>
       </c>
       <c r="N6" t="n">
         <v>22140564.49</v>
       </c>
       <c r="O6" t="n">
-        <v>23517133.413447</v>
+        <v>20373423.010813</v>
       </c>
       <c r="P6" t="n">
-        <v>23412699.341936</v>
+        <v>20235173.621463</v>
       </c>
       <c r="Q6" t="n">
         <v>13485150</v>
@@ -2191,7 +2191,7 @@
         <v>13485150</v>
       </c>
       <c r="S6" t="n">
-        <v>22763671.616006</v>
+        <v>21397523.649581</v>
       </c>
       <c r="T6" t="n">
         <v>16380474.323794</v>
@@ -2239,19 +2239,19 @@
         <v>3810090</v>
       </c>
       <c r="AI6" t="n">
-        <v>25961310.23931</v>
+        <v>21979361.452986</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24892138.198777</v>
+        <v>21347257.917781</v>
       </c>
       <c r="AK6" t="n">
-        <v>24686115.556711</v>
+        <v>21072996.605832</v>
       </c>
       <c r="AL6" t="n">
-        <v>13488400.991811</v>
+        <v>13485150</v>
       </c>
       <c r="AM6" t="n">
-        <v>13488400.991811</v>
+        <v>13485150</v>
       </c>
       <c r="AN6" t="n">
         <v>6824440.230221</v>
@@ -2275,13 +2275,13 @@
         <v>5672368.448949</v>
       </c>
       <c r="AU6" t="n">
-        <v>19624061.246359</v>
+        <v>22015346.417611</v>
       </c>
       <c r="AV6" t="n">
-        <v>24723536.669485</v>
+        <v>20802925.697514</v>
       </c>
       <c r="AW6" t="n">
-        <v>24639270.174533</v>
+        <v>20675056.224469</v>
       </c>
       <c r="AX6" t="n">
         <v>6837869.245585</v>
@@ -2305,16 +2305,16 @@
         <v>6038284.348862</v>
       </c>
       <c r="BE6" t="n">
-        <v>31564486.9561</v>
+        <v>21864848.890564</v>
       </c>
       <c r="BF6" t="n">
         <v>15884823.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>19218523.764666</v>
+        <v>17049433.772182</v>
       </c>
       <c r="BH6" t="n">
-        <v>30912671.063107</v>
+        <v>21527165.308358</v>
       </c>
       <c r="BI6" t="n">
         <v>15644187.224575</v>
@@ -2353,7 +2353,7 @@
         <v>5779949.917689</v>
       </c>
       <c r="BU6" t="n">
-        <v>20080334.889443</v>
+        <v>20461148.648433</v>
       </c>
       <c r="BV6" t="n">
         <v>53630856.95</v>
@@ -2362,7 +2362,7 @@
         <v>13485150</v>
       </c>
       <c r="BX6" t="n">
-        <v>19885359.537219</v>
+        <v>20111225.874038</v>
       </c>
       <c r="BY6" t="n">
         <v>15705564.562754</v>
@@ -2432,16 +2432,16 @@
         <v>189060.452751</v>
       </c>
       <c r="M7" t="n">
-        <v>690261.784907</v>
+        <v>634931.812965</v>
       </c>
       <c r="N7" t="n">
         <v>664216.9300000001</v>
       </c>
       <c r="O7" t="n">
-        <v>705514.002403</v>
+        <v>611202.690324</v>
       </c>
       <c r="P7" t="n">
-        <v>702380.980258</v>
+        <v>607055.208644</v>
       </c>
       <c r="Q7" t="n">
         <v>404554.5</v>
@@ -2450,7 +2450,7 @@
         <v>404554.5</v>
       </c>
       <c r="S7" t="n">
-        <v>682910.14848</v>
+        <v>641925.709487</v>
       </c>
       <c r="T7" t="n">
         <v>491414.229714</v>
@@ -2498,19 +2498,19 @@
         <v>114302.7</v>
       </c>
       <c r="AI7" t="n">
-        <v>778839.307179</v>
+        <v>659380.8435899999</v>
       </c>
       <c r="AJ7" t="n">
-        <v>746764.145963</v>
+        <v>640417.7375329999</v>
       </c>
       <c r="AK7" t="n">
-        <v>740583.466701</v>
+        <v>632189.898175</v>
       </c>
       <c r="AL7" t="n">
-        <v>404652.029754</v>
+        <v>404554.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>404652.029754</v>
+        <v>404554.5</v>
       </c>
       <c r="AN7" t="n">
         <v>204733.206907</v>
@@ -2534,13 +2534,13 @@
         <v>170171.053468</v>
       </c>
       <c r="AU7" t="n">
-        <v>588721.837391</v>
+        <v>660460.3925280001</v>
       </c>
       <c r="AV7" t="n">
-        <v>741706.100085</v>
+        <v>624087.770925</v>
       </c>
       <c r="AW7" t="n">
-        <v>739178.105236</v>
+        <v>620251.686734</v>
       </c>
       <c r="AX7" t="n">
         <v>205136.077368</v>
@@ -2564,16 +2564,16 @@
         <v>181148.530466</v>
       </c>
       <c r="BE7" t="n">
-        <v>946934.608683</v>
+        <v>655945.466717</v>
       </c>
       <c r="BF7" t="n">
         <v>476544.69</v>
       </c>
       <c r="BG7" t="n">
-        <v>576555.71294</v>
+        <v>511483.013165</v>
       </c>
       <c r="BH7" t="n">
-        <v>927380.131893</v>
+        <v>645814.959251</v>
       </c>
       <c r="BI7" t="n">
         <v>469325.616737</v>
@@ -2612,7 +2612,7 @@
         <v>173398.497531</v>
       </c>
       <c r="BU7" t="n">
-        <v>602410.0466830001</v>
+        <v>613834.459453</v>
       </c>
       <c r="BV7" t="n">
         <v>1608925.71</v>
@@ -2621,7 +2621,7 @@
         <v>404554.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>596560.786117</v>
+        <v>603336.776221</v>
       </c>
       <c r="BY7" t="n">
         <v>471166.936883</v>
@@ -2691,16 +2691,16 @@
         <v>641874.157127</v>
       </c>
       <c r="M8" t="n">
-        <v>2343489.581967</v>
+        <v>2155640.253419</v>
       </c>
       <c r="N8" t="n">
         <v>2255065.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2395271.983348</v>
+        <v>2075078.13494</v>
       </c>
       <c r="P8" t="n">
-        <v>2384635.142489</v>
+        <v>2060997.129266</v>
       </c>
       <c r="Q8" t="n">
         <v>1373492.313812</v>
@@ -2709,7 +2709,7 @@
         <v>1373492.3138</v>
       </c>
       <c r="S8" t="n">
-        <v>2318530.235015</v>
+        <v>2179385.047055</v>
       </c>
       <c r="T8" t="n">
         <v>1668387.491449</v>
@@ -2757,19 +2757,19 @@
         <v>388066.082315</v>
       </c>
       <c r="AI8" t="n">
-        <v>2644216.791817</v>
+        <v>2238646.512509</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2535319.257877</v>
+        <v>2174265.371243</v>
       </c>
       <c r="AK8" t="n">
-        <v>2514335.396715</v>
+        <v>2146331.250827</v>
       </c>
       <c r="AL8" t="n">
-        <v>1373823.434508</v>
+        <v>1373492.313812</v>
       </c>
       <c r="AM8" t="n">
-        <v>1373823.434508</v>
+        <v>1373492.313812</v>
       </c>
       <c r="AN8" t="n">
         <v>695084.31143</v>
@@ -2793,13 +2793,13 @@
         <v>577743.255784</v>
       </c>
       <c r="AU8" t="n">
-        <v>1998753.984022</v>
+        <v>2242311.66064</v>
       </c>
       <c r="AV8" t="n">
-        <v>2518146.819707</v>
+        <v>2118823.932276</v>
       </c>
       <c r="AW8" t="n">
-        <v>2509564.091067</v>
+        <v>2105800.144005</v>
       </c>
       <c r="AX8" t="n">
         <v>696452.086307</v>
@@ -2823,16 +2823,16 @@
         <v>615012.598434</v>
       </c>
       <c r="BE8" t="n">
-        <v>3408636.18061</v>
+        <v>2361176.188785</v>
       </c>
       <c r="BF8" t="n">
         <v>1617904.31</v>
       </c>
       <c r="BG8" t="n">
-        <v>2075400.608705</v>
+        <v>1841161.457673</v>
       </c>
       <c r="BH8" t="n">
-        <v>3338246.845943</v>
+        <v>2324709.875313</v>
       </c>
       <c r="BI8" t="n">
         <v>1593395.024066</v>
@@ -2871,7 +2871,7 @@
         <v>588700.666004</v>
       </c>
       <c r="BU8" t="n">
-        <v>2488695.787849</v>
+        <v>2535892.689852</v>
       </c>
       <c r="BV8" t="n">
         <v>5462421.24</v>
@@ -2880,7 +2880,7 @@
         <v>1671308.580673</v>
       </c>
       <c r="BX8" t="n">
-        <v>2464531.134197</v>
+        <v>2492524.322765</v>
       </c>
       <c r="BY8" t="n">
         <v>1599646.441531</v>
@@ -2950,16 +2950,16 @@
         <v>12837483.142549</v>
       </c>
       <c r="M9" t="n">
-        <v>46869791.639346</v>
+        <v>43112805.06837</v>
       </c>
       <c r="N9" t="n">
         <v>45101307.96</v>
       </c>
       <c r="O9" t="n">
-        <v>47905439.666965</v>
+        <v>41501562.698793</v>
       </c>
       <c r="P9" t="n">
-        <v>47692702.84977</v>
+        <v>41219942.585319</v>
       </c>
       <c r="Q9" t="n">
         <v>27469846.27623</v>
@@ -2968,7 +2968,7 @@
         <v>27469846.2762</v>
       </c>
       <c r="S9" t="n">
-        <v>46370604.7003</v>
+        <v>43587700.941109</v>
       </c>
       <c r="T9" t="n">
         <v>33367749.828987</v>
@@ -3016,19 +3016,19 @@
         <v>7761321.6463</v>
       </c>
       <c r="AI9" t="n">
-        <v>52884335.836335</v>
+        <v>44772930.250181</v>
       </c>
       <c r="AJ9" t="n">
-        <v>50706385.157532</v>
+        <v>43485307.424869</v>
       </c>
       <c r="AK9" t="n">
-        <v>50286707.934292</v>
+        <v>42926625.016535</v>
       </c>
       <c r="AL9" t="n">
-        <v>27476468.690166</v>
+        <v>27469846.27623</v>
       </c>
       <c r="AM9" t="n">
-        <v>27476468.690166</v>
+        <v>27469846.27623</v>
       </c>
       <c r="AN9" t="n">
         <v>13901686.228593</v>
@@ -3052,13 +3052,13 @@
         <v>11554865.115683</v>
       </c>
       <c r="AU9" t="n">
-        <v>39975079.680448</v>
+        <v>44846233.21281</v>
       </c>
       <c r="AV9" t="n">
-        <v>50362936.394144</v>
+        <v>42376478.645514</v>
       </c>
       <c r="AW9" t="n">
-        <v>50191281.821331</v>
+        <v>42116002.880099</v>
       </c>
       <c r="AX9" t="n">
         <v>13929041.726135</v>
@@ -3082,16 +3082,16 @@
         <v>12300251.968677</v>
       </c>
       <c r="BE9" t="n">
-        <v>68172723.612207</v>
+        <v>47223523.775697</v>
       </c>
       <c r="BF9" t="n">
         <v>32358086.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>41508012.174105</v>
+        <v>36823229.153451</v>
       </c>
       <c r="BH9" t="n">
-        <v>66764936.918861</v>
+        <v>46494197.50627</v>
       </c>
       <c r="BI9" t="n">
         <v>31867900.481317</v>
@@ -3130,7 +3130,7 @@
         <v>11774013.320075</v>
       </c>
       <c r="BU9" t="n">
-        <v>49773915.756984</v>
+        <v>50717853.797034</v>
       </c>
       <c r="BV9" t="n">
         <v>109248424.83</v>
@@ -3139,7 +3139,7 @@
         <v>33426171.613461</v>
       </c>
       <c r="BX9" t="n">
-        <v>49290622.683948</v>
+        <v>49850486.455299</v>
       </c>
       <c r="BY9" t="n">
         <v>31992928.830621</v>
@@ -3209,16 +3209,16 @@
         <v>830934.609879</v>
       </c>
       <c r="M10" t="n">
-        <v>3033751.366875</v>
+        <v>2790572.066383</v>
       </c>
       <c r="N10" t="n">
         <v>2919282.33</v>
       </c>
       <c r="O10" t="n">
-        <v>3100785.985752</v>
+        <v>2686280.825264</v>
       </c>
       <c r="P10" t="n">
-        <v>3087016.122747</v>
+        <v>2668052.33791</v>
       </c>
       <c r="Q10" t="n">
         <v>1778046.813812</v>
@@ -3227,7 +3227,7 @@
         <v>1778046.8138</v>
       </c>
       <c r="S10" t="n">
-        <v>3001440.383495</v>
+        <v>2821310.756543</v>
       </c>
       <c r="T10" t="n">
         <v>2159801.721163</v>
@@ -3275,19 +3275,19 @@
         <v>502368.782315</v>
       </c>
       <c r="AI10" t="n">
-        <v>3423056.098996</v>
+        <v>2898027.356099</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3282083.40384</v>
+        <v>2814683.108777</v>
       </c>
       <c r="AK10" t="n">
-        <v>3254918.863416</v>
+        <v>2778521.149002</v>
       </c>
       <c r="AL10" t="n">
-        <v>1778475.464263</v>
+        <v>1778046.813812</v>
       </c>
       <c r="AM10" t="n">
-        <v>1778475.464263</v>
+        <v>1778046.813812</v>
       </c>
       <c r="AN10" t="n">
         <v>899817.518336</v>
@@ -3311,13 +3311,13 @@
         <v>747914.309253</v>
       </c>
       <c r="AU10" t="n">
-        <v>2587475.821413</v>
+        <v>2902772.053169</v>
       </c>
       <c r="AV10" t="n">
-        <v>3259852.919792</v>
+        <v>2742911.703201</v>
       </c>
       <c r="AW10" t="n">
-        <v>3248742.196303</v>
+        <v>2726051.830739</v>
       </c>
       <c r="AX10" t="n">
         <v>901588.163674</v>
@@ -3341,16 +3341,16 @@
         <v>796161.1289</v>
       </c>
       <c r="BE10" t="n">
-        <v>4355570.789293</v>
+        <v>3017121.655502</v>
       </c>
       <c r="BF10" t="n">
         <v>2094449</v>
       </c>
       <c r="BG10" t="n">
-        <v>2651956.321645</v>
+        <v>2352644.470838</v>
       </c>
       <c r="BH10" t="n">
-        <v>4265626.977836</v>
+        <v>2970524.834564</v>
       </c>
       <c r="BI10" t="n">
         <v>2062720.640803</v>
@@ -3389,7 +3389,7 @@
         <v>762099.1635340001</v>
       </c>
       <c r="BU10" t="n">
-        <v>3091105.834532</v>
+        <v>3149727.149305</v>
       </c>
       <c r="BV10" t="n">
         <v>7071346.95</v>
@@ -3398,7 +3398,7 @@
         <v>2075863.080673</v>
       </c>
       <c r="BX10" t="n">
-        <v>3061091.920314</v>
+        <v>3095861.098986</v>
       </c>
       <c r="BY10" t="n">
         <v>2070813.378414</v>
@@ -6211,73 +6211,73 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>97479.05495999999</v>
+        <v>25001.04</v>
       </c>
       <c r="N49" t="n">
         <v>8450.35</v>
       </c>
       <c r="O49" t="n">
-        <v>97479.05495999999</v>
+        <v>25001.04</v>
       </c>
       <c r="P49" t="n">
-        <v>97479.05495999999</v>
+        <v>25001.04</v>
       </c>
       <c r="Q49" t="n">
-        <v>97479.05495999999</v>
+        <v>25001.04</v>
       </c>
       <c r="R49" t="n">
-        <v>97479.05499999999</v>
+        <v>25001.04</v>
       </c>
       <c r="S49" t="n">
-        <v>97479.05495999999</v>
+        <v>25001.04</v>
       </c>
       <c r="AI49" t="n">
-        <v>97479.05495999999</v>
+        <v>25001.04</v>
       </c>
       <c r="AJ49" t="n">
-        <v>97479.05495999999</v>
+        <v>25001.04</v>
       </c>
       <c r="AK49" t="n">
-        <v>97479.05495999999</v>
+        <v>25001.04</v>
       </c>
       <c r="AL49" t="n">
-        <v>97479.05495999999</v>
+        <v>25001.04</v>
       </c>
       <c r="AM49" t="n">
-        <v>97479.05495999999</v>
+        <v>25001.04</v>
       </c>
       <c r="AU49" t="n">
-        <v>97479.05495999999</v>
+        <v>25001.04</v>
       </c>
       <c r="AV49" t="n">
-        <v>97479.05495999999</v>
+        <v>25001.04</v>
       </c>
       <c r="AW49" t="n">
-        <v>97479.05495999999</v>
+        <v>25001.04</v>
       </c>
       <c r="BE49" t="n">
-        <v>97479.05495999999</v>
+        <v>25001.04</v>
       </c>
       <c r="BF49" t="n">
         <v>8450.35</v>
       </c>
       <c r="BG49" t="n">
-        <v>97479.05495999999</v>
+        <v>25001.04</v>
       </c>
       <c r="BH49" t="n">
-        <v>97479.05495999999</v>
+        <v>25001.04</v>
       </c>
       <c r="BU49" t="n">
-        <v>97479.05495999999</v>
+        <v>25001.04</v>
       </c>
       <c r="BV49" t="n">
         <v>97479.05</v>
       </c>
       <c r="BW49" t="n">
-        <v>97479.05495999999</v>
+        <v>25001.04</v>
       </c>
       <c r="BX49" t="n">
-        <v>97479.05495999999</v>
+        <v>25001.04</v>
       </c>
     </row>
     <row r="50" customFormat="1" s="14">
@@ -7934,25 +7934,25 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>757.424519</v>
+        <v>876.985744</v>
       </c>
       <c r="N70" t="n">
         <v>908.3</v>
       </c>
       <c r="O70" t="n">
-        <v>962.1273619999999</v>
+        <v>949.063167</v>
       </c>
       <c r="P70" t="n">
-        <v>515.819829</v>
+        <v>513.451825</v>
       </c>
       <c r="Q70" t="n">
-        <v>559.662906</v>
+        <v>456.324474</v>
       </c>
       <c r="R70" t="n">
-        <v>559.6629</v>
+        <v>456.3245</v>
       </c>
       <c r="S70" t="n">
-        <v>403.268767</v>
+        <v>489.52777</v>
       </c>
       <c r="T70" t="n">
         <v>536.003603</v>
@@ -7976,19 +7976,19 @@
         <v>150.250107</v>
       </c>
       <c r="AI70" t="n">
-        <v>751.871909</v>
+        <v>806.917647</v>
       </c>
       <c r="AJ70" t="n">
-        <v>850.041272</v>
+        <v>861.5555450000001</v>
       </c>
       <c r="AK70" t="n">
-        <v>457.838988</v>
+        <v>476.992777</v>
       </c>
       <c r="AL70" t="n">
-        <v>531.98514</v>
+        <v>446.462498</v>
       </c>
       <c r="AM70" t="n">
-        <v>531.98514</v>
+        <v>446.462498</v>
       </c>
       <c r="AN70" t="n">
         <v>247.909696</v>
@@ -8006,13 +8006,13 @@
         <v>119.844675</v>
       </c>
       <c r="AU70" t="n">
-        <v>710.324485</v>
+        <v>814.072567</v>
       </c>
       <c r="AV70" t="n">
-        <v>1037.160664</v>
+        <v>1010.89545</v>
       </c>
       <c r="AW70" t="n">
-        <v>556.802817</v>
+        <v>543.038142</v>
       </c>
       <c r="AX70" t="n">
         <v>251.201672</v>
@@ -8027,16 +8027,16 @@
         <v>119.450338</v>
       </c>
       <c r="BE70" t="n">
-        <v>704.71466</v>
+        <v>710.454219</v>
       </c>
       <c r="BF70" t="n">
         <v>620.22</v>
       </c>
       <c r="BG70" t="n">
-        <v>779.617868</v>
+        <v>765.287408</v>
       </c>
       <c r="BH70" t="n">
-        <v>373.730938</v>
+        <v>378.333251</v>
       </c>
       <c r="BI70" t="n">
         <v>400.996533</v>
@@ -8054,7 +8054,7 @@
         <v>112.466975</v>
       </c>
       <c r="BU70" t="n">
-        <v>681.134421</v>
+        <v>703.326878</v>
       </c>
       <c r="BV70" t="n">
         <v>678.47</v>
@@ -8063,7 +8063,7 @@
         <v>655.37829</v>
       </c>
       <c r="BX70" t="n">
-        <v>361.226944</v>
+        <v>376.720028</v>
       </c>
       <c r="BY70" t="n">
         <v>396.115733</v>
@@ -8103,25 +8103,25 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>5842.587337</v>
+        <v>5882.597643</v>
       </c>
       <c r="N71" t="n">
         <v>5477.87</v>
       </c>
       <c r="O71" t="n">
-        <v>5880.218669</v>
+        <v>5861.47676</v>
       </c>
       <c r="P71" t="n">
-        <v>3113.229852</v>
+        <v>3111.890106</v>
       </c>
       <c r="Q71" t="n">
-        <v>3135.907409</v>
+        <v>3084.347962</v>
       </c>
       <c r="R71" t="n">
-        <v>3133.6334</v>
+        <v>3093.5617</v>
       </c>
       <c r="S71" t="n">
-        <v>3098.233188</v>
+        <v>3126.497076</v>
       </c>
       <c r="T71" t="n">
         <v>3095.38186</v>
@@ -8145,19 +8145,19 @@
         <v>887.6088580000001</v>
       </c>
       <c r="AI71" t="n">
-        <v>5865.575994</v>
+        <v>5855.169314</v>
       </c>
       <c r="AJ71" t="n">
-        <v>5810.061448</v>
+        <v>5813.721666</v>
       </c>
       <c r="AK71" t="n">
-        <v>3082.570355</v>
+        <v>3093.01074</v>
       </c>
       <c r="AL71" t="n">
-        <v>3141.282512</v>
+        <v>3082.975368</v>
       </c>
       <c r="AM71" t="n">
-        <v>3122.911008</v>
+        <v>3082.17255</v>
       </c>
       <c r="AN71" t="n">
         <v>1661.8821</v>
@@ -8175,13 +8175,13 @@
         <v>869.368284</v>
       </c>
       <c r="AU71" t="n">
-        <v>5810.222757</v>
+        <v>5852.092525</v>
       </c>
       <c r="AV71" t="n">
-        <v>5863.343979</v>
+        <v>5852.46428</v>
       </c>
       <c r="AW71" t="n">
-        <v>3114.967748</v>
+        <v>3106.281261</v>
       </c>
       <c r="AX71" t="n">
         <v>1662.86399</v>
@@ -8196,16 +8196,16 @@
         <v>868.1701839999999</v>
       </c>
       <c r="BE71" t="n">
-        <v>5835.456154</v>
+        <v>5795.126416</v>
       </c>
       <c r="BF71" t="n">
         <v>5267.46</v>
       </c>
       <c r="BG71" t="n">
-        <v>5805.737859</v>
+        <v>5798.571509</v>
       </c>
       <c r="BH71" t="n">
-        <v>3094.554407</v>
+        <v>3074.691555</v>
       </c>
       <c r="BI71" t="n">
         <v>3048.87867</v>
@@ -8223,7 +8223,7 @@
         <v>874.4802529999999</v>
       </c>
       <c r="BU71" t="n">
-        <v>5779.325303</v>
+        <v>5775.226415</v>
       </c>
       <c r="BV71" t="n">
         <v>5781.07</v>
@@ -8232,7 +8232,7 @@
         <v>5741.11382</v>
       </c>
       <c r="BX71" t="n">
-        <v>3064.547807</v>
+        <v>3064.510192</v>
       </c>
       <c r="BY71" t="n">
         <v>3032.224283</v>
@@ -8272,25 +8272,25 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>21639212.358903</v>
+        <v>21787398.679013</v>
       </c>
       <c r="N72" t="n">
         <v>20288392.85</v>
       </c>
       <c r="O72" t="n">
-        <v>21778587.662003</v>
+        <v>21709173.186322</v>
       </c>
       <c r="P72" t="n">
-        <v>11530480.932209</v>
+        <v>11525518.9121</v>
       </c>
       <c r="Q72" t="n">
-        <v>11614471.88612</v>
+        <v>11423510.969329</v>
       </c>
       <c r="R72" t="n">
-        <v>11606049.674</v>
+        <v>11457636.0263</v>
       </c>
       <c r="S72" t="n">
-        <v>11474937.734229</v>
+        <v>11579618.799376</v>
       </c>
       <c r="T72" t="n">
         <v>11464377.259219</v>
@@ -8314,19 +8314,19 @@
         <v>3287440.214365</v>
       </c>
       <c r="AI72" t="n">
-        <v>21724355.533963</v>
+        <v>21685812.275362</v>
       </c>
       <c r="AJ72" t="n">
-        <v>21518746.105141</v>
+        <v>21532302.46659</v>
       </c>
       <c r="AK72" t="n">
-        <v>11416927.242364</v>
+        <v>11455595.331755</v>
       </c>
       <c r="AL72" t="n">
-        <v>11634379.672677</v>
+        <v>11418427.288376</v>
       </c>
       <c r="AM72" t="n">
-        <v>11566337.065189</v>
+        <v>11415453.890522</v>
       </c>
       <c r="AN72" t="n">
         <v>6155118.889116</v>
@@ -8344,13 +8344,13 @@
         <v>3219882.53297</v>
       </c>
       <c r="AU72" t="n">
-        <v>21519343.545444</v>
+        <v>21674416.7577</v>
       </c>
       <c r="AV72" t="n">
-        <v>21716088.810854</v>
+        <v>21675793.631151</v>
       </c>
       <c r="AW72" t="n">
-        <v>11536917.583859</v>
+        <v>11504745.41174</v>
       </c>
       <c r="AX72" t="n">
         <v>6158755.516774</v>
@@ -8365,16 +8365,16 @@
         <v>3215445.125995</v>
       </c>
       <c r="BE72" t="n">
-        <v>21612800.57025</v>
+        <v>21463431.171638</v>
       </c>
       <c r="BF72" t="n">
         <v>19509096.02</v>
       </c>
       <c r="BG72" t="n">
-        <v>21502732.809744</v>
+        <v>21476190.775592</v>
       </c>
       <c r="BH72" t="n">
-        <v>11461312.617785</v>
+        <v>11387746.500139</v>
       </c>
       <c r="BI72" t="n">
         <v>11292143.221958</v>
@@ -8392,7 +8392,7 @@
         <v>3238815.751532</v>
       </c>
       <c r="BU72" t="n">
-        <v>21404908.530248</v>
+        <v>21389727.464172</v>
       </c>
       <c r="BV72" t="n">
         <v>21411382.48</v>
@@ -8401,7 +8401,7 @@
         <v>21263384.52</v>
       </c>
       <c r="BX72" t="n">
-        <v>11350177.064023</v>
+        <v>11350037.747358</v>
       </c>
       <c r="BY72" t="n">
         <v>11230460.306534</v>
@@ -8441,25 +8441,25 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>1963693.196958</v>
+        <v>2273666.743505</v>
       </c>
       <c r="N73" t="n">
         <v>2354861.61</v>
       </c>
       <c r="O73" t="n">
-        <v>2494404.271786</v>
+        <v>2460534.135426</v>
       </c>
       <c r="P73" t="n">
-        <v>1337310.667033</v>
+        <v>1331171.39871</v>
       </c>
       <c r="Q73" t="n">
-        <v>1450977.904265</v>
+        <v>1183063.44983</v>
       </c>
       <c r="R73" t="n">
-        <v>1450977.9043</v>
+        <v>1183063.4498</v>
       </c>
       <c r="S73" t="n">
-        <v>1045511.617755</v>
+        <v>1269146.070929</v>
       </c>
       <c r="T73" t="n">
         <v>1389638.970917</v>
@@ -8483,19 +8483,19 @@
         <v>389537.314735</v>
       </c>
       <c r="AI73" t="n">
-        <v>1949297.542516</v>
+        <v>2092008.714108</v>
       </c>
       <c r="AJ73" t="n">
-        <v>2203810.706331</v>
+        <v>2233662.524112</v>
       </c>
       <c r="AK73" t="n">
-        <v>1186989.968874</v>
+        <v>1236647.941586</v>
       </c>
       <c r="AL73" t="n">
-        <v>1379220.732549</v>
+        <v>1157495.364672</v>
       </c>
       <c r="AM73" t="n">
-        <v>1379220.732549</v>
+        <v>1157495.364672</v>
       </c>
       <c r="AN73" t="n">
         <v>642728.842082</v>
@@ -8513,13 +8513,13 @@
         <v>310708.416595</v>
       </c>
       <c r="AU73" t="n">
-        <v>1841581.998102</v>
+        <v>2110558.507635</v>
       </c>
       <c r="AV73" t="n">
-        <v>2688935.05521</v>
+        <v>2620840.055114</v>
       </c>
       <c r="AW73" t="n">
-        <v>1443562.859318</v>
+        <v>1407876.66482</v>
       </c>
       <c r="AX73" t="n">
         <v>651263.5930089999</v>
@@ -8534,16 +8534,16 @@
         <v>309686.06244</v>
       </c>
       <c r="BE73" t="n">
-        <v>1827038.007614</v>
+        <v>1841918.345958</v>
       </c>
       <c r="BF73" t="n">
         <v>1607989.27</v>
       </c>
       <c r="BG73" t="n">
-        <v>2021231.509768</v>
+        <v>1984078.464075</v>
       </c>
       <c r="BH73" t="n">
-        <v>968932.061356</v>
+        <v>980863.984365</v>
       </c>
       <c r="BI73" t="n">
         <v>1039620.641668</v>
@@ -8561,7 +8561,7 @@
         <v>291581.045939</v>
       </c>
       <c r="BU73" t="n">
-        <v>1765904.054896</v>
+        <v>1823440.052843</v>
       </c>
       <c r="BV73" t="n">
         <v>1759006.73</v>
@@ -8570,7 +8570,7 @@
         <v>1699128.9</v>
       </c>
       <c r="BX73" t="n">
-        <v>936514.299526</v>
+        <v>976681.554047</v>
       </c>
       <c r="BY73" t="n">
         <v>1026966.71586</v>
@@ -8610,25 +8610,25 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>39273.863939</v>
+        <v>45473.33487</v>
       </c>
       <c r="N74" t="n">
         <v>47097.23</v>
       </c>
       <c r="O74" t="n">
-        <v>49888.085436</v>
+        <v>49210.682709</v>
       </c>
       <c r="P74" t="n">
-        <v>26746.213341</v>
+        <v>26623.427974</v>
       </c>
       <c r="Q74" t="n">
-        <v>29019.558085</v>
+        <v>23661.268997</v>
       </c>
       <c r="R74" t="n">
-        <v>29019.5581</v>
+        <v>23661.269</v>
       </c>
       <c r="S74" t="n">
-        <v>20910.232355</v>
+        <v>25382.921419</v>
       </c>
       <c r="T74" t="n">
         <v>27792.779418</v>
@@ -8652,19 +8652,19 @@
         <v>7790.746295</v>
       </c>
       <c r="AI74" t="n">
-        <v>38985.95085</v>
+        <v>41840.174282</v>
       </c>
       <c r="AJ74" t="n">
-        <v>44076.214127</v>
+        <v>44673.250482</v>
       </c>
       <c r="AK74" t="n">
-        <v>23739.799377</v>
+        <v>24732.958832</v>
       </c>
       <c r="AL74" t="n">
-        <v>27584.414651</v>
+        <v>23149.907293</v>
       </c>
       <c r="AM74" t="n">
-        <v>27584.414651</v>
+        <v>23149.907293</v>
       </c>
       <c r="AN74" t="n">
         <v>12854.576842</v>
@@ -8682,13 +8682,13 @@
         <v>6214.168332</v>
       </c>
       <c r="AU74" t="n">
-        <v>36831.639962</v>
+        <v>42211.170153</v>
       </c>
       <c r="AV74" t="n">
-        <v>53778.701104</v>
+        <v>52416.801102</v>
       </c>
       <c r="AW74" t="n">
-        <v>28871.257186</v>
+        <v>28157.533296</v>
       </c>
       <c r="AX74" t="n">
         <v>13025.27186</v>
@@ -8703,16 +8703,16 @@
         <v>6193.721249</v>
       </c>
       <c r="BE74" t="n">
-        <v>36540.760152</v>
+        <v>36838.366919</v>
       </c>
       <c r="BF74" t="n">
         <v>32159.79</v>
       </c>
       <c r="BG74" t="n">
-        <v>40424.630195</v>
+        <v>39681.569282</v>
       </c>
       <c r="BH74" t="n">
-        <v>19378.641227</v>
+        <v>19617.279687</v>
       </c>
       <c r="BI74" t="n">
         <v>20792.412833</v>
@@ -8730,7 +8730,7 @@
         <v>5831.620919</v>
       </c>
       <c r="BU74" t="n">
-        <v>35318.081098</v>
+        <v>36468.801057</v>
       </c>
       <c r="BV74" t="n">
         <v>35180.13</v>
@@ -8739,7 +8739,7 @@
         <v>33982.578</v>
       </c>
       <c r="BX74" t="n">
-        <v>18730.285991</v>
+        <v>19533.631081</v>
       </c>
       <c r="BY74" t="n">
         <v>20539.334317</v>
@@ -8779,25 +8779,25 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>157571.822573</v>
+        <v>182444.901908</v>
       </c>
       <c r="N75" t="n">
         <v>188960.19</v>
       </c>
       <c r="O75" t="n">
-        <v>200157.452268</v>
+        <v>197439.624898</v>
       </c>
       <c r="P75" t="n">
-        <v>107309.2678</v>
+        <v>106816.637027</v>
       </c>
       <c r="Q75" t="n">
-        <v>116430.220995</v>
+        <v>94932.072025</v>
       </c>
       <c r="R75" t="n">
-        <v>116430.221</v>
+        <v>94932.072</v>
       </c>
       <c r="S75" t="n">
-        <v>83894.557147</v>
+        <v>101839.564254</v>
       </c>
       <c r="T75" t="n">
         <v>111508.226287</v>
@@ -8821,19 +8821,19 @@
         <v>31257.481942</v>
       </c>
       <c r="AI75" t="n">
-        <v>156416.678016</v>
+        <v>167868.191646</v>
       </c>
       <c r="AJ75" t="n">
-        <v>176839.472755</v>
+        <v>179234.859846</v>
       </c>
       <c r="AK75" t="n">
-        <v>95247.146072</v>
+        <v>99231.830277</v>
       </c>
       <c r="AL75" t="n">
-        <v>110672.239887</v>
+        <v>92880.422723</v>
       </c>
       <c r="AM75" t="n">
-        <v>110672.239887</v>
+        <v>92880.422723</v>
       </c>
       <c r="AN75" t="n">
         <v>51574.225151</v>
@@ -8851,13 +8851,13 @@
         <v>24932.047209</v>
       </c>
       <c r="AU75" t="n">
-        <v>147773.304052</v>
+        <v>169356.67507</v>
       </c>
       <c r="AV75" t="n">
-        <v>215767.105618</v>
+        <v>210302.986635</v>
       </c>
       <c r="AW75" t="n">
-        <v>115835.218604</v>
+        <v>112971.666031</v>
       </c>
       <c r="AX75" t="n">
         <v>52259.075646</v>
@@ -8872,16 +8872,16 @@
         <v>24850.010867</v>
       </c>
       <c r="BE75" t="n">
-        <v>156713.02823</v>
+        <v>157989.37983</v>
       </c>
       <c r="BF75" t="n">
         <v>129029.22</v>
       </c>
       <c r="BG75" t="n">
-        <v>173369.852915</v>
+        <v>170183.073946</v>
       </c>
       <c r="BH75" t="n">
-        <v>83109.53403900001</v>
+        <v>84132.98718</v>
       </c>
       <c r="BI75" t="n">
         <v>83421.849984</v>
@@ -8899,7 +8899,7 @@
         <v>23397.217502</v>
       </c>
       <c r="BU75" t="n">
-        <v>177192.64881</v>
+        <v>182965.870662</v>
       </c>
       <c r="BV75" t="n">
         <v>141147.25</v>
@@ -8908,7 +8908,7 @@
         <v>170492.360344</v>
       </c>
       <c r="BX75" t="n">
-        <v>93970.818472</v>
+        <v>98001.242551</v>
       </c>
       <c r="BY75" t="n">
         <v>82406.466239</v>
@@ -8948,25 +8948,25 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>3151436.451454</v>
+        <v>3648898.038165</v>
       </c>
       <c r="N76" t="n">
         <v>3779203.76</v>
       </c>
       <c r="O76" t="n">
-        <v>4003149.045353</v>
+        <v>3948792.497953</v>
       </c>
       <c r="P76" t="n">
-        <v>2146185.356008</v>
+        <v>2136332.740535</v>
       </c>
       <c r="Q76" t="n">
-        <v>2328604.419895</v>
+        <v>1898641.440502</v>
       </c>
       <c r="R76" t="n">
-        <v>2328604.4199</v>
+        <v>1898641.4405</v>
       </c>
       <c r="S76" t="n">
-        <v>1677891.142932</v>
+        <v>2036791.285085</v>
       </c>
       <c r="T76" t="n">
         <v>2230164.525748</v>
@@ -8990,19 +8990,19 @@
         <v>625149.638833</v>
       </c>
       <c r="AI76" t="n">
-        <v>3128333.560319</v>
+        <v>3357363.83291</v>
       </c>
       <c r="AJ76" t="n">
-        <v>3536789.455091</v>
+        <v>3584697.196912</v>
       </c>
       <c r="AK76" t="n">
-        <v>1904942.921436</v>
+        <v>1984636.605538</v>
       </c>
       <c r="AL76" t="n">
-        <v>2213444.797735</v>
+        <v>1857608.454451</v>
       </c>
       <c r="AM76" t="n">
-        <v>2213444.797735</v>
+        <v>1857608.454451</v>
       </c>
       <c r="AN76" t="n">
         <v>1031484.503015</v>
@@ -9020,13 +9020,13 @@
         <v>498640.94419</v>
       </c>
       <c r="AU76" t="n">
-        <v>2955466.081031</v>
+        <v>3387133.501398</v>
       </c>
       <c r="AV76" t="n">
-        <v>4315342.112356</v>
+        <v>4206059.732707</v>
       </c>
       <c r="AW76" t="n">
-        <v>2316704.372081</v>
+        <v>2259433.320611</v>
       </c>
       <c r="AX76" t="n">
         <v>1045181.512923</v>
@@ -9041,16 +9041,16 @@
         <v>497000.217342</v>
       </c>
       <c r="BE76" t="n">
-        <v>3134260.564609</v>
+        <v>3159787.596595</v>
       </c>
       <c r="BF76" t="n">
         <v>2580584.39</v>
       </c>
       <c r="BG76" t="n">
-        <v>3467397.058306</v>
+        <v>3403661.478922</v>
       </c>
       <c r="BH76" t="n">
-        <v>1662190.680784</v>
+        <v>1682659.743601</v>
       </c>
       <c r="BI76" t="n">
         <v>1668436.999685</v>
@@ -9068,7 +9068,7 @@
         <v>467944.350038</v>
       </c>
       <c r="BU76" t="n">
-        <v>3543852.976193</v>
+        <v>3659317.413232</v>
       </c>
       <c r="BV76" t="n">
         <v>2822945.01</v>
@@ -9077,7 +9077,7 @@
         <v>3409847.206877</v>
       </c>
       <c r="BX76" t="n">
-        <v>1879416.369435</v>
+        <v>1960024.851013</v>
       </c>
       <c r="BY76" t="n">
         <v>1648129.324786</v>
@@ -9117,25 +9117,25 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>196845.686512</v>
+        <v>227918.236778</v>
       </c>
       <c r="N77" t="n">
         <v>236057.42</v>
       </c>
       <c r="O77" t="n">
-        <v>250045.537703</v>
+        <v>246650.307606</v>
       </c>
       <c r="P77" t="n">
-        <v>134055.481141</v>
+        <v>133440.065001</v>
       </c>
       <c r="Q77" t="n">
-        <v>145449.77908</v>
+        <v>118593.341022</v>
       </c>
       <c r="R77" t="n">
-        <v>145449.7791</v>
+        <v>118593.341</v>
       </c>
       <c r="S77" t="n">
-        <v>104804.789502</v>
+        <v>127222.485673</v>
       </c>
       <c r="T77" t="n">
         <v>139301.005706</v>
@@ -9159,19 +9159,19 @@
         <v>39048.228236</v>
       </c>
       <c r="AI77" t="n">
-        <v>195402.628866</v>
+        <v>209708.365928</v>
       </c>
       <c r="AJ77" t="n">
-        <v>220915.686881</v>
+        <v>223908.110328</v>
       </c>
       <c r="AK77" t="n">
-        <v>118986.945449</v>
+        <v>123964.789109</v>
       </c>
       <c r="AL77" t="n">
-        <v>138256.654538</v>
+        <v>116030.330016</v>
       </c>
       <c r="AM77" t="n">
-        <v>138256.654538</v>
+        <v>116030.330016</v>
       </c>
       <c r="AN77" t="n">
         <v>64428.801992</v>
@@ -9189,13 +9189,13 @@
         <v>31146.215541</v>
       </c>
       <c r="AU77" t="n">
-        <v>184604.944014</v>
+        <v>211567.845223</v>
       </c>
       <c r="AV77" t="n">
-        <v>269545.806722</v>
+        <v>262719.787738</v>
       </c>
       <c r="AW77" t="n">
-        <v>144706.47579</v>
+        <v>141129.199327</v>
       </c>
       <c r="AX77" t="n">
         <v>65284.347506</v>
@@ -9210,16 +9210,16 @@
         <v>31043.732116</v>
       </c>
       <c r="BE77" t="n">
-        <v>193253.788383</v>
+        <v>194827.746749</v>
       </c>
       <c r="BF77" t="n">
         <v>161189.01</v>
       </c>
       <c r="BG77" t="n">
-        <v>213794.483111</v>
+        <v>209864.643228</v>
       </c>
       <c r="BH77" t="n">
-        <v>102488.175266</v>
+        <v>103750.266867</v>
       </c>
       <c r="BI77" t="n">
         <v>104214.262818</v>
@@ -9237,7 +9237,7 @@
         <v>29228.838421</v>
       </c>
       <c r="BU77" t="n">
-        <v>212510.729908</v>
+        <v>219434.671718</v>
       </c>
       <c r="BV77" t="n">
         <v>176327.39</v>
@@ -9246,7 +9246,7 @@
         <v>204474.938344</v>
       </c>
       <c r="BX77" t="n">
-        <v>112701.104462</v>
+        <v>117534.873632</v>
       </c>
       <c r="BY77" t="n">
         <v>102945.800557</v>
@@ -11453,16 +11453,16 @@
         <v>7019.463636</v>
       </c>
       <c r="M102" t="n">
-        <v>15255.610997</v>
+        <v>28671.156877</v>
       </c>
       <c r="N102" t="n">
         <v>23948.86</v>
       </c>
       <c r="O102" t="n">
-        <v>8890.623390000001</v>
+        <v>6159.976605</v>
       </c>
       <c r="P102" t="n">
-        <v>9007.267078999999</v>
+        <v>6193.70401</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -11471,7 +11471,7 @@
         <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>15025.600128</v>
+        <v>27681.486852</v>
       </c>
       <c r="T102" t="n">
         <v>16229.904262</v>
@@ -11519,19 +11519,19 @@
         <v>0</v>
       </c>
       <c r="AI102" t="n">
-        <v>15925.068334</v>
+        <v>20205.626378</v>
       </c>
       <c r="AJ102" t="n">
-        <v>9153.519147000001</v>
+        <v>6595.270197</v>
       </c>
       <c r="AK102" t="n">
-        <v>8989.45139</v>
+        <v>6411.084081</v>
       </c>
       <c r="AL102" t="n">
-        <v>1.516212</v>
+        <v>0</v>
       </c>
       <c r="AM102" t="n">
-        <v>1.516212</v>
+        <v>0</v>
       </c>
       <c r="AN102" t="n">
         <v>5458.636219</v>
@@ -11555,13 +11555,13 @@
         <v>1425.796728</v>
       </c>
       <c r="AU102" t="n">
-        <v>23645.38027</v>
+        <v>19326.477094</v>
       </c>
       <c r="AV102" t="n">
-        <v>6776.729822</v>
+        <v>5143.844384</v>
       </c>
       <c r="AW102" t="n">
-        <v>6831.727463</v>
+        <v>5176.467905</v>
       </c>
       <c r="AX102" t="n">
         <v>4987.303057</v>
@@ -11585,16 +11585,16 @@
         <v>3750.854791</v>
       </c>
       <c r="BE102" t="n">
-        <v>14317.142898</v>
+        <v>14763.507238</v>
       </c>
       <c r="BF102" t="n">
         <v>12323.19</v>
       </c>
       <c r="BG102" t="n">
-        <v>4881.099909</v>
+        <v>3826.06104</v>
       </c>
       <c r="BH102" t="n">
-        <v>14275.125415</v>
+        <v>14341.471184</v>
       </c>
       <c r="BI102" t="n">
         <v>8899.167207</v>
@@ -11633,7 +11633,7 @@
         <v>1876.446934</v>
       </c>
       <c r="BU102" t="n">
-        <v>7364.667368</v>
+        <v>7134.241677</v>
       </c>
       <c r="BV102" t="n">
         <v>7217.89</v>
@@ -11642,7 +11642,7 @@
         <v>0</v>
       </c>
       <c r="BX102" t="n">
-        <v>7328.342498</v>
+        <v>7015.171856</v>
       </c>
       <c r="BY102" t="n">
         <v>4591.536466</v>
@@ -11712,25 +11712,25 @@
         <v>88448.41220399999</v>
       </c>
       <c r="M103" t="n">
-        <v>141358.640094</v>
+        <v>293629.149667</v>
       </c>
       <c r="N103" t="n">
         <v>296758.31</v>
       </c>
       <c r="O103" t="n">
-        <v>363209.796364</v>
+        <v>246797.964497</v>
       </c>
       <c r="P103" t="n">
-        <v>364280.168048</v>
+        <v>245822.999609</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R103" t="n">
         <v>-0</v>
       </c>
       <c r="S103" t="n">
-        <v>142211.899824</v>
+        <v>297275.658089</v>
       </c>
       <c r="T103" t="n">
         <v>214235.014896</v>
@@ -11778,19 +11778,19 @@
         <v>0</v>
       </c>
       <c r="AI103" t="n">
-        <v>140040.308176</v>
+        <v>232839.841344</v>
       </c>
       <c r="AJ103" t="n">
-        <v>395781.224605</v>
+        <v>272039.81563</v>
       </c>
       <c r="AK103" t="n">
-        <v>390637.926298</v>
+        <v>265124.361065</v>
       </c>
       <c r="AL103" t="n">
-        <v>122.323985</v>
+        <v>-0</v>
       </c>
       <c r="AM103" t="n">
-        <v>122.323985</v>
+        <v>0</v>
       </c>
       <c r="AN103" t="n">
         <v>73742.167437</v>
@@ -11814,13 +11814,13 @@
         <v>70229.259361</v>
       </c>
       <c r="AU103" t="n">
-        <v>188206.975173</v>
+        <v>276361.021628</v>
       </c>
       <c r="AV103" t="n">
-        <v>379517.577731</v>
+        <v>261771.169124</v>
       </c>
       <c r="AW103" t="n">
-        <v>381033.821735</v>
+        <v>261767.068409</v>
       </c>
       <c r="AX103" t="n">
         <v>86200.597308</v>
@@ -11844,16 +11844,16 @@
         <v>51163.879139</v>
       </c>
       <c r="BE103" t="n">
-        <v>83594.279828</v>
+        <v>169024.967314</v>
       </c>
       <c r="BF103" t="n">
         <v>196538.63</v>
       </c>
       <c r="BG103" t="n">
-        <v>261324.881444</v>
+        <v>184302.536295</v>
       </c>
       <c r="BH103" t="n">
-        <v>83358.48147699999</v>
+        <v>170150.384408</v>
       </c>
       <c r="BI103" t="n">
         <v>151287.908137</v>
@@ -11892,7 +11892,7 @@
         <v>61337.686024</v>
       </c>
       <c r="BU103" t="n">
-        <v>90017.572872</v>
+        <v>179561.995132</v>
       </c>
       <c r="BV103" t="n">
         <v>93261.25999999999</v>
@@ -11901,7 +11901,7 @@
         <v>0</v>
       </c>
       <c r="BX103" t="n">
-        <v>89642.04058099999</v>
+        <v>185218.748503</v>
       </c>
       <c r="BY103" t="n">
         <v>192659.323273</v>
@@ -11971,25 +11971,25 @@
         <v>61253.316431</v>
       </c>
       <c r="M104" t="n">
-        <v>97947.108257</v>
+        <v>203195.877369</v>
       </c>
       <c r="N104" t="n">
         <v>205513.07</v>
       </c>
       <c r="O104" t="n">
-        <v>251889.439556</v>
+        <v>171156.881083</v>
       </c>
       <c r="P104" t="n">
-        <v>252631.247635</v>
+        <v>170480.549922</v>
       </c>
       <c r="Q104" t="n">
         <v>-0</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S104" t="n">
-        <v>98539.23980900001</v>
+        <v>205762.473782</v>
       </c>
       <c r="T104" t="n">
         <v>148389.573369</v>
@@ -12037,19 +12037,19 @@
         <v>0</v>
       </c>
       <c r="AI104" t="n">
-        <v>97075.84746200001</v>
+        <v>161307.673957</v>
       </c>
       <c r="AJ104" t="n">
-        <v>274483.357483</v>
+        <v>188664.561246</v>
       </c>
       <c r="AK104" t="n">
-        <v>270918.473086</v>
+        <v>183869.623875</v>
       </c>
       <c r="AL104" t="n">
-        <v>84.868424</v>
+        <v>0</v>
       </c>
       <c r="AM104" t="n">
-        <v>84.868424</v>
+        <v>0</v>
       </c>
       <c r="AN104" t="n">
         <v>51098.656781</v>
@@ -12073,13 +12073,13 @@
         <v>48712.224606</v>
       </c>
       <c r="AU104" t="n">
-        <v>130292.149299</v>
+        <v>191426.068516</v>
       </c>
       <c r="AV104" t="n">
-        <v>263244.701057</v>
+        <v>181570.329334</v>
       </c>
       <c r="AW104" t="n">
-        <v>264296.57061</v>
+        <v>181567.353169</v>
       </c>
       <c r="AX104" t="n">
         <v>59731.300613</v>
@@ -12103,16 +12103,16 @@
         <v>35474.386875</v>
       </c>
       <c r="BE104" t="n">
-        <v>57970.478437</v>
+        <v>117186.701681</v>
       </c>
       <c r="BF104" t="n">
         <v>136282.86</v>
       </c>
       <c r="BG104" t="n">
-        <v>181242.150897</v>
+        <v>127809.891528</v>
       </c>
       <c r="BH104" t="n">
-        <v>57806.446718</v>
+        <v>117967.813345</v>
       </c>
       <c r="BI104" t="n">
         <v>104902.238752</v>
@@ -12151,16 +12151,16 @@
         <v>42546.103558</v>
       </c>
       <c r="BU104" t="n">
-        <v>62436.21487</v>
+        <v>124546.994183</v>
       </c>
       <c r="BV104" t="n">
         <v>64700.44</v>
       </c>
       <c r="BW104" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX104" t="n">
-        <v>62175.456913</v>
+        <v>128469.622041</v>
       </c>
       <c r="BY104" t="n">
         <v>133643.077474</v>
@@ -12230,16 +12230,16 @@
         <v>3439537.181843</v>
       </c>
       <c r="M105" t="n">
-        <v>7475249.388585</v>
+        <v>14048866.869861</v>
       </c>
       <c r="N105" t="n">
         <v>11734943.8</v>
       </c>
       <c r="O105" t="n">
-        <v>4356405.460866</v>
+        <v>3018388.536542</v>
       </c>
       <c r="P105" t="n">
-        <v>4413560.868792</v>
+        <v>3034914.964897</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -12248,7 +12248,7 @@
         <v>0</v>
       </c>
       <c r="S105" t="n">
-        <v>7362544.062886</v>
+        <v>13563928.557687</v>
       </c>
       <c r="T105" t="n">
         <v>7952653.08829</v>
@@ -12296,19 +12296,19 @@
         <v>0</v>
       </c>
       <c r="AI105" t="n">
-        <v>7803283.483664</v>
+        <v>9900756.925028</v>
       </c>
       <c r="AJ105" t="n">
-        <v>4485224.381891</v>
+        <v>3231682.396736</v>
       </c>
       <c r="AK105" t="n">
-        <v>4404831.181064</v>
+        <v>3141431.199715</v>
       </c>
       <c r="AL105" t="n">
-        <v>742.943789</v>
+        <v>0</v>
       </c>
       <c r="AM105" t="n">
-        <v>742.943789</v>
+        <v>0</v>
       </c>
       <c r="AN105" t="n">
         <v>2674731.747299</v>
@@ -12332,13 +12332,13 @@
         <v>698640.396632</v>
       </c>
       <c r="AU105" t="n">
-        <v>11586236.332419</v>
+        <v>9469973.775986001</v>
       </c>
       <c r="AV105" t="n">
-        <v>3320597.612696</v>
+        <v>2520483.748283</v>
       </c>
       <c r="AW105" t="n">
-        <v>3347546.456652</v>
+        <v>2536469.273591</v>
       </c>
       <c r="AX105" t="n">
         <v>2443778.497856</v>
@@ -12362,16 +12362,16 @@
         <v>1837918.847472</v>
       </c>
       <c r="BE105" t="n">
-        <v>7015400.020223</v>
+        <v>7234118.546686</v>
       </c>
       <c r="BF105" t="n">
         <v>6038364.53</v>
       </c>
       <c r="BG105" t="n">
-        <v>2391738.955619</v>
+        <v>1874769.90941</v>
       </c>
       <c r="BH105" t="n">
-        <v>6994811.453342</v>
+        <v>7027320.880142</v>
       </c>
       <c r="BI105" t="n">
         <v>4360591.931608</v>
@@ -12410,7 +12410,7 @@
         <v>919458.997866</v>
       </c>
       <c r="BU105" t="n">
-        <v>3608687.010514</v>
+        <v>3495778.421789</v>
       </c>
       <c r="BV105" t="n">
         <v>3536763.73</v>
@@ -12419,7 +12419,7 @@
         <v>0</v>
       </c>
       <c r="BX105" t="n">
-        <v>3590887.824169</v>
+        <v>3437434.209625</v>
       </c>
       <c r="BY105" t="n">
         <v>2249852.86834</v>
@@ -12489,16 +12489,16 @@
         <v>34395.371818</v>
       </c>
       <c r="M106" t="n">
-        <v>74752.493886</v>
+        <v>140488.668699</v>
       </c>
       <c r="N106" t="n">
         <v>117349.44</v>
       </c>
       <c r="O106" t="n">
-        <v>43564.054609</v>
+        <v>30183.885365</v>
       </c>
       <c r="P106" t="n">
-        <v>44135.608688</v>
+        <v>30349.149649</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -12507,7 +12507,7 @@
         <v>0</v>
       </c>
       <c r="S106" t="n">
-        <v>73625.440629</v>
+        <v>135639.285577</v>
       </c>
       <c r="T106" t="n">
         <v>79526.530883</v>
@@ -12555,19 +12555,19 @@
         <v>0</v>
       </c>
       <c r="AI106" t="n">
-        <v>78032.834837</v>
+        <v>99007.56925</v>
       </c>
       <c r="AJ106" t="n">
-        <v>44852.243819</v>
+        <v>32316.823967</v>
       </c>
       <c r="AK106" t="n">
-        <v>44048.311811</v>
+        <v>31414.311997</v>
       </c>
       <c r="AL106" t="n">
-        <v>7.429438</v>
+        <v>0</v>
       </c>
       <c r="AM106" t="n">
-        <v>7.429438</v>
+        <v>0</v>
       </c>
       <c r="AN106" t="n">
         <v>26747.317473</v>
@@ -12591,13 +12591,13 @@
         <v>6986.403966</v>
       </c>
       <c r="AU106" t="n">
-        <v>115862.363324</v>
+        <v>94699.73776</v>
       </c>
       <c r="AV106" t="n">
-        <v>33205.976127</v>
+        <v>25204.837483</v>
       </c>
       <c r="AW106" t="n">
-        <v>33475.464567</v>
+        <v>25364.692736</v>
       </c>
       <c r="AX106" t="n">
         <v>24437.784979</v>
@@ -12621,16 +12621,16 @@
         <v>18379.188475</v>
       </c>
       <c r="BE106" t="n">
-        <v>70154.000202</v>
+        <v>72341.185467</v>
       </c>
       <c r="BF106" t="n">
         <v>60383.65</v>
       </c>
       <c r="BG106" t="n">
-        <v>23917.389556</v>
+        <v>18747.699094</v>
       </c>
       <c r="BH106" t="n">
-        <v>69948.114533</v>
+        <v>70273.208801</v>
       </c>
       <c r="BI106" t="n">
         <v>43605.919316</v>
@@ -12669,7 +12669,7 @@
         <v>9194.589979</v>
       </c>
       <c r="BU106" t="n">
-        <v>36086.870105</v>
+        <v>34957.784218</v>
       </c>
       <c r="BV106" t="n">
         <v>35367.64</v>
@@ -12678,7 +12678,7 @@
         <v>0</v>
       </c>
       <c r="BX106" t="n">
-        <v>35908.878242</v>
+        <v>34374.342096</v>
       </c>
       <c r="BY106" t="n">
         <v>22498.528683</v>
@@ -12748,16 +12748,16 @@
         <v>275997.36221</v>
       </c>
       <c r="M107" t="n">
-        <v>599833.3508360001</v>
+        <v>1127317.424735</v>
       </c>
       <c r="N107" t="n">
         <v>941642.25</v>
       </c>
       <c r="O107" t="n">
-        <v>349569.245032</v>
+        <v>242203.305319</v>
       </c>
       <c r="P107" t="n">
-        <v>354155.542835</v>
+        <v>243529.428687</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -12766,7 +12766,7 @@
         <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>590789.5839110001</v>
+        <v>1088404.719938</v>
       </c>
       <c r="T107" t="n">
         <v>638141.458834</v>
@@ -12814,19 +12814,19 @@
         <v>0</v>
       </c>
       <c r="AI107" t="n">
-        <v>626155.655312</v>
+        <v>794462.35081</v>
       </c>
       <c r="AJ107" t="n">
-        <v>359906.008534</v>
+        <v>259318.556493</v>
       </c>
       <c r="AK107" t="n">
-        <v>353455.050107</v>
+        <v>252076.566947</v>
       </c>
       <c r="AL107" t="n">
-        <v>59.615732</v>
+        <v>0</v>
       </c>
       <c r="AM107" t="n">
-        <v>59.615732</v>
+        <v>0</v>
       </c>
       <c r="AN107" t="n">
         <v>214627.395444</v>
@@ -12850,13 +12850,13 @@
         <v>56060.712942</v>
       </c>
       <c r="AU107" t="n">
-        <v>929709.579116</v>
+        <v>759895.196413</v>
       </c>
       <c r="AV107" t="n">
-        <v>266453.343462</v>
+        <v>202250.136934</v>
       </c>
       <c r="AW107" t="n">
-        <v>268615.788423</v>
+        <v>203532.856843</v>
       </c>
       <c r="AX107" t="n">
         <v>196095.109189</v>
@@ -12880,16 +12880,16 @@
         <v>147479.363368</v>
       </c>
       <c r="BE107" t="n">
-        <v>601741.494613</v>
+        <v>620501.937729</v>
       </c>
       <c r="BF107" t="n">
         <v>484533.99</v>
       </c>
       <c r="BG107" t="n">
-        <v>205149.894479</v>
+        <v>160807.201883</v>
       </c>
       <c r="BH107" t="n">
-        <v>599975.523326</v>
+        <v>602763.998825</v>
       </c>
       <c r="BI107" t="n">
         <v>349905.178275</v>
@@ -12928,7 +12928,7 @@
         <v>73779.768805</v>
       </c>
       <c r="BU107" t="n">
-        <v>362099.406446</v>
+        <v>350770.041266</v>
       </c>
       <c r="BV107" t="n">
         <v>283799.07</v>
@@ -12937,7 +12937,7 @@
         <v>0</v>
       </c>
       <c r="BX107" t="n">
-        <v>360313.417583</v>
+        <v>344915.72236</v>
       </c>
       <c r="BY107" t="n">
         <v>180534.014954</v>
@@ -13007,16 +13007,16 @@
         <v>5519947.244193</v>
       </c>
       <c r="M108" t="n">
-        <v>11996667.016714</v>
+        <v>22546348.494704</v>
       </c>
       <c r="N108" t="n">
         <v>18832845.02</v>
       </c>
       <c r="O108" t="n">
-        <v>6991384.900631</v>
+        <v>4844066.106376</v>
       </c>
       <c r="P108" t="n">
-        <v>7083110.85671</v>
+        <v>4870588.573742</v>
       </c>
       <c r="Q108" t="n">
         <v>0</v>
@@ -13025,7 +13025,7 @@
         <v>0</v>
       </c>
       <c r="S108" t="n">
-        <v>11815791.678229</v>
+        <v>21768094.39877</v>
       </c>
       <c r="T108" t="n">
         <v>12762829.176688</v>
@@ -13073,19 +13073,19 @@
         <v>0</v>
       </c>
       <c r="AI108" t="n">
-        <v>12523113.106232</v>
+        <v>15889247.016209</v>
       </c>
       <c r="AJ108" t="n">
-        <v>7198120.170674</v>
+        <v>5186371.129853</v>
       </c>
       <c r="AK108" t="n">
-        <v>7069101.002135</v>
+        <v>5041531.338934</v>
       </c>
       <c r="AL108" t="n">
-        <v>1192.314635</v>
+        <v>0</v>
       </c>
       <c r="AM108" t="n">
-        <v>1192.314635</v>
+        <v>0</v>
       </c>
       <c r="AN108" t="n">
         <v>4292547.908887</v>
@@ -13109,13 +13109,13 @@
         <v>1121214.258833</v>
       </c>
       <c r="AU108" t="n">
-        <v>18594191.582322</v>
+        <v>15197903.928263</v>
       </c>
       <c r="AV108" t="n">
-        <v>5329066.869239</v>
+        <v>4045002.738686</v>
       </c>
       <c r="AW108" t="n">
-        <v>5372315.768456</v>
+        <v>4070657.136852</v>
       </c>
       <c r="AX108" t="n">
         <v>3921902.183779</v>
@@ -13139,16 +13139,16 @@
         <v>2949587.267354</v>
       </c>
       <c r="BE108" t="n">
-        <v>12034829.892269</v>
+        <v>12410038.754585</v>
       </c>
       <c r="BF108" t="n">
         <v>9690679.85</v>
       </c>
       <c r="BG108" t="n">
-        <v>4102997.889587</v>
+        <v>3216144.037669</v>
       </c>
       <c r="BH108" t="n">
-        <v>11999510.466517</v>
+        <v>12055279.976497</v>
       </c>
       <c r="BI108" t="n">
         <v>6998103.565502</v>
@@ -13187,7 +13187,7 @@
         <v>1475595.37609</v>
       </c>
       <c r="BU108" t="n">
-        <v>7241988.128915</v>
+        <v>7015400.825328</v>
       </c>
       <c r="BV108" t="n">
         <v>5675981.43</v>
@@ -13196,7 +13196,7 @@
         <v>0</v>
       </c>
       <c r="BX108" t="n">
-        <v>7206268.351655</v>
+        <v>6898314.447194</v>
       </c>
       <c r="BY108" t="n">
         <v>3610680.29908</v>
@@ -13266,16 +13266,16 @@
         <v>310392.734028</v>
       </c>
       <c r="M109" t="n">
-        <v>674585.844722</v>
+        <v>1267806.093434</v>
       </c>
       <c r="N109" t="n">
         <v>1058991.69</v>
       </c>
       <c r="O109" t="n">
-        <v>393133.29964</v>
+        <v>272387.190684</v>
       </c>
       <c r="P109" t="n">
-        <v>398291.151523</v>
+        <v>273878.578336</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
@@ -13284,7 +13284,7 @@
         <v>0</v>
       </c>
       <c r="S109" t="n">
-        <v>664415.02454</v>
+        <v>1224044.005515</v>
       </c>
       <c r="T109" t="n">
         <v>717667.989717</v>
@@ -13332,19 +13332,19 @@
         <v>0</v>
       </c>
       <c r="AI109" t="n">
-        <v>704188.490148</v>
+        <v>893469.920061</v>
       </c>
       <c r="AJ109" t="n">
-        <v>404758.252353</v>
+        <v>291635.38046</v>
       </c>
       <c r="AK109" t="n">
-        <v>397503.361917</v>
+        <v>283490.878944</v>
       </c>
       <c r="AL109" t="n">
-        <v>67.04517</v>
+        <v>0</v>
       </c>
       <c r="AM109" t="n">
-        <v>67.04517</v>
+        <v>0</v>
       </c>
       <c r="AN109" t="n">
         <v>241374.712917</v>
@@ -13368,13 +13368,13 @@
         <v>63047.116908</v>
       </c>
       <c r="AU109" t="n">
-        <v>1045571.94244</v>
+        <v>854594.934173</v>
       </c>
       <c r="AV109" t="n">
-        <v>299659.319589</v>
+        <v>227454.974417</v>
       </c>
       <c r="AW109" t="n">
-        <v>302091.252989</v>
+        <v>228897.549579</v>
       </c>
       <c r="AX109" t="n">
         <v>220532.894167</v>
@@ -13398,16 +13398,16 @@
         <v>165858.551842</v>
       </c>
       <c r="BE109" t="n">
-        <v>671895.494816</v>
+        <v>692843.123196</v>
       </c>
       <c r="BF109" t="n">
         <v>544917.64</v>
       </c>
       <c r="BG109" t="n">
-        <v>229067.284036</v>
+        <v>179554.900978</v>
       </c>
       <c r="BH109" t="n">
-        <v>669923.637859</v>
+        <v>673037.207626</v>
       </c>
       <c r="BI109" t="n">
         <v>393511.097591</v>
@@ -13446,7 +13446,7 @@
         <v>82974.358783</v>
       </c>
       <c r="BU109" t="n">
-        <v>398186.276551</v>
+        <v>385727.825484</v>
       </c>
       <c r="BV109" t="n">
         <v>319166.71</v>
@@ -13455,7 +13455,7 @@
         <v>0</v>
       </c>
       <c r="BX109" t="n">
-        <v>396222.295824</v>
+        <v>379290.064456</v>
       </c>
       <c r="BY109" t="n">
         <v>203032.543637</v>
@@ -13688,25 +13688,25 @@
         </is>
       </c>
       <c r="M112" t="n">
-        <v>101880.740378</v>
+        <v>158185.677816</v>
       </c>
       <c r="N112" t="n">
         <v>156913.57</v>
       </c>
       <c r="O112" t="n">
-        <v>155985.789647</v>
+        <v>141815.020617</v>
       </c>
       <c r="P112" t="n">
-        <v>83955.670747</v>
+        <v>76747.680464</v>
       </c>
       <c r="Q112" t="n">
-        <v>70751.338544</v>
+        <v>33932.637562</v>
       </c>
       <c r="R112" t="n">
-        <v>70751.3385</v>
+        <v>33932.6376</v>
       </c>
       <c r="S112" t="n">
-        <v>53396.473175</v>
+        <v>84170.53679899999</v>
       </c>
       <c r="T112" t="n">
         <v>90446.669393</v>
@@ -13730,19 +13730,19 @@
         <v>26639.653166</v>
       </c>
       <c r="AI112" t="n">
-        <v>150744.436297</v>
+        <v>150901.802604</v>
       </c>
       <c r="AJ112" t="n">
-        <v>69658.362397</v>
+        <v>79935.52873999999</v>
       </c>
       <c r="AK112" t="n">
-        <v>40281.363856</v>
+        <v>51386.659361</v>
       </c>
       <c r="AL112" t="n">
-        <v>57705.306323</v>
+        <v>33555.66932</v>
       </c>
       <c r="AM112" t="n">
-        <v>57705.306323</v>
+        <v>33555.66932</v>
       </c>
       <c r="AN112" t="n">
         <v>45435.237048</v>
@@ -13760,13 +13760,13 @@
         <v>7930.219789</v>
       </c>
       <c r="AU112" t="n">
-        <v>145443.661023</v>
+        <v>152721.403788</v>
       </c>
       <c r="AV112" t="n">
-        <v>121992.834934</v>
+        <v>113600.1794</v>
       </c>
       <c r="AW112" t="n">
-        <v>66867.51714700001</v>
+        <v>62469.22157</v>
       </c>
       <c r="AX112" t="n">
         <v>47594.063278</v>
@@ -13781,16 +13781,16 @@
         <v>5668.393453</v>
       </c>
       <c r="BE112" t="n">
-        <v>151982.859597</v>
+        <v>85551.635131</v>
       </c>
       <c r="BF112" t="n">
         <v>59162.63</v>
       </c>
       <c r="BG112" t="n">
-        <v>61024.607992</v>
+        <v>54165.071464</v>
       </c>
       <c r="BH112" t="n">
-        <v>80689.284904</v>
+        <v>45392.909402</v>
       </c>
       <c r="BI112" t="n">
         <v>57275.485475</v>
@@ -13808,7 +13808,7 @@
         <v>17563.98219</v>
       </c>
       <c r="BU112" t="n">
-        <v>73055.339704</v>
+        <v>42388.442594</v>
       </c>
       <c r="BV112" t="n">
         <v>73123.57000000001</v>
@@ -13817,7 +13817,7 @@
         <v>0</v>
       </c>
       <c r="BX112" t="n">
-        <v>38739.405664</v>
+        <v>26062.922331</v>
       </c>
       <c r="BY112" t="n">
         <v>48010.837297</v>
@@ -13857,25 +13857,25 @@
         </is>
       </c>
       <c r="M113" t="n">
-        <v>2536116.112937</v>
+        <v>4938395.217973</v>
       </c>
       <c r="N113" t="n">
         <v>5825225.25</v>
       </c>
       <c r="O113" t="n">
-        <v>5221128.525041</v>
+        <v>5001063.436278</v>
       </c>
       <c r="P113" t="n">
-        <v>2831873.908871</v>
+        <v>2800214.825082</v>
       </c>
       <c r="Q113" t="n">
-        <v>3655246.64741</v>
+        <v>2009223.780074</v>
       </c>
       <c r="R113" t="n">
-        <v>3650685.9806</v>
+        <v>2885498.1899</v>
       </c>
       <c r="S113" t="n">
-        <v>1415513.398901</v>
+        <v>2900221.47233</v>
       </c>
       <c r="T113" t="n">
         <v>4016428.383562</v>
@@ -13899,19 +13899,19 @@
         <v>987434.308377</v>
       </c>
       <c r="AI113" t="n">
-        <v>2585637.383567</v>
+        <v>3777064.50359</v>
       </c>
       <c r="AJ113" t="n">
-        <v>3255966.632948</v>
+        <v>3463418.65686</v>
       </c>
       <c r="AK113" t="n">
-        <v>1834129.031762</v>
+        <v>2324213.781353</v>
       </c>
       <c r="AL113" t="n">
-        <v>5457112.466632</v>
+        <v>1854779.657314</v>
       </c>
       <c r="AM113" t="n">
-        <v>3692465.047802</v>
+        <v>1837049.329415</v>
       </c>
       <c r="AN113" t="n">
         <v>1333706.139967</v>
@@ -13929,13 +13929,13 @@
         <v>396135.802819</v>
       </c>
       <c r="AU113" t="n">
-        <v>1428428.039457</v>
+        <v>4014045.6782</v>
       </c>
       <c r="AV113" t="n">
-        <v>5882207.656326</v>
+        <v>5488799.009646</v>
       </c>
       <c r="AW113" t="n">
-        <v>3312764.980303</v>
+        <v>3028884.283791</v>
       </c>
       <c r="AX113" t="n">
         <v>1404865.415197</v>
@@ -13950,16 +13950,16 @@
         <v>384402.925367</v>
       </c>
       <c r="BE113" t="n">
-        <v>1400828.519978</v>
+        <v>1461537.19263</v>
       </c>
       <c r="BF113" t="n">
         <v>656646.6899999999</v>
       </c>
       <c r="BG113" t="n">
-        <v>2790552.025273</v>
+        <v>2527547.970268</v>
       </c>
       <c r="BH113" t="n">
-        <v>748698.994668</v>
+        <v>831831.045215</v>
       </c>
       <c r="BI113" t="n">
         <v>1517093.535425</v>
@@ -13977,7 +13977,7 @@
         <v>376785.787322</v>
       </c>
       <c r="BU113" t="n">
-        <v>769347.687638</v>
+        <v>1327887.134541</v>
       </c>
       <c r="BV113" t="n">
         <v>691481.46</v>
@@ -13986,7 +13986,7 @@
         <v>-0</v>
       </c>
       <c r="BX113" t="n">
-        <v>408424.99336</v>
+        <v>803972.087502</v>
       </c>
       <c r="BY113" t="n">
         <v>1409669.197243</v>
@@ -14026,25 +14026,25 @@
         </is>
       </c>
       <c r="M114" t="n">
-        <v>2160288.274035</v>
+        <v>4414381.05896</v>
       </c>
       <c r="N114" t="n">
         <v>5286403.57</v>
       </c>
       <c r="O114" t="n">
-        <v>4752014.851463</v>
+        <v>4561895.6552</v>
       </c>
       <c r="P114" t="n">
-        <v>2577062.024982</v>
+        <v>2557808.893712</v>
       </c>
       <c r="Q114" t="n">
-        <v>3349107.532842</v>
+        <v>1861381.859065</v>
       </c>
       <c r="R114" t="n">
-        <v>3343922.6885</v>
+        <v>2703531.212</v>
       </c>
       <c r="S114" t="n">
-        <v>1216244.712991</v>
+        <v>2603862.517411</v>
       </c>
       <c r="T114" t="n">
         <v>3665729.999873</v>
@@ -14068,19 +14068,19 @@
         <v>892077.202356</v>
       </c>
       <c r="AI114" t="n">
-        <v>2124666.369604</v>
+        <v>3354636.748229</v>
       </c>
       <c r="AJ114" t="n">
-        <v>3016730.409664</v>
+        <v>3198655.307822</v>
       </c>
       <c r="AK114" t="n">
-        <v>1696985.25452</v>
+        <v>2145291.299899</v>
       </c>
       <c r="AL114" t="n">
-        <v>5111381.473779</v>
+        <v>1718387.582848</v>
       </c>
       <c r="AM114" t="n">
-        <v>3416909.289128</v>
+        <v>1701449.2217</v>
       </c>
       <c r="AN114" t="n">
         <v>1194865.381281</v>
@@ -14098,13 +14098,13 @@
         <v>366452.572814</v>
       </c>
       <c r="AU114" t="n">
-        <v>1172469.014013</v>
+        <v>3603013.4405</v>
       </c>
       <c r="AV114" t="n">
-        <v>5456560.789368</v>
+        <v>5096717.60411</v>
       </c>
       <c r="AW114" t="n">
-        <v>3074556.172335</v>
+        <v>2813074.690343</v>
       </c>
       <c r="AX114" t="n">
         <v>1262716.046858</v>
@@ -14119,16 +14119,16 @@
         <v>359781.565376</v>
       </c>
       <c r="BE114" t="n">
-        <v>1051412.469728</v>
+        <v>1261490.540992</v>
       </c>
       <c r="BF114" t="n">
         <v>529606.9300000001</v>
       </c>
       <c r="BG114" t="n">
-        <v>2551203.735529</v>
+        <v>2316892.63177</v>
       </c>
       <c r="BH114" t="n">
-        <v>563055.425203</v>
+        <v>719753.593396</v>
       </c>
       <c r="BI114" t="n">
         <v>1337912.593467</v>
@@ -14146,16 +14146,16 @@
         <v>328102.73979</v>
       </c>
       <c r="BU114" t="n">
-        <v>627823.67739</v>
+        <v>1201544.190369</v>
       </c>
       <c r="BV114" t="n">
         <v>544509.98</v>
       </c>
       <c r="BW114" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX114" t="n">
-        <v>333916.977657</v>
+        <v>729711.470996</v>
       </c>
       <c r="BY114" t="n">
         <v>1292171.170709</v>
@@ -14195,25 +14195,25 @@
         </is>
       </c>
       <c r="M115" t="n">
-        <v>288322.495269</v>
+        <v>447665.46822</v>
       </c>
       <c r="N115" t="n">
         <v>444065.39</v>
       </c>
       <c r="O115" t="n">
-        <v>441439.784701</v>
+        <v>401336.508345</v>
       </c>
       <c r="P115" t="n">
-        <v>237594.548215</v>
+        <v>217195.935714</v>
       </c>
       <c r="Q115" t="n">
-        <v>200226.28808</v>
+        <v>96029.364302</v>
       </c>
       <c r="R115" t="n">
-        <v>200226.2881</v>
+        <v>96029.3643</v>
       </c>
       <c r="S115" t="n">
-        <v>151112.019084</v>
+        <v>238202.619142</v>
       </c>
       <c r="T115" t="n">
         <v>255964.074383</v>
@@ -14237,19 +14237,19 @@
         <v>75390.21846</v>
       </c>
       <c r="AI115" t="n">
-        <v>426606.75472</v>
+        <v>427052.10137</v>
       </c>
       <c r="AJ115" t="n">
-        <v>197133.165585</v>
+        <v>226217.546335</v>
       </c>
       <c r="AK115" t="n">
-        <v>113996.259713</v>
+        <v>145424.245993</v>
       </c>
       <c r="AL115" t="n">
-        <v>163306.016895</v>
+        <v>94962.544176</v>
       </c>
       <c r="AM115" t="n">
-        <v>163306.016895</v>
+        <v>94962.544176</v>
       </c>
       <c r="AN115" t="n">
         <v>128581.720845</v>
@@ -14267,13 +14267,13 @@
         <v>22442.522002</v>
       </c>
       <c r="AU115" t="n">
-        <v>411605.560694</v>
+        <v>432201.572719</v>
       </c>
       <c r="AV115" t="n">
-        <v>345239.722863</v>
+        <v>321488.507701</v>
       </c>
       <c r="AW115" t="n">
-        <v>189235.073526</v>
+        <v>176787.897042</v>
       </c>
       <c r="AX115" t="n">
         <v>134691.199077</v>
@@ -14288,16 +14288,16 @@
         <v>16041.553473</v>
       </c>
       <c r="BE115" t="n">
-        <v>430111.49266</v>
+        <v>242111.12742</v>
       </c>
       <c r="BF115" t="n">
         <v>167430.24</v>
       </c>
       <c r="BG115" t="n">
-        <v>172699.640617</v>
+        <v>153287.152243</v>
       </c>
       <c r="BH115" t="n">
-        <v>228350.676279</v>
+        <v>128461.933609</v>
       </c>
       <c r="BI115" t="n">
         <v>162089.623893</v>
@@ -14315,7 +14315,7 @@
         <v>49706.069597</v>
       </c>
       <c r="BU115" t="n">
-        <v>206746.611362</v>
+        <v>119959.292542</v>
       </c>
       <c r="BV115" t="n">
         <v>206939.69</v>
@@ -14324,7 +14324,7 @@
         <v>0</v>
       </c>
       <c r="BX115" t="n">
-        <v>109632.518028</v>
+        <v>73758.070196</v>
       </c>
       <c r="BY115" t="n">
         <v>135870.669551</v>
@@ -14364,25 +14364,25 @@
         </is>
       </c>
       <c r="M116" t="n">
-        <v>8649.674858</v>
+        <v>13429.964047</v>
       </c>
       <c r="N116" t="n">
         <v>13321.96</v>
       </c>
       <c r="O116" t="n">
-        <v>13243.193541</v>
+        <v>12040.09525</v>
       </c>
       <c r="P116" t="n">
-        <v>7127.836446</v>
+        <v>6515.878071</v>
       </c>
       <c r="Q116" t="n">
-        <v>6006.788642</v>
+        <v>2880.880929</v>
       </c>
       <c r="R116" t="n">
-        <v>6006.7886</v>
+        <v>2880.8809</v>
       </c>
       <c r="S116" t="n">
-        <v>4533.360573</v>
+        <v>7146.078574</v>
       </c>
       <c r="T116" t="n">
         <v>7678.922231</v>
@@ -14406,19 +14406,19 @@
         <v>2261.706554</v>
       </c>
       <c r="AI116" t="n">
-        <v>12798.202642</v>
+        <v>12811.563041</v>
       </c>
       <c r="AJ116" t="n">
-        <v>5913.994968</v>
+        <v>6786.52639</v>
       </c>
       <c r="AK116" t="n">
-        <v>3419.887791</v>
+        <v>4362.72738</v>
       </c>
       <c r="AL116" t="n">
-        <v>4899.180507</v>
+        <v>2848.876325</v>
       </c>
       <c r="AM116" t="n">
-        <v>4899.180507</v>
+        <v>2848.876325</v>
       </c>
       <c r="AN116" t="n">
         <v>3857.451625</v>
@@ -14436,13 +14436,13 @@
         <v>673.27566</v>
       </c>
       <c r="AU116" t="n">
-        <v>12348.166821</v>
+        <v>12966.047182</v>
       </c>
       <c r="AV116" t="n">
-        <v>10357.191686</v>
+        <v>9644.655231000001</v>
       </c>
       <c r="AW116" t="n">
-        <v>5677.052206</v>
+        <v>5303.636911</v>
       </c>
       <c r="AX116" t="n">
         <v>4040.735972</v>
@@ -14457,16 +14457,16 @@
         <v>481.246604</v>
       </c>
       <c r="BE116" t="n">
-        <v>12903.34478</v>
+        <v>7263.333823</v>
       </c>
       <c r="BF116" t="n">
         <v>5022.91</v>
       </c>
       <c r="BG116" t="n">
-        <v>5180.989219</v>
+        <v>4598.614567</v>
       </c>
       <c r="BH116" t="n">
-        <v>6850.520288</v>
+        <v>3853.858008</v>
       </c>
       <c r="BI116" t="n">
         <v>4862.688717</v>
@@ -14484,7 +14484,7 @@
         <v>1491.182088</v>
       </c>
       <c r="BU116" t="n">
-        <v>6202.398341</v>
+        <v>3598.778776</v>
       </c>
       <c r="BV116" t="n">
         <v>6208.19</v>
@@ -14493,7 +14493,7 @@
         <v>0</v>
       </c>
       <c r="BX116" t="n">
-        <v>3288.975541</v>
+        <v>2212.742106</v>
       </c>
       <c r="BY116" t="n">
         <v>4076.120087</v>
@@ -14533,25 +14533,25 @@
         </is>
       </c>
       <c r="M117" t="n">
-        <v>18755.792083</v>
+        <v>29121.281144</v>
       </c>
       <c r="N117" t="n">
         <v>28887.09</v>
       </c>
       <c r="O117" t="n">
-        <v>28716.291496</v>
+        <v>26107.515818</v>
       </c>
       <c r="P117" t="n">
-        <v>15455.866329</v>
+        <v>14128.907312</v>
       </c>
       <c r="Q117" t="n">
-        <v>13025.00738</v>
+        <v>6246.847958</v>
       </c>
       <c r="R117" t="n">
-        <v>13025.0074</v>
+        <v>6246.848</v>
       </c>
       <c r="S117" t="n">
-        <v>9830.053699</v>
+        <v>15495.422215</v>
       </c>
       <c r="T117" t="n">
         <v>16650.830368</v>
@@ -14575,19 +14575,19 @@
         <v>4904.241902</v>
       </c>
       <c r="AI117" t="n">
-        <v>27751.381609</v>
+        <v>27780.352048</v>
       </c>
       <c r="AJ117" t="n">
-        <v>12823.795323</v>
+        <v>14715.776029</v>
       </c>
       <c r="AK117" t="n">
-        <v>7415.620288</v>
+        <v>9460.055897</v>
       </c>
       <c r="AL117" t="n">
-        <v>10623.290756</v>
+        <v>6177.449778</v>
       </c>
       <c r="AM117" t="n">
-        <v>10623.290756</v>
+        <v>6177.449778</v>
       </c>
       <c r="AN117" t="n">
         <v>8364.425466000001</v>
@@ -14605,13 +14605,13 @@
         <v>1459.918263</v>
       </c>
       <c r="AU117" t="n">
-        <v>26775.53241</v>
+        <v>28115.332549</v>
       </c>
       <c r="AV117" t="n">
-        <v>22458.339419</v>
+        <v>20913.288788</v>
       </c>
       <c r="AW117" t="n">
-        <v>12310.0131</v>
+        <v>11500.306407</v>
       </c>
       <c r="AX117" t="n">
         <v>8761.855793000001</v>
@@ -14626,16 +14626,16 @@
         <v>1043.526074</v>
       </c>
       <c r="BE117" t="n">
-        <v>30581.376824</v>
+        <v>17214.354295</v>
       </c>
       <c r="BF117" t="n">
         <v>10891.58</v>
       </c>
       <c r="BG117" t="n">
-        <v>12279.125011</v>
+        <v>10898.876791</v>
       </c>
       <c r="BH117" t="n">
-        <v>16235.971832</v>
+        <v>9133.777791</v>
       </c>
       <c r="BI117" t="n">
         <v>10544.162646</v>
@@ -14653,7 +14653,7 @@
         <v>3233.451159</v>
       </c>
       <c r="BU117" t="n">
-        <v>18019.347351</v>
+        <v>10455.253153</v>
       </c>
       <c r="BV117" t="n">
         <v>13461.72</v>
@@ -14662,7 +14662,7 @@
         <v>0</v>
       </c>
       <c r="BX117" t="n">
-        <v>9555.205816</v>
+        <v>6428.508202</v>
       </c>
       <c r="BY117" t="n">
         <v>8838.582039999999</v>
@@ -14702,25 +14702,25 @@
         </is>
       </c>
       <c r="M118" t="n">
-        <v>562673.762495</v>
+        <v>873638.434308</v>
       </c>
       <c r="N118" t="n">
         <v>866612.73</v>
       </c>
       <c r="O118" t="n">
-        <v>861488.74489</v>
+        <v>783225.474538</v>
       </c>
       <c r="P118" t="n">
-        <v>463675.989859</v>
+        <v>423867.219354</v>
       </c>
       <c r="Q118" t="n">
-        <v>390750.221412</v>
+        <v>187405.43873</v>
       </c>
       <c r="R118" t="n">
-        <v>390750.2214</v>
+        <v>187405.4387</v>
       </c>
       <c r="S118" t="n">
-        <v>294901.610979</v>
+        <v>464862.666452</v>
       </c>
       <c r="T118" t="n">
         <v>499524.911027</v>
@@ -14744,19 +14744,19 @@
         <v>147127.257055</v>
       </c>
       <c r="AI118" t="n">
-        <v>832541.448284</v>
+        <v>833410.561445</v>
       </c>
       <c r="AJ118" t="n">
-        <v>384713.859696</v>
+        <v>441473.280882</v>
       </c>
       <c r="AK118" t="n">
-        <v>222468.608643</v>
+        <v>283801.676918</v>
       </c>
       <c r="AL118" t="n">
-        <v>318698.722687</v>
+        <v>185323.493325</v>
       </c>
       <c r="AM118" t="n">
-        <v>318698.722687</v>
+        <v>185323.493325</v>
       </c>
       <c r="AN118" t="n">
         <v>250932.763981</v>
@@ -14774,13 +14774,13 @@
         <v>43797.547892</v>
       </c>
       <c r="AU118" t="n">
-        <v>803265.9723049999</v>
+        <v>843459.97648</v>
       </c>
       <c r="AV118" t="n">
-        <v>673750.1825690001</v>
+        <v>627398.663633</v>
       </c>
       <c r="AW118" t="n">
-        <v>369300.393012</v>
+        <v>345009.192223</v>
       </c>
       <c r="AX118" t="n">
         <v>262855.67378</v>
@@ -14795,16 +14795,16 @@
         <v>31305.78223</v>
       </c>
       <c r="BE118" t="n">
-        <v>917441.304721</v>
+        <v>516430.628845</v>
       </c>
       <c r="BF118" t="n">
         <v>326747.32</v>
       </c>
       <c r="BG118" t="n">
-        <v>368373.750333</v>
+        <v>326966.303738</v>
       </c>
       <c r="BH118" t="n">
-        <v>487079.15495</v>
+        <v>274013.333724</v>
       </c>
       <c r="BI118" t="n">
         <v>316324.879377</v>
@@ -14822,7 +14822,7 @@
         <v>97003.534784</v>
       </c>
       <c r="BU118" t="n">
-        <v>540580.4205379999</v>
+        <v>313657.594591</v>
       </c>
       <c r="BV118" t="n">
         <v>403851.72</v>
@@ -14831,7 +14831,7 @@
         <v>0</v>
       </c>
       <c r="BX118" t="n">
-        <v>286656.174482</v>
+        <v>192855.246052</v>
       </c>
       <c r="BY118" t="n">
         <v>265157.461188</v>
@@ -14871,25 +14871,25 @@
         </is>
       </c>
       <c r="M119" t="n">
-        <v>27405.466941</v>
+        <v>42551.24519</v>
       </c>
       <c r="N119" t="n">
         <v>42209.05</v>
       </c>
       <c r="O119" t="n">
-        <v>41959.485037</v>
+        <v>38147.611068</v>
       </c>
       <c r="P119" t="n">
-        <v>22583.702775</v>
+        <v>20644.785383</v>
       </c>
       <c r="Q119" t="n">
-        <v>19031.796023</v>
+        <v>9127.728886999999</v>
       </c>
       <c r="R119" t="n">
-        <v>19031.796</v>
+        <v>9127.7289</v>
       </c>
       <c r="S119" t="n">
-        <v>14363.414272</v>
+        <v>22641.500789</v>
       </c>
       <c r="T119" t="n">
         <v>24329.752599</v>
@@ -14913,19 +14913,19 @@
         <v>7165.948456</v>
       </c>
       <c r="AI119" t="n">
-        <v>40549.584251</v>
+        <v>40591.915089</v>
       </c>
       <c r="AJ119" t="n">
-        <v>18737.790291</v>
+        <v>21502.302419</v>
       </c>
       <c r="AK119" t="n">
-        <v>10835.508079</v>
+        <v>13822.783277</v>
       </c>
       <c r="AL119" t="n">
-        <v>15522.471263</v>
+        <v>9026.326102999999</v>
       </c>
       <c r="AM119" t="n">
-        <v>15522.471263</v>
+        <v>9026.326102999999</v>
       </c>
       <c r="AN119" t="n">
         <v>12221.877091</v>
@@ -14943,13 +14943,13 @@
         <v>2133.193923</v>
       </c>
       <c r="AU119" t="n">
-        <v>39123.699231</v>
+        <v>41081.379731</v>
       </c>
       <c r="AV119" t="n">
-        <v>32815.531105</v>
+        <v>30557.944019</v>
       </c>
       <c r="AW119" t="n">
-        <v>17987.065306</v>
+        <v>16803.943319</v>
       </c>
       <c r="AX119" t="n">
         <v>12802.591765</v>
@@ -14964,16 +14964,16 @@
         <v>1524.772678</v>
       </c>
       <c r="BE119" t="n">
-        <v>43484.721604</v>
+        <v>24477.688117</v>
       </c>
       <c r="BF119" t="n">
         <v>15914.48</v>
       </c>
       <c r="BG119" t="n">
-        <v>17460.11423</v>
+        <v>15497.491359</v>
       </c>
       <c r="BH119" t="n">
-        <v>23086.49212</v>
+        <v>12987.635799</v>
       </c>
       <c r="BI119" t="n">
         <v>15406.851363</v>
@@ -14991,7 +14991,7 @@
         <v>4724.633247</v>
       </c>
       <c r="BU119" t="n">
-        <v>24221.745692</v>
+        <v>14054.031929</v>
       </c>
       <c r="BV119" t="n">
         <v>19669.91</v>
@@ -15000,7 +15000,7 @@
         <v>0</v>
       </c>
       <c r="BX119" t="n">
-        <v>12844.181357</v>
+        <v>8641.250308000001</v>
       </c>
       <c r="BY119" t="n">
         <v>12914.702126</v>
@@ -15586,25 +15586,25 @@
         <v>2826.985801</v>
       </c>
       <c r="M123" t="n">
-        <v>217753.709248</v>
+        <v>27151.790244</v>
       </c>
       <c r="N123" t="n">
         <v>6505.74</v>
       </c>
       <c r="O123" t="n">
-        <v>935.832858</v>
+        <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>955.172669</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>5280.017564</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>5280.0176</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
-        <v>209591.864172</v>
+        <v>22580.275693</v>
       </c>
       <c r="T123" t="n">
         <v>1058.392481</v>
@@ -15652,7 +15652,7 @@
         <v>0</v>
       </c>
       <c r="AI123" t="n">
-        <v>207227.443051</v>
+        <v>34844.068507</v>
       </c>
       <c r="AJ123" t="n">
         <v>0</v>
@@ -15661,10 +15661,10 @@
         <v>0</v>
       </c>
       <c r="AL123" t="n">
-        <v>4754.937985</v>
+        <v>0</v>
       </c>
       <c r="AM123" t="n">
-        <v>4754.937985</v>
+        <v>0</v>
       </c>
       <c r="AN123" t="n">
         <v>4414.095566</v>
@@ -15688,13 +15688,13 @@
         <v>31.750098</v>
       </c>
       <c r="AU123" t="n">
-        <v>234532.048388</v>
+        <v>36080.421682</v>
       </c>
       <c r="AV123" t="n">
-        <v>5158.81302</v>
+        <v>497.014938</v>
       </c>
       <c r="AW123" t="n">
-        <v>5012.997119</v>
+        <v>351.08701</v>
       </c>
       <c r="AX123" t="n">
         <v>4515.404534</v>
@@ -15718,7 +15718,7 @@
         <v>8797.000478</v>
       </c>
       <c r="BE123" t="n">
-        <v>260437.614854</v>
+        <v>57781.288132</v>
       </c>
       <c r="BF123" t="n">
         <v>23555.68</v>
@@ -15727,7 +15727,7 @@
         <v>0</v>
       </c>
       <c r="BH123" t="n">
-        <v>251270.110208</v>
+        <v>50596.182122</v>
       </c>
       <c r="BI123" t="n">
         <v>5258.612234</v>
@@ -15766,7 +15766,7 @@
         <v>6281.960593</v>
       </c>
       <c r="BU123" t="n">
-        <v>141102.652883</v>
+        <v>47138.669556</v>
       </c>
       <c r="BV123" t="n">
         <v>134466.98</v>
@@ -15775,7 +15775,7 @@
         <v>0</v>
       </c>
       <c r="BX123" t="n">
-        <v>135938.414494</v>
+        <v>40523.116071</v>
       </c>
       <c r="BY123" t="n">
         <v>2886.879966</v>
@@ -15845,25 +15845,25 @@
         <v>706.74645</v>
       </c>
       <c r="M124" t="n">
-        <v>54438.427312</v>
+        <v>6787.947561</v>
       </c>
       <c r="N124" t="n">
         <v>1626.44</v>
       </c>
       <c r="O124" t="n">
-        <v>233.958214</v>
+        <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>238.793167</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>1320.004391</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>1320.0044</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
-        <v>52397.966043</v>
+        <v>5645.068923</v>
       </c>
       <c r="T124" t="n">
         <v>264.59812</v>
@@ -15911,7 +15911,7 @@
         <v>0</v>
       </c>
       <c r="AI124" t="n">
-        <v>51806.860763</v>
+        <v>8711.017126999999</v>
       </c>
       <c r="AJ124" t="n">
         <v>0</v>
@@ -15920,10 +15920,10 @@
         <v>0</v>
       </c>
       <c r="AL124" t="n">
-        <v>1188.734496</v>
+        <v>0</v>
       </c>
       <c r="AM124" t="n">
-        <v>1188.734496</v>
+        <v>0</v>
       </c>
       <c r="AN124" t="n">
         <v>1103.523891</v>
@@ -15947,13 +15947,13 @@
         <v>7.937525</v>
       </c>
       <c r="AU124" t="n">
-        <v>58633.012097</v>
+        <v>9020.10542</v>
       </c>
       <c r="AV124" t="n">
-        <v>1289.703255</v>
+        <v>124.253734</v>
       </c>
       <c r="AW124" t="n">
-        <v>1253.24928</v>
+        <v>87.77175200000001</v>
       </c>
       <c r="AX124" t="n">
         <v>1128.851134</v>
@@ -15977,7 +15977,7 @@
         <v>2199.25012</v>
       </c>
       <c r="BE124" t="n">
-        <v>65109.403714</v>
+        <v>14445.322033</v>
       </c>
       <c r="BF124" t="n">
         <v>5888.92</v>
@@ -15986,7 +15986,7 @@
         <v>0</v>
       </c>
       <c r="BH124" t="n">
-        <v>62817.527552</v>
+        <v>12649.045531</v>
       </c>
       <c r="BI124" t="n">
         <v>1314.653058</v>
@@ -16025,7 +16025,7 @@
         <v>1570.490148</v>
       </c>
       <c r="BU124" t="n">
-        <v>35275.663221</v>
+        <v>11784.667389</v>
       </c>
       <c r="BV124" t="n">
         <v>33616.75</v>
@@ -16034,7 +16034,7 @@
         <v>0</v>
       </c>
       <c r="BX124" t="n">
-        <v>33984.603624</v>
+        <v>10130.779018</v>
       </c>
       <c r="BY124" t="n">
         <v>721.7199910000001</v>
@@ -16104,25 +16104,25 @@
         <v>1108.569246</v>
       </c>
       <c r="M125" t="n">
-        <v>41045.097979</v>
+        <v>8366.974775999999</v>
       </c>
       <c r="N125" t="n">
         <v>1845.08</v>
       </c>
       <c r="O125" t="n">
-        <v>317.25095</v>
+        <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>342.405727</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>2056.428856</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>1739.5884</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>37427.883327</v>
+        <v>6214.212899</v>
       </c>
       <c r="T125" t="n">
         <v>560.251415</v>
@@ -16170,7 +16170,7 @@
         <v>0</v>
       </c>
       <c r="AI125" t="n">
-        <v>50870.677853</v>
+        <v>14924.535485</v>
       </c>
       <c r="AJ125" t="n">
         <v>0</v>
@@ -16179,10 +16179,10 @@
         <v>0</v>
       </c>
       <c r="AL125" t="n">
-        <v>2447.955502</v>
+        <v>0</v>
       </c>
       <c r="AM125" t="n">
-        <v>1999.115142</v>
+        <v>0</v>
       </c>
       <c r="AN125" t="n">
         <v>1567.298606</v>
@@ -16206,13 +16206,13 @@
         <v>12.308022</v>
       </c>
       <c r="AU125" t="n">
-        <v>39900.252759</v>
+        <v>13872.049688</v>
       </c>
       <c r="AV125" t="n">
-        <v>1753.499802</v>
+        <v>177.557491</v>
       </c>
       <c r="AW125" t="n">
-        <v>1656.727161</v>
+        <v>122.214701</v>
       </c>
       <c r="AX125" t="n">
         <v>1969.437808</v>
@@ -16236,7 +16236,7 @@
         <v>1467.222887</v>
       </c>
       <c r="BE125" t="n">
-        <v>24490.412424</v>
+        <v>6183.084469</v>
       </c>
       <c r="BF125" t="n">
         <v>3122.06</v>
@@ -16245,7 +16245,7 @@
         <v>0</v>
       </c>
       <c r="BH125" t="n">
-        <v>63753.734621</v>
+        <v>7075.497617</v>
       </c>
       <c r="BI125" t="n">
         <v>1250.331341</v>
@@ -16284,7 +16284,7 @@
         <v>1343.88067</v>
       </c>
       <c r="BU125" t="n">
-        <v>32841.815676</v>
+        <v>12821.172544</v>
       </c>
       <c r="BV125" t="n">
         <v>26780.45</v>
@@ -16293,7 +16293,7 @@
         <v>0</v>
       </c>
       <c r="BX125" t="n">
-        <v>28520.042827</v>
+        <v>10740.046192</v>
       </c>
       <c r="BY125" t="n">
         <v>889.758673</v>
@@ -16363,25 +16363,25 @@
         <v>1268.681337</v>
       </c>
       <c r="M126" t="n">
-        <v>47007.64835</v>
+        <v>9577.171897</v>
       </c>
       <c r="N126" t="n">
         <v>2111.56</v>
       </c>
       <c r="O126" t="n">
-        <v>363.069443</v>
+        <v>-0</v>
       </c>
       <c r="P126" t="n">
-        <v>391.843538</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>2353.334493</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>1990.9007</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
-        <v>42866.008769</v>
+        <v>7113.280307</v>
       </c>
       <c r="T126" t="n">
         <v>641.091031</v>
@@ -16429,19 +16429,19 @@
         <v>0</v>
       </c>
       <c r="AI126" t="n">
-        <v>58241.905961</v>
+        <v>17080.428585</v>
       </c>
       <c r="AJ126" t="n">
         <v>0</v>
       </c>
       <c r="AK126" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL126" t="n">
-        <v>2801.138787</v>
+        <v>0</v>
       </c>
       <c r="AM126" t="n">
-        <v>2287.667984</v>
+        <v>0</v>
       </c>
       <c r="AN126" t="n">
         <v>1793.853078</v>
@@ -16465,13 +16465,13 @@
         <v>14.084307</v>
       </c>
       <c r="AU126" t="n">
-        <v>45699.786987</v>
+        <v>15876.862811</v>
       </c>
       <c r="AV126" t="n">
-        <v>2006.720175</v>
+        <v>203.191395</v>
       </c>
       <c r="AW126" t="n">
-        <v>1895.990769</v>
+        <v>139.860446</v>
       </c>
       <c r="AX126" t="n">
         <v>2253.868583</v>
@@ -16495,7 +16495,7 @@
         <v>1680.392882</v>
       </c>
       <c r="BE126" t="n">
-        <v>28055.10342</v>
+        <v>7081.375414</v>
       </c>
       <c r="BF126" t="n">
         <v>3575.13</v>
@@ -16504,7 +16504,7 @@
         <v>0</v>
       </c>
       <c r="BH126" t="n">
-        <v>72996.994296</v>
+        <v>8105.647395</v>
       </c>
       <c r="BI126" t="n">
         <v>1431.43342</v>
@@ -16543,7 +16543,7 @@
         <v>1537.880174</v>
       </c>
       <c r="BU126" t="n">
-        <v>37596.169109</v>
+        <v>14673.2988</v>
       </c>
       <c r="BV126" t="n">
         <v>30659.66</v>
@@ -16552,7 +16552,7 @@
         <v>0</v>
       </c>
       <c r="BX126" t="n">
-        <v>32641.966102</v>
+        <v>12291.010164</v>
       </c>
       <c r="BY126" t="n">
         <v>1018.485225</v>
@@ -16622,25 +16622,25 @@
         <v>599320.989756</v>
       </c>
       <c r="M127" t="n">
-        <v>46163786.360543</v>
+        <v>5756179.531723</v>
       </c>
       <c r="N127" t="n">
         <v>1379217.04</v>
       </c>
       <c r="O127" t="n">
-        <v>198396.565859</v>
+        <v>0</v>
       </c>
       <c r="P127" t="n">
-        <v>202496.605855</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>1119363.723531</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>1119363.7235</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
-        <v>44433475.204458</v>
+        <v>4787018.446913</v>
       </c>
       <c r="T127" t="n">
         <v>224379.205921</v>
@@ -16688,7 +16688,7 @@
         <v>0</v>
       </c>
       <c r="AI127" t="n">
-        <v>43932217.926845</v>
+        <v>7386942.523433</v>
       </c>
       <c r="AJ127" t="n">
         <v>0</v>
@@ -16697,10 +16697,10 @@
         <v>0</v>
       </c>
       <c r="AL127" t="n">
-        <v>1008046.852734</v>
+        <v>0</v>
       </c>
       <c r="AM127" t="n">
-        <v>1008046.852734</v>
+        <v>0</v>
       </c>
       <c r="AN127" t="n">
         <v>935788.259987</v>
@@ -16724,13 +16724,13 @@
         <v>6731.020815</v>
       </c>
       <c r="AU127" t="n">
-        <v>49720794.258341</v>
+        <v>7649049.396558</v>
       </c>
       <c r="AV127" t="n">
-        <v>1093668.360148</v>
+        <v>105367.166795</v>
       </c>
       <c r="AW127" t="n">
-        <v>1062755.389132</v>
+        <v>74430.44606</v>
       </c>
       <c r="AX127" t="n">
         <v>957265.761288</v>
@@ -16754,7 +16754,7 @@
         <v>1864964.101376</v>
       </c>
       <c r="BE127" t="n">
-        <v>55212774.349087</v>
+        <v>12249633.083994</v>
       </c>
       <c r="BF127" t="n">
         <v>4993804.19</v>
@@ -16763,7 +16763,7 @@
         <v>0</v>
       </c>
       <c r="BH127" t="n">
-        <v>53269263.364032</v>
+        <v>10726390.609955</v>
       </c>
       <c r="BI127" t="n">
         <v>1114825.793534</v>
@@ -16802,7 +16802,7 @@
         <v>1331775.645751</v>
       </c>
       <c r="BU127" t="n">
-        <v>29913762.411092</v>
+        <v>9993397.945873</v>
       </c>
       <c r="BV127" t="n">
         <v>28507000.73</v>
@@ -16811,7 +16811,7 @@
         <v>0</v>
       </c>
       <c r="BX127" t="n">
-        <v>28818943.872825</v>
+        <v>8590900.606996</v>
       </c>
       <c r="BY127" t="n">
         <v>612018.55275</v>
@@ -16881,25 +16881,25 @@
         <v>7491.512372</v>
       </c>
       <c r="M128" t="n">
-        <v>577047.329507</v>
+        <v>71952.244147</v>
       </c>
       <c r="N128" t="n">
         <v>17240.21</v>
       </c>
       <c r="O128" t="n">
-        <v>2479.957073</v>
+        <v>0</v>
       </c>
       <c r="P128" t="n">
-        <v>2531.207573</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>13992.046544</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>13992.0465</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
-        <v>555418.440056</v>
+        <v>59837.730586</v>
       </c>
       <c r="T128" t="n">
         <v>2804.740074</v>
@@ -16947,7 +16947,7 @@
         <v>0</v>
       </c>
       <c r="AI128" t="n">
-        <v>549152.724086</v>
+        <v>92336.781543</v>
       </c>
       <c r="AJ128" t="n">
         <v>0</v>
@@ -16956,10 +16956,10 @@
         <v>0</v>
       </c>
       <c r="AL128" t="n">
-        <v>12600.585659</v>
+        <v>0</v>
       </c>
       <c r="AM128" t="n">
-        <v>12600.585659</v>
+        <v>0</v>
       </c>
       <c r="AN128" t="n">
         <v>11697.35325</v>
@@ -16983,13 +16983,13 @@
         <v>84.13776</v>
       </c>
       <c r="AU128" t="n">
-        <v>621509.928229</v>
+        <v>95613.117457</v>
       </c>
       <c r="AV128" t="n">
-        <v>13670.854502</v>
+        <v>1317.089585</v>
       </c>
       <c r="AW128" t="n">
-        <v>13284.442364</v>
+        <v>930.380576</v>
       </c>
       <c r="AX128" t="n">
         <v>11965.822016</v>
@@ -17013,7 +17013,7 @@
         <v>23312.051267</v>
       </c>
       <c r="BE128" t="n">
-        <v>690159.679364</v>
+        <v>153120.41355</v>
       </c>
       <c r="BF128" t="n">
         <v>62422.55</v>
@@ -17022,7 +17022,7 @@
         <v>0</v>
       </c>
       <c r="BH128" t="n">
-        <v>665865.79205</v>
+        <v>134079.882624</v>
       </c>
       <c r="BI128" t="n">
         <v>13935.322419</v>
@@ -17061,7 +17061,7 @@
         <v>16647.195572</v>
       </c>
       <c r="BU128" t="n">
-        <v>373922.030139</v>
+        <v>124917.474323</v>
       </c>
       <c r="BV128" t="n">
         <v>356337.51</v>
@@ -17070,7 +17070,7 @@
         <v>0</v>
       </c>
       <c r="BX128" t="n">
-        <v>360236.79841</v>
+        <v>107386.257587</v>
       </c>
       <c r="BY128" t="n">
         <v>7650.231909</v>
@@ -17140,25 +17140,25 @@
         <v>65802.223146</v>
       </c>
       <c r="M129" t="n">
-        <v>5068535.598233</v>
+        <v>631997.571397</v>
       </c>
       <c r="N129" t="n">
         <v>181330.87</v>
       </c>
       <c r="O129" t="n">
-        <v>21782.87649</v>
+        <v>0</v>
       </c>
       <c r="P129" t="n">
-        <v>22233.038843</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>122900.119929</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>122900.1199</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
-        <v>4878556.734235</v>
+        <v>525588.893816</v>
       </c>
       <c r="T129" t="n">
         <v>29499.981657</v>
@@ -17206,7 +17206,7 @@
         <v>0</v>
       </c>
       <c r="AI129" t="n">
-        <v>4823521.379561</v>
+        <v>811046.582048</v>
       </c>
       <c r="AJ129" t="n">
         <v>0</v>
@@ -17215,10 +17215,10 @@
         <v>0</v>
       </c>
       <c r="AL129" t="n">
-        <v>110678.125877</v>
+        <v>0</v>
       </c>
       <c r="AM129" t="n">
-        <v>110678.125877</v>
+        <v>0</v>
       </c>
       <c r="AN129" t="n">
         <v>102744.520805</v>
@@ -17242,13 +17242,13 @@
         <v>739.029904</v>
       </c>
       <c r="AU129" t="n">
-        <v>5459075.945431</v>
+        <v>839824.507815</v>
       </c>
       <c r="AV129" t="n">
-        <v>120078.90715</v>
+        <v>11568.748534</v>
       </c>
       <c r="AW129" t="n">
-        <v>116684.829099</v>
+        <v>8172.062891</v>
       </c>
       <c r="AX129" t="n">
         <v>105102.635</v>
@@ -17272,7 +17272,7 @@
         <v>204763.033591</v>
       </c>
       <c r="BE129" t="n">
-        <v>6371925.58664</v>
+        <v>1413690.063487</v>
       </c>
       <c r="BF129" t="n">
         <v>656554.3</v>
@@ -17281,7 +17281,7 @@
         <v>0</v>
       </c>
       <c r="BH129" t="n">
-        <v>6147631.344599</v>
+        <v>1237897.634843</v>
       </c>
       <c r="BI129" t="n">
         <v>146570.357647</v>
@@ -17320,7 +17320,7 @@
         <v>146221.807211</v>
       </c>
       <c r="BU129" t="n">
-        <v>3888082.664651</v>
+        <v>1298905.727081</v>
       </c>
       <c r="BV129" t="n">
         <v>3747923.05</v>
@@ -17329,7 +17329,7 @@
         <v>0</v>
       </c>
       <c r="BX129" t="n">
-        <v>3745782.110108</v>
+        <v>1116614.194656</v>
       </c>
       <c r="BY129" t="n">
         <v>80464.390655</v>
@@ -17399,25 +17399,25 @@
         <v>987033.347185</v>
       </c>
       <c r="M130" t="n">
-        <v>76028033.973498</v>
+        <v>9479963.570956999</v>
       </c>
       <c r="N130" t="n">
         <v>2719963.1</v>
       </c>
       <c r="O130" t="n">
-        <v>326743.147356</v>
+        <v>0</v>
       </c>
       <c r="P130" t="n">
-        <v>333495.582647</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>1843501.798935</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>1843501.7989</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
-        <v>73178351.013524</v>
+        <v>7883833.407234</v>
       </c>
       <c r="T130" t="n">
         <v>442499.72486</v>
@@ -17465,7 +17465,7 @@
         <v>0</v>
       </c>
       <c r="AI130" t="n">
-        <v>72352820.69341201</v>
+        <v>12165698.730723</v>
       </c>
       <c r="AJ130" t="n">
         <v>0</v>
@@ -17474,10 +17474,10 @@
         <v>0</v>
       </c>
       <c r="AL130" t="n">
-        <v>1660171.888155</v>
+        <v>0</v>
       </c>
       <c r="AM130" t="n">
-        <v>1660171.888155</v>
+        <v>0</v>
       </c>
       <c r="AN130" t="n">
         <v>1541167.812073</v>
@@ -17501,13 +17501,13 @@
         <v>11085.448563</v>
       </c>
       <c r="AU130" t="n">
-        <v>81886139.181458</v>
+        <v>12597367.617218</v>
       </c>
       <c r="AV130" t="n">
-        <v>1801183.607248</v>
+        <v>173531.228011</v>
       </c>
       <c r="AW130" t="n">
-        <v>1750272.436481</v>
+        <v>122580.943372</v>
       </c>
       <c r="AX130" t="n">
         <v>1576539.524996</v>
@@ -17531,7 +17531,7 @@
         <v>3071445.503871</v>
       </c>
       <c r="BE130" t="n">
-        <v>95578883.799597</v>
+        <v>21205350.952304</v>
       </c>
       <c r="BF130" t="n">
         <v>9848314.48</v>
@@ -17540,7 +17540,7 @@
         <v>0</v>
       </c>
       <c r="BH130" t="n">
-        <v>92214470.168988</v>
+        <v>18568464.522648</v>
       </c>
       <c r="BI130" t="n">
         <v>2198555.36471</v>
@@ -17579,7 +17579,7 @@
         <v>2193327.108168</v>
       </c>
       <c r="BU130" t="n">
-        <v>58321239.969765</v>
+        <v>19483585.906214</v>
       </c>
       <c r="BV130" t="n">
         <v>56218845.81</v>
@@ -17588,7 +17588,7 @@
         <v>0</v>
       </c>
       <c r="BX130" t="n">
-        <v>56186731.651615</v>
+        <v>16749212.919845</v>
       </c>
       <c r="BY130" t="n">
         <v>1206965.859827</v>
@@ -17658,25 +17658,25 @@
         <v>73293.735518</v>
       </c>
       <c r="M131" t="n">
-        <v>5645582.92774</v>
+        <v>703949.815544</v>
       </c>
       <c r="N131" t="n">
         <v>198571.09</v>
       </c>
       <c r="O131" t="n">
-        <v>24262.833564</v>
+        <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>24764.246416</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>136892.166473</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>136892.1665</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
-        <v>5433975.174291</v>
+        <v>585426.624402</v>
       </c>
       <c r="T131" t="n">
         <v>32304.721731</v>
@@ -17724,7 +17724,7 @@
         <v>0</v>
       </c>
       <c r="AI131" t="n">
-        <v>5372674.103646</v>
+        <v>903383.363591</v>
       </c>
       <c r="AJ131" t="n">
         <v>0</v>
@@ -17733,10 +17733,10 @@
         <v>0</v>
       </c>
       <c r="AL131" t="n">
-        <v>123278.711536</v>
+        <v>0</v>
       </c>
       <c r="AM131" t="n">
-        <v>123278.711536</v>
+        <v>0</v>
       </c>
       <c r="AN131" t="n">
         <v>114441.874055</v>
@@ -17760,13 +17760,13 @@
         <v>823.1676639999999</v>
       </c>
       <c r="AU131" t="n">
-        <v>6080585.87366</v>
+        <v>935437.625271</v>
       </c>
       <c r="AV131" t="n">
-        <v>133749.761652</v>
+        <v>12885.838119</v>
       </c>
       <c r="AW131" t="n">
-        <v>129969.271463</v>
+        <v>9102.443466999999</v>
       </c>
       <c r="AX131" t="n">
         <v>117068.457016</v>
@@ -17790,7 +17790,7 @@
         <v>228075.084859</v>
       </c>
       <c r="BE131" t="n">
-        <v>7062085.266003</v>
+        <v>1566810.477037</v>
       </c>
       <c r="BF131" t="n">
         <v>718976.85</v>
@@ -17799,7 +17799,7 @@
         <v>0</v>
       </c>
       <c r="BH131" t="n">
-        <v>6813497.13665</v>
+        <v>1371977.517468</v>
       </c>
       <c r="BI131" t="n">
         <v>160505.680067</v>
@@ -17838,7 +17838,7 @@
         <v>162869.002783</v>
       </c>
       <c r="BU131" t="n">
-        <v>4262004.69479</v>
+        <v>1423823.201404</v>
       </c>
       <c r="BV131" t="n">
         <v>4104260.56</v>
@@ -17847,7 +17847,7 @@
         <v>0</v>
       </c>
       <c r="BX131" t="n">
-        <v>4106018.908518</v>
+        <v>1224000.452244</v>
       </c>
       <c r="BY131" t="n">
         <v>88114.622564</v>
@@ -17941,16 +17941,16 @@
         <v>0</v>
       </c>
       <c r="O133" t="n">
-        <v>20079.607254</v>
+        <v>10678.15847</v>
       </c>
       <c r="P133" t="n">
-        <v>19369.56684</v>
+        <v>10041.564473</v>
       </c>
       <c r="Q133" t="n">
-        <v>10808.023212</v>
+        <v>1203.985643</v>
       </c>
       <c r="R133" t="n">
-        <v>10808.0232</v>
+        <v>1203.9856</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -18004,16 +18004,16 @@
         <v>0</v>
       </c>
       <c r="AJ133" t="n">
-        <v>17980.454724</v>
+        <v>9413.574549999999</v>
       </c>
       <c r="AK133" t="n">
-        <v>17336.217906</v>
+        <v>8823.263747000001</v>
       </c>
       <c r="AL133" t="n">
-        <v>10476.573704</v>
+        <v>1413.32409</v>
       </c>
       <c r="AM133" t="n">
-        <v>10476.573704</v>
+        <v>1413.32409</v>
       </c>
       <c r="AN133" t="n">
         <v>0</v>
@@ -18040,10 +18040,10 @@
         <v>0</v>
       </c>
       <c r="AV133" t="n">
-        <v>22575.750533</v>
+        <v>13022.395074</v>
       </c>
       <c r="AW133" t="n">
-        <v>21821.719703</v>
+        <v>12307.092438</v>
       </c>
       <c r="AX133" t="n">
         <v>0</v>
@@ -18073,7 +18073,7 @@
         <v>0</v>
       </c>
       <c r="BG133" t="n">
-        <v>14170.232223</v>
+        <v>7703.974632</v>
       </c>
       <c r="BH133" t="n">
         <v>0</v>
@@ -18121,7 +18121,7 @@
         <v>0</v>
       </c>
       <c r="BW133" t="n">
-        <v>59363.867391</v>
+        <v>36483.755345</v>
       </c>
       <c r="BX133" t="n">
         <v>0</v>
@@ -18200,16 +18200,16 @@
         <v>0</v>
       </c>
       <c r="O134" t="n">
-        <v>3411525.272478</v>
+        <v>1814219.124081</v>
       </c>
       <c r="P134" t="n">
-        <v>3290889.406101</v>
+        <v>1706061.803973</v>
       </c>
       <c r="Q134" t="n">
-        <v>1836283.143658</v>
+        <v>204557.160707</v>
       </c>
       <c r="R134" t="n">
-        <v>1836283.1437</v>
+        <v>204557.1607</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -18263,16 +18263,16 @@
         <v>0</v>
       </c>
       <c r="AJ134" t="n">
-        <v>3054879.25763</v>
+        <v>1599366.316082</v>
       </c>
       <c r="AK134" t="n">
-        <v>2945423.422236</v>
+        <v>1499072.510606</v>
       </c>
       <c r="AL134" t="n">
-        <v>1779969.872308</v>
+        <v>240123.762918</v>
       </c>
       <c r="AM134" t="n">
-        <v>1779969.872308</v>
+        <v>240123.762918</v>
       </c>
       <c r="AN134" t="n">
         <v>0</v>
@@ -18299,10 +18299,10 @@
         <v>0</v>
       </c>
       <c r="AV134" t="n">
-        <v>3835620.015473</v>
+        <v>2212504.923085</v>
       </c>
       <c r="AW134" t="n">
-        <v>3707510.17751</v>
+        <v>2090975.005151</v>
       </c>
       <c r="AX134" t="n">
         <v>0</v>
@@ -18332,7 +18332,7 @@
         <v>0</v>
       </c>
       <c r="BG134" t="n">
-        <v>1662168.239784</v>
+        <v>903676.224324</v>
       </c>
       <c r="BH134" t="n">
         <v>0</v>
@@ -18380,7 +18380,7 @@
         <v>0</v>
       </c>
       <c r="BW134" t="n">
-        <v>5520839.667322</v>
+        <v>3392989.247092</v>
       </c>
       <c r="BX134" t="n">
         <v>0</v>
@@ -18530,10 +18530,10 @@
         <v>172379.203605</v>
       </c>
       <c r="Q139" t="n">
-        <v>722837.078035</v>
+        <v>646077.262577</v>
       </c>
       <c r="R139" t="n">
-        <v>722837.078</v>
+        <v>646077.2626</v>
       </c>
       <c r="W139" t="n">
         <v>366198.857555</v>
@@ -18551,10 +18551,10 @@
         <v>160382.706654</v>
       </c>
       <c r="AL139" t="n">
-        <v>671705.2407279999</v>
+        <v>596044.89147</v>
       </c>
       <c r="AM139" t="n">
-        <v>671705.2407279999</v>
+        <v>596044.89147</v>
       </c>
       <c r="AQ139" t="n">
         <v>170688.692364</v>
@@ -18609,10 +18609,10 @@
         <v>861896.018025</v>
       </c>
       <c r="Q140" t="n">
-        <v>3614185.390177</v>
+        <v>3230386.312887</v>
       </c>
       <c r="R140" t="n">
-        <v>3614185.3902</v>
+        <v>3230386.3129</v>
       </c>
       <c r="W140" t="n">
         <v>1830994.287775</v>
@@ -18630,10 +18630,10 @@
         <v>801913.533271</v>
       </c>
       <c r="AL140" t="n">
-        <v>3358526.20364</v>
+        <v>2980224.45735</v>
       </c>
       <c r="AM140" t="n">
-        <v>3358526.20364</v>
+        <v>2980224.45735</v>
       </c>
       <c r="AQ140" t="n">
         <v>853443.46182</v>
@@ -19213,25 +19213,25 @@
         <v>5773.243676</v>
       </c>
       <c r="M146" t="n">
-        <v>46979.275255</v>
+        <v>23597.541638</v>
       </c>
       <c r="N146" t="n">
         <v>20576.63</v>
       </c>
       <c r="O146" t="n">
-        <v>23547.577654</v>
+        <v>14601.808147</v>
       </c>
       <c r="P146" t="n">
-        <v>22755.975103</v>
+        <v>13778.952139</v>
       </c>
       <c r="Q146" t="n">
-        <v>14958.811308</v>
+        <v>5087.675257</v>
       </c>
       <c r="R146" t="n">
-        <v>14958.8113</v>
+        <v>5087.6753</v>
       </c>
       <c r="S146" t="n">
-        <v>45412.697747</v>
+        <v>22332.730539</v>
       </c>
       <c r="T146" t="n">
         <v>13382.7568</v>
@@ -19279,19 +19279,19 @@
         <v>283.457423</v>
       </c>
       <c r="AI146" t="n">
-        <v>15555.847006</v>
+        <v>22951.623187</v>
       </c>
       <c r="AJ146" t="n">
-        <v>16539.146588</v>
+        <v>9495.474756</v>
       </c>
       <c r="AK146" t="n">
-        <v>16066.631685</v>
+        <v>8986.464830999999</v>
       </c>
       <c r="AL146" t="n">
-        <v>10492.940804</v>
+        <v>2525.358567</v>
       </c>
       <c r="AM146" t="n">
-        <v>10492.940804</v>
+        <v>2525.358567</v>
       </c>
       <c r="AN146" t="n">
         <v>6088.652104</v>
@@ -19315,13 +19315,13 @@
         <v>4347.211764</v>
       </c>
       <c r="AU146" t="n">
-        <v>34004.494511</v>
+        <v>19490.164122</v>
       </c>
       <c r="AV146" t="n">
-        <v>30640.064719</v>
+        <v>18606.765314</v>
       </c>
       <c r="AW146" t="n">
-        <v>29549.932865</v>
+        <v>17549.998168</v>
       </c>
       <c r="AX146" t="n">
         <v>5440.911819</v>
@@ -19345,7 +19345,7 @@
         <v>887.65664</v>
       </c>
       <c r="BE146" t="n">
-        <v>10421.126353</v>
+        <v>6252.282449</v>
       </c>
       <c r="BF146" t="n">
         <v>2216.85</v>
@@ -19354,7 +19354,7 @@
         <v>0</v>
       </c>
       <c r="BH146" t="n">
-        <v>10054.29868</v>
+        <v>5421.105945</v>
       </c>
       <c r="BI146" t="n">
         <v>143.580822</v>
@@ -19393,7 +19393,7 @@
         <v>0</v>
       </c>
       <c r="BU146" t="n">
-        <v>15053.337619</v>
+        <v>0</v>
       </c>
       <c r="BV146" t="n">
         <v>16709.88</v>
@@ -19402,7 +19402,7 @@
         <v>0</v>
       </c>
       <c r="BX146" t="n">
-        <v>14516.975547</v>
+        <v>0</v>
       </c>
       <c r="BY146" t="n">
         <v>0</v>
@@ -19472,25 +19472,25 @@
         <v>7442.126773</v>
       </c>
       <c r="M147" t="n">
-        <v>60559.668312</v>
+        <v>30418.930194</v>
       </c>
       <c r="N147" t="n">
         <v>26524.76</v>
       </c>
       <c r="O147" t="n">
-        <v>30354.523022</v>
+        <v>18822.782032</v>
       </c>
       <c r="P147" t="n">
-        <v>29334.090338</v>
+        <v>17762.061392</v>
       </c>
       <c r="Q147" t="n">
-        <v>19282.984811</v>
+        <v>6558.379719</v>
       </c>
       <c r="R147" t="n">
-        <v>19282.9848</v>
+        <v>6558.3797</v>
       </c>
       <c r="S147" t="n">
-        <v>58540.237111</v>
+        <v>28788.497622</v>
       </c>
       <c r="T147" t="n">
         <v>17251.337073</v>
@@ -19538,19 +19538,19 @@
         <v>344.012999</v>
       </c>
       <c r="AI147" t="n">
-        <v>18879.073713</v>
+        <v>27854.824351</v>
       </c>
       <c r="AJ147" t="n">
-        <v>20072.437552</v>
+        <v>11524.012019</v>
       </c>
       <c r="AK147" t="n">
-        <v>19498.978345</v>
+        <v>10906.261286</v>
       </c>
       <c r="AL147" t="n">
-        <v>12734.568733</v>
+        <v>3064.855969</v>
       </c>
       <c r="AM147" t="n">
-        <v>12734.568733</v>
+        <v>3064.855969</v>
       </c>
       <c r="AN147" t="n">
         <v>7389.383031</v>
@@ -19574,13 +19574,13 @@
         <v>5532.670329</v>
       </c>
       <c r="AU147" t="n">
-        <v>43277.316137</v>
+        <v>24805.014938</v>
       </c>
       <c r="AV147" t="n">
-        <v>38995.426527</v>
+        <v>23680.718574</v>
       </c>
       <c r="AW147" t="n">
-        <v>37608.022258</v>
+        <v>22335.777368</v>
       </c>
       <c r="AX147" t="n">
         <v>6924.615827</v>
@@ -19604,7 +19604,7 @@
         <v>971.697307</v>
       </c>
       <c r="BE147" t="n">
-        <v>11407.767333</v>
+        <v>6844.229795</v>
       </c>
       <c r="BF147" t="n">
         <v>2426.74</v>
@@ -19613,7 +19613,7 @@
         <v>0</v>
       </c>
       <c r="BH147" t="n">
-        <v>11006.209516</v>
+        <v>5934.359993</v>
       </c>
       <c r="BI147" t="n">
         <v>157.174623</v>
@@ -19652,7 +19652,7 @@
         <v>0</v>
       </c>
       <c r="BU147" t="n">
-        <v>26432.095311</v>
+        <v>0</v>
       </c>
       <c r="BV147" t="n">
         <v>29340.81</v>
@@ -19661,7 +19661,7 @@
         <v>0</v>
       </c>
       <c r="BX147" t="n">
-        <v>25490.299294</v>
+        <v>0</v>
       </c>
       <c r="BY147" t="n">
         <v>0</v>
@@ -19731,25 +19731,25 @@
         <v>6350568.044119</v>
       </c>
       <c r="M148" t="n">
-        <v>51677202.780843</v>
+        <v>25957295.801546</v>
       </c>
       <c r="N148" t="n">
         <v>22634292.91</v>
       </c>
       <c r="O148" t="n">
-        <v>25902335.419794</v>
+        <v>16061988.961785</v>
       </c>
       <c r="P148" t="n">
-        <v>25031572.613662</v>
+        <v>15156847.353388</v>
       </c>
       <c r="Q148" t="n">
-        <v>16454692.438932</v>
+        <v>5596442.782837</v>
       </c>
       <c r="R148" t="n">
-        <v>16454692.4389</v>
+        <v>5596442.7828</v>
       </c>
       <c r="S148" t="n">
-        <v>49953967.522182</v>
+        <v>24566003.593139</v>
       </c>
       <c r="T148" t="n">
         <v>14721032.479714</v>
@@ -19797,19 +19797,19 @@
         <v>311803.164965</v>
       </c>
       <c r="AI148" t="n">
-        <v>17111431.706516</v>
+        <v>25246785.505315</v>
       </c>
       <c r="AJ148" t="n">
-        <v>18193061.247268</v>
+        <v>10445022.231097</v>
       </c>
       <c r="AK148" t="n">
-        <v>17673294.85365</v>
+        <v>9885111.314325999</v>
       </c>
       <c r="AL148" t="n">
-        <v>11542234.884023</v>
+        <v>2777894.424207</v>
       </c>
       <c r="AM148" t="n">
-        <v>11542234.884023</v>
+        <v>2777894.424207</v>
       </c>
       <c r="AN148" t="n">
         <v>6697517.314799</v>
@@ -19833,13 +19833,13 @@
         <v>4781932.940177</v>
       </c>
       <c r="AU148" t="n">
-        <v>37404943.961844</v>
+        <v>21439180.534625</v>
       </c>
       <c r="AV148" t="n">
-        <v>33704071.190818</v>
+        <v>20467441.844984</v>
       </c>
       <c r="AW148" t="n">
-        <v>32504926.151908</v>
+        <v>19304997.984284</v>
       </c>
       <c r="AX148" t="n">
         <v>5985003.001345</v>
@@ -19863,7 +19863,7 @@
         <v>976422.303565</v>
       </c>
       <c r="BE148" t="n">
-        <v>11463238.988581</v>
+        <v>6877510.694386</v>
       </c>
       <c r="BF148" t="n">
         <v>2438537.43</v>
@@ -19872,7 +19872,7 @@
         <v>0</v>
       </c>
       <c r="BH148" t="n">
-        <v>11059728.548084</v>
+        <v>5963216.54</v>
       </c>
       <c r="BI148" t="n">
         <v>157938.903812</v>
@@ -19911,7 +19911,7 @@
         <v>0</v>
       </c>
       <c r="BU148" t="n">
-        <v>16558671.380361</v>
+        <v>0</v>
       </c>
       <c r="BV148" t="n">
         <v>18380869.14</v>
@@ -19920,7 +19920,7 @@
         <v>0</v>
       </c>
       <c r="BX148" t="n">
-        <v>15968673.101179</v>
+        <v>0</v>
       </c>
       <c r="BY148" t="n">
         <v>0</v>
@@ -19990,25 +19990,25 @@
         <v>102994.667188</v>
       </c>
       <c r="M149" t="n">
-        <v>838110.2705550001</v>
+        <v>420980.142818</v>
       </c>
       <c r="N149" t="n">
         <v>367087.08</v>
       </c>
       <c r="O149" t="n">
-        <v>420088.785354</v>
+        <v>260496.257344</v>
       </c>
       <c r="P149" t="n">
-        <v>405966.595843</v>
+        <v>245816.506168</v>
       </c>
       <c r="Q149" t="n">
-        <v>266865.193737</v>
+        <v>90764.12658700001</v>
       </c>
       <c r="R149" t="n">
-        <v>266865.1937</v>
+        <v>90764.1266</v>
       </c>
       <c r="S149" t="n">
-        <v>810162.527814</v>
+        <v>398415.91282</v>
       </c>
       <c r="T149" t="n">
         <v>238748.381307</v>
@@ -20056,19 +20056,19 @@
         <v>5056.880421</v>
       </c>
       <c r="AI149" t="n">
-        <v>277516.310586</v>
+        <v>409456.95765</v>
       </c>
       <c r="AJ149" t="n">
-        <v>295058.375138</v>
+        <v>169399.269639</v>
       </c>
       <c r="AK149" t="n">
-        <v>286628.709263</v>
+        <v>160318.532589</v>
       </c>
       <c r="AL149" t="n">
-        <v>187194.063937</v>
+        <v>45052.396844</v>
       </c>
       <c r="AM149" t="n">
-        <v>187194.063937</v>
+        <v>45052.396844</v>
       </c>
       <c r="AN149" t="n">
         <v>108621.553542</v>
@@ -20092,13 +20092,13 @@
         <v>77554.257866</v>
       </c>
       <c r="AU149" t="n">
-        <v>606640.182072</v>
+        <v>347704.527943</v>
       </c>
       <c r="AV149" t="n">
-        <v>546618.754586</v>
+        <v>331944.693195</v>
       </c>
       <c r="AW149" t="n">
-        <v>527170.802318</v>
+        <v>313091.967309</v>
       </c>
       <c r="AX149" t="n">
         <v>97065.86685799999</v>
@@ -20122,7 +20122,7 @@
         <v>15835.794451</v>
       </c>
       <c r="BE149" t="n">
-        <v>185912.894142</v>
+        <v>111540.718898</v>
       </c>
       <c r="BF149" t="n">
         <v>39548.64</v>
@@ -20131,7 +20131,7 @@
         <v>0</v>
       </c>
       <c r="BH149" t="n">
-        <v>179368.688453</v>
+        <v>96712.530067</v>
       </c>
       <c r="BI149" t="n">
         <v>2561.481858</v>
@@ -20170,7 +20170,7 @@
         <v>0</v>
       </c>
       <c r="BU149" t="n">
-        <v>268551.543114</v>
+        <v>0</v>
       </c>
       <c r="BV149" t="n">
         <v>298104.28</v>
@@ -20179,7 +20179,7 @@
         <v>0</v>
       </c>
       <c r="BX149" t="n">
-        <v>258982.84375</v>
+        <v>0</v>
       </c>
       <c r="BY149" t="n">
         <v>0</v>
@@ -20508,25 +20508,25 @@
         <v>468820.773373</v>
       </c>
       <c r="M151" t="n">
-        <v>3814988.833307</v>
+        <v>1916256.846287</v>
       </c>
       <c r="N151" t="n">
         <v>1654584.21</v>
       </c>
       <c r="O151" t="n">
-        <v>1912199.481891</v>
+        <v>1185751.264243</v>
       </c>
       <c r="P151" t="n">
-        <v>1847916.776886</v>
+        <v>1118930.597822</v>
       </c>
       <c r="Q151" t="n">
-        <v>1214741.98548</v>
+        <v>413148.653059</v>
       </c>
       <c r="R151" t="n">
-        <v>1214741.9855</v>
+        <v>413148.6531</v>
       </c>
       <c r="S151" t="n">
-        <v>3687773.680103</v>
+        <v>1813546.870644</v>
       </c>
       <c r="T151" t="n">
         <v>1076118.788497</v>
@@ -20574,19 +20574,19 @@
         <v>23018.381966</v>
       </c>
       <c r="AI151" t="n">
-        <v>1263224.736817</v>
+        <v>1863804.53269</v>
       </c>
       <c r="AJ151" t="n">
-        <v>1343074.349367</v>
+        <v>771087.462769</v>
       </c>
       <c r="AK151" t="n">
-        <v>1304703.406652</v>
+        <v>729752.913293</v>
       </c>
       <c r="AL151" t="n">
-        <v>852087.474252</v>
+        <v>205073.719903</v>
       </c>
       <c r="AM151" t="n">
-        <v>852087.474252</v>
+        <v>205073.719903</v>
       </c>
       <c r="AN151" t="n">
         <v>494433.761734</v>
@@ -20610,13 +20610,13 @@
         <v>353018.735278</v>
       </c>
       <c r="AU151" t="n">
-        <v>2761361.603299</v>
+        <v>1582714.038949</v>
       </c>
       <c r="AV151" t="n">
-        <v>2488150.447602</v>
+        <v>1510976.946955</v>
       </c>
       <c r="AW151" t="n">
-        <v>2399625.436828</v>
+        <v>1425161.343376</v>
       </c>
       <c r="AX151" t="n">
         <v>441833.504694</v>
@@ -20640,7 +20640,7 @@
         <v>72082.85248099999</v>
       </c>
       <c r="BE151" t="n">
-        <v>913843.791499</v>
+        <v>548271.780366</v>
       </c>
       <c r="BF151" t="n">
         <v>178258.96</v>
@@ -20649,7 +20649,7 @@
         <v>0</v>
       </c>
       <c r="BH151" t="n">
-        <v>881676.137032</v>
+        <v>475384.698676</v>
       </c>
       <c r="BI151" t="n">
         <v>11545.455257</v>
@@ -20688,7 +20688,7 @@
         <v>0</v>
       </c>
       <c r="BU151" t="n">
-        <v>1577782.09049</v>
+        <v>0</v>
       </c>
       <c r="BV151" t="n">
         <v>1343655.66</v>
@@ -20697,7 +20697,7 @@
         <v>0</v>
       </c>
       <c r="BX151" t="n">
-        <v>1521564.493261</v>
+        <v>0</v>
       </c>
       <c r="BY151" t="n">
         <v>0</v>
@@ -20767,25 +20767,25 @@
         <v>11720519.334326</v>
       </c>
       <c r="M152" t="n">
-        <v>95374720.832683</v>
+        <v>47906421.157176</v>
       </c>
       <c r="N152" t="n">
         <v>41364605.19</v>
       </c>
       <c r="O152" t="n">
-        <v>47804987.047271</v>
+        <v>29643781.60607</v>
       </c>
       <c r="P152" t="n">
-        <v>46197919.422141</v>
+        <v>27973264.945541</v>
       </c>
       <c r="Q152" t="n">
-        <v>30368549.63699</v>
+        <v>10328716.326477</v>
       </c>
       <c r="R152" t="n">
-        <v>30368549.637</v>
+        <v>10328716.3265</v>
       </c>
       <c r="S152" t="n">
-        <v>92194342.00256699</v>
+        <v>45338671.766091</v>
       </c>
       <c r="T152" t="n">
         <v>26902969.712423</v>
@@ -20833,19 +20833,19 @@
         <v>575459.549143</v>
       </c>
       <c r="AI152" t="n">
-        <v>31580618.420421</v>
+        <v>46595113.317253</v>
       </c>
       <c r="AJ152" t="n">
-        <v>33576858.734183</v>
+        <v>19277186.569226</v>
       </c>
       <c r="AK152" t="n">
-        <v>32617585.166306</v>
+        <v>18243822.832325</v>
       </c>
       <c r="AL152" t="n">
-        <v>21302186.85631</v>
+        <v>5126842.997579</v>
       </c>
       <c r="AM152" t="n">
-        <v>21302186.85631</v>
+        <v>5126842.997579</v>
       </c>
       <c r="AN152" t="n">
         <v>12360844.043359</v>
@@ -20869,13 +20869,13 @@
         <v>8825468.381951001</v>
       </c>
       <c r="AU152" t="n">
-        <v>69034040.082478</v>
+        <v>39567850.973725</v>
       </c>
       <c r="AV152" t="n">
-        <v>62203761.190046</v>
+        <v>37774423.673878</v>
       </c>
       <c r="AW152" t="n">
-        <v>59990635.920689</v>
+        <v>35629033.584403</v>
       </c>
       <c r="AX152" t="n">
         <v>11045837.617351</v>
@@ -20899,7 +20899,7 @@
         <v>1802071.31203</v>
       </c>
       <c r="BE152" t="n">
-        <v>22846094.787465</v>
+        <v>13706794.50915</v>
       </c>
       <c r="BF152" t="n">
         <v>4456474.01</v>
@@ -20908,7 +20908,7 @@
         <v>0</v>
       </c>
       <c r="BH152" t="n">
-        <v>22041903.425801</v>
+        <v>11884617.466908</v>
       </c>
       <c r="BI152" t="n">
         <v>288636.381418</v>
@@ -20947,7 +20947,7 @@
         <v>0</v>
       </c>
       <c r="BU152" t="n">
-        <v>39444552.26225</v>
+        <v>0</v>
       </c>
       <c r="BV152" t="n">
         <v>33591391.53</v>
@@ -20956,7 +20956,7 @@
         <v>0</v>
       </c>
       <c r="BX152" t="n">
-        <v>38039112.331517</v>
+        <v>0</v>
       </c>
       <c r="BY152" t="n">
         <v>0</v>
@@ -21026,25 +21026,25 @@
         <v>571815.440561</v>
       </c>
       <c r="M153" t="n">
-        <v>4653099.103862</v>
+        <v>2337236.989105</v>
       </c>
       <c r="N153" t="n">
         <v>2021671.29</v>
       </c>
       <c r="O153" t="n">
-        <v>2332288.267245</v>
+        <v>1446247.521587</v>
       </c>
       <c r="P153" t="n">
-        <v>2253883.372729</v>
+        <v>1364747.103989</v>
       </c>
       <c r="Q153" t="n">
-        <v>1481607.179216</v>
+        <v>503912.779646</v>
       </c>
       <c r="R153" t="n">
-        <v>1481607.1792</v>
+        <v>503912.7796</v>
       </c>
       <c r="S153" t="n">
-        <v>4497936.207917</v>
+        <v>2211962.783463</v>
       </c>
       <c r="T153" t="n">
         <v>1314867.169804</v>
@@ -21092,19 +21092,19 @@
         <v>28075.262387</v>
       </c>
       <c r="AI153" t="n">
-        <v>1540741.047403</v>
+        <v>2273261.49034</v>
       </c>
       <c r="AJ153" t="n">
-        <v>1638132.724505</v>
+        <v>940486.732408</v>
       </c>
       <c r="AK153" t="n">
-        <v>1591332.115915</v>
+        <v>890071.445882</v>
       </c>
       <c r="AL153" t="n">
-        <v>1039281.53819</v>
+        <v>250126.116747</v>
       </c>
       <c r="AM153" t="n">
-        <v>1039281.53819</v>
+        <v>250126.116747</v>
       </c>
       <c r="AN153" t="n">
         <v>603055.315276</v>
@@ -21128,13 +21128,13 @@
         <v>430572.993144</v>
       </c>
       <c r="AU153" t="n">
-        <v>3368001.785371</v>
+        <v>1930418.566892</v>
       </c>
       <c r="AV153" t="n">
-        <v>3034769.202187</v>
+        <v>1842921.64015</v>
       </c>
       <c r="AW153" t="n">
-        <v>2926796.239146</v>
+        <v>1738253.310685</v>
       </c>
       <c r="AX153" t="n">
         <v>538899.3715520001</v>
@@ -21158,7 +21158,7 @@
         <v>87918.646932</v>
       </c>
       <c r="BE153" t="n">
-        <v>1099756.685641</v>
+        <v>659812.499264</v>
       </c>
       <c r="BF153" t="n">
         <v>217807.6</v>
@@ -21167,7 +21167,7 @@
         <v>0</v>
       </c>
       <c r="BH153" t="n">
-        <v>1061044.825485</v>
+        <v>572097.228743</v>
       </c>
       <c r="BI153" t="n">
         <v>14106.937115</v>
@@ -21206,7 +21206,7 @@
         <v>0</v>
       </c>
       <c r="BU153" t="n">
-        <v>1846333.633604</v>
+        <v>0</v>
       </c>
       <c r="BV153" t="n">
         <v>1641759.94</v>
@@ -21215,7 +21215,7 @@
         <v>0</v>
       </c>
       <c r="BX153" t="n">
-        <v>1780547.337011</v>
+        <v>0</v>
       </c>
       <c r="BY153" t="n">
         <v>0</v>
@@ -21553,25 +21553,25 @@
         <v>11825.413354</v>
       </c>
       <c r="M156" t="n">
-        <v>86142.944064</v>
+        <v>50163.499202</v>
       </c>
       <c r="N156" t="n">
         <v>41983.29</v>
       </c>
       <c r="O156" t="n">
-        <v>70504.772773</v>
+        <v>44310.948955</v>
       </c>
       <c r="P156" t="n">
-        <v>68226.619223</v>
+        <v>41997.49111</v>
       </c>
       <c r="Q156" t="n">
-        <v>52784.175585</v>
+        <v>30319.794438</v>
       </c>
       <c r="R156" t="n">
-        <v>52784.1756</v>
+        <v>30319.7944</v>
       </c>
       <c r="S156" t="n">
-        <v>83255.358091</v>
+        <v>47410.823364</v>
       </c>
       <c r="T156" t="n">
         <v>28657.697116</v>
@@ -21619,19 +21619,19 @@
         <v>7204.805671</v>
       </c>
       <c r="AI156" t="n">
-        <v>114387.349601</v>
+        <v>46505.85139</v>
       </c>
       <c r="AJ156" t="n">
-        <v>67688.12609000001</v>
+        <v>42851.914537</v>
       </c>
       <c r="AK156" t="n">
-        <v>65405.090437</v>
+        <v>40585.68184</v>
       </c>
       <c r="AL156" t="n">
-        <v>50484.132446</v>
+        <v>29092.526152</v>
       </c>
       <c r="AM156" t="n">
-        <v>50484.132446</v>
+        <v>29092.526152</v>
       </c>
       <c r="AN156" t="n">
         <v>12398.277443</v>
@@ -21655,13 +21655,13 @@
         <v>10148.750358</v>
       </c>
       <c r="AU156" t="n">
-        <v>104715.835561</v>
+        <v>64356.098976</v>
       </c>
       <c r="AV156" t="n">
-        <v>69259.31295799999</v>
+        <v>42843.621977</v>
       </c>
       <c r="AW156" t="n">
-        <v>67061.961568</v>
+        <v>40584.21964</v>
       </c>
       <c r="AX156" t="n">
         <v>17106.1625</v>
@@ -21685,16 +21685,16 @@
         <v>5929.143624</v>
       </c>
       <c r="BE156" t="n">
-        <v>51546.328601</v>
+        <v>25012.672173</v>
       </c>
       <c r="BF156" t="n">
         <v>21014.06</v>
       </c>
       <c r="BG156" t="n">
-        <v>32034.103662</v>
+        <v>19697.360036</v>
       </c>
       <c r="BH156" t="n">
-        <v>49731.877922</v>
+        <v>23675.782114</v>
       </c>
       <c r="BI156" t="n">
         <v>14316.421651</v>
@@ -21733,16 +21733,16 @@
         <v>16811.263308</v>
       </c>
       <c r="BU156" t="n">
-        <v>116036.466432</v>
+        <v>71313.51508100001</v>
       </c>
       <c r="BV156" t="n">
         <v>116036.47</v>
       </c>
       <c r="BW156" t="n">
-        <v>32476.166853</v>
+        <v>19959.153238</v>
       </c>
       <c r="BX156" t="n">
-        <v>112123.202944</v>
+        <v>67400.25159299999</v>
       </c>
       <c r="BY156" t="n">
         <v>39848.242216</v>
@@ -21812,25 +21812,25 @@
         <v>34524.554445</v>
       </c>
       <c r="M157" t="n">
-        <v>251496.220339</v>
+        <v>146453.439516</v>
       </c>
       <c r="N157" t="n">
         <v>122571.14</v>
       </c>
       <c r="O157" t="n">
-        <v>205840.235217</v>
+        <v>129366.790316</v>
       </c>
       <c r="P157" t="n">
-        <v>199189.115809</v>
+        <v>122612.59924</v>
       </c>
       <c r="Q157" t="n">
-        <v>154104.561872</v>
+        <v>88519.30689599999</v>
       </c>
       <c r="R157" t="n">
-        <v>154104.5619</v>
+        <v>88519.3069</v>
       </c>
       <c r="S157" t="n">
-        <v>243065.849564</v>
+        <v>138416.941848</v>
       </c>
       <c r="T157" t="n">
         <v>83666.777199</v>
@@ -21878,19 +21878,19 @@
         <v>24240.936124</v>
       </c>
       <c r="AI157" t="n">
-        <v>384862.071489</v>
+        <v>156471.308801</v>
       </c>
       <c r="AJ157" t="n">
-        <v>227740.152325</v>
+        <v>144177.451907</v>
       </c>
       <c r="AK157" t="n">
-        <v>220058.762434</v>
+        <v>136552.596421</v>
       </c>
       <c r="AL157" t="n">
-        <v>169856.438304</v>
+        <v>97883.287958</v>
       </c>
       <c r="AM157" t="n">
-        <v>169856.438304</v>
+        <v>97883.287958</v>
       </c>
       <c r="AN157" t="n">
         <v>41714.636769</v>
@@ -21914,13 +21914,13 @@
         <v>29161.155412</v>
       </c>
       <c r="AU157" t="n">
-        <v>300887.759289</v>
+        <v>184919.141538</v>
       </c>
       <c r="AV157" t="n">
-        <v>199007.909113</v>
+        <v>123105.749454</v>
       </c>
       <c r="AW157" t="n">
-        <v>192694.096759</v>
+        <v>116613.641525</v>
       </c>
       <c r="AX157" t="n">
         <v>49152.402567</v>
@@ -21944,16 +21944,16 @@
         <v>38756.712956</v>
       </c>
       <c r="BE157" t="n">
-        <v>336940.102662</v>
+        <v>163498.983508</v>
       </c>
       <c r="BF157" t="n">
         <v>137361.49</v>
       </c>
       <c r="BG157" t="n">
-        <v>209395.595564</v>
+        <v>128754.669693</v>
       </c>
       <c r="BH157" t="n">
-        <v>325079.680893</v>
+        <v>154760.206452</v>
       </c>
       <c r="BI157" t="n">
         <v>93581.380322</v>
@@ -21992,16 +21992,16 @@
         <v>78637.054512</v>
       </c>
       <c r="BU157" t="n">
-        <v>542776.932879</v>
+        <v>333579.021997</v>
       </c>
       <c r="BV157" t="n">
         <v>542776.9300000001</v>
       </c>
       <c r="BW157" t="n">
-        <v>151911.849596</v>
+        <v>93361.753509</v>
       </c>
       <c r="BX157" t="n">
-        <v>524472.091142</v>
+        <v>315274.18026</v>
       </c>
       <c r="BY157" t="n">
         <v>186395.771569</v>
@@ -22071,25 +22071,25 @@
         <v>12771446.421901</v>
       </c>
       <c r="M158" t="n">
-        <v>93034379.5888</v>
+        <v>54176579.137643</v>
       </c>
       <c r="N158" t="n">
         <v>45341952.69</v>
       </c>
       <c r="O158" t="n">
-        <v>76145154.59515201</v>
+        <v>47855824.871638</v>
       </c>
       <c r="P158" t="n">
-        <v>73684748.761347</v>
+        <v>45357290.398744</v>
       </c>
       <c r="Q158" t="n">
-        <v>57006909.631845</v>
+        <v>32745377.992748</v>
       </c>
       <c r="R158" t="n">
-        <v>57006909.6318</v>
+        <v>32745377.9927</v>
       </c>
       <c r="S158" t="n">
-        <v>89915786.73810101</v>
+        <v>51203689.232742</v>
       </c>
       <c r="T158" t="n">
         <v>30950312.885081</v>
@@ -22137,19 +22137,19 @@
         <v>7781190.124343</v>
       </c>
       <c r="AI158" t="n">
-        <v>123538337.569483</v>
+        <v>50226319.501576</v>
       </c>
       <c r="AJ158" t="n">
-        <v>73103176.177481</v>
+        <v>46280067.699811</v>
       </c>
       <c r="AK158" t="n">
-        <v>70637497.671745</v>
+        <v>43832536.38729</v>
       </c>
       <c r="AL158" t="n">
-        <v>54522863.041208</v>
+        <v>31419928.244505</v>
       </c>
       <c r="AM158" t="n">
-        <v>54522863.041208</v>
+        <v>31419928.244505</v>
       </c>
       <c r="AN158" t="n">
         <v>13390139.638318</v>
@@ -22173,13 +22173,13 @@
         <v>10960650.387135</v>
       </c>
       <c r="AU158" t="n">
-        <v>113093102.405854</v>
+        <v>69504586.893659</v>
       </c>
       <c r="AV158" t="n">
-        <v>74800057.995077</v>
+        <v>46271111.734892</v>
       </c>
       <c r="AW158" t="n">
-        <v>72426918.493688</v>
+        <v>43830957.211473</v>
       </c>
       <c r="AX158" t="n">
         <v>18474655.5</v>
@@ -22203,16 +22203,16 @@
         <v>6403475.114378</v>
       </c>
       <c r="BE158" t="n">
-        <v>55670034.888718</v>
+        <v>27013685.946738</v>
       </c>
       <c r="BF158" t="n">
         <v>22695187.09</v>
       </c>
       <c r="BG158" t="n">
-        <v>34596831.954745</v>
+        <v>21273148.839383</v>
       </c>
       <c r="BH158" t="n">
-        <v>53710428.156034</v>
+        <v>25569844.682996</v>
       </c>
       <c r="BI158" t="n">
         <v>15461735.38348</v>
@@ -22251,16 +22251,16 @@
         <v>18156164.372757</v>
       </c>
       <c r="BU158" t="n">
-        <v>125319383.747027</v>
+        <v>77018596.287568</v>
       </c>
       <c r="BV158" t="n">
         <v>125319383.75</v>
       </c>
       <c r="BW158" t="n">
-        <v>35074260.201513</v>
+        <v>21555885.49652</v>
       </c>
       <c r="BX158" t="n">
-        <v>121093059.17952</v>
+        <v>72792271.720061</v>
       </c>
       <c r="BY158" t="n">
         <v>43036101.593514</v>
@@ -22330,25 +22330,25 @@
         <v>149946.241324</v>
       </c>
       <c r="M159" t="n">
-        <v>1092292.530728</v>
+        <v>636073.169875</v>
       </c>
       <c r="N159" t="n">
         <v>532348.11</v>
       </c>
       <c r="O159" t="n">
-        <v>894000.518765</v>
+        <v>561862.832752</v>
       </c>
       <c r="P159" t="n">
-        <v>865113.531754</v>
+        <v>532528.187274</v>
       </c>
       <c r="Q159" t="n">
-        <v>669303.3464179999</v>
+        <v>384454.99347</v>
       </c>
       <c r="R159" t="n">
-        <v>669303.3464</v>
+        <v>384454.9935</v>
       </c>
       <c r="S159" t="n">
-        <v>1055677.940592</v>
+        <v>601169.240251</v>
       </c>
       <c r="T159" t="n">
         <v>363379.599429</v>
@@ -22396,19 +22396,19 @@
         <v>91356.935904</v>
       </c>
       <c r="AI159" t="n">
-        <v>1450431.592945</v>
+        <v>589694.19563</v>
       </c>
       <c r="AJ159" t="n">
-        <v>858285.438825</v>
+        <v>543362.276327</v>
       </c>
       <c r="AK159" t="n">
-        <v>829336.546739</v>
+        <v>514626.445732</v>
       </c>
       <c r="AL159" t="n">
-        <v>640138.79941</v>
+        <v>368893.231611</v>
       </c>
       <c r="AM159" t="n">
-        <v>640138.79941</v>
+        <v>368893.231611</v>
       </c>
       <c r="AN159" t="n">
         <v>157210.157976</v>
@@ -22432,13 +22432,13 @@
         <v>128686.154545</v>
       </c>
       <c r="AU159" t="n">
-        <v>1327796.794913</v>
+        <v>816035.335011</v>
       </c>
       <c r="AV159" t="n">
-        <v>878208.088313</v>
+        <v>543257.126665</v>
       </c>
       <c r="AW159" t="n">
-        <v>850345.672685</v>
+        <v>514607.905038</v>
       </c>
       <c r="AX159" t="n">
         <v>216906.1405</v>
@@ -22462,16 +22462,16 @@
         <v>75181.54115800001</v>
       </c>
       <c r="BE159" t="n">
-        <v>653607.446656</v>
+        <v>317160.683152</v>
       </c>
       <c r="BF159" t="n">
         <v>266458.31</v>
       </c>
       <c r="BG159" t="n">
-        <v>406192.434432</v>
+        <v>249762.525262</v>
       </c>
       <c r="BH159" t="n">
-        <v>630600.212054</v>
+        <v>300208.917204</v>
       </c>
       <c r="BI159" t="n">
         <v>181532.226539</v>
@@ -22510,16 +22510,16 @@
         <v>213166.818747</v>
       </c>
       <c r="BU159" t="n">
-        <v>1471342.394363</v>
+        <v>904255.371228</v>
       </c>
       <c r="BV159" t="n">
         <v>1471342.39</v>
       </c>
       <c r="BW159" t="n">
-        <v>411797.795699</v>
+        <v>253082.063052</v>
       </c>
       <c r="BX159" t="n">
-        <v>1421722.21333</v>
+        <v>854635.190195</v>
       </c>
       <c r="BY159" t="n">
         <v>505275.711302</v>
@@ -22589,25 +22589,25 @@
         <v>172622.772225</v>
       </c>
       <c r="M160" t="n">
-        <v>1257481.101694</v>
+        <v>732267.197579</v>
       </c>
       <c r="N160" t="n">
         <v>612855.6899999999</v>
       </c>
       <c r="O160" t="n">
-        <v>1029201.176083</v>
+        <v>646833.951578</v>
       </c>
       <c r="P160" t="n">
-        <v>995945.579043</v>
+        <v>613062.9962009999</v>
       </c>
       <c r="Q160" t="n">
-        <v>770522.809362</v>
+        <v>442596.534482</v>
       </c>
       <c r="R160" t="n">
-        <v>770522.8094</v>
+        <v>442596.5345</v>
       </c>
       <c r="S160" t="n">
-        <v>1215329.24782</v>
+        <v>692084.709241</v>
       </c>
       <c r="T160" t="n">
         <v>418333.885995</v>
@@ -22655,19 +22655,19 @@
         <v>121204.680621</v>
       </c>
       <c r="AI160" t="n">
-        <v>1924310.357443</v>
+        <v>782356.544006</v>
       </c>
       <c r="AJ160" t="n">
-        <v>1138700.761626</v>
+        <v>720887.259535</v>
       </c>
       <c r="AK160" t="n">
-        <v>1100293.812171</v>
+        <v>682762.9821040001</v>
       </c>
       <c r="AL160" t="n">
-        <v>849282.191519</v>
+        <v>489416.439792</v>
       </c>
       <c r="AM160" t="n">
-        <v>849282.191519</v>
+        <v>489416.439792</v>
       </c>
       <c r="AN160" t="n">
         <v>208573.183844</v>
@@ -22691,13 +22691,13 @@
         <v>145805.777062</v>
       </c>
       <c r="AU160" t="n">
-        <v>1504438.796446</v>
+        <v>924595.70769</v>
       </c>
       <c r="AV160" t="n">
-        <v>995039.545563</v>
+        <v>615528.747269</v>
       </c>
       <c r="AW160" t="n">
-        <v>963470.483796</v>
+        <v>583068.207623</v>
       </c>
       <c r="AX160" t="n">
         <v>245762.012836</v>
@@ -22721,16 +22721,16 @@
         <v>193783.56478</v>
       </c>
       <c r="BE160" t="n">
-        <v>1684700.513311</v>
+        <v>817494.917542</v>
       </c>
       <c r="BF160" t="n">
         <v>686807.4300000001</v>
       </c>
       <c r="BG160" t="n">
-        <v>1046977.977822</v>
+        <v>643773.348465</v>
       </c>
       <c r="BH160" t="n">
-        <v>1625398.404465</v>
+        <v>773801.032258</v>
       </c>
       <c r="BI160" t="n">
         <v>467906.901609</v>
@@ -22769,16 +22769,16 @@
         <v>393185.272559</v>
       </c>
       <c r="BU160" t="n">
-        <v>2713884.664397</v>
+        <v>1667895.109987</v>
       </c>
       <c r="BV160" t="n">
         <v>2713884.66</v>
       </c>
       <c r="BW160" t="n">
-        <v>759559.247978</v>
+        <v>466808.767546</v>
       </c>
       <c r="BX160" t="n">
-        <v>2622360.455711</v>
+        <v>1576370.9013</v>
       </c>
       <c r="BY160" t="n">
         <v>931978.857843</v>
@@ -22848,25 +22848,25 @@
         <v>980161.39834</v>
       </c>
       <c r="M161" t="n">
-        <v>7140045.424699</v>
+        <v>4157852.588552</v>
       </c>
       <c r="N161" t="n">
         <v>3479827.6</v>
       </c>
       <c r="O161" t="n">
-        <v>5843859.71168</v>
+        <v>3672758.016232</v>
       </c>
       <c r="P161" t="n">
-        <v>5655032.640503</v>
+        <v>3481004.712663</v>
       </c>
       <c r="Q161" t="n">
-        <v>4375070.012743</v>
+        <v>2513086.961514</v>
       </c>
       <c r="R161" t="n">
-        <v>4375070.0127</v>
+        <v>2513086.9615</v>
       </c>
       <c r="S161" t="n">
-        <v>6900704.928062</v>
+        <v>3929694.255498</v>
       </c>
       <c r="T161" t="n">
         <v>2375322.336591</v>
@@ -22914,19 +22914,19 @@
         <v>597177.636822</v>
       </c>
       <c r="AI161" t="n">
-        <v>9481111.669004001</v>
+        <v>3854684.7342</v>
       </c>
       <c r="AJ161" t="n">
-        <v>5610399.090143</v>
+        <v>3551824.466346</v>
       </c>
       <c r="AK161" t="n">
-        <v>5421167.360846</v>
+        <v>3363985.467182</v>
       </c>
       <c r="AL161" t="n">
-        <v>4184428.600691</v>
+        <v>2411363.582991</v>
       </c>
       <c r="AM161" t="n">
-        <v>4184428.600691</v>
+        <v>2411363.582991</v>
       </c>
       <c r="AN161" t="n">
         <v>1027643.820308</v>
@@ -22950,13 +22950,13 @@
         <v>841189.482794</v>
       </c>
       <c r="AU161" t="n">
-        <v>8679478.40322</v>
+        <v>5334220.637995</v>
       </c>
       <c r="AV161" t="n">
-        <v>5740628.509757</v>
+        <v>3551137.129077</v>
       </c>
       <c r="AW161" t="n">
-        <v>5558498.807662</v>
+        <v>3363864.271264</v>
       </c>
       <c r="AX161" t="n">
         <v>1417861.655645</v>
@@ -22980,16 +22980,16 @@
         <v>491443.092271</v>
       </c>
       <c r="BE161" t="n">
-        <v>4606219.24686</v>
+        <v>2235151.466767</v>
       </c>
       <c r="BF161" t="n">
         <v>1741771.89</v>
       </c>
       <c r="BG161" t="n">
-        <v>2862591.941049</v>
+        <v>1760171.119367</v>
       </c>
       <c r="BH161" t="n">
-        <v>4444078.550049</v>
+        <v>2115685.951221</v>
       </c>
       <c r="BI161" t="n">
         <v>1186631.151523</v>
@@ -23028,16 +23028,16 @@
         <v>1393418.63656</v>
       </c>
       <c r="BU161" t="n">
-        <v>12347187.841592</v>
+        <v>7588315.927071</v>
       </c>
       <c r="BV161" t="n">
         <v>9617800.390000001</v>
       </c>
       <c r="BW161" t="n">
-        <v>3455718.231005</v>
+        <v>2123810.055232</v>
       </c>
       <c r="BX161" t="n">
-        <v>11930785.990942</v>
+        <v>7171914.076421</v>
       </c>
       <c r="BY161" t="n">
         <v>3302862.03485</v>
@@ -23107,25 +23107,25 @@
         <v>24504034.958509</v>
       </c>
       <c r="M162" t="n">
-        <v>178501135.617481</v>
+        <v>103946314.713789</v>
       </c>
       <c r="N162" t="n">
         <v>86995690</v>
       </c>
       <c r="O162" t="n">
-        <v>146096492.791999</v>
+        <v>91818950.40580299</v>
       </c>
       <c r="P162" t="n">
-        <v>141375816.012564</v>
+        <v>87025117.816578</v>
       </c>
       <c r="Q162" t="n">
-        <v>109376750.318572</v>
+        <v>62827174.037853</v>
       </c>
       <c r="R162" t="n">
-        <v>109376750.3186</v>
+        <v>62827174.0379</v>
       </c>
       <c r="S162" t="n">
-        <v>172517623.201547</v>
+        <v>98242356.38745899</v>
       </c>
       <c r="T162" t="n">
         <v>59383058.414767</v>
@@ -23173,19 +23173,19 @@
         <v>14929440.920548</v>
       </c>
       <c r="AI162" t="n">
-        <v>237027791.725106</v>
+        <v>96367118.35499901</v>
       </c>
       <c r="AJ162" t="n">
-        <v>140259977.253571</v>
+        <v>88795611.658647</v>
       </c>
       <c r="AK162" t="n">
-        <v>135529184.021146</v>
+        <v>84099636.679554</v>
       </c>
       <c r="AL162" t="n">
-        <v>104610715.017266</v>
+        <v>60284089.574766</v>
       </c>
       <c r="AM162" t="n">
-        <v>104610715.017266</v>
+        <v>60284089.574766</v>
       </c>
       <c r="AN162" t="n">
         <v>25691095.507711</v>
@@ -23209,13 +23209,13 @@
         <v>21029737.069858</v>
       </c>
       <c r="AU162" t="n">
-        <v>216986960.080499</v>
+        <v>133355515.949886</v>
       </c>
       <c r="AV162" t="n">
-        <v>143515712.743916</v>
+        <v>88778428.226934</v>
       </c>
       <c r="AW162" t="n">
-        <v>138962470.191551</v>
+        <v>84096606.781597</v>
       </c>
       <c r="AX162" t="n">
         <v>35446541.391122</v>
@@ -23239,16 +23239,16 @@
         <v>12286077.306763</v>
       </c>
       <c r="BE162" t="n">
-        <v>115155481.171505</v>
+        <v>55878786.669181</v>
       </c>
       <c r="BF162" t="n">
         <v>43544297.14</v>
       </c>
       <c r="BG162" t="n">
-        <v>71564798.52621301</v>
+        <v>44004277.98418</v>
       </c>
       <c r="BH162" t="n">
-        <v>111101963.751224</v>
+        <v>52892148.780524</v>
       </c>
       <c r="BI162" t="n">
         <v>29665778.788086</v>
@@ -23287,16 +23287,16 @@
         <v>34835465.913989</v>
       </c>
       <c r="BU162" t="n">
-        <v>308679696.039792</v>
+        <v>189707898.17678</v>
       </c>
       <c r="BV162" t="n">
         <v>240445009.82</v>
       </c>
       <c r="BW162" t="n">
-        <v>86392955.775131</v>
+        <v>53095251.380793</v>
       </c>
       <c r="BX162" t="n">
-        <v>298269649.773549</v>
+        <v>179297851.910537</v>
       </c>
       <c r="BY162" t="n">
         <v>82571550.871246</v>
@@ -23366,25 +23366,25 @@
         <v>1302730.411889</v>
       </c>
       <c r="M163" t="n">
-        <v>9489819.057120999</v>
+        <v>5526192.956006</v>
       </c>
       <c r="N163" t="n">
         <v>4625031.4</v>
       </c>
       <c r="O163" t="n">
-        <v>7767061.406528</v>
+        <v>4881454.800563</v>
       </c>
       <c r="P163" t="n">
-        <v>7516091.751299</v>
+        <v>4626595.896139</v>
       </c>
       <c r="Q163" t="n">
-        <v>5814896.168523</v>
+        <v>3340138.489467</v>
       </c>
       <c r="R163" t="n">
-        <v>5814896.1685</v>
+        <v>3340138.4895</v>
       </c>
       <c r="S163" t="n">
-        <v>9171712.116474001</v>
+        <v>5222948.204991</v>
       </c>
       <c r="T163" t="n">
         <v>3157035.822014</v>
@@ -23432,19 +23432,19 @@
         <v>809739.253347</v>
       </c>
       <c r="AI163" t="n">
-        <v>12855853.619393</v>
+        <v>5226735.473836</v>
       </c>
       <c r="AJ163" t="n">
-        <v>7607385.290593</v>
+        <v>4816074.002208</v>
       </c>
       <c r="AK163" t="n">
-        <v>7350797.719756</v>
+        <v>4561374.895018</v>
       </c>
       <c r="AL163" t="n">
-        <v>5673849.59162</v>
+        <v>3269673.254394</v>
       </c>
       <c r="AM163" t="n">
-        <v>5673849.59162</v>
+        <v>3269673.254394</v>
       </c>
       <c r="AN163" t="n">
         <v>1393427.162128</v>
@@ -23468,13 +23468,13 @@
         <v>1115681.414402</v>
       </c>
       <c r="AU163" t="n">
-        <v>11511713.994579</v>
+        <v>7074851.680696</v>
       </c>
       <c r="AV163" t="n">
-        <v>7613876.143632</v>
+        <v>4709923.003012</v>
       </c>
       <c r="AW163" t="n">
-        <v>7372314.964143</v>
+        <v>4461540.383925</v>
       </c>
       <c r="AX163" t="n">
         <v>1880529.808981</v>
@@ -23498,16 +23498,16 @@
         <v>760408.198208</v>
       </c>
       <c r="BE163" t="n">
-        <v>6944527.206828</v>
+        <v>3369807.067461</v>
       </c>
       <c r="BF163" t="n">
         <v>2695037.62</v>
       </c>
       <c r="BG163" t="n">
-        <v>4315762.353303</v>
+        <v>2653706.993094</v>
       </c>
       <c r="BH163" t="n">
-        <v>6700077.166568</v>
+        <v>3189695.900683</v>
       </c>
       <c r="BI163" t="n">
         <v>1836070.279672</v>
@@ -23546,16 +23546,16 @@
         <v>1999770.727865</v>
       </c>
       <c r="BU163" t="n">
-        <v>16532414.900352</v>
+        <v>10160466.408286</v>
       </c>
       <c r="BV163" t="n">
         <v>13803027.45</v>
       </c>
       <c r="BW163" t="n">
-        <v>4627075.274683</v>
+        <v>2843700.885829</v>
       </c>
       <c r="BX163" t="n">
-        <v>15974868.659983</v>
+        <v>9602920.167917</v>
       </c>
       <c r="BY163" t="n">
         <v>4740116.603994</v>
@@ -23640,25 +23640,25 @@
         <v>9372.458237000001</v>
       </c>
       <c r="M165" t="n">
-        <v>84085.142205</v>
+        <v>43696.56524</v>
       </c>
       <c r="N165" t="n">
         <v>32961.01</v>
       </c>
       <c r="O165" t="n">
-        <v>52551.274498</v>
+        <v>32417.041311</v>
       </c>
       <c r="P165" t="n">
-        <v>50850.20949</v>
+        <v>30669.457143</v>
       </c>
       <c r="Q165" t="n">
-        <v>38242.178702</v>
+        <v>19316.770337</v>
       </c>
       <c r="R165" t="n">
-        <v>38290.0461</v>
+        <v>19307.5566</v>
       </c>
       <c r="S165" t="n">
-        <v>81607.431839</v>
+        <v>40337.626145</v>
       </c>
       <c r="T165" t="n">
         <v>22305.556918</v>
@@ -23706,19 +23706,19 @@
         <v>5548.794755</v>
       </c>
       <c r="AI165" t="n">
-        <v>157325.565291</v>
+        <v>44516.269404</v>
       </c>
       <c r="AJ165" t="n">
-        <v>57658.183668</v>
+        <v>35652.566039</v>
       </c>
       <c r="AK165" t="n">
-        <v>55557.816503</v>
+        <v>33722.891953</v>
       </c>
       <c r="AL165" t="n">
-        <v>44491.68376</v>
+        <v>22896.320135</v>
       </c>
       <c r="AM165" t="n">
-        <v>44574.685707</v>
+        <v>22897.122952</v>
       </c>
       <c r="AN165" t="n">
         <v>11192.217325</v>
@@ -23742,13 +23742,13 @@
         <v>8050.943115</v>
       </c>
       <c r="AU165" t="n">
-        <v>130585.42649</v>
+        <v>71861.22433500001</v>
       </c>
       <c r="AV165" t="n">
-        <v>55701.912245</v>
+        <v>33979.814168</v>
       </c>
       <c r="AW165" t="n">
-        <v>53885.361943</v>
+        <v>32117.008613</v>
       </c>
       <c r="AX165" t="n">
         <v>18554.174925</v>
@@ -23772,16 +23772,16 @@
         <v>4311.945146</v>
       </c>
       <c r="BE165" t="n">
-        <v>68173.659189</v>
+        <v>22058.1654</v>
       </c>
       <c r="BF165" t="n">
         <v>6453.84</v>
       </c>
       <c r="BG165" t="n">
-        <v>22459.738992</v>
+        <v>13538.739862</v>
       </c>
       <c r="BH165" t="n">
-        <v>59964.261017</v>
+        <v>20322.698475</v>
       </c>
       <c r="BI165" t="n">
         <v>9559.073350000001</v>
@@ -23820,16 +23820,16 @@
         <v>44307.142157</v>
       </c>
       <c r="BU165" t="n">
-        <v>345088.133606</v>
+        <v>189380.567255</v>
       </c>
       <c r="BV165" t="n">
         <v>111415.53</v>
       </c>
       <c r="BW165" t="n">
-        <v>23227.019486</v>
+        <v>14274.826314</v>
       </c>
       <c r="BX165" t="n">
-        <v>333850.090043</v>
+        <v>179738.191274</v>
       </c>
       <c r="BY165" t="n">
         <v>102379.724204</v>
@@ -24243,19 +24243,19 @@
         <v>367514.92</v>
       </c>
       <c r="O169" t="n">
-        <v>46089.468425</v>
+        <v>6620.885244</v>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>7443.93241</v>
       </c>
       <c r="Q169" t="n">
-        <v>32663.723232</v>
+        <v>0</v>
       </c>
       <c r="R169" t="n">
-        <v>23617.3336</v>
+        <v>0</v>
       </c>
       <c r="S169" t="n">
-        <v>0</v>
+        <v>7590.796138</v>
       </c>
       <c r="T169" t="n">
         <v>716.5955300000001</v>
@@ -24282,16 +24282,16 @@
         <v>0</v>
       </c>
       <c r="AJ169" t="n">
-        <v>16125.361857</v>
+        <v>4154.597552</v>
       </c>
       <c r="AK169" t="n">
-        <v>4114.416802</v>
+        <v>1003.801982</v>
       </c>
       <c r="AL169" t="n">
-        <v>12979.631504</v>
+        <v>6366.16559</v>
       </c>
       <c r="AM169" t="n">
-        <v>15112.258195</v>
+        <v>4184.734487</v>
       </c>
       <c r="AN169" t="n">
         <v>402.88043</v>
@@ -24312,10 +24312,10 @@
         <v>0</v>
       </c>
       <c r="AV169" t="n">
-        <v>27057.423896</v>
+        <v>20327.705615</v>
       </c>
       <c r="AW169" t="n">
-        <v>23039.727571</v>
+        <v>13266.769972</v>
       </c>
       <c r="AX169" t="n">
         <v>730.898434</v>
@@ -24336,7 +24336,7 @@
         <v>0</v>
       </c>
       <c r="BG169" t="n">
-        <v>0</v>
+        <v>2150.917094</v>
       </c>
       <c r="BH169" t="n">
         <v>0</v>
@@ -24366,7 +24366,7 @@
         <v>0</v>
       </c>
       <c r="BX169" t="n">
-        <v>0</v>
+        <v>108.082531</v>
       </c>
       <c r="BY169" t="n">
         <v>0</v>
@@ -24651,25 +24651,25 @@
         <v>76600.45569</v>
       </c>
       <c r="M173" t="n">
-        <v>633748.96932</v>
+        <v>234635.547426</v>
       </c>
       <c r="N173" t="n">
         <v>286739.45</v>
       </c>
       <c r="O173" t="n">
-        <v>198469.046245</v>
+        <v>139551.797103</v>
       </c>
       <c r="P173" t="n">
-        <v>192700.355307</v>
+        <v>133666.765672</v>
       </c>
       <c r="Q173" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R173" t="n">
         <v>-0</v>
       </c>
       <c r="S173" t="n">
-        <v>612324.62314</v>
+        <v>241643.450756</v>
       </c>
       <c r="T173" t="n">
         <v>211330.045631</v>
@@ -24717,19 +24717,19 @@
         <v>0</v>
       </c>
       <c r="AI173" t="n">
-        <v>974459.381878</v>
+        <v>367852.484895</v>
       </c>
       <c r="AJ173" t="n">
-        <v>279046.448976</v>
+        <v>193008.386622</v>
       </c>
       <c r="AK173" t="n">
-        <v>272103.342367</v>
+        <v>184381.296274</v>
       </c>
       <c r="AL173" t="n">
-        <v>47.767906</v>
+        <v>-0</v>
       </c>
       <c r="AM173" t="n">
-        <v>47.767906</v>
+        <v>0</v>
       </c>
       <c r="AN173" t="n">
         <v>115924.601385</v>
@@ -24753,13 +24753,13 @@
         <v>28125.654948</v>
       </c>
       <c r="AU173" t="n">
-        <v>335331.339549</v>
+        <v>318594.202352</v>
       </c>
       <c r="AV173" t="n">
-        <v>212787.641226</v>
+        <v>122226.800808</v>
       </c>
       <c r="AW173" t="n">
-        <v>207699.016333</v>
+        <v>116423.457225</v>
       </c>
       <c r="AX173" t="n">
         <v>103142.471401</v>
@@ -24783,16 +24783,16 @@
         <v>143489.743826</v>
       </c>
       <c r="BE173" t="n">
-        <v>1743705.798131</v>
+        <v>583402.9708069999</v>
       </c>
       <c r="BF173" t="n">
         <v>662195.28</v>
       </c>
       <c r="BG173" t="n">
-        <v>179772.614594</v>
+        <v>89342.639897</v>
       </c>
       <c r="BH173" t="n">
-        <v>1676875.630491</v>
+        <v>549469.61991</v>
       </c>
       <c r="BI173" t="n">
         <v>341053.117135</v>
@@ -24831,7 +24831,7 @@
         <v>119040.008211</v>
       </c>
       <c r="BU173" t="n">
-        <v>598011.285376</v>
+        <v>479815.66607</v>
       </c>
       <c r="BV173" t="n">
         <v>5346126.36</v>
@@ -24840,7 +24840,7 @@
         <v>0</v>
       </c>
       <c r="BX173" t="n">
-        <v>577801.361602</v>
+        <v>437972.828205</v>
       </c>
       <c r="BY173" t="n">
         <v>326534.454398</v>
@@ -24910,25 +24910,25 @@
         <v>114900.683535</v>
       </c>
       <c r="M174" t="n">
-        <v>950623.453979</v>
+        <v>351953.321139</v>
       </c>
       <c r="N174" t="n">
         <v>430109.17</v>
       </c>
       <c r="O174" t="n">
-        <v>297703.569368</v>
+        <v>209327.695655</v>
       </c>
       <c r="P174" t="n">
-        <v>289050.532961</v>
+        <v>200500.148509</v>
       </c>
       <c r="Q174" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R174" t="n">
         <v>-0</v>
       </c>
       <c r="S174" t="n">
-        <v>918486.9347090001</v>
+        <v>362465.176133</v>
       </c>
       <c r="T174" t="n">
         <v>316995.068447</v>
@@ -24976,19 +24976,19 @@
         <v>0</v>
       </c>
       <c r="AI174" t="n">
-        <v>1461689.072817</v>
+        <v>551778.727342</v>
       </c>
       <c r="AJ174" t="n">
-        <v>418569.673463</v>
+        <v>289512.579933</v>
       </c>
       <c r="AK174" t="n">
-        <v>408155.01355</v>
+        <v>276571.944411</v>
       </c>
       <c r="AL174" t="n">
-        <v>71.65186</v>
+        <v>-0</v>
       </c>
       <c r="AM174" t="n">
-        <v>71.65186</v>
+        <v>0</v>
       </c>
       <c r="AN174" t="n">
         <v>173886.902078</v>
@@ -25012,13 +25012,13 @@
         <v>42188.482423</v>
       </c>
       <c r="AU174" t="n">
-        <v>502997.009323</v>
+        <v>477891.303527</v>
       </c>
       <c r="AV174" t="n">
-        <v>319181.461839</v>
+        <v>183340.201212</v>
       </c>
       <c r="AW174" t="n">
-        <v>311548.524499</v>
+        <v>174635.185838</v>
       </c>
       <c r="AX174" t="n">
         <v>154713.707102</v>
@@ -25042,16 +25042,16 @@
         <v>215234.615739</v>
       </c>
       <c r="BE174" t="n">
-        <v>2615558.697197</v>
+        <v>875104.456211</v>
       </c>
       <c r="BF174" t="n">
         <v>993292.92</v>
       </c>
       <c r="BG174" t="n">
-        <v>269658.921891</v>
+        <v>134013.959846</v>
       </c>
       <c r="BH174" t="n">
-        <v>2515313.445736</v>
+        <v>824204.429865</v>
       </c>
       <c r="BI174" t="n">
         <v>511579.675702</v>
@@ -25090,7 +25090,7 @@
         <v>178560.012317</v>
       </c>
       <c r="BU174" t="n">
-        <v>897016.928064</v>
+        <v>719723.499104</v>
       </c>
       <c r="BV174" t="n">
         <v>8019189.54</v>
@@ -25099,7 +25099,7 @@
         <v>0</v>
       </c>
       <c r="BX174" t="n">
-        <v>866702.0424020001</v>
+        <v>656959.242308</v>
       </c>
       <c r="BY174" t="n">
         <v>489801.681597</v>
@@ -26079,25 +26079,25 @@
         <v>56662370.252028</v>
       </c>
       <c r="M191" t="n">
-        <v>438453386.782208</v>
+        <v>257483316.966005</v>
       </c>
       <c r="N191" t="n">
         <v>224214362.57</v>
       </c>
       <c r="O191" t="n">
-        <v>279958612.833</v>
+        <v>198509306.27807</v>
       </c>
       <c r="P191" t="n">
-        <v>260598786.263604</v>
+        <v>178954994.074975</v>
       </c>
       <c r="Q191" t="n">
-        <v>187083882.86594</v>
+        <v>118017663.713697</v>
       </c>
       <c r="R191" t="n">
-        <v>177105402.7969</v>
+        <v>108039183.6447</v>
       </c>
       <c r="S191" t="n">
-        <v>403376905.474944</v>
+        <v>224649710.977065</v>
       </c>
       <c r="T191" t="n">
         <v>147777844.485699</v>
@@ -26145,19 +26145,19 @@
         <v>30421945.004276</v>
       </c>
       <c r="AI191" t="n">
-        <v>436298482.278645</v>
+        <v>245949809.552257</v>
       </c>
       <c r="AJ191" t="n">
-        <v>261631772.119284</v>
+        <v>186739574.748926</v>
       </c>
       <c r="AK191" t="n">
-        <v>242935869.847863</v>
+        <v>167885934.34371</v>
       </c>
       <c r="AL191" t="n">
-        <v>172888758.48086</v>
+        <v>110229590.990255</v>
       </c>
       <c r="AM191" t="n">
-        <v>162910278.411821</v>
+        <v>100251110.921216</v>
       </c>
       <c r="AN191" t="n">
         <v>67009319.337857</v>
@@ -26181,13 +26181,13 @@
         <v>49698093.163173</v>
       </c>
       <c r="AU191" t="n">
-        <v>456204070.149077</v>
+        <v>275764392.648315</v>
       </c>
       <c r="AV191" t="n">
-        <v>294170680.588055</v>
+        <v>203950250.3979</v>
       </c>
       <c r="AW191" t="n">
-        <v>274258861.097506</v>
+        <v>183945204.033063</v>
       </c>
       <c r="AX191" t="n">
         <v>75167460.200324</v>
@@ -26211,16 +26211,16 @@
         <v>33502785.58396</v>
       </c>
       <c r="BE191" t="n">
-        <v>345254775.064788</v>
+        <v>181515772.818769</v>
       </c>
       <c r="BF191" t="n">
         <v>123846375.97</v>
       </c>
       <c r="BG191" t="n">
-        <v>148426639.330958</v>
+        <v>115189338.890374</v>
       </c>
       <c r="BH191" t="n">
-        <v>311599454.691991</v>
+        <v>149178781.455038</v>
       </c>
       <c r="BI191" t="n">
         <v>85192784.65129399</v>
@@ -26259,16 +26259,16 @@
         <v>51371753.943587</v>
       </c>
       <c r="BU191" t="n">
-        <v>498723374.63279</v>
+        <v>302075262.791532</v>
       </c>
       <c r="BV191" t="n">
         <v>465711556.94</v>
       </c>
       <c r="BW191" t="n">
-        <v>154406523.673822</v>
+        <v>121108819.279485</v>
       </c>
       <c r="BX191" t="n">
-        <v>456485857.461068</v>
+        <v>260276145.954806</v>
       </c>
       <c r="BY191" t="n">
         <v>133484460.837946</v>
@@ -26338,25 +26338,25 @@
         <v>29929739.341328</v>
       </c>
       <c r="M192" t="n">
-        <v>238606275.974575</v>
+        <v>138819563.317991</v>
       </c>
       <c r="N192" t="n">
         <v>120165759.92</v>
       </c>
       <c r="O192" t="n">
-        <v>148050185.511604</v>
+        <v>105166412.024549</v>
       </c>
       <c r="P192" t="n">
-        <v>135880343.56684</v>
+        <v>92892953.83291601</v>
       </c>
       <c r="Q192" t="n">
-        <v>97277680.14665399</v>
+        <v>60666423.749717</v>
       </c>
       <c r="R192" t="n">
-        <v>91992072.14669999</v>
+        <v>55380815.7497</v>
       </c>
       <c r="S192" t="n">
-        <v>217900820.940472</v>
+        <v>119300264.330133</v>
       </c>
       <c r="T192" t="n">
         <v>79146447.028098</v>
@@ -26404,19 +26404,19 @@
         <v>14958512.901308</v>
       </c>
       <c r="AI192" t="n">
-        <v>235717401.223055</v>
+        <v>132254142.723817</v>
       </c>
       <c r="AJ192" t="n">
-        <v>138069459.877334</v>
+        <v>98758826.315871</v>
       </c>
       <c r="AK192" t="n">
-        <v>126263085.651756</v>
+        <v>86874507.85474201</v>
       </c>
       <c r="AL192" t="n">
-        <v>89665175.623009</v>
+        <v>56495790.737561</v>
       </c>
       <c r="AM192" t="n">
-        <v>84379567.623009</v>
+        <v>51210182.737561</v>
       </c>
       <c r="AN192" t="n">
         <v>35499296.753552</v>
@@ -26440,13 +26440,13 @@
         <v>25175752.805707</v>
       </c>
       <c r="AU192" t="n">
-        <v>248677241.763613</v>
+        <v>147615813.098792</v>
       </c>
       <c r="AV192" t="n">
-        <v>155671022.606298</v>
+        <v>108104574.755283</v>
       </c>
       <c r="AW192" t="n">
-        <v>143174574.758757</v>
+        <v>95566935.86173899</v>
       </c>
       <c r="AX192" t="n">
         <v>39689895.798161</v>
@@ -26470,16 +26470,16 @@
         <v>17587916.327653</v>
       </c>
       <c r="BE192" t="n">
-        <v>178178000.702981</v>
+        <v>92318742.635745</v>
       </c>
       <c r="BF192" t="n">
         <v>66101189.77</v>
       </c>
       <c r="BG192" t="n">
-        <v>73395941.825414</v>
+        <v>57329634.137293</v>
       </c>
       <c r="BH192" t="n">
-        <v>159418937.482234</v>
+        <v>74198016.099425</v>
       </c>
       <c r="BI192" t="n">
         <v>45212981.502571</v>
@@ -26518,16 +26518,16 @@
         <v>26654200.546062</v>
       </c>
       <c r="BU192" t="n">
-        <v>212448406.104695</v>
+        <v>127907236.649047</v>
       </c>
       <c r="BV192" t="n">
         <v>241746504.72</v>
       </c>
       <c r="BW192" t="n">
-        <v>65253455.101513</v>
+        <v>51735080.39652</v>
       </c>
       <c r="BX192" t="n">
-        <v>192677822.492465</v>
+        <v>108257024.194963</v>
       </c>
       <c r="BY192" t="n">
         <v>70038366.962767</v>
@@ -26609,25 +26609,25 @@
         <v>809282.4982790001</v>
       </c>
       <c r="M194" t="n">
-        <v>5221902.690073</v>
+        <v>3339630.174999</v>
       </c>
       <c r="N194" t="n">
         <v>2972597.6</v>
       </c>
       <c r="O194" t="n">
-        <v>7213538.685743</v>
+        <v>4630083.159404</v>
       </c>
       <c r="P194" t="n">
-        <v>6608621.043607</v>
+        <v>4035797.242515</v>
       </c>
       <c r="Q194" t="n">
-        <v>7878516.861184</v>
+        <v>5051639.862619</v>
       </c>
       <c r="R194" t="n">
-        <v>7878516.8612</v>
+        <v>5051639.8626</v>
       </c>
       <c r="S194" t="n">
-        <v>4686351.422879</v>
+        <v>2829385.672516</v>
       </c>
       <c r="T194" t="n">
         <v>1993278.669051</v>
@@ -26675,19 +26675,19 @@
         <v>1318724.721186</v>
       </c>
       <c r="AI194" t="n">
-        <v>5754100.920568</v>
+        <v>3330918.268992</v>
       </c>
       <c r="AJ194" t="n">
-        <v>6832564.072094</v>
+        <v>4401243.099956</v>
       </c>
       <c r="AK194" t="n">
-        <v>6241258.040649</v>
+        <v>3817264.451974</v>
       </c>
       <c r="AL194" t="n">
-        <v>7532638.855383</v>
+        <v>4822047.656693</v>
       </c>
       <c r="AM194" t="n">
-        <v>7532638.855383</v>
+        <v>4822047.656693</v>
       </c>
       <c r="AN194" t="n">
         <v>944563.251458</v>
@@ -26711,13 +26711,13 @@
         <v>1206262.177559</v>
       </c>
       <c r="AU194" t="n">
-        <v>5458183.349158</v>
+        <v>3638319.675723</v>
       </c>
       <c r="AV194" t="n">
-        <v>7752238.867437</v>
+        <v>5059940.284541</v>
       </c>
       <c r="AW194" t="n">
-        <v>7136767.542428</v>
+        <v>4449535.099935</v>
       </c>
       <c r="AX194" t="n">
         <v>1028608.162389</v>
@@ -26741,16 +26741,16 @@
         <v>660412.151196</v>
       </c>
       <c r="BE194" t="n">
-        <v>4924946.88729</v>
+        <v>2815738.726068</v>
       </c>
       <c r="BF194" t="n">
         <v>2174604.66</v>
       </c>
       <c r="BG194" t="n">
-        <v>4405451.013949</v>
+        <v>3015756.634159</v>
       </c>
       <c r="BH194" t="n">
-        <v>4392574.589524</v>
+        <v>2312145.752461</v>
       </c>
       <c r="BI194" t="n">
         <v>1568122.170029</v>
@@ -26789,16 +26789,16 @@
         <v>958363.854987</v>
       </c>
       <c r="BU194" t="n">
-        <v>6151751.668241</v>
+        <v>4029961.419042</v>
       </c>
       <c r="BV194" t="n">
         <v>7031707.2</v>
       </c>
       <c r="BW194" t="n">
-        <v>7774767.429</v>
+        <v>5195450.79569</v>
       </c>
       <c r="BX194" t="n">
-        <v>5585575.321651</v>
+        <v>3465633.925147</v>
       </c>
       <c r="BY194" t="n">
         <v>2326785.321023</v>
@@ -26850,25 +26850,25 @@
         </is>
       </c>
       <c r="M195" t="n">
-        <v>20708174.235117</v>
+        <v>11765584.69886</v>
       </c>
       <c r="N195" t="n">
         <v>10200931.93</v>
       </c>
       <c r="O195" t="n">
-        <v>12316510.873623</v>
+        <v>8964291.692867</v>
       </c>
       <c r="P195" t="n">
-        <v>11098758.284131</v>
+        <v>7737427.421223</v>
       </c>
       <c r="Q195" t="n">
-        <v>7927679.668785</v>
+        <v>5112926.856814</v>
       </c>
       <c r="R195" t="n">
-        <v>7428755.6653</v>
+        <v>4614002.8534</v>
       </c>
       <c r="S195" t="n">
-        <v>18683175.777166</v>
+        <v>9867050.778415</v>
       </c>
       <c r="T195" t="n">
         <v>6664367.313523</v>
@@ -26904,19 +26904,19 @@
         <v>2660851.656023</v>
       </c>
       <c r="AI195" t="n">
-        <v>20587352.123554</v>
+        <v>11323247.08737</v>
       </c>
       <c r="AJ195" t="n">
-        <v>11603315.805417</v>
+        <v>8515400.324144</v>
       </c>
       <c r="AK195" t="n">
-        <v>10408343.989126</v>
+        <v>7312858.092869</v>
       </c>
       <c r="AL195" t="n">
-        <v>7354392.79015</v>
+        <v>4801007.497652</v>
       </c>
       <c r="AM195" t="n">
-        <v>6855468.786698</v>
+        <v>4302083.4942</v>
       </c>
       <c r="AN195" t="n">
         <v>3032696.118823</v>
@@ -26934,13 +26934,13 @@
         <v>1154065.715518</v>
       </c>
       <c r="AU195" t="n">
-        <v>21567882.182968</v>
+        <v>12521391.88085</v>
       </c>
       <c r="AV195" t="n">
-        <v>12936637.304133</v>
+        <v>9190927.000618</v>
       </c>
       <c r="AW195" t="n">
-        <v>11693154.193229</v>
+        <v>7943022.659264</v>
       </c>
       <c r="AX195" t="n">
         <v>3356589.580758</v>
@@ -26955,16 +26955,16 @@
         <v>1350533.066092</v>
       </c>
       <c r="BE195" t="n">
-        <v>17740543.566785</v>
+        <v>9004878.032765999</v>
       </c>
       <c r="BF195" t="n">
         <v>6113931.45</v>
       </c>
       <c r="BG195" t="n">
-        <v>6979674.283667</v>
+        <v>5594104.591168</v>
       </c>
       <c r="BH195" t="n">
-        <v>15724049.911815</v>
+        <v>7062804.928844</v>
       </c>
       <c r="BI195" t="n">
         <v>4130751.379238</v>
@@ -26994,16 +26994,16 @@
         <v>1662796.378198</v>
       </c>
       <c r="BU195" t="n">
-        <v>22733432.426915</v>
+        <v>13841678.148812</v>
       </c>
       <c r="BV195" t="n">
         <v>21741971.19</v>
       </c>
       <c r="BW195" t="n">
-        <v>7171891.811749</v>
+        <v>5839983.635975</v>
       </c>
       <c r="BX195" t="n">
-        <v>20339599.175373</v>
+        <v>11443494.07195</v>
       </c>
       <c r="BY195" t="n">
         <v>6003490.130108</v>
@@ -27073,16 +27073,16 @@
         <v>2114983.883535</v>
       </c>
       <c r="M196" t="n">
-        <v>6987124.561979</v>
+        <v>6388454.429139</v>
       </c>
       <c r="N196" t="n">
         <v>6494111.42</v>
       </c>
       <c r="O196" t="n">
-        <v>6334204.677368</v>
+        <v>6245828.803655</v>
       </c>
       <c r="P196" t="n">
-        <v>6325551.640961</v>
+        <v>6237001.256509</v>
       </c>
       <c r="Q196" t="n">
         <v>6036501.108</v>
@@ -27091,7 +27091,7 @@
         <v>6036501.108</v>
       </c>
       <c r="S196" t="n">
-        <v>6954988.042709</v>
+        <v>6398966.284133</v>
       </c>
       <c r="T196" t="n">
         <v>4567171.868447</v>
@@ -27139,19 +27139,19 @@
         <v>2000083.2</v>
       </c>
       <c r="AI196" t="n">
-        <v>7498190.180817</v>
+        <v>6588279.835342</v>
       </c>
       <c r="AJ196" t="n">
-        <v>6455070.781463</v>
+        <v>6326013.687933</v>
       </c>
       <c r="AK196" t="n">
-        <v>6444656.12155</v>
+        <v>6313073.052411</v>
       </c>
       <c r="AL196" t="n">
-        <v>6036572.75986</v>
+        <v>6036501.108</v>
       </c>
       <c r="AM196" t="n">
-        <v>6036572.75986</v>
+        <v>6036501.108</v>
       </c>
       <c r="AN196" t="n">
         <v>1673949.302078</v>
@@ -27175,13 +27175,13 @@
         <v>2042271.682423</v>
       </c>
       <c r="AU196" t="n">
-        <v>6539498.117323</v>
+        <v>6514392.411527</v>
       </c>
       <c r="AV196" t="n">
-        <v>6355682.569839</v>
+        <v>6219841.309212</v>
       </c>
       <c r="AW196" t="n">
-        <v>6348049.632499</v>
+        <v>6211136.293838</v>
       </c>
       <c r="AX196" t="n">
         <v>1654776.107102</v>
@@ -27205,16 +27205,16 @@
         <v>2215317.815739</v>
       </c>
       <c r="BE196" t="n">
-        <v>8652059.805197001</v>
+        <v>6911605.564211</v>
       </c>
       <c r="BF196" t="n">
         <v>7057295.18</v>
       </c>
       <c r="BG196" t="n">
-        <v>6306160.029891</v>
+        <v>6170515.067846</v>
       </c>
       <c r="BH196" t="n">
-        <v>8551814.553735999</v>
+        <v>6860705.537865</v>
       </c>
       <c r="BI196" t="n">
         <v>4761756.475702</v>
@@ -27253,7 +27253,7 @@
         <v>2178643.212317</v>
       </c>
       <c r="BU196" t="n">
-        <v>6933518.036064</v>
+        <v>6756224.607104</v>
       </c>
       <c r="BV196" t="n">
         <v>14055690.64</v>
@@ -27262,7 +27262,7 @@
         <v>6036501.108</v>
       </c>
       <c r="BX196" t="n">
-        <v>6903203.150402</v>
+        <v>6693460.350308</v>
       </c>
       <c r="BY196" t="n">
         <v>4739978.481597</v>
@@ -27332,25 +27332,25 @@
         <v>3285672.501485</v>
       </c>
       <c r="M197" t="n">
-        <v>25930076.925191</v>
+        <v>15105214.873859</v>
       </c>
       <c r="N197" t="n">
         <v>13173529.52</v>
       </c>
       <c r="O197" t="n">
-        <v>19530049.559366</v>
+        <v>13594374.852271</v>
       </c>
       <c r="P197" t="n">
-        <v>17707379.327738</v>
+        <v>11773224.663738</v>
       </c>
       <c r="Q197" t="n">
-        <v>15806196.529969</v>
+        <v>10164566.719433</v>
       </c>
       <c r="R197" t="n">
-        <v>15307272.5265</v>
+        <v>9665642.716</v>
       </c>
       <c r="S197" t="n">
-        <v>23369527.200045</v>
+        <v>12696436.450931</v>
       </c>
       <c r="T197" t="n">
         <v>8657645.982573999</v>
@@ -27398,19 +27398,19 @@
         <v>2613215.73782</v>
       </c>
       <c r="AI197" t="n">
-        <v>26341453.044122</v>
+        <v>14654165.356362</v>
       </c>
       <c r="AJ197" t="n">
-        <v>18435879.87751</v>
+        <v>12916643.4241</v>
       </c>
       <c r="AK197" t="n">
-        <v>16649602.029775</v>
+        <v>11130122.544844</v>
       </c>
       <c r="AL197" t="n">
-        <v>14887031.645533</v>
+        <v>9623055.154345</v>
       </c>
       <c r="AM197" t="n">
-        <v>14388107.642081</v>
+        <v>9124131.150893001</v>
       </c>
       <c r="AN197" t="n">
         <v>3977259.370281</v>
@@ -27434,13 +27434,13 @@
         <v>3321242.309793</v>
       </c>
       <c r="AU197" t="n">
-        <v>27026065.532127</v>
+        <v>16159711.556573</v>
       </c>
       <c r="AV197" t="n">
-        <v>20688876.17157</v>
+        <v>14250867.285159</v>
       </c>
       <c r="AW197" t="n">
-        <v>18829921.735657</v>
+        <v>12392557.759199</v>
       </c>
       <c r="AX197" t="n">
         <v>4385197.743147</v>
@@ -27464,16 +27464,16 @@
         <v>2234927.180351</v>
       </c>
       <c r="BE197" t="n">
-        <v>22665490.454075</v>
+        <v>11820616.758834</v>
       </c>
       <c r="BF197" t="n">
         <v>8288536.11</v>
       </c>
       <c r="BG197" t="n">
-        <v>11385125.297616</v>
+        <v>8609861.225327</v>
       </c>
       <c r="BH197" t="n">
-        <v>20116624.501339</v>
+        <v>9374950.681305001</v>
       </c>
       <c r="BI197" t="n">
         <v>5698873.549267</v>
@@ -27512,16 +27512,16 @@
         <v>3204218.822577</v>
       </c>
       <c r="BU197" t="n">
-        <v>28885184.095156</v>
+        <v>17871639.567854</v>
       </c>
       <c r="BV197" t="n">
         <v>28773678.39</v>
       </c>
       <c r="BW197" t="n">
-        <v>14946659.240749</v>
+        <v>11035434.431665</v>
       </c>
       <c r="BX197" t="n">
-        <v>25925174.497024</v>
+        <v>14909127.997096</v>
       </c>
       <c r="BY197" t="n">
         <v>8330275.451132</v>
@@ -27591,25 +27591,25 @@
         <v>-1170688.61795</v>
       </c>
       <c r="M198" t="n">
-        <v>-18942952.363211</v>
+        <v>-8716760.44472</v>
       </c>
       <c r="N198" t="n">
         <v>-6679418.1</v>
       </c>
       <c r="O198" t="n">
-        <v>-13195844.881998</v>
+        <v>-7348546.048616</v>
       </c>
       <c r="P198" t="n">
-        <v>-11381827.686777</v>
+        <v>-5536223.407229</v>
       </c>
       <c r="Q198" t="n">
-        <v>-9769695.421969</v>
+        <v>-4128065.611433</v>
       </c>
       <c r="R198" t="n">
-        <v>-9270771.418500001</v>
+        <v>-3629141.608</v>
       </c>
       <c r="S198" t="n">
-        <v>-16414539.157336</v>
+        <v>-6297470.166798</v>
       </c>
       <c r="T198" t="n">
         <v>-4090474.114127</v>
@@ -27657,19 +27657,19 @@
         <v>-613132.53782</v>
       </c>
       <c r="AI198" t="n">
-        <v>-18843262.863305</v>
+        <v>-8065885.521019</v>
       </c>
       <c r="AJ198" t="n">
-        <v>-11980809.096047</v>
+        <v>-6590629.736167</v>
       </c>
       <c r="AK198" t="n">
-        <v>-10204945.908225</v>
+        <v>-4817049.492432</v>
       </c>
       <c r="AL198" t="n">
-        <v>-8850458.885673</v>
+        <v>-3586554.046345</v>
       </c>
       <c r="AM198" t="n">
-        <v>-8351534.882221</v>
+        <v>-3087630.042893</v>
       </c>
       <c r="AN198" t="n">
         <v>-2303310.068203</v>
@@ -27693,13 +27693,13 @@
         <v>-1278970.62737</v>
       </c>
       <c r="AU198" t="n">
-        <v>-20486567.414804</v>
+        <v>-9645319.145045999</v>
       </c>
       <c r="AV198" t="n">
-        <v>-14333193.601731</v>
+        <v>-8031025.975946</v>
       </c>
       <c r="AW198" t="n">
-        <v>-12481872.103158</v>
+        <v>-6181421.465361</v>
       </c>
       <c r="AX198" t="n">
         <v>-2730421.636045</v>
@@ -27723,16 +27723,16 @@
         <v>-19609.364613</v>
       </c>
       <c r="BE198" t="n">
-        <v>-14013430.648878</v>
+        <v>-4909011.194623</v>
       </c>
       <c r="BF198" t="n">
         <v>-1231240.93</v>
       </c>
       <c r="BG198" t="n">
-        <v>-5078965.267725</v>
+        <v>-2439346.157481</v>
       </c>
       <c r="BH198" t="n">
-        <v>-11564809.947603</v>
+        <v>-2514245.143441</v>
       </c>
       <c r="BI198" t="n">
         <v>-937117.073565</v>
@@ -27771,16 +27771,16 @@
         <v>-1025575.61026</v>
       </c>
       <c r="BU198" t="n">
-        <v>-21951666.059092</v>
+        <v>-11115414.96075</v>
       </c>
       <c r="BV198" t="n">
         <v>-14717987.74</v>
       </c>
       <c r="BW198" t="n">
-        <v>-8910158.132749001</v>
+        <v>-4998933.323665</v>
       </c>
       <c r="BX198" t="n">
-        <v>-19021971.346621</v>
+        <v>-8215667.646788</v>
       </c>
       <c r="BY198" t="n">
         <v>-3590296.969535</v>
@@ -27850,25 +27850,25 @@
         <v>3285672.501485</v>
       </c>
       <c r="M199" t="n">
-        <v>25930076.925191</v>
+        <v>15105214.873859</v>
       </c>
       <c r="N199" t="n">
         <v>13173529.52</v>
       </c>
       <c r="O199" t="n">
-        <v>19530049.559366</v>
+        <v>13594374.852271</v>
       </c>
       <c r="P199" t="n">
-        <v>17707379.327738</v>
+        <v>11773224.663738</v>
       </c>
       <c r="Q199" t="n">
-        <v>15806196.529969</v>
+        <v>10164566.719433</v>
       </c>
       <c r="R199" t="n">
-        <v>15307272.5265</v>
+        <v>9665642.716</v>
       </c>
       <c r="S199" t="n">
-        <v>23369527.200045</v>
+        <v>12696436.450931</v>
       </c>
       <c r="T199" t="n">
         <v>8657645.982573999</v>
@@ -27916,19 +27916,19 @@
         <v>2613215.73782</v>
       </c>
       <c r="AI199" t="n">
-        <v>26341453.044122</v>
+        <v>14654165.356362</v>
       </c>
       <c r="AJ199" t="n">
-        <v>18435879.87751</v>
+        <v>12916643.4241</v>
       </c>
       <c r="AK199" t="n">
-        <v>16649602.029775</v>
+        <v>11130122.544844</v>
       </c>
       <c r="AL199" t="n">
-        <v>14887031.645533</v>
+        <v>9623055.154345</v>
       </c>
       <c r="AM199" t="n">
-        <v>14388107.642081</v>
+        <v>9124131.150893001</v>
       </c>
       <c r="AN199" t="n">
         <v>3977259.370281</v>
@@ -27952,13 +27952,13 @@
         <v>3321242.309793</v>
       </c>
       <c r="AU199" t="n">
-        <v>27026065.532127</v>
+        <v>16159711.556573</v>
       </c>
       <c r="AV199" t="n">
-        <v>20688876.17157</v>
+        <v>14250867.285159</v>
       </c>
       <c r="AW199" t="n">
-        <v>18829921.735657</v>
+        <v>12392557.759199</v>
       </c>
       <c r="AX199" t="n">
         <v>4385197.743147</v>
@@ -27982,16 +27982,16 @@
         <v>2234927.180351</v>
       </c>
       <c r="BE199" t="n">
-        <v>22665490.454075</v>
+        <v>11820616.758834</v>
       </c>
       <c r="BF199" t="n">
         <v>8288536.11</v>
       </c>
       <c r="BG199" t="n">
-        <v>11385125.297616</v>
+        <v>8609861.225327</v>
       </c>
       <c r="BH199" t="n">
-        <v>20116624.501339</v>
+        <v>9374950.681305001</v>
       </c>
       <c r="BI199" t="n">
         <v>5698873.549267</v>
@@ -28030,16 +28030,16 @@
         <v>3204218.822577</v>
       </c>
       <c r="BU199" t="n">
-        <v>28885184.095156</v>
+        <v>17871639.567854</v>
       </c>
       <c r="BV199" t="n">
         <v>28773678.39</v>
       </c>
       <c r="BW199" t="n">
-        <v>14946659.240749</v>
+        <v>11035434.431665</v>
       </c>
       <c r="BX199" t="n">
-        <v>25925174.497024</v>
+        <v>14909127.997096</v>
       </c>
       <c r="BY199" t="n">
         <v>8330275.451132</v>
@@ -28557,7 +28557,7 @@
         <v>0</v>
       </c>
       <c r="BU202" t="n">
-        <v>6.985196</v>
+        <v>0</v>
       </c>
       <c r="BV202" t="n">
         <v>5.6</v>
@@ -28566,7 +28566,7 @@
         <v>0</v>
       </c>
       <c r="BX202" t="n">
-        <v>6.985196</v>
+        <v>0</v>
       </c>
       <c r="BY202" t="n">
         <v>0</v>
@@ -28636,25 +28636,25 @@
         <v>6.611561</v>
       </c>
       <c r="M203" t="n">
-        <v>13.754585</v>
+        <v>8.413432999999999</v>
       </c>
       <c r="N203" t="n">
         <v>10.76</v>
       </c>
       <c r="O203" t="n">
-        <v>7.647836</v>
+        <v>0</v>
       </c>
       <c r="P203" t="n">
-        <v>7.232428</v>
+        <v>0</v>
       </c>
       <c r="Q203" t="n">
-        <v>6.656791</v>
+        <v>0</v>
       </c>
       <c r="R203" t="n">
-        <v>7.8692</v>
+        <v>0</v>
       </c>
       <c r="S203" t="n">
-        <v>14.518521</v>
+        <v>9.420769</v>
       </c>
       <c r="T203" t="n">
         <v>5.766112</v>
@@ -28702,7 +28702,7 @@
         <v>0</v>
       </c>
       <c r="AI203" t="n">
-        <v>10.561436</v>
+        <v>6.053008</v>
       </c>
       <c r="AJ203" t="n">
         <v>0</v>
@@ -28711,10 +28711,10 @@
         <v>0</v>
       </c>
       <c r="AL203" t="n">
-        <v>5.035987</v>
+        <v>0</v>
       </c>
       <c r="AM203" t="n">
-        <v>6.166664</v>
+        <v>0</v>
       </c>
       <c r="AN203" t="n">
         <v>7.301855</v>
@@ -28738,13 +28738,13 @@
         <v>6.688058</v>
       </c>
       <c r="AU203" t="n">
-        <v>15.239467</v>
+        <v>6.743327</v>
       </c>
       <c r="AV203" t="n">
-        <v>7.627589</v>
+        <v>7.257277</v>
       </c>
       <c r="AW203" t="n">
-        <v>7.844941</v>
+        <v>7.447912</v>
       </c>
       <c r="AX203" t="n">
         <v>5.944258</v>
@@ -28768,7 +28768,7 @@
         <v>15.544679</v>
       </c>
       <c r="BE203" t="n">
-        <v>28.836122</v>
+        <v>25.340273</v>
       </c>
       <c r="BF203" t="n">
         <v>23.03</v>
@@ -28777,7 +28777,7 @@
         <v>0</v>
       </c>
       <c r="BH203" t="n">
-        <v>10.687213</v>
+        <v>19.390545</v>
       </c>
       <c r="BI203" t="n">
         <v>12.837052</v>
@@ -28816,7 +28816,7 @@
         <v>12.119305</v>
       </c>
       <c r="BU203" t="n">
-        <v>12.977372</v>
+        <v>11.10525</v>
       </c>
       <c r="BV203" t="n">
         <v>15.33</v>
@@ -28825,7 +28825,7 @@
         <v>0</v>
       </c>
       <c r="BX203" t="n">
-        <v>14.396959</v>
+        <v>11.396603</v>
       </c>
       <c r="BY203" t="n">
         <v>9.903205</v>
@@ -28895,25 +28895,25 @@
         <v>6.005528</v>
       </c>
       <c r="M204" t="n">
-        <v>8.913410000000001</v>
+        <v>6.492131</v>
       </c>
       <c r="N204" t="n">
         <v>4.59</v>
       </c>
       <c r="O204" t="n">
-        <v>6.645384</v>
+        <v>6.438811</v>
       </c>
       <c r="P204" t="n">
-        <v>6.642683</v>
+        <v>6.428069</v>
       </c>
       <c r="Q204" t="n">
-        <v>6.364069</v>
+        <v>5.260331</v>
       </c>
       <c r="R204" t="n">
-        <v>6.3642</v>
+        <v>5.2597</v>
       </c>
       <c r="S204" t="n">
-        <v>8.903606</v>
+        <v>6.366927</v>
       </c>
       <c r="T204" t="n">
         <v>5.735527</v>
@@ -28961,19 +28961,19 @@
         <v>4.524963</v>
       </c>
       <c r="AI204" t="n">
-        <v>8.270125999999999</v>
+        <v>6.104713</v>
       </c>
       <c r="AJ204" t="n">
-        <v>5.909821</v>
+        <v>5.681899</v>
       </c>
       <c r="AK204" t="n">
-        <v>5.904331</v>
+        <v>5.671151</v>
       </c>
       <c r="AL204" t="n">
-        <v>5.81313</v>
+        <v>4.731537</v>
       </c>
       <c r="AM204" t="n">
-        <v>5.813851</v>
+        <v>4.731585</v>
       </c>
       <c r="AN204" t="n">
         <v>5.601461</v>
@@ -28997,13 +28997,13 @@
         <v>6.967799</v>
       </c>
       <c r="AU204" t="n">
-        <v>10.087732</v>
+        <v>7.316977</v>
       </c>
       <c r="AV204" t="n">
-        <v>7.143844</v>
+        <v>6.97774</v>
       </c>
       <c r="AW204" t="n">
-        <v>7.139721</v>
+        <v>6.967547</v>
       </c>
       <c r="AX204" t="n">
         <v>6.811508</v>
@@ -29027,16 +29027,16 @@
         <v>3.057674</v>
       </c>
       <c r="BE204" t="n">
-        <v>5.461261</v>
+        <v>3.797105</v>
       </c>
       <c r="BF204" t="n">
         <v>2.6</v>
       </c>
       <c r="BG204" t="n">
-        <v>2.972526</v>
+        <v>2.894066</v>
       </c>
       <c r="BH204" t="n">
-        <v>5.461147</v>
+        <v>3.684303</v>
       </c>
       <c r="BI204" t="n">
         <v>2.393716</v>
@@ -29075,7 +29075,7 @@
         <v>6.33538</v>
       </c>
       <c r="BU204" t="n">
-        <v>10.320969</v>
+        <v>8.138102</v>
       </c>
       <c r="BV204" t="n">
         <v>3.42</v>
@@ -29084,7 +29084,7 @@
         <v>5.396429</v>
       </c>
       <c r="BX204" t="n">
-        <v>10.312466</v>
+        <v>8.080695</v>
       </c>
       <c r="BY204" t="n">
         <v>5.755615</v>
@@ -29136,25 +29136,25 @@
         </is>
       </c>
       <c r="M205" t="n">
-        <v>3.316292</v>
+        <v>2.798976</v>
       </c>
       <c r="N205" t="n">
         <v>2.4</v>
       </c>
       <c r="O205" t="n">
-        <v>2.942379</v>
+        <v>2.874636</v>
       </c>
       <c r="P205" t="n">
-        <v>2.956143</v>
+        <v>2.893358</v>
       </c>
       <c r="Q205" t="n">
-        <v>2.970614</v>
+        <v>2.458441</v>
       </c>
       <c r="R205" t="n">
-        <v>2.9715</v>
+        <v>2.4552</v>
       </c>
       <c r="S205" t="n">
-        <v>3.31731</v>
+        <v>2.817746</v>
       </c>
       <c r="T205" t="n">
         <v>2.763669</v>
@@ -29178,19 +29178,19 @@
         <v>2.784817</v>
       </c>
       <c r="AI205" t="n">
-        <v>3.132397</v>
+        <v>2.615303</v>
       </c>
       <c r="AJ205" t="n">
-        <v>2.622271</v>
+        <v>2.573983</v>
       </c>
       <c r="AK205" t="n">
-        <v>2.636367</v>
+        <v>2.613344</v>
       </c>
       <c r="AL205" t="n">
-        <v>2.757891</v>
+        <v>2.293682</v>
       </c>
       <c r="AM205" t="n">
-        <v>2.765076</v>
+        <v>2.29396</v>
       </c>
       <c r="AN205" t="n">
         <v>2.559146</v>
@@ -29208,13 +29208,13 @@
         <v>2.173424</v>
       </c>
       <c r="AU205" t="n">
-        <v>3.581544</v>
+        <v>2.951702</v>
       </c>
       <c r="AV205" t="n">
-        <v>3.170064</v>
+        <v>3.096032</v>
       </c>
       <c r="AW205" t="n">
-        <v>3.182015</v>
+        <v>3.107942</v>
       </c>
       <c r="AX205" t="n">
         <v>2.899132</v>
@@ -29229,16 +29229,16 @@
         <v>2.386991</v>
       </c>
       <c r="BE205" t="n">
-        <v>2.368704</v>
+        <v>1.932938</v>
       </c>
       <c r="BF205" t="n">
         <v>1.53</v>
       </c>
       <c r="BG205" t="n">
-        <v>1.796849</v>
+        <v>1.758595</v>
       </c>
       <c r="BH205" t="n">
-        <v>2.368719</v>
+        <v>1.905831</v>
       </c>
       <c r="BI205" t="n">
         <v>1.569195</v>
@@ -29256,7 +29256,7 @@
         <v>1.672543</v>
       </c>
       <c r="BU205" t="n">
-        <v>3.779475</v>
+        <v>3.223176</v>
       </c>
       <c r="BV205" t="n">
         <v>1.75</v>
@@ -29265,7 +29265,7 @@
         <v>2.418665</v>
       </c>
       <c r="BX205" t="n">
-        <v>3.777312</v>
+        <v>3.217334</v>
       </c>
       <c r="BY205" t="n">
         <v>2.470682</v>
@@ -29305,25 +29305,25 @@
         </is>
       </c>
       <c r="M206" t="n">
-        <v>1.268602</v>
+        <v>0.963923</v>
       </c>
       <c r="N206" t="n">
         <v>0.8</v>
       </c>
       <c r="O206" t="n">
-        <v>0.882983</v>
+        <v>0.836223</v>
       </c>
       <c r="P206" t="n">
-        <v>0.876335</v>
+        <v>0.807128</v>
       </c>
       <c r="Q206" t="n">
-        <v>0.568265</v>
+        <v>0.490374</v>
       </c>
       <c r="R206" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.3376</v>
       </c>
       <c r="S206" t="n">
-        <v>1.180964</v>
+        <v>0.8695349999999999</v>
       </c>
       <c r="T206" t="n">
         <v>0.663708</v>
@@ -29347,19 +29347,19 @@
         <v>0.803288</v>
       </c>
       <c r="AI206" t="n">
-        <v>1.908515</v>
+        <v>1.210024</v>
       </c>
       <c r="AJ206" t="n">
-        <v>0.621129</v>
+        <v>0.672229</v>
       </c>
       <c r="AK206" t="n">
-        <v>0.6385150000000001</v>
+        <v>0.644331</v>
       </c>
       <c r="AL206" t="n">
-        <v>0.303684</v>
+        <v>0.5252790000000001</v>
       </c>
       <c r="AM206" t="n">
-        <v>0.454284</v>
+        <v>0.530508</v>
       </c>
       <c r="AN206" t="n">
         <v>1.022866</v>
@@ -29377,13 +29377,13 @@
         <v>0.58212</v>
       </c>
       <c r="AU206" t="n">
-        <v>3.336864</v>
+        <v>1.140195</v>
       </c>
       <c r="AV206" t="n">
-        <v>0.601396</v>
+        <v>0.599561</v>
       </c>
       <c r="AW206" t="n">
-        <v>0.58503</v>
+        <v>0.597351</v>
       </c>
       <c r="AX206" t="n">
         <v>1.013893</v>
@@ -29398,16 +29398,16 @@
         <v>0.423805</v>
       </c>
       <c r="BE206" t="n">
-        <v>4.135838</v>
+        <v>1.940378</v>
       </c>
       <c r="BF206" t="n">
         <v>3</v>
       </c>
       <c r="BG206" t="n">
-        <v>0.684387</v>
+        <v>0.668891</v>
       </c>
       <c r="BH206" t="n">
-        <v>4.100217</v>
+        <v>1.804456</v>
       </c>
       <c r="BI206" t="n">
         <v>1.151559</v>
@@ -29425,7 +29425,7 @@
         <v>1.439986</v>
       </c>
       <c r="BU206" t="n">
-        <v>3.858049</v>
+        <v>1.169664</v>
       </c>
       <c r="BV206" t="n">
         <v>3.61</v>
@@ -29434,7 +29434,7 @@
         <v>0</v>
       </c>
       <c r="BX206" t="n">
-        <v>3.846519</v>
+        <v>1.184201</v>
       </c>
       <c r="BY206" t="n">
         <v>0.999458</v>
@@ -29474,25 +29474,25 @@
         </is>
       </c>
       <c r="M207" t="n">
-        <v>3.503793</v>
+        <v>3.068069</v>
       </c>
       <c r="N207" t="n">
         <v>2.61</v>
       </c>
       <c r="O207" t="n">
-        <v>3.211004</v>
+        <v>3.114308</v>
       </c>
       <c r="P207" t="n">
-        <v>3.223234</v>
+        <v>3.140561</v>
       </c>
       <c r="Q207" t="n">
-        <v>3.228659</v>
+        <v>2.571625</v>
       </c>
       <c r="R207" t="n">
-        <v>3.2274</v>
+        <v>2.5758</v>
       </c>
       <c r="S207" t="n">
-        <v>3.503319</v>
+        <v>3.094502</v>
       </c>
       <c r="T207" t="n">
         <v>3.069993</v>
@@ -29516,19 +29516,19 @@
         <v>3.09439</v>
       </c>
       <c r="AI207" t="n">
-        <v>3.391006</v>
+        <v>2.85816</v>
       </c>
       <c r="AJ207" t="n">
-        <v>2.741886</v>
+        <v>2.70766</v>
       </c>
       <c r="AK207" t="n">
-        <v>2.765491</v>
+        <v>2.777635</v>
       </c>
       <c r="AL207" t="n">
-        <v>2.983291</v>
+        <v>2.402773</v>
       </c>
       <c r="AM207" t="n">
-        <v>2.974019</v>
+        <v>2.40245</v>
       </c>
       <c r="AN207" t="n">
         <v>2.82154</v>
@@ -29546,13 +29546,13 @@
         <v>2.260561</v>
       </c>
       <c r="AU207" t="n">
-        <v>3.808652</v>
+        <v>3.201962</v>
       </c>
       <c r="AV207" t="n">
-        <v>3.391885</v>
+        <v>3.299792</v>
       </c>
       <c r="AW207" t="n">
-        <v>3.415261</v>
+        <v>3.320111</v>
       </c>
       <c r="AX207" t="n">
         <v>3.180802</v>
@@ -29567,16 +29567,16 @@
         <v>2.453728</v>
       </c>
       <c r="BE207" t="n">
-        <v>2.612134</v>
+        <v>2.06624</v>
       </c>
       <c r="BF207" t="n">
         <v>1.61</v>
       </c>
       <c r="BG207" t="n">
-        <v>1.899188</v>
+        <v>1.849078</v>
       </c>
       <c r="BH207" t="n">
-        <v>2.612464</v>
+        <v>2.039957</v>
       </c>
       <c r="BI207" t="n">
         <v>1.733135</v>
@@ -29594,7 +29594,7 @@
         <v>1.846168</v>
       </c>
       <c r="BU207" t="n">
-        <v>3.918543</v>
+        <v>3.308422</v>
       </c>
       <c r="BV207" t="n">
         <v>1.84</v>
@@ -29603,7 +29603,7 @@
         <v>2.418665</v>
       </c>
       <c r="BX207" t="n">
-        <v>3.916182</v>
+        <v>3.31519</v>
       </c>
       <c r="BY207" t="n">
         <v>2.613018</v>
@@ -29661,16 +29661,16 @@
         <v>5.067362</v>
       </c>
       <c r="M208" t="n">
-        <v>6.887246</v>
+        <v>6.23933</v>
       </c>
       <c r="N208" t="n">
         <v>5.15</v>
       </c>
       <c r="O208" t="n">
-        <v>1.560738</v>
+        <v>1.591448</v>
       </c>
       <c r="P208" t="n">
-        <v>1.576571</v>
+        <v>1.606509</v>
       </c>
       <c r="Q208" t="n">
         <v>0</v>
@@ -29679,7 +29679,7 @@
         <v>0</v>
       </c>
       <c r="S208" t="n">
-        <v>6.742644</v>
+        <v>5.94882</v>
       </c>
       <c r="T208" t="n">
         <v>4.836377</v>
@@ -29727,19 +29727,19 @@
         <v>0</v>
       </c>
       <c r="AI208" t="n">
-        <v>7.254003</v>
+        <v>5.538918</v>
       </c>
       <c r="AJ208" t="n">
-        <v>1.474619</v>
+        <v>1.545788</v>
       </c>
       <c r="AK208" t="n">
-        <v>1.467243</v>
+        <v>1.541804</v>
       </c>
       <c r="AL208" t="n">
-        <v>0.78999</v>
+        <v>0</v>
       </c>
       <c r="AM208" t="n">
-        <v>0.78999</v>
+        <v>0</v>
       </c>
       <c r="AN208" t="n">
         <v>4.7237</v>
@@ -29763,13 +29763,13 @@
         <v>1.294277</v>
       </c>
       <c r="AU208" t="n">
-        <v>8.024827</v>
+        <v>4.46436</v>
       </c>
       <c r="AV208" t="n">
-        <v>1.13833</v>
+        <v>1.25271</v>
       </c>
       <c r="AW208" t="n">
-        <v>1.143001</v>
+        <v>1.260676</v>
       </c>
       <c r="AX208" t="n">
         <v>3.692083</v>
@@ -29793,16 +29793,16 @@
         <v>4.675445</v>
       </c>
       <c r="BE208" t="n">
-        <v>11.590304</v>
+        <v>5.912302</v>
       </c>
       <c r="BF208" t="n">
         <v>4</v>
       </c>
       <c r="BG208" t="n">
-        <v>1.263874</v>
+        <v>1.404859</v>
       </c>
       <c r="BH208" t="n">
-        <v>11.589082</v>
+        <v>5.705261</v>
       </c>
       <c r="BI208" t="n">
         <v>3.751217</v>
@@ -29841,7 +29841,7 @@
         <v>1.950222</v>
       </c>
       <c r="BU208" t="n">
-        <v>6.377489</v>
+        <v>3.097046</v>
       </c>
       <c r="BV208" t="n">
         <v>4.93</v>
@@ -29850,7 +29850,7 @@
         <v>0</v>
       </c>
       <c r="BX208" t="n">
-        <v>6.372648</v>
+        <v>2.952372</v>
       </c>
       <c r="BY208" t="n">
         <v>1.519215</v>
@@ -29920,25 +29920,25 @@
         <v>4.516819</v>
       </c>
       <c r="M209" t="n">
-        <v>5.803706</v>
+        <v>4.714684</v>
       </c>
       <c r="N209" t="n">
         <v>3.81</v>
       </c>
       <c r="O209" t="n">
-        <v>4.967798</v>
+        <v>4.719905</v>
       </c>
       <c r="P209" t="n">
-        <v>4.963883</v>
+        <v>4.709517</v>
       </c>
       <c r="Q209" t="n">
-        <v>5.268384</v>
+        <v>4.544126</v>
       </c>
       <c r="R209" t="n">
-        <v>5.2684</v>
+        <v>4.5438</v>
       </c>
       <c r="S209" t="n">
-        <v>5.797099</v>
+        <v>4.661966</v>
       </c>
       <c r="T209" t="n">
         <v>4.381053</v>
@@ -29986,19 +29986,19 @@
         <v>4.027434</v>
       </c>
       <c r="AI209" t="n">
-        <v>5.455437</v>
+        <v>4.490976</v>
       </c>
       <c r="AJ209" t="n">
-        <v>4.61638</v>
+        <v>4.361209</v>
       </c>
       <c r="AK209" t="n">
-        <v>4.607023</v>
+        <v>4.345066</v>
       </c>
       <c r="AL209" t="n">
-        <v>4.875113</v>
+        <v>4.181917</v>
       </c>
       <c r="AM209" t="n">
-        <v>4.875473</v>
+        <v>4.181941</v>
       </c>
       <c r="AN209" t="n">
         <v>4.273215</v>
@@ -30022,13 +30022,13 @@
         <v>4.995872</v>
       </c>
       <c r="AU209" t="n">
-        <v>6.358432</v>
+        <v>5.125576</v>
       </c>
       <c r="AV209" t="n">
-        <v>5.283916</v>
+        <v>5.032005</v>
       </c>
       <c r="AW209" t="n">
-        <v>5.280173</v>
+        <v>5.022448</v>
       </c>
       <c r="AX209" t="n">
         <v>4.903082</v>
@@ -30052,16 +30052,16 @@
         <v>2.846553</v>
       </c>
       <c r="BE209" t="n">
-        <v>4.03298</v>
+        <v>3.263576</v>
       </c>
       <c r="BF209" t="n">
         <v>2.22</v>
       </c>
       <c r="BG209" t="n">
-        <v>2.931533</v>
+        <v>2.814134</v>
       </c>
       <c r="BH209" t="n">
-        <v>4.032064</v>
+        <v>3.206832</v>
       </c>
       <c r="BI209" t="n">
         <v>2.538477</v>
@@ -30100,7 +30100,7 @@
         <v>4.475229</v>
       </c>
       <c r="BU209" t="n">
-        <v>6.565113</v>
+        <v>5.561886</v>
       </c>
       <c r="BV209" t="n">
         <v>2.73</v>
@@ -30109,7 +30109,7 @@
         <v>4.016168</v>
       </c>
       <c r="BX209" t="n">
-        <v>6.560189</v>
+        <v>5.536086</v>
       </c>
       <c r="BY209" t="n">
         <v>4.226346</v>
@@ -30179,25 +30179,25 @@
         <v>6.009606</v>
       </c>
       <c r="M210" t="n">
-        <v>8.123612</v>
+        <v>6.26919</v>
       </c>
       <c r="N210" t="n">
         <v>4.36</v>
       </c>
       <c r="O210" t="n">
-        <v>6.00547</v>
+        <v>5.404796</v>
       </c>
       <c r="P210" t="n">
-        <v>5.992408</v>
+        <v>5.381051</v>
       </c>
       <c r="Q210" t="n">
-        <v>5.145216</v>
+        <v>4.731121</v>
       </c>
       <c r="R210" t="n">
-        <v>5.1452</v>
+        <v>4.7309</v>
       </c>
       <c r="S210" t="n">
-        <v>8.050217999999999</v>
+        <v>6.195072</v>
       </c>
       <c r="T210" t="n">
         <v>5.785336</v>
@@ -30245,19 +30245,19 @@
         <v>4.377943</v>
       </c>
       <c r="AI210" t="n">
-        <v>8.498480000000001</v>
+        <v>5.960729</v>
       </c>
       <c r="AJ210" t="n">
-        <v>5.780986</v>
+        <v>5.127837</v>
       </c>
       <c r="AK210" t="n">
-        <v>5.746331</v>
+        <v>5.082257</v>
       </c>
       <c r="AL210" t="n">
-        <v>4.928633</v>
+        <v>4.491501</v>
       </c>
       <c r="AM210" t="n">
-        <v>4.92884</v>
+        <v>4.491515</v>
       </c>
       <c r="AN210" t="n">
         <v>5.669177</v>
@@ -30281,13 +30281,13 @@
         <v>5.600043</v>
       </c>
       <c r="AU210" t="n">
-        <v>8.290418000000001</v>
+        <v>6.677908</v>
       </c>
       <c r="AV210" t="n">
-        <v>6.37543</v>
+        <v>5.706727</v>
       </c>
       <c r="AW210" t="n">
-        <v>6.361793</v>
+        <v>5.683875</v>
       </c>
       <c r="AX210" t="n">
         <v>6.387288</v>
@@ -30311,16 +30311,16 @@
         <v>3.753787</v>
       </c>
       <c r="BE210" t="n">
-        <v>7.329356</v>
+        <v>4.464096</v>
       </c>
       <c r="BF210" t="n">
         <v>2.46</v>
       </c>
       <c r="BG210" t="n">
-        <v>3.389408</v>
+        <v>3.103608</v>
       </c>
       <c r="BH210" t="n">
-        <v>7.218539</v>
+        <v>4.33582</v>
       </c>
       <c r="BI210" t="n">
         <v>3.290998</v>
@@ -30359,7 +30359,7 @@
         <v>5.646511</v>
       </c>
       <c r="BU210" t="n">
-        <v>8.855973000000001</v>
+        <v>7.238433</v>
       </c>
       <c r="BV210" t="n">
         <v>2.77</v>
@@ -30368,7 +30368,7 @@
         <v>4.016168</v>
       </c>
       <c r="BX210" t="n">
-        <v>8.782439999999999</v>
+        <v>7.098658</v>
       </c>
       <c r="BY210" t="n">
         <v>5.393864</v>
@@ -30763,22 +30763,22 @@
         </is>
       </c>
       <c r="M215" t="n">
-        <v>0.233573</v>
+        <v>0.213842</v>
       </c>
       <c r="O215" t="n">
-        <v>0.217109</v>
+        <v>0.214384</v>
       </c>
       <c r="P215" t="n">
-        <v>0.06972399999999999</v>
+        <v>0.068527</v>
       </c>
       <c r="Q215" t="n">
-        <v>0.069217</v>
+        <v>0.060912</v>
       </c>
       <c r="R215" t="n">
-        <v>0.0692</v>
+        <v>0.0609</v>
       </c>
       <c r="S215" t="n">
-        <v>0.076845</v>
+        <v>0.067977</v>
       </c>
       <c r="Z215" t="n">
         <v>0.211501</v>
@@ -30796,19 +30796,19 @@
         <v>0.06707200000000001</v>
       </c>
       <c r="AI215" t="n">
-        <v>0.228383</v>
+        <v>0.208231</v>
       </c>
       <c r="AJ215" t="n">
-        <v>0.205222</v>
+        <v>0.203483</v>
       </c>
       <c r="AK215" t="n">
-        <v>0.063999</v>
+        <v>0.06364499999999999</v>
       </c>
       <c r="AL215" t="n">
-        <v>0.06583799999999999</v>
+        <v>0.058287</v>
       </c>
       <c r="AM215" t="n">
-        <v>0.06575300000000001</v>
+        <v>0.058285</v>
       </c>
       <c r="AN215" t="n">
         <v>0.205074</v>
@@ -30826,13 +30826,13 @@
         <v>0.056439</v>
       </c>
       <c r="AU215" t="n">
-        <v>0.24478</v>
+        <v>0.220309</v>
       </c>
       <c r="AV215" t="n">
-        <v>0.222767</v>
+        <v>0.220325</v>
       </c>
       <c r="AW215" t="n">
-        <v>0.0725</v>
+        <v>0.071272</v>
       </c>
       <c r="AX215" t="n">
         <v>0.217411</v>
@@ -30847,13 +30847,13 @@
         <v>0.059827</v>
       </c>
       <c r="BE215" t="n">
-        <v>0.205193</v>
+        <v>0.187319</v>
       </c>
       <c r="BG215" t="n">
-        <v>0.180273</v>
+        <v>0.179004</v>
       </c>
       <c r="BH215" t="n">
-        <v>0.061693</v>
+        <v>0.052826</v>
       </c>
       <c r="BO215" t="n">
         <v>0.182253</v>
@@ -30865,13 +30865,13 @@
         <v>0.049363</v>
       </c>
       <c r="BU215" t="n">
-        <v>0.263996</v>
+        <v>0.242405</v>
       </c>
       <c r="BW215" t="n">
         <v>0.213126</v>
       </c>
       <c r="BX215" t="n">
-        <v>0.083494</v>
+        <v>0.073453</v>
       </c>
       <c r="CE215" t="n">
         <v>0.239171</v>
@@ -30905,73 +30905,73 @@
         </is>
       </c>
       <c r="M216" t="n">
-        <v>25618.886532</v>
+        <v>15130.920864</v>
       </c>
       <c r="N216" t="n">
         <v>4368.96</v>
       </c>
       <c r="O216" t="n">
-        <v>19724.662521</v>
+        <v>13727.682422</v>
       </c>
       <c r="P216" t="n">
-        <v>17864.209459</v>
+        <v>11868.967292</v>
       </c>
       <c r="Q216" t="n">
-        <v>16210.809251</v>
+        <v>10424.762965</v>
       </c>
       <c r="R216" t="n">
-        <v>15699.1136</v>
+        <v>9913.067300000001</v>
       </c>
       <c r="S216" t="n">
-        <v>23025.750093</v>
+        <v>12649.700721</v>
       </c>
       <c r="AI216" t="n">
-        <v>25516.645145</v>
+        <v>14463.384609</v>
       </c>
       <c r="AJ216" t="n">
-        <v>18478.52381</v>
+        <v>12950.364695</v>
       </c>
       <c r="AK216" t="n">
-        <v>16657.201436</v>
+        <v>11131.383704</v>
       </c>
       <c r="AL216" t="n">
-        <v>15268.041766</v>
+        <v>9869.389592</v>
       </c>
       <c r="AM216" t="n">
-        <v>14756.346126</v>
+        <v>9357.693952</v>
       </c>
       <c r="AU216" t="n">
-        <v>27202.015599</v>
+        <v>16083.249145</v>
       </c>
       <c r="AV216" t="n">
-        <v>20891.125503</v>
+        <v>14427.632717</v>
       </c>
       <c r="AW216" t="n">
-        <v>18992.413209</v>
+        <v>12530.681363</v>
       </c>
       <c r="BE216" t="n">
-        <v>20563.177143</v>
+        <v>11225.699475</v>
       </c>
       <c r="BF216" t="n">
         <v>2776.9</v>
       </c>
       <c r="BG216" t="n">
-        <v>11400.004094</v>
+        <v>8692.815060999999</v>
       </c>
       <c r="BH216" t="n">
-        <v>18051.875766</v>
+        <v>8769.631339</v>
       </c>
       <c r="BU216" t="n">
-        <v>28704.618367</v>
+        <v>17590.977004</v>
       </c>
       <c r="BV216" t="n">
         <v>4027.34</v>
       </c>
       <c r="BW216" t="n">
-        <v>15329.269216</v>
+        <v>11317.923463</v>
       </c>
       <c r="BX216" t="n">
-        <v>25699.928272</v>
+        <v>14617.000912</v>
       </c>
     </row>
     <row r="217" customFormat="1" s="14">
@@ -30996,73 +30996,73 @@
         </is>
       </c>
       <c r="M217" t="n">
-        <v>9991.365748</v>
+        <v>5901.059137</v>
       </c>
       <c r="N217" t="n">
         <v>3990.52</v>
       </c>
       <c r="O217" t="n">
-        <v>7692.618383</v>
+        <v>5353.796145</v>
       </c>
       <c r="P217" t="n">
-        <v>6967.041689</v>
+        <v>4628.897244</v>
       </c>
       <c r="Q217" t="n">
-        <v>6322.215608</v>
+        <v>4065.657556</v>
       </c>
       <c r="R217" t="n">
-        <v>6122.6543</v>
+        <v>3866.0963</v>
       </c>
       <c r="S217" t="n">
-        <v>8980.042536000001</v>
+        <v>4933.383281</v>
       </c>
       <c r="AI217" t="n">
-        <v>9951.491606</v>
+        <v>5640.719998</v>
       </c>
       <c r="AJ217" t="n">
-        <v>7206.624286</v>
+        <v>5050.642231</v>
       </c>
       <c r="AK217" t="n">
-        <v>6496.30856</v>
+        <v>4341.239645</v>
       </c>
       <c r="AL217" t="n">
-        <v>5954.536289</v>
+        <v>3849.061941</v>
       </c>
       <c r="AM217" t="n">
-        <v>5754.974989</v>
+        <v>3649.500641</v>
       </c>
       <c r="AU217" t="n">
-        <v>10608.786084</v>
+        <v>6272.467167</v>
       </c>
       <c r="AV217" t="n">
-        <v>8147.538946</v>
+        <v>5626.77676</v>
       </c>
       <c r="AW217" t="n">
-        <v>7407.041152</v>
+        <v>4886.965732</v>
       </c>
       <c r="BE217" t="n">
-        <v>8019.639086</v>
+        <v>4378.022795</v>
       </c>
       <c r="BF217" t="n">
         <v>2531.68</v>
       </c>
       <c r="BG217" t="n">
-        <v>4446.001597</v>
+        <v>3390.197874</v>
       </c>
       <c r="BH217" t="n">
-        <v>7040.231549</v>
+        <v>3420.156222</v>
       </c>
       <c r="BU217" t="n">
-        <v>11194.801163</v>
+        <v>6860.481031</v>
       </c>
       <c r="BV217" t="n">
         <v>3973.14</v>
       </c>
       <c r="BW217" t="n">
-        <v>5978.414994</v>
+        <v>4413.990151</v>
       </c>
       <c r="BX217" t="n">
-        <v>10022.972026</v>
+        <v>5700.630356</v>
       </c>
     </row>
     <row r="218" customFormat="1" s="14">
@@ -31087,73 +31087,73 @@
         </is>
       </c>
       <c r="M218" t="n">
-        <v>7188.032912</v>
+        <v>4245.366286</v>
       </c>
       <c r="N218" t="n">
         <v>3914.05</v>
       </c>
       <c r="O218" t="n">
-        <v>5534.25783</v>
+        <v>3851.651903</v>
       </c>
       <c r="P218" t="n">
-        <v>5012.260208</v>
+        <v>3330.141902</v>
       </c>
       <c r="Q218" t="n">
-        <v>4548.356552</v>
+        <v>2924.933494</v>
       </c>
       <c r="R218" t="n">
-        <v>4404.7873</v>
+        <v>2781.3642</v>
       </c>
       <c r="S218" t="n">
-        <v>6460.462256</v>
+        <v>3549.196605</v>
       </c>
       <c r="AI218" t="n">
-        <v>7159.346479</v>
+        <v>4058.071941</v>
       </c>
       <c r="AJ218" t="n">
-        <v>5184.621789</v>
+        <v>3633.555562</v>
       </c>
       <c r="AK218" t="n">
-        <v>4673.603281</v>
+        <v>3123.193989</v>
       </c>
       <c r="AL218" t="n">
-        <v>4283.839057</v>
+        <v>2769.10931</v>
       </c>
       <c r="AM218" t="n">
-        <v>4140.269776</v>
+        <v>2625.54003</v>
       </c>
       <c r="AU218" t="n">
-        <v>7632.220204</v>
+        <v>4512.566307</v>
       </c>
       <c r="AV218" t="n">
-        <v>5861.53881</v>
+        <v>4048.040834</v>
       </c>
       <c r="AW218" t="n">
-        <v>5328.806584</v>
+        <v>3515.802685</v>
       </c>
       <c r="BE218" t="n">
-        <v>5769.524522</v>
+        <v>3149.656687</v>
       </c>
       <c r="BF218" t="n">
         <v>2482.13</v>
       </c>
       <c r="BG218" t="n">
-        <v>3198.5623</v>
+        <v>2438.991276</v>
       </c>
       <c r="BH218" t="n">
-        <v>5064.914783</v>
+        <v>2460.544045</v>
       </c>
       <c r="BU218" t="n">
-        <v>8053.813786</v>
+        <v>4935.597864</v>
       </c>
       <c r="BV218" t="n">
         <v>3963.42</v>
       </c>
       <c r="BW218" t="n">
-        <v>4301.017981</v>
+        <v>3175.532483</v>
       </c>
       <c r="BX218" t="n">
-        <v>7210.771242</v>
+        <v>4101.172918</v>
       </c>
     </row>
     <row r="219" customFormat="1" s="14">
@@ -31325,25 +31325,25 @@
         <v>6.005528</v>
       </c>
       <c r="M223" t="n">
-        <v>8.913410000000001</v>
+        <v>6.492131</v>
       </c>
       <c r="N223" t="n">
         <v>4.59</v>
       </c>
       <c r="O223" t="n">
-        <v>6.645384</v>
+        <v>6.438811</v>
       </c>
       <c r="P223" t="n">
-        <v>6.642683</v>
+        <v>6.428069</v>
       </c>
       <c r="Q223" t="n">
-        <v>6.364069</v>
+        <v>5.260331</v>
       </c>
       <c r="R223" t="n">
-        <v>6.3642</v>
+        <v>5.2597</v>
       </c>
       <c r="S223" t="n">
-        <v>8.903606</v>
+        <v>6.366927</v>
       </c>
       <c r="T223" t="n">
         <v>5.735527</v>
@@ -31391,19 +31391,19 @@
         <v>4.524963</v>
       </c>
       <c r="AI223" t="n">
-        <v>8.270125999999999</v>
+        <v>6.104713</v>
       </c>
       <c r="AJ223" t="n">
-        <v>5.909821</v>
+        <v>5.681899</v>
       </c>
       <c r="AK223" t="n">
-        <v>5.904331</v>
+        <v>5.671151</v>
       </c>
       <c r="AL223" t="n">
-        <v>5.81313</v>
+        <v>4.731537</v>
       </c>
       <c r="AM223" t="n">
-        <v>5.813851</v>
+        <v>4.731585</v>
       </c>
       <c r="AN223" t="n">
         <v>5.601461</v>
@@ -31427,13 +31427,13 @@
         <v>6.967799</v>
       </c>
       <c r="AU223" t="n">
-        <v>10.087732</v>
+        <v>7.316977</v>
       </c>
       <c r="AV223" t="n">
-        <v>7.143844</v>
+        <v>6.97774</v>
       </c>
       <c r="AW223" t="n">
-        <v>7.139721</v>
+        <v>6.967547</v>
       </c>
       <c r="AX223" t="n">
         <v>6.811508</v>
@@ -31457,16 +31457,16 @@
         <v>3.057674</v>
       </c>
       <c r="BE223" t="n">
-        <v>5.461261</v>
+        <v>3.797105</v>
       </c>
       <c r="BF223" t="n">
         <v>2.6</v>
       </c>
       <c r="BG223" t="n">
-        <v>2.972526</v>
+        <v>2.894066</v>
       </c>
       <c r="BH223" t="n">
-        <v>5.461147</v>
+        <v>3.684303</v>
       </c>
       <c r="BI223" t="n">
         <v>2.393716</v>
@@ -31505,7 +31505,7 @@
         <v>6.33538</v>
       </c>
       <c r="BU223" t="n">
-        <v>10.320969</v>
+        <v>8.138102</v>
       </c>
       <c r="BV223" t="n">
         <v>3.42</v>
@@ -31514,7 +31514,7 @@
         <v>5.396429</v>
       </c>
       <c r="BX223" t="n">
-        <v>10.312466</v>
+        <v>8.080695</v>
       </c>
       <c r="BY223" t="n">
         <v>5.755615</v>
@@ -31566,25 +31566,25 @@
         </is>
       </c>
       <c r="M224" t="n">
-        <v>3.503793</v>
+        <v>3.068069</v>
       </c>
       <c r="N224" t="n">
         <v>0.03</v>
       </c>
       <c r="O224" t="n">
-        <v>3.211004</v>
+        <v>3.114308</v>
       </c>
       <c r="P224" t="n">
-        <v>3.223234</v>
+        <v>3.140561</v>
       </c>
       <c r="Q224" t="n">
-        <v>3.228659</v>
+        <v>2.571625</v>
       </c>
       <c r="R224" t="n">
-        <v>3.2274</v>
+        <v>2.5758</v>
       </c>
       <c r="S224" t="n">
-        <v>3.503319</v>
+        <v>3.094502</v>
       </c>
       <c r="T224" t="n">
         <v>3.069993</v>
@@ -31608,19 +31608,19 @@
         <v>3.09439</v>
       </c>
       <c r="AI224" t="n">
-        <v>3.391006</v>
+        <v>2.85816</v>
       </c>
       <c r="AJ224" t="n">
-        <v>2.741886</v>
+        <v>2.70766</v>
       </c>
       <c r="AK224" t="n">
-        <v>2.765491</v>
+        <v>2.777635</v>
       </c>
       <c r="AL224" t="n">
-        <v>2.983291</v>
+        <v>2.402773</v>
       </c>
       <c r="AM224" t="n">
-        <v>2.974019</v>
+        <v>2.40245</v>
       </c>
       <c r="AN224" t="n">
         <v>2.82154</v>
@@ -31638,13 +31638,13 @@
         <v>2.260561</v>
       </c>
       <c r="AU224" t="n">
-        <v>3.808652</v>
+        <v>3.201962</v>
       </c>
       <c r="AV224" t="n">
-        <v>3.391885</v>
+        <v>3.299792</v>
       </c>
       <c r="AW224" t="n">
-        <v>3.415261</v>
+        <v>3.320111</v>
       </c>
       <c r="AX224" t="n">
         <v>3.180802</v>
@@ -31659,16 +31659,16 @@
         <v>2.453728</v>
       </c>
       <c r="BE224" t="n">
-        <v>2.612134</v>
+        <v>2.06624</v>
       </c>
       <c r="BF224" t="n">
         <v>0.02</v>
       </c>
       <c r="BG224" t="n">
-        <v>1.899188</v>
+        <v>1.849078</v>
       </c>
       <c r="BH224" t="n">
-        <v>2.612464</v>
+        <v>2.039957</v>
       </c>
       <c r="BI224" t="n">
         <v>1.733135</v>
@@ -31686,7 +31686,7 @@
         <v>1.846168</v>
       </c>
       <c r="BU224" t="n">
-        <v>3.918543</v>
+        <v>3.308422</v>
       </c>
       <c r="BV224" t="n">
         <v>0.02</v>
@@ -31695,7 +31695,7 @@
         <v>2.418665</v>
       </c>
       <c r="BX224" t="n">
-        <v>3.916182</v>
+        <v>3.31519</v>
       </c>
       <c r="BY224" t="n">
         <v>2.613018</v>
@@ -31753,25 +31753,25 @@
         <v>6.009606</v>
       </c>
       <c r="M225" t="n">
-        <v>8.123612</v>
+        <v>6.26919</v>
       </c>
       <c r="N225" t="n">
         <v>4.36</v>
       </c>
       <c r="O225" t="n">
-        <v>6.00547</v>
+        <v>5.404796</v>
       </c>
       <c r="P225" t="n">
-        <v>5.992408</v>
+        <v>5.381051</v>
       </c>
       <c r="Q225" t="n">
-        <v>5.145216</v>
+        <v>4.731121</v>
       </c>
       <c r="R225" t="n">
-        <v>5.1452</v>
+        <v>4.7309</v>
       </c>
       <c r="S225" t="n">
-        <v>8.050217999999999</v>
+        <v>6.195072</v>
       </c>
       <c r="T225" t="n">
         <v>5.785336</v>
@@ -31819,19 +31819,19 @@
         <v>4.377943</v>
       </c>
       <c r="AI225" t="n">
-        <v>8.498480000000001</v>
+        <v>5.960729</v>
       </c>
       <c r="AJ225" t="n">
-        <v>5.780986</v>
+        <v>5.127837</v>
       </c>
       <c r="AK225" t="n">
-        <v>5.746331</v>
+        <v>5.082257</v>
       </c>
       <c r="AL225" t="n">
-        <v>4.928633</v>
+        <v>4.491501</v>
       </c>
       <c r="AM225" t="n">
-        <v>4.92884</v>
+        <v>4.491515</v>
       </c>
       <c r="AN225" t="n">
         <v>5.669177</v>
@@ -31855,13 +31855,13 @@
         <v>5.600043</v>
       </c>
       <c r="AU225" t="n">
-        <v>8.290418000000001</v>
+        <v>6.677908</v>
       </c>
       <c r="AV225" t="n">
-        <v>6.37543</v>
+        <v>5.706727</v>
       </c>
       <c r="AW225" t="n">
-        <v>6.361793</v>
+        <v>5.683875</v>
       </c>
       <c r="AX225" t="n">
         <v>6.387288</v>
@@ -31885,16 +31885,16 @@
         <v>3.753787</v>
       </c>
       <c r="BE225" t="n">
-        <v>7.329356</v>
+        <v>4.464096</v>
       </c>
       <c r="BF225" t="n">
         <v>2.46</v>
       </c>
       <c r="BG225" t="n">
-        <v>3.389408</v>
+        <v>3.103608</v>
       </c>
       <c r="BH225" t="n">
-        <v>7.218539</v>
+        <v>4.33582</v>
       </c>
       <c r="BI225" t="n">
         <v>3.290998</v>
@@ -31933,7 +31933,7 @@
         <v>5.646511</v>
       </c>
       <c r="BU225" t="n">
-        <v>8.855973000000001</v>
+        <v>7.238433</v>
       </c>
       <c r="BV225" t="n">
         <v>2.77</v>
@@ -31942,7 +31942,7 @@
         <v>4.016168</v>
       </c>
       <c r="BX225" t="n">
-        <v>8.782439999999999</v>
+        <v>7.098658</v>
       </c>
       <c r="BY225" t="n">
         <v>5.393864</v>
@@ -31994,25 +31994,25 @@
         </is>
       </c>
       <c r="M226" t="n">
-        <v>0.233573</v>
+        <v>0.213842</v>
       </c>
       <c r="N226" t="n">
         <v>0.2</v>
       </c>
       <c r="O226" t="n">
-        <v>0.217109</v>
+        <v>0.214384</v>
       </c>
       <c r="P226" t="n">
-        <v>0.06972399999999999</v>
+        <v>0.068527</v>
       </c>
       <c r="Q226" t="n">
-        <v>0.069217</v>
+        <v>0.060912</v>
       </c>
       <c r="R226" t="n">
-        <v>0.0692</v>
+        <v>0.0609</v>
       </c>
       <c r="S226" t="n">
-        <v>0.076845</v>
+        <v>0.067977</v>
       </c>
       <c r="T226" t="n">
         <v>0.210092</v>
@@ -32048,19 +32048,19 @@
         <v>0.06707200000000001</v>
       </c>
       <c r="AI226" t="n">
-        <v>0.228383</v>
+        <v>0.208231</v>
       </c>
       <c r="AJ226" t="n">
-        <v>0.205222</v>
+        <v>0.203483</v>
       </c>
       <c r="AK226" t="n">
-        <v>0.063999</v>
+        <v>0.06364499999999999</v>
       </c>
       <c r="AL226" t="n">
-        <v>0.06583799999999999</v>
+        <v>0.058287</v>
       </c>
       <c r="AM226" t="n">
-        <v>0.06575300000000001</v>
+        <v>0.058285</v>
       </c>
       <c r="AN226" t="n">
         <v>0.205074</v>
@@ -32078,13 +32078,13 @@
         <v>0.056439</v>
       </c>
       <c r="AU226" t="n">
-        <v>0.24478</v>
+        <v>0.220309</v>
       </c>
       <c r="AV226" t="n">
-        <v>0.222767</v>
+        <v>0.220325</v>
       </c>
       <c r="AW226" t="n">
-        <v>0.0725</v>
+        <v>0.071272</v>
       </c>
       <c r="AX226" t="n">
         <v>0.217411</v>
@@ -32099,16 +32099,16 @@
         <v>0.059827</v>
       </c>
       <c r="BE226" t="n">
-        <v>0.205193</v>
+        <v>0.187319</v>
       </c>
       <c r="BF226" t="n">
         <v>0.17</v>
       </c>
       <c r="BG226" t="n">
-        <v>0.180273</v>
+        <v>0.179004</v>
       </c>
       <c r="BH226" t="n">
-        <v>0.061693</v>
+        <v>0.052826</v>
       </c>
       <c r="BI226" t="n">
         <v>0.169988</v>
@@ -32138,7 +32138,7 @@
         <v>0.049363</v>
       </c>
       <c r="BU226" t="n">
-        <v>0.263996</v>
+        <v>0.242405</v>
       </c>
       <c r="BV226" t="n">
         <v>0.18</v>
@@ -32147,7 +32147,7 @@
         <v>0.213126</v>
       </c>
       <c r="BX226" t="n">
-        <v>0.083494</v>
+        <v>0.073453</v>
       </c>
       <c r="BY226" t="n">
         <v>0.202196</v>
@@ -32509,73 +32509,73 @@
         </is>
       </c>
       <c r="M231" t="n">
-        <v>9991.365748</v>
+        <v>5901.059137</v>
       </c>
       <c r="N231" t="n">
         <v>3990.52</v>
       </c>
       <c r="O231" t="n">
-        <v>7692.618383</v>
+        <v>5353.796145</v>
       </c>
       <c r="P231" t="n">
-        <v>6967.041689</v>
+        <v>4628.897244</v>
       </c>
       <c r="Q231" t="n">
-        <v>6322.215608</v>
+        <v>4065.657556</v>
       </c>
       <c r="R231" t="n">
-        <v>6122.6543</v>
+        <v>3866.0963</v>
       </c>
       <c r="S231" t="n">
-        <v>8980.042536000001</v>
+        <v>4933.383281</v>
       </c>
       <c r="AI231" t="n">
-        <v>9951.491606</v>
+        <v>5640.719998</v>
       </c>
       <c r="AJ231" t="n">
-        <v>7206.624286</v>
+        <v>5050.642231</v>
       </c>
       <c r="AK231" t="n">
-        <v>6496.30856</v>
+        <v>4341.239645</v>
       </c>
       <c r="AL231" t="n">
-        <v>5954.536289</v>
+        <v>3849.061941</v>
       </c>
       <c r="AM231" t="n">
-        <v>5754.974989</v>
+        <v>3649.500641</v>
       </c>
       <c r="AU231" t="n">
-        <v>10608.786084</v>
+        <v>6272.467167</v>
       </c>
       <c r="AV231" t="n">
-        <v>8147.538946</v>
+        <v>5626.77676</v>
       </c>
       <c r="AW231" t="n">
-        <v>7407.041152</v>
+        <v>4886.965732</v>
       </c>
       <c r="BE231" t="n">
-        <v>8019.639086</v>
+        <v>4378.022795</v>
       </c>
       <c r="BF231" t="n">
         <v>2531.68</v>
       </c>
       <c r="BG231" t="n">
-        <v>4446.001597</v>
+        <v>3390.197874</v>
       </c>
       <c r="BH231" t="n">
-        <v>7040.231549</v>
+        <v>3420.156222</v>
       </c>
       <c r="BU231" t="n">
-        <v>11194.801163</v>
+        <v>6860.481031</v>
       </c>
       <c r="BV231" t="n">
         <v>3973.14</v>
       </c>
       <c r="BW231" t="n">
-        <v>5978.414994</v>
+        <v>4413.990151</v>
       </c>
       <c r="BX231" t="n">
-        <v>10022.972026</v>
+        <v>5700.630356</v>
       </c>
     </row>
     <row r="232">
@@ -32627,25 +32627,25 @@
         <v>1.314214</v>
       </c>
       <c r="M233" t="n">
-        <v>10.371599</v>
+        <v>6.041835</v>
       </c>
       <c r="N233" t="n">
         <v>5.27</v>
       </c>
       <c r="O233" t="n">
-        <v>7.811695</v>
+        <v>5.437524</v>
       </c>
       <c r="P233" t="n">
-        <v>7.082657</v>
+        <v>4.709094</v>
       </c>
       <c r="Q233" t="n">
-        <v>6.322216</v>
+        <v>4.065658</v>
       </c>
       <c r="R233" t="n">
-        <v>6.1227</v>
+        <v>3.8661</v>
       </c>
       <c r="S233" t="n">
-        <v>9.347422</v>
+        <v>5.078363</v>
       </c>
       <c r="T233" t="n">
         <v>3.462914</v>
@@ -32693,19 +32693,19 @@
         <v>1.045243</v>
       </c>
       <c r="AI233" t="n">
-        <v>10.536143</v>
+        <v>5.861422</v>
       </c>
       <c r="AJ233" t="n">
-        <v>7.374045</v>
+        <v>5.166442</v>
       </c>
       <c r="AK233" t="n">
-        <v>6.659564</v>
+        <v>4.451864</v>
       </c>
       <c r="AL233" t="n">
-        <v>5.954565</v>
+        <v>3.849062</v>
       </c>
       <c r="AM233" t="n">
-        <v>5.755004</v>
+        <v>3.649501</v>
       </c>
       <c r="AN233" t="n">
         <v>1.590838</v>
@@ -32729,13 +32729,13 @@
         <v>1.328442</v>
       </c>
       <c r="AU233" t="n">
-        <v>10.809977</v>
+        <v>6.463616</v>
       </c>
       <c r="AV233" t="n">
-        <v>8.275206000000001</v>
+        <v>5.70011</v>
       </c>
       <c r="AW233" t="n">
-        <v>7.531655</v>
+        <v>4.956817</v>
       </c>
       <c r="AX233" t="n">
         <v>1.754006</v>
@@ -32759,16 +32759,16 @@
         <v>0.893934</v>
       </c>
       <c r="BE233" t="n">
-        <v>9.065818999999999</v>
+        <v>4.72805</v>
       </c>
       <c r="BF233" t="n">
         <v>3.32</v>
       </c>
       <c r="BG233" t="n">
-        <v>4.553861</v>
+        <v>3.443801</v>
       </c>
       <c r="BH233" t="n">
-        <v>8.046315</v>
+        <v>3.749824</v>
       </c>
       <c r="BI233" t="n">
         <v>2.279455</v>
@@ -32807,16 +32807,16 @@
         <v>1.281634</v>
       </c>
       <c r="BU233" t="n">
-        <v>11.553593</v>
+        <v>7.148358</v>
       </c>
       <c r="BV233" t="n">
         <v>11.51</v>
       </c>
       <c r="BW233" t="n">
-        <v>5.978415</v>
+        <v>4.41399</v>
       </c>
       <c r="BX233" t="n">
-        <v>10.369638</v>
+        <v>5.963403</v>
       </c>
       <c r="BY233" t="n">
         <v>3.331972</v>
@@ -32886,25 +32886,25 @@
         <v>1.268256</v>
       </c>
       <c r="M234" t="n">
-        <v>9.991365999999999</v>
+        <v>5.901059</v>
       </c>
       <c r="N234" t="n">
         <v>4.87</v>
       </c>
       <c r="O234" t="n">
-        <v>7.692618</v>
+        <v>5.353796</v>
       </c>
       <c r="P234" t="n">
-        <v>6.967042</v>
+        <v>4.628897</v>
       </c>
       <c r="Q234" t="n">
-        <v>6.322216</v>
+        <v>4.065658</v>
       </c>
       <c r="R234" t="n">
-        <v>6.1227</v>
+        <v>3.8661</v>
       </c>
       <c r="S234" t="n">
-        <v>8.980043</v>
+        <v>4.933383</v>
       </c>
       <c r="T234" t="n">
         <v>3.336122</v>
@@ -32952,19 +32952,19 @@
         <v>1.045243</v>
       </c>
       <c r="AI234" t="n">
-        <v>9.951492</v>
+        <v>5.64072</v>
       </c>
       <c r="AJ234" t="n">
-        <v>7.206624</v>
+        <v>5.050642</v>
       </c>
       <c r="AK234" t="n">
-        <v>6.496309</v>
+        <v>4.34124</v>
       </c>
       <c r="AL234" t="n">
-        <v>5.954536</v>
+        <v>3.849062</v>
       </c>
       <c r="AM234" t="n">
-        <v>5.754975</v>
+        <v>3.649501</v>
       </c>
       <c r="AN234" t="n">
         <v>1.521286</v>
@@ -32988,13 +32988,13 @@
         <v>1.311567</v>
       </c>
       <c r="AU234" t="n">
-        <v>10.608786</v>
+        <v>6.272467</v>
       </c>
       <c r="AV234" t="n">
-        <v>8.147539</v>
+        <v>5.626777</v>
       </c>
       <c r="AW234" t="n">
-        <v>7.407041</v>
+        <v>4.886966</v>
       </c>
       <c r="AX234" t="n">
         <v>1.692123</v>
@@ -33018,16 +33018,16 @@
         <v>0.807843</v>
       </c>
       <c r="BE234" t="n">
-        <v>8.019639</v>
+        <v>4.378023</v>
       </c>
       <c r="BF234" t="n">
         <v>2.69</v>
       </c>
       <c r="BG234" t="n">
-        <v>4.446002</v>
+        <v>3.390198</v>
       </c>
       <c r="BH234" t="n">
-        <v>7.040232</v>
+        <v>3.420156</v>
       </c>
       <c r="BI234" t="n">
         <v>2.074831</v>
@@ -33066,16 +33066,16 @@
         <v>1.210213</v>
       </c>
       <c r="BU234" t="n">
-        <v>11.194801</v>
+        <v>6.860481</v>
       </c>
       <c r="BV234" t="n">
         <v>8.09</v>
       </c>
       <c r="BW234" t="n">
-        <v>5.978415</v>
+        <v>4.41399</v>
       </c>
       <c r="BX234" t="n">
-        <v>10.022972</v>
+        <v>5.70063</v>
       </c>
       <c r="BY234" t="n">
         <v>3.136059</v>
